--- a/EXCEL/7 - COMPLETE.xlsx
+++ b/EXCEL/7 - COMPLETE.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SIDMAP" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'7 · COMPLETE'!$A$2:$G$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'7 · COMPLETE'!$A$2:$G$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -67,7 +67,7 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="FFed7d31"/>
+      <color rgb="FF2e7d32"/>
       <sz val="10"/>
     </font>
     <font>
@@ -79,7 +79,7 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="FFc00000"/>
+      <color rgb="FFed7d31"/>
       <sz val="10"/>
     </font>
     <font>
@@ -96,7 +96,7 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="FF2e7d32"/>
+      <color rgb="FFc00000"/>
       <sz val="10"/>
     </font>
     <font>
@@ -172,7 +172,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="38">
     <fill>
       <patternFill/>
     </fill>
@@ -241,6 +241,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFffeb9c"/>
+        <bgColor rgb="FFffeb9c"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFe8d5c4"/>
         <bgColor rgb="FFe8d5c4"/>
       </patternFill>
@@ -289,8 +295,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFc00000"/>
-        <bgColor rgb="FFc00000"/>
+        <fgColor rgb="FF2e7d32"/>
+        <bgColor rgb="FF2e7d32"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF000000"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
     <fill>
@@ -301,26 +313,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFBDD7EE"/>
+        <bgColor rgb="FFBDD7EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFed7d31"/>
         <bgColor rgb="FFed7d31"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFffeb9c"/>
-        <bgColor rgb="FFffeb9c"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2e7d32"/>
-        <bgColor rgb="FF2e7d32"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF000000"/>
-        <bgColor rgb="FF000000"/>
+        <fgColor rgb="FFc00000"/>
+        <bgColor rgb="FFc00000"/>
       </patternFill>
     </fill>
     <fill>
@@ -498,7 +504,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -512,9 +518,6 @@
     <xf numFmtId="0" fontId="19" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -524,12 +527,12 @@
     <xf numFmtId="0" fontId="19" fillId="32" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -539,16 +542,19 @@
     <xf numFmtId="0" fontId="2" fillId="32" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -558,151 +564,154 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="36" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="37" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="36" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -713,7 +722,13 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -722,28 +737,52 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1113,7 +1152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1131,12 +1170,12 @@
           <t>PS5 COMPLETION PLATFORM  |  DONE - subsystems at 100%</t>
         </is>
       </c>
-      <c r="B1" s="89" t="n"/>
-      <c r="C1" s="89" t="n"/>
-      <c r="D1" s="89" t="n"/>
-      <c r="E1" s="89" t="n"/>
-      <c r="F1" s="89" t="n"/>
-      <c r="G1" s="90" t="n"/>
+      <c r="B1" s="100" t="n"/>
+      <c r="C1" s="100" t="n"/>
+      <c r="D1" s="100" t="n"/>
+      <c r="E1" s="100" t="n"/>
+      <c r="F1" s="100" t="n"/>
+      <c r="G1" s="101" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="22" t="inlineStr">
@@ -1176,1053 +1215,1031 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="78" t="n">
+      <c r="A3" s="81" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="80" t="inlineStr">
+      <c r="B3" s="83" t="inlineStr">
+        <is>
+          <t>PS5-01-01 - Fire Water Jockey Pump A/B</t>
+        </is>
+      </c>
+      <c r="C3" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D3" s="24" t="inlineStr">
+        <is>
+          <t>DONE(partial)</t>
+        </is>
+      </c>
+      <c r="E3" s="27" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="F3" s="23" t="inlineStr"/>
+      <c r="G3" s="67" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="81" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="83" t="inlineStr">
+        <is>
+          <t>PS5-01-04 - Fire Water Pump Mini Flow Recycle</t>
+        </is>
+      </c>
+      <c r="C4" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D4" s="24" t="inlineStr"/>
+      <c r="E4" s="27" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="F4" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="67" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="81" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="83" t="inlineStr">
         <is>
           <t>PS5-01-09 - Inergen for EITS Building</t>
         </is>
       </c>
-      <c r="C3" s="27" t="inlineStr">
+      <c r="C5" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="D3" s="24" t="inlineStr">
-        <is>
-          <t>PS5 - Milestone A</t>
-        </is>
-      </c>
-      <c r="E3" s="27" t="inlineStr">
-        <is>
-          <t>2026-08-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="F3" s="23" t="inlineStr">
+      <c r="D5" s="24" t="inlineStr"/>
+      <c r="E5" s="27" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="F5" s="23" t="inlineStr"/>
+      <c r="G5" s="67" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="83" t="inlineStr">
+        <is>
+          <t>PS5-03-20 - FZ-20 - Emergency Diesel Generator Enclosure</t>
+        </is>
+      </c>
+      <c r="C6" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D6" s="24" t="inlineStr"/>
+      <c r="E6" s="27" t="inlineStr">
+        <is>
+          <t>07-Aug-26</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="inlineStr"/>
+      <c r="G6" s="67" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="83" t="inlineStr">
+        <is>
+          <t>PS5-05-02 - Emergency Diesel Generator Package (UCP)</t>
+        </is>
+      </c>
+      <c r="C7" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D7" s="24" t="inlineStr"/>
+      <c r="E7" s="27" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+      <c r="F7" s="23" t="inlineStr"/>
+      <c r="G7" s="67" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="81" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="83" t="inlineStr">
+        <is>
+          <t>PS5-06-02 - AC UPS - Power Generator Building</t>
+        </is>
+      </c>
+      <c r="C8" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D8" s="24" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="E8" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G3" s="64" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="78" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" s="80" t="inlineStr">
-        <is>
-          <t>PS5-03-20 - FZ-20 - Emergency Diesel Generator Enclosure</t>
-        </is>
-      </c>
-      <c r="C4" s="27" t="inlineStr">
+      <c r="G8" s="67" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="81" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="83" t="inlineStr">
+        <is>
+          <t>PS5-09-05 - HVAC for EITS Building</t>
+        </is>
+      </c>
+      <c r="C9" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="D4" s="24" t="inlineStr">
-        <is>
-          <t>PS5 - Milestone C</t>
-        </is>
-      </c>
-      <c r="E4" s="27" t="inlineStr">
-        <is>
-          <t>2026-08-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="F4" s="23" t="inlineStr">
+      <c r="D9" s="24" t="inlineStr"/>
+      <c r="E9" s="27" t="inlineStr">
+        <is>
+          <t>DONE(partial)</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G4" s="64" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="78" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" s="80" t="inlineStr">
-        <is>
-          <t>PS5-05-01 - Emergency Diesel Generator Package</t>
-        </is>
-      </c>
-      <c r="C5" s="27" t="inlineStr">
+      <c r="G9" s="67" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="81" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="83" t="inlineStr">
+        <is>
+          <t>PS5-28-02 - Closed Drain Header 2</t>
+        </is>
+      </c>
+      <c r="C10" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="D5" s="24" t="inlineStr">
-        <is>
-          <t>PS5 - Milestone C</t>
-        </is>
-      </c>
-      <c r="E5" s="53" t="inlineStr">
-        <is>
-          <t>PARTIAL(22-08-2026)</t>
-        </is>
-      </c>
-      <c r="F5" s="23" t="inlineStr">
+      <c r="D10" s="24" t="inlineStr"/>
+      <c r="E10" s="27" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="F10" s="23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G5" s="64" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="78" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" s="80" t="inlineStr">
-        <is>
-          <t>PS5-05-02 - Emergency Diesel Generator Package (UCP)</t>
-        </is>
-      </c>
-      <c r="C6" s="27" t="inlineStr">
+      <c r="G10" s="67" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="81" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-01 - Power Generation Package A</t>
+        </is>
+      </c>
+      <c r="C11" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="D6" s="24" t="inlineStr">
-        <is>
-          <t>PS5 - Milestone C</t>
-        </is>
-      </c>
-      <c r="E6" s="66" t="inlineStr">
+      <c r="D11" s="24" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="E11" s="27" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="F11" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="67" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="81" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-02 - Power Gen Package A (UCP)</t>
+        </is>
+      </c>
+      <c r="C12" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D12" s="24" t="inlineStr">
+        <is>
+          <t>PS5 - Milestone B</t>
+        </is>
+      </c>
+      <c r="E12" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="23" t="inlineStr">
+        <is>
+          <t>WALKDOWN COMPLETE-20-08-26--ATTENDENCE SHEET TO BE SUBMITTED</t>
+        </is>
+      </c>
+      <c r="G12" s="67" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="81" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-04 - Power Generation Package B</t>
+        </is>
+      </c>
+      <c r="C13" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D13" s="24" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="E13" s="27" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="F13" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="67" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="81" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-23 - Instrument Air Distribution lines</t>
+        </is>
+      </c>
+      <c r="C14" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr"/>
+      <c r="E14" s="27" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="F14" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="67" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="81" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-26 - Instrument Air Compressor Skid</t>
+        </is>
+      </c>
+      <c r="C15" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="E15" s="27" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="F15" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G15" s="67" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="81" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-27 - Compressed Air Starting Skid</t>
+        </is>
+      </c>
+      <c r="C16" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="E16" s="27" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="67" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="81" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-28 - Air Receiver A &amp; Air Regulator A</t>
+        </is>
+      </c>
+      <c r="C17" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D17" s="24" t="inlineStr"/>
+      <c r="E17" s="27" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="F17" s="23" t="inlineStr"/>
+      <c r="G17" s="67" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="81" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-29 - Air Receiver B &amp; Air Regulator B</t>
+        </is>
+      </c>
+      <c r="C18" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="E18" s="27" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="F18" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G18" s="67" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="81" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-30 - Air Receiver C &amp; Air Regulator C</t>
+        </is>
+      </c>
+      <c r="C19" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D19" s="24" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="E19" s="27" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="F19" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="67" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="81" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-31 - Air Receiver D &amp; Air Regulator D</t>
+        </is>
+      </c>
+      <c r="C20" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D20" s="24" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="E20" s="27" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="F20" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="67" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="81" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-35 - Injector Tip Cooling Module A</t>
+        </is>
+      </c>
+      <c r="C21" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D21" s="24" t="inlineStr"/>
+      <c r="E21" s="27" t="inlineStr">
         <is>
           <t>COMPLETE</t>
         </is>
       </c>
-      <c r="F6" s="23" t="inlineStr">
+      <c r="F21" s="23" t="inlineStr"/>
+      <c r="G21" s="67" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="81" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-36 - Injector Tip Cooling Module B</t>
+        </is>
+      </c>
+      <c r="C22" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="E22" s="27" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="F22" s="23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G6" s="64" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="78" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" s="80" t="inlineStr">
-        <is>
-          <t>PS5-06-02 - AC UPS - Power Generator Building</t>
-        </is>
-      </c>
-      <c r="C7" s="27" t="inlineStr">
+      <c r="G22" s="67" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="81" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-37 - Injector Tip Cooling Module C</t>
+        </is>
+      </c>
+      <c r="C23" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="D7" s="24" t="inlineStr">
-        <is>
-          <t>PS5 - Milestone B</t>
-        </is>
-      </c>
-      <c r="E7" s="66" t="inlineStr">
+      <c r="D23" s="24" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="E23" s="27" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="F23" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G23" s="67" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="81" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-38 - Injector Tip Cooling Module D</t>
+        </is>
+      </c>
+      <c r="C24" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D24" s="24" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="E24" s="27" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="F24" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G24" s="67" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="81" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-42 - Oil Mist Separator Skid PS5-60-VS-9100A</t>
+        </is>
+      </c>
+      <c r="C25" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D25" s="24" t="inlineStr"/>
+      <c r="E25" s="27" t="inlineStr">
         <is>
           <t>COMPLETE</t>
         </is>
       </c>
-      <c r="F7" s="23" t="inlineStr">
+      <c r="F25" s="23" t="inlineStr"/>
+      <c r="G25" s="67" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="81" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-43 - Oil Mist Separator Skid PS5-60-VS-9100B</t>
+        </is>
+      </c>
+      <c r="C26" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D26" s="24" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="E26" s="27" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="F26" s="23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G7" s="64" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="82" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" s="80" t="inlineStr">
-        <is>
-          <t>PS5-09-05 - HVAC for EITS Building</t>
-        </is>
-      </c>
-      <c r="C8" s="27" t="inlineStr">
-        <is>
-          <t>80%</t>
-        </is>
-      </c>
-      <c r="D8" s="24" t="inlineStr">
-        <is>
-          <t>PS5 - Milestone A</t>
-        </is>
-      </c>
-      <c r="E8" s="53" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="F8" s="23" t="inlineStr">
+      <c r="G26" s="67" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="81" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-44 - Oil Mist Separator Skid PS5-60-VS-9100C</t>
+        </is>
+      </c>
+      <c r="C27" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D27" s="24" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="E27" s="27" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="F27" s="23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G8" s="64" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="82" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" s="80" t="inlineStr">
-        <is>
-          <t>PS5-60-01 - Power Generation Package A</t>
-        </is>
-      </c>
-      <c r="C9" s="27" t="inlineStr">
-        <is>
-          <t>99%</t>
-        </is>
-      </c>
-      <c r="D9" s="24" t="inlineStr">
-        <is>
-          <t>PS5 - Milestone B</t>
-        </is>
-      </c>
-      <c r="E9" s="53" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="F9" s="23" t="inlineStr">
+      <c r="G27" s="67" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="81" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-45 - Oil Mist Separator Skid PS5-60-VS-9100D</t>
+        </is>
+      </c>
+      <c r="C28" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D28" s="24" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="E28" s="27" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="F28" s="23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G9" s="64" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="78" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" s="80" t="inlineStr">
-        <is>
-          <t>PS5-60-02 - Power Gen Package A (UCP)</t>
-        </is>
-      </c>
-      <c r="C10" s="27" t="inlineStr">
+      <c r="G28" s="67" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="81" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-70 - Engine A Cooling system</t>
+        </is>
+      </c>
+      <c r="C29" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="D10" s="24" t="inlineStr">
-        <is>
-          <t>PS5 - Milestone B</t>
-        </is>
-      </c>
-      <c r="E10" s="66" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
-        </is>
-      </c>
-      <c r="F10" s="23" t="inlineStr">
+      <c r="D29" s="24" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="E29" s="27" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="F29" s="23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G10" s="64" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="82" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" s="80" t="inlineStr">
-        <is>
-          <t>PS5-60-03 - Power Gen Package A Generator Auxiliary MCCs &amp; DBs</t>
-        </is>
-      </c>
-      <c r="C11" s="27" t="inlineStr">
-        <is>
-          <t>71%</t>
-        </is>
-      </c>
-      <c r="D11" s="24" t="inlineStr">
-        <is>
-          <t>PS5 - Milestone B</t>
-        </is>
-      </c>
-      <c r="E11" s="53" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="F11" s="23" t="inlineStr">
+      <c r="G29" s="67" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="81" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-71 - Engine B Cooling system</t>
+        </is>
+      </c>
+      <c r="C30" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D30" s="24" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="E30" s="27" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="F30" s="23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G11" s="64" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="82" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" s="80" t="inlineStr">
-        <is>
-          <t>PS5-60-04 - Power Generation Package B</t>
-        </is>
-      </c>
-      <c r="C12" s="27" t="inlineStr">
-        <is>
-          <t>98%</t>
-        </is>
-      </c>
-      <c r="D12" s="24" t="inlineStr">
-        <is>
-          <t>PS5 - Milestone B</t>
-        </is>
-      </c>
-      <c r="E12" s="53" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="F12" s="23" t="inlineStr">
+      <c r="G30" s="67" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="81" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-72 - Engine C Cooling system</t>
+        </is>
+      </c>
+      <c r="C31" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D31" s="24" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="E31" s="27" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="F31" s="23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G12" s="64" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="82" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" s="80" t="inlineStr">
-        <is>
-          <t>PS5-60-05 - Power Gen Package B (UCP)</t>
-        </is>
-      </c>
-      <c r="C13" s="27" t="inlineStr">
-        <is>
-          <t>92%</t>
-        </is>
-      </c>
-      <c r="D13" s="24" t="inlineStr">
-        <is>
-          <t>PS5 - Milestone B</t>
-        </is>
-      </c>
-      <c r="E13" s="53" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="F13" s="23" t="inlineStr">
+      <c r="G31" s="67" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="81" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-73 - Engine D Cooling system</t>
+        </is>
+      </c>
+      <c r="C32" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D32" s="24" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="E32" s="27" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="F32" s="23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G13" s="64" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="82" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" s="80" t="inlineStr">
-        <is>
-          <t>PS5-60-12 - Power Gen Package D Generator Auxiliary MCCs &amp; DBs</t>
-        </is>
-      </c>
-      <c r="C14" s="27" t="inlineStr">
-        <is>
-          <t>73%</t>
-        </is>
-      </c>
-      <c r="D14" s="24" t="inlineStr">
-        <is>
-          <t>PS5 - Milestone D</t>
-        </is>
-      </c>
-      <c r="E14" s="53" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="F14" s="23" t="inlineStr">
+      <c r="G32" s="67" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="81" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="83" t="inlineStr">
+        <is>
+          <t>PS5-61-05 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0003)</t>
+        </is>
+      </c>
+      <c r="C33" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D33" s="24" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="E33" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F33" s="23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G14" s="64" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="78" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" s="80" t="inlineStr">
-        <is>
-          <t>PS5-60-26 - Instrument Air Compressor Skid</t>
-        </is>
-      </c>
-      <c r="C15" s="27" t="inlineStr">
+      <c r="G33" s="67" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="81" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" s="83" t="inlineStr">
+        <is>
+          <t>PS5-63-04 - Electrical Earthing - EITS Building</t>
+        </is>
+      </c>
+      <c r="C34" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="D15" s="24" t="inlineStr">
-        <is>
-          <t>PS5 - Milestone B</t>
-        </is>
-      </c>
-      <c r="E15" s="66" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
-        </is>
-      </c>
-      <c r="F15" s="23" t="inlineStr">
+      <c r="D34" s="24" t="inlineStr"/>
+      <c r="E34" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F34" s="23" t="inlineStr"/>
+      <c r="G34" s="67" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="81" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="83" t="inlineStr">
+        <is>
+          <t>PS5-71-22 - Diesel Fuel Pre Pressure Module</t>
+        </is>
+      </c>
+      <c r="C35" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D35" s="24" t="inlineStr"/>
+      <c r="E35" s="27" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="F35" s="23" t="inlineStr"/>
+      <c r="G35" s="67" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="81" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" s="83" t="inlineStr">
+        <is>
+          <t>PS5-84-03 - Shelters</t>
+        </is>
+      </c>
+      <c r="C36" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D36" s="24" t="inlineStr"/>
+      <c r="E36" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F36" s="23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G15" s="64" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="78" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" s="80" t="inlineStr">
-        <is>
-          <t>PS5-60-27 - Compressed Air Starting Skid</t>
-        </is>
-      </c>
-      <c r="C16" s="27" t="inlineStr">
+      <c r="G36" s="67" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="81" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" s="83" t="inlineStr">
+        <is>
+          <t>PS5-86-01 - Shelters</t>
+        </is>
+      </c>
+      <c r="C37" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="D16" s="24" t="inlineStr">
-        <is>
-          <t>PS5 - Milestone B</t>
-        </is>
-      </c>
-      <c r="E16" s="53" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="F16" s="23" t="inlineStr">
+      <c r="D37" s="24" t="inlineStr"/>
+      <c r="E37" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F37" s="23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G16" s="64" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="82" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" s="80" t="inlineStr">
-        <is>
-          <t>PS5-60-28 - Air Receiver A &amp; Air Regulator A</t>
-        </is>
-      </c>
-      <c r="C17" s="27" t="inlineStr">
-        <is>
-          <t>92%</t>
-        </is>
-      </c>
-      <c r="D17" s="24" t="inlineStr">
-        <is>
-          <t>PS5 - Milestone B</t>
-        </is>
-      </c>
-      <c r="E17" s="53" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="F17" s="23" t="inlineStr">
+      <c r="G37" s="67" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="81" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" s="83" t="inlineStr">
+        <is>
+          <t>PS5-91-01 - Multicore cables &amp; JB</t>
+        </is>
+      </c>
+      <c r="C38" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D38" s="24" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="E38" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F38" s="23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G17" s="64" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="82" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" s="80" t="inlineStr">
-        <is>
-          <t>PS5-60-29 - Air Receiver B &amp; Air Regulator B</t>
-        </is>
-      </c>
-      <c r="C18" s="27" t="inlineStr">
-        <is>
-          <t>92%</t>
-        </is>
-      </c>
-      <c r="D18" s="24" t="inlineStr">
-        <is>
-          <t>PS5 - Milestone B</t>
-        </is>
-      </c>
-      <c r="E18" s="53" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="F18" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G18" s="64" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="78" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" s="80" t="inlineStr">
-        <is>
-          <t>PS5-60-35 - Injector Tip Cooling Module A</t>
-        </is>
-      </c>
-      <c r="C19" s="27" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D19" s="24" t="inlineStr">
-        <is>
-          <t>PS5 - Milestone B</t>
-        </is>
-      </c>
-      <c r="E19" s="66" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
-        </is>
-      </c>
-      <c r="F19" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G19" s="64" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="78" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" s="80" t="inlineStr">
-        <is>
-          <t>PS5-60-36 - Injector Tip Cooling Module B</t>
-        </is>
-      </c>
-      <c r="C20" s="27" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D20" s="24" t="inlineStr">
-        <is>
-          <t>PS5 - Milestone B</t>
-        </is>
-      </c>
-      <c r="E20" s="66" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
-        </is>
-      </c>
-      <c r="F20" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G20" s="64" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="78" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" s="80" t="inlineStr">
-        <is>
-          <t>PS5-60-42 - Oil Mist Separator Skid PS5-60-VS-9100A</t>
-        </is>
-      </c>
-      <c r="C21" s="27" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D21" s="24" t="inlineStr">
-        <is>
-          <t>PS5 - Milestone B</t>
-        </is>
-      </c>
-      <c r="E21" s="66" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
-        </is>
-      </c>
-      <c r="F21" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G21" s="64" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="78" t="n">
-        <v>20</v>
-      </c>
-      <c r="B22" s="80" t="inlineStr">
-        <is>
-          <t>PS5-60-43 - Oil Mist Separator Skid PS5-60-VS-9100B</t>
-        </is>
-      </c>
-      <c r="C22" s="27" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D22" s="24" t="inlineStr">
-        <is>
-          <t>PS5 - Milestone B</t>
-        </is>
-      </c>
-      <c r="E22" s="66" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
-        </is>
-      </c>
-      <c r="F22" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G22" s="64" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="82" t="n">
-        <v>21</v>
-      </c>
-      <c r="B23" s="80" t="inlineStr">
-        <is>
-          <t>PS5-60-49 - Lube Oil Separator Module PS5-60-UO-81100A</t>
-        </is>
-      </c>
-      <c r="C23" s="27" t="inlineStr">
-        <is>
-          <t>97%</t>
-        </is>
-      </c>
-      <c r="D23" s="24" t="inlineStr">
-        <is>
-          <t>PS5 - Milestone B</t>
-        </is>
-      </c>
-      <c r="E23" s="53" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="F23" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G23" s="64" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="82" t="n">
-        <v>22</v>
-      </c>
-      <c r="B24" s="80" t="inlineStr">
-        <is>
-          <t>PS5-60-50 - Lube Oil Separator Module PS5-60-UO-81100B</t>
-        </is>
-      </c>
-      <c r="C24" s="27" t="inlineStr">
-        <is>
-          <t>97%</t>
-        </is>
-      </c>
-      <c r="D24" s="24" t="inlineStr">
-        <is>
-          <t>PS5 - Milestone B</t>
-        </is>
-      </c>
-      <c r="E24" s="53" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="F24" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G24" s="64" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="82" t="n">
-        <v>23</v>
-      </c>
-      <c r="B25" s="80" t="inlineStr">
-        <is>
-          <t>PS5-60-56 - Fuel Conditioning Module PS5-60-UZ-8900A</t>
-        </is>
-      </c>
-      <c r="C25" s="27" t="inlineStr">
-        <is>
-          <t>95%</t>
-        </is>
-      </c>
-      <c r="D25" s="24" t="inlineStr">
-        <is>
-          <t>PS5 - Milestone B</t>
-        </is>
-      </c>
-      <c r="E25" s="53" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="F25" s="23" t="inlineStr">
-        <is>
-          <t>THERMAL INSULATION</t>
-        </is>
-      </c>
-      <c r="G25" s="64" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="82" t="n">
-        <v>24</v>
-      </c>
-      <c r="B26" s="80" t="inlineStr">
-        <is>
-          <t>PS5-60-57 - Fuel Conditioning Module PS5-60-UZ-8900A (UCP)</t>
-        </is>
-      </c>
-      <c r="C26" s="27" t="inlineStr">
-        <is>
-          <t>88%</t>
-        </is>
-      </c>
-      <c r="D26" s="24" t="inlineStr">
-        <is>
-          <t>PS5 - Milestone B</t>
-        </is>
-      </c>
-      <c r="E26" s="53" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="F26" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G26" s="64" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="82" t="n">
-        <v>25</v>
-      </c>
-      <c r="B27" s="80" t="inlineStr">
-        <is>
-          <t>PS5-60-58 - Fuel Conditioning Module PS5-60-UZ-8900B</t>
-        </is>
-      </c>
-      <c r="C27" s="27" t="inlineStr">
-        <is>
-          <t>96%</t>
-        </is>
-      </c>
-      <c r="D27" s="24" t="inlineStr">
-        <is>
-          <t>PS5 - Milestone B</t>
-        </is>
-      </c>
-      <c r="E27" s="53" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="F27" s="23" t="inlineStr">
-        <is>
-          <t>THERMAL INSULATION</t>
-        </is>
-      </c>
-      <c r="G27" s="64" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="82" t="n">
-        <v>26</v>
-      </c>
-      <c r="B28" s="80" t="inlineStr">
-        <is>
-          <t>PS5-60-59 - Fuel Conditioning Module PS5-60-UZ-8900B (UCP)</t>
-        </is>
-      </c>
-      <c r="C28" s="27" t="inlineStr">
-        <is>
-          <t>88%</t>
-        </is>
-      </c>
-      <c r="D28" s="24" t="inlineStr">
-        <is>
-          <t>PS5 - Milestone B</t>
-        </is>
-      </c>
-      <c r="E28" s="53" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="F28" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G28" s="64" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="78" t="n">
-        <v>27</v>
-      </c>
-      <c r="B29" s="80" t="inlineStr">
-        <is>
-          <t>PS5-60-70 - Engine A Cooling system</t>
-        </is>
-      </c>
-      <c r="C29" s="27" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D29" s="24" t="inlineStr">
-        <is>
-          <t>PS5 - Milestone B</t>
-        </is>
-      </c>
-      <c r="E29" s="53" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="F29" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G29" s="64" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="78" t="n">
-        <v>28</v>
-      </c>
-      <c r="B30" s="80" t="inlineStr">
-        <is>
-          <t>PS5-60-71 - Engine B Cooling system</t>
-        </is>
-      </c>
-      <c r="C30" s="27" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D30" s="24" t="inlineStr">
-        <is>
-          <t>PS5 - Milestone B</t>
-        </is>
-      </c>
-      <c r="E30" s="53" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="F30" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G30" s="64" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="78" t="n">
-        <v>29</v>
-      </c>
-      <c r="B31" s="80" t="inlineStr">
-        <is>
-          <t>PS5-61-05 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0003)</t>
-        </is>
-      </c>
-      <c r="C31" s="27" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D31" s="24" t="inlineStr">
-        <is>
-          <t>PS5 - Milestone B</t>
-        </is>
-      </c>
-      <c r="E31" s="66" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
-        </is>
-      </c>
-      <c r="F31" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G31" s="64" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="82" t="n">
-        <v>30</v>
-      </c>
-      <c r="B32" s="80" t="inlineStr">
-        <is>
-          <t>PS5-63-03 - Electrical Earthing - Generator Building</t>
-        </is>
-      </c>
-      <c r="C32" s="27" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="D32" s="24" t="inlineStr">
-        <is>
-          <t>PS5 - Milestone B</t>
-        </is>
-      </c>
-      <c r="E32" s="53" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="F32" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G32" s="64" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="78" t="n">
-        <v>31</v>
-      </c>
-      <c r="B33" s="80" t="inlineStr">
-        <is>
-          <t>PS5-63-04 - Electrical Earthing - EITS Building</t>
-        </is>
-      </c>
-      <c r="C33" s="27" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D33" s="24" t="inlineStr"/>
-      <c r="E33" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F33" s="23" t="inlineStr"/>
-      <c r="G33" s="64" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="82" t="n">
-        <v>32</v>
-      </c>
-      <c r="B34" s="80" t="inlineStr">
-        <is>
-          <t>PS5-71-09 - CFO Pre-Pressure Modules (UCP)</t>
-        </is>
-      </c>
-      <c r="C34" s="27" t="inlineStr">
-        <is>
-          <t>95%</t>
-        </is>
-      </c>
-      <c r="D34" s="24" t="inlineStr">
-        <is>
-          <t>PS5 - Milestone H</t>
-        </is>
-      </c>
-      <c r="E34" s="53" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="F34" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G34" s="64" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="78" t="n">
-        <v>33</v>
-      </c>
-      <c r="B35" s="80" t="inlineStr">
-        <is>
-          <t>PS5-71-22 - Diesel Fuel Pre Pressure Module</t>
-        </is>
-      </c>
-      <c r="C35" s="27" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D35" s="24" t="inlineStr">
-        <is>
-          <t>PS5 - Milestone B</t>
-        </is>
-      </c>
-      <c r="E35" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F35" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G35" s="64" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="78" t="n">
-        <v>34</v>
-      </c>
-      <c r="B36" s="80" t="inlineStr">
-        <is>
-          <t>PS5-91-01 - Multicore cables &amp; JB</t>
-        </is>
-      </c>
-      <c r="C36" s="27" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D36" s="24" t="inlineStr">
-        <is>
-          <t>PS5 - Milestone A</t>
-        </is>
-      </c>
-      <c r="E36" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F36" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G36" s="64" t="inlineStr"/>
+      <c r="G38" s="67" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:G36"/>
+  <autoFilter ref="A2:G38"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
@@ -2261,6 +2278,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B36" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B37" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B38" r:id="rId36"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXCEL/7 - COMPLETE.xlsx
+++ b/EXCEL/7 - COMPLETE.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SIDMAP" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'7 · COMPLETE'!$A$2:$G$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'7 · COMPLETE'!$A$2:$G$60</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -241,12 +241,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFffeb9c"/>
-        <bgColor rgb="FFffeb9c"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFe8d5c4"/>
         <bgColor rgb="FFe8d5c4"/>
       </patternFill>
@@ -315,6 +309,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFBDD7EE"/>
         <bgColor rgb="FFBDD7EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFffeb9c"/>
+        <bgColor rgb="FFffeb9c"/>
       </patternFill>
     </fill>
     <fill>
@@ -576,7 +576,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -644,12 +644,15 @@
     <xf numFmtId="0" fontId="2" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -671,25 +674,22 @@
     <xf numFmtId="0" fontId="6" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -698,13 +698,13 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -722,10 +722,10 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -740,7 +740,7 @@
     <xf numFmtId="0" fontId="4" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -773,16 +773,16 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1152,7 +1152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="B3" s="83" t="inlineStr">
         <is>
-          <t>PS5-01-01 - Fire Water Jockey Pump A/B</t>
+          <t>PS5-01-04 - Fire Water Pump Mini Flow Recycle</t>
         </is>
       </c>
       <c r="C3" s="27" t="inlineStr">
@@ -1228,17 +1228,17 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="D3" s="24" t="inlineStr">
-        <is>
-          <t>DONE(partial)</t>
-        </is>
-      </c>
+      <c r="D3" s="24" t="inlineStr"/>
       <c r="E3" s="27" t="inlineStr">
         <is>
           <t>DONE(full)</t>
         </is>
       </c>
-      <c r="F3" s="23" t="inlineStr"/>
+      <c r="F3" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="G3" s="67" t="inlineStr"/>
     </row>
     <row r="4">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B4" s="83" t="inlineStr">
         <is>
-          <t>PS5-01-04 - Fire Water Pump Mini Flow Recycle</t>
+          <t>PS5-01-06 - Foam Concentrate Distribution</t>
         </is>
       </c>
       <c r="C4" s="27" t="inlineStr">
@@ -1288,7 +1288,11 @@
           <t>2026-08-08</t>
         </is>
       </c>
-      <c r="F5" s="23" t="inlineStr"/>
+      <c r="F5" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="G5" s="67" t="inlineStr"/>
     </row>
     <row r="6">
@@ -1297,7 +1301,7 @@
       </c>
       <c r="B6" s="83" t="inlineStr">
         <is>
-          <t>PS5-03-20 - FZ-20 - Emergency Diesel Generator Enclosure</t>
+          <t>PS5-01-10 - Water Mist Package</t>
         </is>
       </c>
       <c r="C6" s="27" t="inlineStr">
@@ -1305,13 +1309,21 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="D6" s="24" t="inlineStr"/>
+      <c r="D6" s="24" t="inlineStr">
+        <is>
+          <t>DONE (PARTIAL)</t>
+        </is>
+      </c>
       <c r="E6" s="27" t="inlineStr">
         <is>
-          <t>07-Aug-26</t>
-        </is>
-      </c>
-      <c r="F6" s="23" t="inlineStr"/>
+          <t>DONE(FULL)</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="G6" s="67" t="inlineStr"/>
     </row>
     <row r="7">
@@ -1320,7 +1332,7 @@
       </c>
       <c r="B7" s="83" t="inlineStr">
         <is>
-          <t>PS5-05-02 - Emergency Diesel Generator Package (UCP)</t>
+          <t>PS5-03-07 - FZ-07 - Pretreatment Area</t>
         </is>
       </c>
       <c r="C7" s="27" t="inlineStr">
@@ -1328,13 +1340,21 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="D7" s="24" t="inlineStr"/>
+      <c r="D7" s="24" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
       <c r="E7" s="27" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
-        </is>
-      </c>
-      <c r="F7" s="23" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="G7" s="67" t="inlineStr"/>
     </row>
     <row r="8">
@@ -1343,7 +1363,7 @@
       </c>
       <c r="B8" s="83" t="inlineStr">
         <is>
-          <t>PS5-06-02 - AC UPS - Power Generator Building</t>
+          <t>PS5-03-09 - FZ-09 - Power Generation Building - Engine Bay 1</t>
         </is>
       </c>
       <c r="C8" s="27" t="inlineStr">
@@ -1363,7 +1383,7 @@
       </c>
       <c r="F8" s="23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Due to gland plate issue of SEA-0001 we cannot terminate the cablesof F&amp;G Instruments.</t>
         </is>
       </c>
       <c r="G8" s="67" t="inlineStr"/>
@@ -1374,7 +1394,7 @@
       </c>
       <c r="B9" s="83" t="inlineStr">
         <is>
-          <t>PS5-09-05 - HVAC for EITS Building</t>
+          <t>PS5-03-10 - FZ-10 - Power Generation Building - Engine Bay 2</t>
         </is>
       </c>
       <c r="C9" s="27" t="inlineStr">
@@ -1382,17 +1402,17 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="D9" s="24" t="inlineStr"/>
+      <c r="D9" s="24" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
       <c r="E9" s="27" t="inlineStr">
         <is>
-          <t>DONE(partial)</t>
-        </is>
-      </c>
-      <c r="F9" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="inlineStr"/>
       <c r="G9" s="67" t="inlineStr"/>
     </row>
     <row r="10">
@@ -1401,7 +1421,7 @@
       </c>
       <c r="B10" s="83" t="inlineStr">
         <is>
-          <t>PS5-28-02 - Closed Drain Header 2</t>
+          <t>PS5-03-13 - FZ-13 - Power Generation Building - Instrument Air Room</t>
         </is>
       </c>
       <c r="C10" s="27" t="inlineStr">
@@ -1409,10 +1429,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="D10" s="24" t="inlineStr"/>
+      <c r="D10" s="24" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
       <c r="E10" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F10" s="23" t="inlineStr">
@@ -1428,7 +1452,7 @@
       </c>
       <c r="B11" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-01 - Power Generation Package A</t>
+          <t>PS5-03-20 - FZ-20 - Emergency Diesel Generator Enclosure</t>
         </is>
       </c>
       <c r="C11" s="27" t="inlineStr">
@@ -1443,7 +1467,7 @@
       </c>
       <c r="E11" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>07-Aug-26</t>
         </is>
       </c>
       <c r="F11" s="23" t="inlineStr">
@@ -1459,7 +1483,7 @@
       </c>
       <c r="B12" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-02 - Power Gen Package A (UCP)</t>
+          <t>PS5-05-01 - Emergency Diesel Generator Package</t>
         </is>
       </c>
       <c r="C12" s="27" t="inlineStr">
@@ -1469,17 +1493,17 @@
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>PS5 - Milestone B</t>
+          <t>DONE(full)</t>
         </is>
       </c>
       <c r="E12" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="F12" s="23" t="inlineStr">
         <is>
-          <t>WALKDOWN COMPLETE-20-08-26--ATTENDENCE SHEET TO BE SUBMITTED</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G12" s="67" t="inlineStr"/>
@@ -1490,7 +1514,7 @@
       </c>
       <c r="B13" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-04 - Power Generation Package B</t>
+          <t>PS5-05-02 - Emergency Diesel Generator Package (UCP)</t>
         </is>
       </c>
       <c r="C13" s="27" t="inlineStr">
@@ -1505,7 +1529,7 @@
       </c>
       <c r="E13" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="F13" s="23" t="inlineStr">
@@ -1521,7 +1545,7 @@
       </c>
       <c r="B14" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-23 - Instrument Air Distribution lines</t>
+          <t>PS5-06-02 - AC UPS - Power Generator Building</t>
         </is>
       </c>
       <c r="C14" s="27" t="inlineStr">
@@ -1529,10 +1553,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="D14" s="24" t="inlineStr"/>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
       <c r="E14" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F14" s="23" t="inlineStr">
@@ -1548,7 +1576,7 @@
       </c>
       <c r="B15" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-26 - Instrument Air Compressor Skid</t>
+          <t>PS5-09-05 - HVAC for EITS Building</t>
         </is>
       </c>
       <c r="C15" s="27" t="inlineStr">
@@ -1556,21 +1584,13 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="D15" s="24" t="inlineStr">
-        <is>
-          <t>DONE(full)</t>
-        </is>
-      </c>
+      <c r="D15" s="24" t="inlineStr"/>
       <c r="E15" s="27" t="inlineStr">
         <is>
           <t>DONE(full)</t>
         </is>
       </c>
-      <c r="F15" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F15" s="23" t="inlineStr"/>
       <c r="G15" s="67" t="inlineStr"/>
     </row>
     <row r="16">
@@ -1579,7 +1599,7 @@
       </c>
       <c r="B16" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-27 - Compressed Air Starting Skid</t>
+          <t>PS5-28-02 - Closed Drain Header 2</t>
         </is>
       </c>
       <c r="C16" s="27" t="inlineStr">
@@ -1589,7 +1609,7 @@
       </c>
       <c r="D16" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="E16" s="27" t="inlineStr">
@@ -1610,7 +1630,7 @@
       </c>
       <c r="B17" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-28 - Air Receiver A &amp; Air Regulator A</t>
+          <t>PS5-60-01 - Power Generation Package A</t>
         </is>
       </c>
       <c r="C17" s="27" t="inlineStr">
@@ -1618,13 +1638,21 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="D17" s="24" t="inlineStr"/>
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
       <c r="E17" s="27" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="F17" s="23" t="inlineStr"/>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="F17" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="G17" s="67" t="inlineStr"/>
     </row>
     <row r="18">
@@ -1633,7 +1661,7 @@
       </c>
       <c r="B18" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-29 - Air Receiver B &amp; Air Regulator B</t>
+          <t>PS5-60-02 - Power Gen Package A (UCP)</t>
         </is>
       </c>
       <c r="C18" s="27" t="inlineStr">
@@ -1643,17 +1671,17 @@
       </c>
       <c r="D18" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>PS5 - Milestone B</t>
         </is>
       </c>
       <c r="E18" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F18" s="23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>WALKDOWN COMPLETE-20-08-26--ATTENDENCE SHEET TO BE SUBMITTED</t>
         </is>
       </c>
       <c r="G18" s="67" t="inlineStr"/>
@@ -1664,7 +1692,7 @@
       </c>
       <c r="B19" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-30 - Air Receiver C &amp; Air Regulator C</t>
+          <t>PS5-60-04 - Power Generation Package B</t>
         </is>
       </c>
       <c r="C19" s="27" t="inlineStr">
@@ -1695,7 +1723,7 @@
       </c>
       <c r="B20" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-31 - Air Receiver D &amp; Air Regulator D</t>
+          <t>PS5-60-23 - Instrument Air Distribution lines</t>
         </is>
       </c>
       <c r="C20" s="27" t="inlineStr">
@@ -1703,11 +1731,7 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="D20" s="24" t="inlineStr">
-        <is>
-          <t>DONE(full)</t>
-        </is>
-      </c>
+      <c r="D20" s="24" t="inlineStr"/>
       <c r="E20" s="27" t="inlineStr">
         <is>
           <t>DONE(full)</t>
@@ -1726,7 +1750,7 @@
       </c>
       <c r="B21" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-35 - Injector Tip Cooling Module A</t>
+          <t>PS5-60-26 - Instrument Air Compressor Skid</t>
         </is>
       </c>
       <c r="C21" s="27" t="inlineStr">
@@ -1734,13 +1758,21 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="D21" s="24" t="inlineStr"/>
+      <c r="D21" s="24" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
       <c r="E21" s="27" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
-        </is>
-      </c>
-      <c r="F21" s="23" t="inlineStr"/>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="F21" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="G21" s="67" t="inlineStr"/>
     </row>
     <row r="22">
@@ -1749,7 +1781,7 @@
       </c>
       <c r="B22" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-36 - Injector Tip Cooling Module B</t>
+          <t>PS5-60-27 - Compressed Air Starting Skid</t>
         </is>
       </c>
       <c r="C22" s="27" t="inlineStr">
@@ -1780,7 +1812,7 @@
       </c>
       <c r="B23" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-37 - Injector Tip Cooling Module C</t>
+          <t>PS5-60-28 - Air Receiver A &amp; Air Regulator A</t>
         </is>
       </c>
       <c r="C23" s="27" t="inlineStr">
@@ -1795,7 +1827,7 @@
       </c>
       <c r="E23" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="F23" s="23" t="inlineStr">
@@ -1811,7 +1843,7 @@
       </c>
       <c r="B24" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-38 - Injector Tip Cooling Module D</t>
+          <t>PS5-60-29 - Air Receiver B &amp; Air Regulator B</t>
         </is>
       </c>
       <c r="C24" s="27" t="inlineStr">
@@ -1842,7 +1874,7 @@
       </c>
       <c r="B25" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-42 - Oil Mist Separator Skid PS5-60-VS-9100A</t>
+          <t>PS5-60-30 - Air Receiver C &amp; Air Regulator C</t>
         </is>
       </c>
       <c r="C25" s="27" t="inlineStr">
@@ -1850,13 +1882,21 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="D25" s="24" t="inlineStr"/>
+      <c r="D25" s="24" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
       <c r="E25" s="27" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
-        </is>
-      </c>
-      <c r="F25" s="23" t="inlineStr"/>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="F25" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="G25" s="67" t="inlineStr"/>
     </row>
     <row r="26">
@@ -1865,7 +1905,7 @@
       </c>
       <c r="B26" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-43 - Oil Mist Separator Skid PS5-60-VS-9100B</t>
+          <t>PS5-60-31 - Air Receiver D &amp; Air Regulator D</t>
         </is>
       </c>
       <c r="C26" s="27" t="inlineStr">
@@ -1875,7 +1915,7 @@
       </c>
       <c r="D26" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="E26" s="27" t="inlineStr">
@@ -1896,7 +1936,7 @@
       </c>
       <c r="B27" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-44 - Oil Mist Separator Skid PS5-60-VS-9100C</t>
+          <t>PS5-60-32 - Air Receiver E &amp; Air Regulator E</t>
         </is>
       </c>
       <c r="C27" s="27" t="inlineStr">
@@ -1927,7 +1967,7 @@
       </c>
       <c r="B28" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-45 - Oil Mist Separator Skid PS5-60-VS-9100D</t>
+          <t>PS5-60-33 - Air Receiver F &amp; Air Regulator F</t>
         </is>
       </c>
       <c r="C28" s="27" t="inlineStr">
@@ -1958,7 +1998,7 @@
       </c>
       <c r="B29" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-70 - Engine A Cooling system</t>
+          <t>PS5-60-34 - Air Receiver G &amp; Air Regulator G</t>
         </is>
       </c>
       <c r="C29" s="27" t="inlineStr">
@@ -1989,7 +2029,7 @@
       </c>
       <c r="B30" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-71 - Engine B Cooling system</t>
+          <t>PS5-60-35 - Injector Tip Cooling Module A</t>
         </is>
       </c>
       <c r="C30" s="27" t="inlineStr">
@@ -2004,7 +2044,7 @@
       </c>
       <c r="E30" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="F30" s="23" t="inlineStr">
@@ -2020,7 +2060,7 @@
       </c>
       <c r="B31" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-72 - Engine C Cooling system</t>
+          <t>PS5-60-36 - Injector Tip Cooling Module B</t>
         </is>
       </c>
       <c r="C31" s="27" t="inlineStr">
@@ -2051,7 +2091,7 @@
       </c>
       <c r="B32" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-73 - Engine D Cooling system</t>
+          <t>PS5-60-37 - Injector Tip Cooling Module C</t>
         </is>
       </c>
       <c r="C32" s="27" t="inlineStr">
@@ -2061,7 +2101,7 @@
       </c>
       <c r="D32" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="E32" s="27" t="inlineStr">
@@ -2082,7 +2122,7 @@
       </c>
       <c r="B33" s="83" t="inlineStr">
         <is>
-          <t>PS5-61-05 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0003)</t>
+          <t>PS5-60-38 - Injector Tip Cooling Module D</t>
         </is>
       </c>
       <c r="C33" s="27" t="inlineStr">
@@ -2092,12 +2132,12 @@
       </c>
       <c r="D33" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="E33" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>DONE(full)</t>
         </is>
       </c>
       <c r="F33" s="23" t="inlineStr">
@@ -2113,7 +2153,7 @@
       </c>
       <c r="B34" s="83" t="inlineStr">
         <is>
-          <t>PS5-63-04 - Electrical Earthing - EITS Building</t>
+          <t>PS5-60-39 - Injector Tip Cooling Module E</t>
         </is>
       </c>
       <c r="C34" s="27" t="inlineStr">
@@ -2121,13 +2161,21 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="D34" s="24" t="inlineStr"/>
+      <c r="D34" s="24" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
       <c r="E34" s="27" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F34" s="23" t="inlineStr"/>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="F34" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="G34" s="67" t="inlineStr"/>
     </row>
     <row r="35">
@@ -2136,7 +2184,7 @@
       </c>
       <c r="B35" s="83" t="inlineStr">
         <is>
-          <t>PS5-71-22 - Diesel Fuel Pre Pressure Module</t>
+          <t>PS5-60-40 - Injector Tip Cooling Module F</t>
         </is>
       </c>
       <c r="C35" s="27" t="inlineStr">
@@ -2144,13 +2192,21 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="D35" s="24" t="inlineStr"/>
+      <c r="D35" s="24" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
       <c r="E35" s="27" t="inlineStr">
         <is>
           <t>DONE(full)</t>
         </is>
       </c>
-      <c r="F35" s="23" t="inlineStr"/>
+      <c r="F35" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="G35" s="67" t="inlineStr"/>
     </row>
     <row r="36">
@@ -2159,7 +2215,7 @@
       </c>
       <c r="B36" s="83" t="inlineStr">
         <is>
-          <t>PS5-84-03 - Shelters</t>
+          <t>PS5-60-42 - Oil Mist Separator Skid PS5-60-VS-9100A</t>
         </is>
       </c>
       <c r="C36" s="27" t="inlineStr">
@@ -2167,10 +2223,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="D36" s="24" t="inlineStr"/>
+      <c r="D36" s="24" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
       <c r="E36" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="F36" s="23" t="inlineStr">
@@ -2186,7 +2246,7 @@
       </c>
       <c r="B37" s="83" t="inlineStr">
         <is>
-          <t>PS5-86-01 - Shelters</t>
+          <t>PS5-60-43 - Oil Mist Separator Skid PS5-60-VS-9100B</t>
         </is>
       </c>
       <c r="C37" s="27" t="inlineStr">
@@ -2194,10 +2254,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="D37" s="24" t="inlineStr"/>
+      <c r="D37" s="24" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
       <c r="E37" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>DONE(full)</t>
         </is>
       </c>
       <c r="F37" s="23" t="inlineStr">
@@ -2213,33 +2277,687 @@
       </c>
       <c r="B38" s="83" t="inlineStr">
         <is>
+          <t>PS5-60-44 - Oil Mist Separator Skid PS5-60-VS-9100C</t>
+        </is>
+      </c>
+      <c r="C38" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D38" s="24" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="E38" s="27" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="F38" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G38" s="67" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="81" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-45 - Oil Mist Separator Skid PS5-60-VS-9100D</t>
+        </is>
+      </c>
+      <c r="C39" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D39" s="24" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="E39" s="27" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="F39" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G39" s="67" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="81" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-46 - Oil Mist Separator Skid PS5-60-VS-9100E</t>
+        </is>
+      </c>
+      <c r="C40" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D40" s="24" t="inlineStr"/>
+      <c r="E40" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F40" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G40" s="67" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="81" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-47 - Oil Mist Separator Skid PS5-60-VS-9100F</t>
+        </is>
+      </c>
+      <c r="C41" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D41" s="24" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="E41" s="27" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="F41" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G41" s="67" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="81" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-56 - Fuel Conditioning Module PS5-60-UZ-8900A</t>
+        </is>
+      </c>
+      <c r="C42" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D42" s="24" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="E42" s="27" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="F42" s="23" t="inlineStr"/>
+      <c r="G42" s="67" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="81" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-62 - Fuel Conditioning Module PS5-60-UZ-8900D</t>
+        </is>
+      </c>
+      <c r="C43" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D43" s="24" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="E43" s="27" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="F43" s="23" t="inlineStr"/>
+      <c r="G43" s="67" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="81" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-70 - Engine A Cooling system</t>
+        </is>
+      </c>
+      <c r="C44" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D44" s="24" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="E44" s="27" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="F44" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G44" s="67" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="81" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-71 - Engine B Cooling system</t>
+        </is>
+      </c>
+      <c r="C45" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D45" s="24" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="E45" s="27" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="F45" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G45" s="67" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="81" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-72 - Engine C Cooling system</t>
+        </is>
+      </c>
+      <c r="C46" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D46" s="24" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="E46" s="27" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="F46" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G46" s="67" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="81" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-73 - Engine D Cooling system</t>
+        </is>
+      </c>
+      <c r="C47" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D47" s="24" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="E47" s="27" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="F47" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G47" s="67" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="81" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-74 - Engine E Cooling system</t>
+        </is>
+      </c>
+      <c r="C48" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D48" s="24" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="E48" s="27" t="inlineStr">
+        <is>
+          <t>PLATFORM ISSUE</t>
+        </is>
+      </c>
+      <c r="F48" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G48" s="67" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="81" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-75 - Engine F Cooling system</t>
+        </is>
+      </c>
+      <c r="C49" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D49" s="24" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="E49" s="27" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="F49" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G49" s="67" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="81" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" s="83" t="inlineStr">
+        <is>
+          <t>PS5-61-05 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0003)</t>
+        </is>
+      </c>
+      <c r="C50" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D50" s="24" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="E50" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F50" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G50" s="67" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="81" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" s="83" t="inlineStr">
+        <is>
+          <t>PS5-61-10 - Outdoor Valves Distribution Board - PS5-61-IG-0042</t>
+        </is>
+      </c>
+      <c r="C51" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D51" s="24" t="inlineStr">
+        <is>
+          <t>DONE(FULL)</t>
+        </is>
+      </c>
+      <c r="E51" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F51" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G51" s="67" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="81" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" s="83" t="inlineStr">
+        <is>
+          <t>PS5-61-11 - Outdoor Valves Distribution Board - PS5-61-IG-0043</t>
+        </is>
+      </c>
+      <c r="C52" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D52" s="24" t="inlineStr">
+        <is>
+          <t>DONE(FULL)</t>
+        </is>
+      </c>
+      <c r="E52" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F52" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G52" s="67" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="81" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" s="83" t="inlineStr">
+        <is>
+          <t>PS5-62-04 - Outdoor Emergency Lighting DB  - PS5-05-IG-0006</t>
+        </is>
+      </c>
+      <c r="C53" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D53" s="24" t="inlineStr">
+        <is>
+          <t>DONE(FULL)</t>
+        </is>
+      </c>
+      <c r="E53" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F53" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G53" s="67" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="81" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" s="83" t="inlineStr">
+        <is>
+          <t>PS5-63-04 - Electrical Earthing - EITS Building</t>
+        </is>
+      </c>
+      <c r="C54" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D54" s="24" t="inlineStr"/>
+      <c r="E54" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F54" s="23" t="inlineStr"/>
+      <c r="G54" s="67" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="81" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" s="83" t="inlineStr">
+        <is>
+          <t>PS5-71-22 - Diesel Fuel Pre Pressure Module</t>
+        </is>
+      </c>
+      <c r="C55" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D55" s="24" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="E55" s="27" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="F55" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G55" s="67" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="81" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" s="83" t="inlineStr">
+        <is>
+          <t>PS5-74-03 - Nitrogen Receiver</t>
+        </is>
+      </c>
+      <c r="C56" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D56" s="24" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="E56" s="27" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="F56" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G56" s="67" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="81" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" s="83" t="inlineStr">
+        <is>
+          <t>PS5-83-01 - EITS Building</t>
+        </is>
+      </c>
+      <c r="C57" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D57" s="24" t="inlineStr">
+        <is>
+          <t>DONE(FULL)</t>
+        </is>
+      </c>
+      <c r="E57" s="27" t="inlineStr">
+        <is>
+          <t>DONE(FULL)</t>
+        </is>
+      </c>
+      <c r="F57" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G57" s="67" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="81" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" s="83" t="inlineStr">
+        <is>
+          <t>PS5-84-03 - Shelters</t>
+        </is>
+      </c>
+      <c r="C58" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D58" s="24" t="inlineStr"/>
+      <c r="E58" s="27" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="F58" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G58" s="67" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="81" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" s="83" t="inlineStr">
+        <is>
+          <t>PS5-86-01 - Shelters</t>
+        </is>
+      </c>
+      <c r="C59" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D59" s="24" t="inlineStr"/>
+      <c r="E59" s="27" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="F59" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G59" s="67" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="81" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" s="83" t="inlineStr">
+        <is>
           <t>PS5-91-01 - Multicore cables &amp; JB</t>
         </is>
       </c>
-      <c r="C38" s="27" t="inlineStr">
+      <c r="C60" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="D38" s="24" t="inlineStr">
-        <is>
-          <t>DONE(full)</t>
-        </is>
-      </c>
-      <c r="E38" s="27" t="inlineStr">
+      <c r="D60" s="24" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="E60" s="27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F38" s="23" t="inlineStr">
+      <c r="F60" s="23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G38" s="67" t="inlineStr"/>
+      <c r="G60" s="67" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:G38"/>
+  <autoFilter ref="A2:G60"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
@@ -2280,6 +2998,28 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B36" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B37" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B38" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B39" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B40" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B41" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B42" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B43" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B44" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B45" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B46" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B47" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B48" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B49" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B50" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B51" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B52" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B53" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B54" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B55" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B56" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B57" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B58" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B59" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B60" r:id="rId58"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXCEL/7 - COMPLETE.xlsx
+++ b/EXCEL/7 - COMPLETE.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SIDMAP" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'7 · COMPLETE'!$A$2:$G$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'7 · COMPLETE'!$A$2:$G$66</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1152,7 +1152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1231,7 +1231,7 @@
       <c r="D3" s="24" t="inlineStr"/>
       <c r="E3" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F3" s="23" t="inlineStr">
@@ -1258,7 +1258,7 @@
       <c r="D4" s="24" t="inlineStr"/>
       <c r="E4" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F4" s="23" t="inlineStr">
@@ -1311,12 +1311,12 @@
       </c>
       <c r="D6" s="24" t="inlineStr">
         <is>
-          <t>DONE (PARTIAL)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="E6" s="27" t="inlineStr">
         <is>
-          <t>DONE(FULL)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F6" s="23" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="D7" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="E7" s="27" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="D8" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="E8" s="27" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="D9" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="E9" s="27" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="D10" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="E10" s="27" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="D11" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="E11" s="27" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="E12" s="27" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="D13" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="E13" s="27" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="E14" s="27" t="inlineStr">
@@ -1587,7 +1587,7 @@
       <c r="D15" s="24" t="inlineStr"/>
       <c r="E15" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F15" s="23" t="inlineStr"/>
@@ -1607,14 +1607,10 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="D16" s="24" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
+      <c r="D16" s="24" t="inlineStr"/>
       <c r="E16" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F16" s="23" t="inlineStr">
@@ -1630,7 +1626,7 @@
       </c>
       <c r="B17" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-01 - Power Generation Package A</t>
+          <t>PS5-28-05 - HP Relief Header</t>
         </is>
       </c>
       <c r="C17" s="27" t="inlineStr">
@@ -1640,12 +1636,12 @@
       </c>
       <c r="D17" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="E17" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F17" s="23" t="inlineStr">
@@ -1656,32 +1652,32 @@
       <c r="G17" s="67" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="81" t="n">
+      <c r="A18" s="85" t="n">
         <v>16</v>
       </c>
       <c r="B18" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-02 - Power Gen Package A (UCP)</t>
+          <t>PS5-53-01 - Utility Water / Storage Tank</t>
         </is>
       </c>
       <c r="C18" s="27" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="D18" s="24" t="inlineStr">
         <is>
-          <t>PS5 - Milestone B</t>
-        </is>
-      </c>
-      <c r="E18" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E18" s="69" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F18" s="23" t="inlineStr">
         <is>
-          <t>WALKDOWN COMPLETE-20-08-26--ATTENDENCE SHEET TO BE SUBMITTED</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G18" s="67" t="inlineStr"/>
@@ -1692,7 +1688,7 @@
       </c>
       <c r="B19" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-04 - Power Generation Package B</t>
+          <t>PS5-60-01 - Power Generation Package A</t>
         </is>
       </c>
       <c r="C19" s="27" t="inlineStr">
@@ -1702,12 +1698,12 @@
       </c>
       <c r="D19" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="E19" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F19" s="23" t="inlineStr">
@@ -1723,7 +1719,7 @@
       </c>
       <c r="B20" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-23 - Instrument Air Distribution lines</t>
+          <t>PS5-60-02 - Power Gen Package A (UCP)</t>
         </is>
       </c>
       <c r="C20" s="27" t="inlineStr">
@@ -1731,15 +1727,19 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="D20" s="24" t="inlineStr"/>
+      <c r="D20" s="24" t="inlineStr">
+        <is>
+          <t>PS5 - Milestone B</t>
+        </is>
+      </c>
       <c r="E20" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F20" s="23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>WALKDOWN COMPLETE-20-08-26--ATTENDENCE SHEET TO BE SUBMITTED</t>
         </is>
       </c>
       <c r="G20" s="67" t="inlineStr"/>
@@ -1750,7 +1750,7 @@
       </c>
       <c r="B21" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-26 - Instrument Air Compressor Skid</t>
+          <t>PS5-60-04 - Power Generation Package B</t>
         </is>
       </c>
       <c r="C21" s="27" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="D21" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="E21" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F21" s="23" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="B22" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-27 - Compressed Air Starting Skid</t>
+          <t>PS5-60-23 - Instrument Air Distribution lines</t>
         </is>
       </c>
       <c r="C22" s="27" t="inlineStr">
@@ -1789,14 +1789,10 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="D22" s="24" t="inlineStr">
-        <is>
-          <t>DONE(full)</t>
-        </is>
-      </c>
+      <c r="D22" s="24" t="inlineStr"/>
       <c r="E22" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F22" s="23" t="inlineStr">
@@ -1812,7 +1808,7 @@
       </c>
       <c r="B23" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-28 - Air Receiver A &amp; Air Regulator A</t>
+          <t>PS5-60-26 - Instrument Air Compressor Skid</t>
         </is>
       </c>
       <c r="C23" s="27" t="inlineStr">
@@ -1822,12 +1818,12 @@
       </c>
       <c r="D23" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="E23" s="27" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F23" s="23" t="inlineStr">
@@ -1843,7 +1839,7 @@
       </c>
       <c r="B24" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-29 - Air Receiver B &amp; Air Regulator B</t>
+          <t>PS5-60-27 - Compressed Air Starting Skid</t>
         </is>
       </c>
       <c r="C24" s="27" t="inlineStr">
@@ -1853,12 +1849,12 @@
       </c>
       <c r="D24" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="E24" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F24" s="23" t="inlineStr">
@@ -1874,7 +1870,7 @@
       </c>
       <c r="B25" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-30 - Air Receiver C &amp; Air Regulator C</t>
+          <t>PS5-60-28 - Air Receiver A &amp; Air Regulator A</t>
         </is>
       </c>
       <c r="C25" s="27" t="inlineStr">
@@ -1884,12 +1880,12 @@
       </c>
       <c r="D25" s="24" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="E25" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="F25" s="23" t="inlineStr">
@@ -1905,7 +1901,7 @@
       </c>
       <c r="B26" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-31 - Air Receiver D &amp; Air Regulator D</t>
+          <t>PS5-60-29 - Air Receiver B &amp; Air Regulator B</t>
         </is>
       </c>
       <c r="C26" s="27" t="inlineStr">
@@ -1915,12 +1911,12 @@
       </c>
       <c r="D26" s="24" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="E26" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F26" s="23" t="inlineStr">
@@ -1936,7 +1932,7 @@
       </c>
       <c r="B27" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-32 - Air Receiver E &amp; Air Regulator E</t>
+          <t>PS5-60-30 - Air Receiver C &amp; Air Regulator C</t>
         </is>
       </c>
       <c r="C27" s="27" t="inlineStr">
@@ -1946,12 +1942,12 @@
       </c>
       <c r="D27" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="E27" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F27" s="23" t="inlineStr">
@@ -1967,7 +1963,7 @@
       </c>
       <c r="B28" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-33 - Air Receiver F &amp; Air Regulator F</t>
+          <t>PS5-60-31 - Air Receiver D &amp; Air Regulator D</t>
         </is>
       </c>
       <c r="C28" s="27" t="inlineStr">
@@ -1977,12 +1973,12 @@
       </c>
       <c r="D28" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="E28" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F28" s="23" t="inlineStr">
@@ -1998,7 +1994,7 @@
       </c>
       <c r="B29" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-34 - Air Receiver G &amp; Air Regulator G</t>
+          <t>PS5-60-32 - Air Receiver E &amp; Air Regulator E</t>
         </is>
       </c>
       <c r="C29" s="27" t="inlineStr">
@@ -2008,12 +2004,12 @@
       </c>
       <c r="D29" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="E29" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F29" s="23" t="inlineStr">
@@ -2029,7 +2025,7 @@
       </c>
       <c r="B30" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-35 - Injector Tip Cooling Module A</t>
+          <t>PS5-60-33 - Air Receiver F &amp; Air Regulator F</t>
         </is>
       </c>
       <c r="C30" s="27" t="inlineStr">
@@ -2039,12 +2035,12 @@
       </c>
       <c r="D30" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="E30" s="27" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F30" s="23" t="inlineStr">
@@ -2060,7 +2056,7 @@
       </c>
       <c r="B31" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-36 - Injector Tip Cooling Module B</t>
+          <t>PS5-60-34 - Air Receiver G &amp; Air Regulator G</t>
         </is>
       </c>
       <c r="C31" s="27" t="inlineStr">
@@ -2070,12 +2066,12 @@
       </c>
       <c r="D31" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="E31" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F31" s="23" t="inlineStr">
@@ -2091,7 +2087,7 @@
       </c>
       <c r="B32" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-37 - Injector Tip Cooling Module C</t>
+          <t>PS5-60-35 - Injector Tip Cooling Module A</t>
         </is>
       </c>
       <c r="C32" s="27" t="inlineStr">
@@ -2101,12 +2097,12 @@
       </c>
       <c r="D32" s="24" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="E32" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="F32" s="23" t="inlineStr">
@@ -2122,7 +2118,7 @@
       </c>
       <c r="B33" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-38 - Injector Tip Cooling Module D</t>
+          <t>PS5-60-36 - Injector Tip Cooling Module B</t>
         </is>
       </c>
       <c r="C33" s="27" t="inlineStr">
@@ -2132,12 +2128,12 @@
       </c>
       <c r="D33" s="24" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="E33" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F33" s="23" t="inlineStr">
@@ -2153,7 +2149,7 @@
       </c>
       <c r="B34" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-39 - Injector Tip Cooling Module E</t>
+          <t>PS5-60-37 - Injector Tip Cooling Module C</t>
         </is>
       </c>
       <c r="C34" s="27" t="inlineStr">
@@ -2163,12 +2159,12 @@
       </c>
       <c r="D34" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="E34" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F34" s="23" t="inlineStr">
@@ -2184,7 +2180,7 @@
       </c>
       <c r="B35" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-40 - Injector Tip Cooling Module F</t>
+          <t>PS5-60-38 - Injector Tip Cooling Module D</t>
         </is>
       </c>
       <c r="C35" s="27" t="inlineStr">
@@ -2194,12 +2190,12 @@
       </c>
       <c r="D35" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="E35" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F35" s="23" t="inlineStr">
@@ -2215,7 +2211,7 @@
       </c>
       <c r="B36" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-42 - Oil Mist Separator Skid PS5-60-VS-9100A</t>
+          <t>PS5-60-39 - Injector Tip Cooling Module E</t>
         </is>
       </c>
       <c r="C36" s="27" t="inlineStr">
@@ -2225,12 +2221,12 @@
       </c>
       <c r="D36" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="E36" s="27" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F36" s="23" t="inlineStr">
@@ -2246,7 +2242,7 @@
       </c>
       <c r="B37" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-43 - Oil Mist Separator Skid PS5-60-VS-9100B</t>
+          <t>PS5-60-40 - Injector Tip Cooling Module F</t>
         </is>
       </c>
       <c r="C37" s="27" t="inlineStr">
@@ -2256,12 +2252,12 @@
       </c>
       <c r="D37" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="E37" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F37" s="23" t="inlineStr">
@@ -2277,7 +2273,7 @@
       </c>
       <c r="B38" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-44 - Oil Mist Separator Skid PS5-60-VS-9100C</t>
+          <t>PS5-60-42 - Oil Mist Separator Skid PS5-60-VS-9100A</t>
         </is>
       </c>
       <c r="C38" s="27" t="inlineStr">
@@ -2287,12 +2283,12 @@
       </c>
       <c r="D38" s="24" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="E38" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="F38" s="23" t="inlineStr">
@@ -2308,7 +2304,7 @@
       </c>
       <c r="B39" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-45 - Oil Mist Separator Skid PS5-60-VS-9100D</t>
+          <t>PS5-60-43 - Oil Mist Separator Skid PS5-60-VS-9100B</t>
         </is>
       </c>
       <c r="C39" s="27" t="inlineStr">
@@ -2318,12 +2314,12 @@
       </c>
       <c r="D39" s="24" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="E39" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F39" s="23" t="inlineStr">
@@ -2339,7 +2335,7 @@
       </c>
       <c r="B40" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-46 - Oil Mist Separator Skid PS5-60-VS-9100E</t>
+          <t>PS5-60-44 - Oil Mist Separator Skid PS5-60-VS-9100C</t>
         </is>
       </c>
       <c r="C40" s="27" t="inlineStr">
@@ -2347,10 +2343,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="D40" s="24" t="inlineStr"/>
+      <c r="D40" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
       <c r="E40" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F40" s="23" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="B41" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-47 - Oil Mist Separator Skid PS5-60-VS-9100F</t>
+          <t>PS5-60-45 - Oil Mist Separator Skid PS5-60-VS-9100D</t>
         </is>
       </c>
       <c r="C41" s="27" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="D41" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="E41" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F41" s="23" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="B42" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-56 - Fuel Conditioning Module PS5-60-UZ-8900A</t>
+          <t>PS5-60-46 - Oil Mist Separator Skid PS5-60-VS-9100E</t>
         </is>
       </c>
       <c r="C42" s="27" t="inlineStr">
@@ -2405,17 +2405,17 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="D42" s="24" t="inlineStr">
-        <is>
-          <t>DONE(full)</t>
-        </is>
-      </c>
+      <c r="D42" s="24" t="inlineStr"/>
       <c r="E42" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
-        </is>
-      </c>
-      <c r="F42" s="23" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F42" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="G42" s="67" t="inlineStr"/>
     </row>
     <row r="43">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="B43" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-62 - Fuel Conditioning Module PS5-60-UZ-8900D</t>
+          <t>PS5-60-47 - Oil Mist Separator Skid PS5-60-VS-9100F</t>
         </is>
       </c>
       <c r="C43" s="27" t="inlineStr">
@@ -2434,15 +2434,19 @@
       </c>
       <c r="D43" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="E43" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
-        </is>
-      </c>
-      <c r="F43" s="23" t="inlineStr"/>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F43" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="G43" s="67" t="inlineStr"/>
     </row>
     <row r="44">
@@ -2451,7 +2455,7 @@
       </c>
       <c r="B44" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-70 - Engine A Cooling system</t>
+          <t>PS5-60-56 - Fuel Conditioning Module PS5-60-UZ-8900A</t>
         </is>
       </c>
       <c r="C44" s="27" t="inlineStr">
@@ -2461,19 +2465,15 @@
       </c>
       <c r="D44" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="E44" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
-        </is>
-      </c>
-      <c r="F44" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F44" s="23" t="inlineStr"/>
       <c r="G44" s="67" t="inlineStr"/>
     </row>
     <row r="45">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="B45" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-71 - Engine B Cooling system</t>
+          <t>PS5-60-58 - Fuel Conditioning Module PS5-60-UZ-8900B</t>
         </is>
       </c>
       <c r="C45" s="27" t="inlineStr">
@@ -2492,19 +2492,15 @@
       </c>
       <c r="D45" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="E45" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
-        </is>
-      </c>
-      <c r="F45" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F45" s="23" t="inlineStr"/>
       <c r="G45" s="67" t="inlineStr"/>
     </row>
     <row r="46">
@@ -2513,7 +2509,7 @@
       </c>
       <c r="B46" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-72 - Engine C Cooling system</t>
+          <t>PS5-60-60 - Fuel Conditioning Module PS5-60-UZ-8900C</t>
         </is>
       </c>
       <c r="C46" s="27" t="inlineStr">
@@ -2523,19 +2519,15 @@
       </c>
       <c r="D46" s="24" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="E46" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
-        </is>
-      </c>
-      <c r="F46" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F46" s="23" t="inlineStr"/>
       <c r="G46" s="67" t="inlineStr"/>
     </row>
     <row r="47">
@@ -2544,7 +2536,7 @@
       </c>
       <c r="B47" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-73 - Engine D Cooling system</t>
+          <t>PS5-60-62 - Fuel Conditioning Module PS5-60-UZ-8900D</t>
         </is>
       </c>
       <c r="C47" s="27" t="inlineStr">
@@ -2554,19 +2546,15 @@
       </c>
       <c r="D47" s="24" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="E47" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
-        </is>
-      </c>
-      <c r="F47" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F47" s="23" t="inlineStr"/>
       <c r="G47" s="67" t="inlineStr"/>
     </row>
     <row r="48">
@@ -2575,7 +2563,7 @@
       </c>
       <c r="B48" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-74 - Engine E Cooling system</t>
+          <t>PS5-60-70 - Engine A Cooling system</t>
         </is>
       </c>
       <c r="C48" s="27" t="inlineStr">
@@ -2585,12 +2573,12 @@
       </c>
       <c r="D48" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="E48" s="27" t="inlineStr">
         <is>
-          <t>PLATFORM ISSUE</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F48" s="23" t="inlineStr">
@@ -2606,7 +2594,7 @@
       </c>
       <c r="B49" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-75 - Engine F Cooling system</t>
+          <t>PS5-60-71 - Engine B Cooling system</t>
         </is>
       </c>
       <c r="C49" s="27" t="inlineStr">
@@ -2616,12 +2604,12 @@
       </c>
       <c r="D49" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="E49" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F49" s="23" t="inlineStr">
@@ -2637,7 +2625,7 @@
       </c>
       <c r="B50" s="83" t="inlineStr">
         <is>
-          <t>PS5-61-05 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0003)</t>
+          <t>PS5-60-72 - Engine C Cooling system</t>
         </is>
       </c>
       <c r="C50" s="27" t="inlineStr">
@@ -2647,12 +2635,12 @@
       </c>
       <c r="D50" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="E50" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F50" s="23" t="inlineStr">
@@ -2668,7 +2656,7 @@
       </c>
       <c r="B51" s="83" t="inlineStr">
         <is>
-          <t>PS5-61-10 - Outdoor Valves Distribution Board - PS5-61-IG-0042</t>
+          <t>PS5-60-73 - Engine D Cooling system</t>
         </is>
       </c>
       <c r="C51" s="27" t="inlineStr">
@@ -2678,12 +2666,12 @@
       </c>
       <c r="D51" s="24" t="inlineStr">
         <is>
-          <t>DONE(FULL)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="E51" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F51" s="23" t="inlineStr">
@@ -2699,7 +2687,7 @@
       </c>
       <c r="B52" s="83" t="inlineStr">
         <is>
-          <t>PS5-61-11 - Outdoor Valves Distribution Board - PS5-61-IG-0043</t>
+          <t>PS5-60-74 - Engine E Cooling system</t>
         </is>
       </c>
       <c r="C52" s="27" t="inlineStr">
@@ -2709,12 +2697,12 @@
       </c>
       <c r="D52" s="24" t="inlineStr">
         <is>
-          <t>DONE(FULL)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="E52" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PLATFORM ISSUE</t>
         </is>
       </c>
       <c r="F52" s="23" t="inlineStr">
@@ -2730,7 +2718,7 @@
       </c>
       <c r="B53" s="83" t="inlineStr">
         <is>
-          <t>PS5-62-04 - Outdoor Emergency Lighting DB  - PS5-05-IG-0006</t>
+          <t>PS5-60-75 - Engine F Cooling system</t>
         </is>
       </c>
       <c r="C53" s="27" t="inlineStr">
@@ -2740,12 +2728,12 @@
       </c>
       <c r="D53" s="24" t="inlineStr">
         <is>
-          <t>DONE(FULL)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="E53" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F53" s="23" t="inlineStr">
@@ -2761,7 +2749,7 @@
       </c>
       <c r="B54" s="83" t="inlineStr">
         <is>
-          <t>PS5-63-04 - Electrical Earthing - EITS Building</t>
+          <t>PS5-61-05 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0003)</t>
         </is>
       </c>
       <c r="C54" s="27" t="inlineStr">
@@ -2769,13 +2757,21 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="D54" s="24" t="inlineStr"/>
+      <c r="D54" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
       <c r="E54" s="27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F54" s="23" t="inlineStr"/>
+      <c r="F54" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="G54" s="67" t="inlineStr"/>
     </row>
     <row r="55">
@@ -2784,7 +2780,7 @@
       </c>
       <c r="B55" s="83" t="inlineStr">
         <is>
-          <t>PS5-71-22 - Diesel Fuel Pre Pressure Module</t>
+          <t>PS5-61-07 - 0.4kV Switchboard EITS Building (PS5-61-IK-0001)</t>
         </is>
       </c>
       <c r="C55" s="27" t="inlineStr">
@@ -2794,17 +2790,17 @@
       </c>
       <c r="D55" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="E55" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F55" s="23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>PS5-61-IV-0001B cannot close ITR due to transformer leakage issue.</t>
         </is>
       </c>
       <c r="G55" s="67" t="inlineStr"/>
@@ -2815,7 +2811,7 @@
       </c>
       <c r="B56" s="83" t="inlineStr">
         <is>
-          <t>PS5-74-03 - Nitrogen Receiver</t>
+          <t>PS5-61-10 - Outdoor Valves Distribution Board - PS5-61-IG-0042</t>
         </is>
       </c>
       <c r="C56" s="27" t="inlineStr">
@@ -2825,12 +2821,12 @@
       </c>
       <c r="D56" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="E56" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F56" s="23" t="inlineStr">
@@ -2846,7 +2842,7 @@
       </c>
       <c r="B57" s="83" t="inlineStr">
         <is>
-          <t>PS5-83-01 - EITS Building</t>
+          <t>PS5-61-11 - Outdoor Valves Distribution Board - PS5-61-IG-0043</t>
         </is>
       </c>
       <c r="C57" s="27" t="inlineStr">
@@ -2856,12 +2852,12 @@
       </c>
       <c r="D57" s="24" t="inlineStr">
         <is>
-          <t>DONE(FULL)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="E57" s="27" t="inlineStr">
         <is>
-          <t>DONE(FULL)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F57" s="23" t="inlineStr">
@@ -2877,7 +2873,7 @@
       </c>
       <c r="B58" s="83" t="inlineStr">
         <is>
-          <t>PS5-84-03 - Shelters</t>
+          <t>PS5-62-04 - Outdoor Emergency Lighting DB  - PS5-05-IG-0006</t>
         </is>
       </c>
       <c r="C58" s="27" t="inlineStr">
@@ -2885,10 +2881,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="D58" s="24" t="inlineStr"/>
+      <c r="D58" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
       <c r="E58" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F58" s="23" t="inlineStr">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="B59" s="83" t="inlineStr">
         <is>
-          <t>PS5-86-01 - Shelters</t>
+          <t>PS5-63-04 - Electrical Earthing - EITS Building</t>
         </is>
       </c>
       <c r="C59" s="27" t="inlineStr">
@@ -2915,14 +2915,10 @@
       <c r="D59" s="24" t="inlineStr"/>
       <c r="E59" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
-        </is>
-      </c>
-      <c r="F59" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F59" s="23" t="inlineStr"/>
       <c r="G59" s="67" t="inlineStr"/>
     </row>
     <row r="60">
@@ -2931,33 +2927,211 @@
       </c>
       <c r="B60" s="83" t="inlineStr">
         <is>
+          <t>PS5-71-22 - Diesel Fuel Pre Pressure Module</t>
+        </is>
+      </c>
+      <c r="C60" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D60" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E60" s="27" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="F60" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G60" s="67" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="81" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" s="83" t="inlineStr">
+        <is>
+          <t>PS5-74-03 - Nitrogen Receiver</t>
+        </is>
+      </c>
+      <c r="C61" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D61" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E61" s="27" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F61" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G61" s="67" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="85" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" s="83" t="inlineStr">
+        <is>
+          <t>PS5-78-01 - Lifting and handling equipment</t>
+        </is>
+      </c>
+      <c r="C62" s="27" t="inlineStr">
+        <is>
+          <t>73%</t>
+        </is>
+      </c>
+      <c r="D62" s="24" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E62" s="69" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="F62" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G62" s="67" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="81" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" s="83" t="inlineStr">
+        <is>
+          <t>PS5-83-01 - EITS Building</t>
+        </is>
+      </c>
+      <c r="C63" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D63" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E63" s="27" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F63" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G63" s="67" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="81" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" s="83" t="inlineStr">
+        <is>
+          <t>PS5-84-03 - Shelters</t>
+        </is>
+      </c>
+      <c r="C64" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D64" s="24" t="inlineStr"/>
+      <c r="E64" s="27" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F64" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G64" s="67" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="81" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" s="83" t="inlineStr">
+        <is>
+          <t>PS5-86-01 - Shelters</t>
+        </is>
+      </c>
+      <c r="C65" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D65" s="24" t="inlineStr"/>
+      <c r="E65" s="27" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F65" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G65" s="67" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="81" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" s="83" t="inlineStr">
+        <is>
           <t>PS5-91-01 - Multicore cables &amp; JB</t>
         </is>
       </c>
-      <c r="C60" s="27" t="inlineStr">
+      <c r="C66" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="D60" s="24" t="inlineStr">
-        <is>
-          <t>DONE(full)</t>
-        </is>
-      </c>
-      <c r="E60" s="27" t="inlineStr">
+      <c r="D66" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E66" s="27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F60" s="23" t="inlineStr">
+      <c r="F66" s="23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G60" s="67" t="inlineStr"/>
+      <c r="G66" s="67" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:G60"/>
+  <autoFilter ref="A2:G66"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
@@ -3020,6 +3194,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B58" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B59" r:id="rId57"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B60" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B61" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B62" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B63" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B64" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B65" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B66" r:id="rId64"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXCEL/7 - COMPLETE.xlsx
+++ b/EXCEL/7 - COMPLETE.xlsx
@@ -172,7 +172,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="37">
     <fill>
       <patternFill/>
     </fill>
@@ -303,12 +303,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFfff8e1"/>
         <bgColor rgb="FFfff8e1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
-        <bgColor rgb="FFBDD7EE"/>
       </patternFill>
     </fill>
     <fill>
@@ -504,7 +498,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -518,6 +512,9 @@
     <xf numFmtId="0" fontId="19" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -527,12 +524,12 @@
     <xf numFmtId="0" fontId="19" fillId="32" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -542,19 +539,16 @@
     <xf numFmtId="0" fontId="2" fillId="32" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -564,12 +558,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -579,23 +573,23 @@
     <xf numFmtId="0" fontId="10" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="36" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="37" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
@@ -683,13 +677,10 @@
     <xf numFmtId="0" fontId="11" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -707,10 +698,7 @@
     <xf numFmtId="0" fontId="7" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -722,52 +710,46 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1170,12 +1152,12 @@
           <t>PS5 COMPLETION PLATFORM  |  DONE - subsystems at 100%</t>
         </is>
       </c>
-      <c r="B1" s="100" t="n"/>
-      <c r="C1" s="100" t="n"/>
-      <c r="D1" s="100" t="n"/>
-      <c r="E1" s="100" t="n"/>
-      <c r="F1" s="100" t="n"/>
-      <c r="G1" s="101" t="n"/>
+      <c r="B1" s="96" t="n"/>
+      <c r="C1" s="96" t="n"/>
+      <c r="D1" s="96" t="n"/>
+      <c r="E1" s="96" t="n"/>
+      <c r="F1" s="96" t="n"/>
+      <c r="G1" s="97" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="22" t="inlineStr">
@@ -1215,10 +1197,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="81" t="n">
+      <c r="A3" s="77" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="83" t="inlineStr">
+      <c r="B3" s="79" t="inlineStr">
         <is>
           <t>PS5-01-04 - Fire Water Pump Mini Flow Recycle</t>
         </is>
@@ -1239,13 +1221,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G3" s="67" t="inlineStr"/>
+      <c r="G3" s="66" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="81" t="n">
+      <c r="A4" s="77" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="83" t="inlineStr">
+      <c r="B4" s="79" t="inlineStr">
         <is>
           <t>PS5-01-06 - Foam Concentrate Distribution</t>
         </is>
@@ -1266,13 +1248,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G4" s="67" t="inlineStr"/>
+      <c r="G4" s="66" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="81" t="n">
+      <c r="A5" s="77" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="83" t="inlineStr">
+      <c r="B5" s="79" t="inlineStr">
         <is>
           <t>PS5-01-09 - Inergen for EITS Building</t>
         </is>
@@ -1285,7 +1267,7 @@
       <c r="D5" s="24" t="inlineStr"/>
       <c r="E5" s="27" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F5" s="23" t="inlineStr">
@@ -1293,13 +1275,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G5" s="67" t="inlineStr"/>
+      <c r="G5" s="66" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="81" t="n">
+      <c r="A6" s="77" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="83" t="inlineStr">
+      <c r="B6" s="79" t="inlineStr">
         <is>
           <t>PS5-01-10 - Water Mist Package</t>
         </is>
@@ -1324,13 +1306,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G6" s="67" t="inlineStr"/>
+      <c r="G6" s="66" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="81" t="n">
+      <c r="A7" s="77" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="83" t="inlineStr">
+      <c r="B7" s="79" t="inlineStr">
         <is>
           <t>PS5-03-07 - FZ-07 - Pretreatment Area</t>
         </is>
@@ -1355,13 +1337,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G7" s="67" t="inlineStr"/>
+      <c r="G7" s="66" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="81" t="n">
+      <c r="A8" s="77" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="83" t="inlineStr">
+      <c r="B8" s="79" t="inlineStr">
         <is>
           <t>PS5-03-09 - FZ-09 - Power Generation Building - Engine Bay 1</t>
         </is>
@@ -1386,13 +1368,13 @@
           <t>Due to gland plate issue of SEA-0001 we cannot terminate the cablesof F&amp;G Instruments.</t>
         </is>
       </c>
-      <c r="G8" s="67" t="inlineStr"/>
+      <c r="G8" s="66" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="81" t="n">
+      <c r="A9" s="77" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="83" t="inlineStr">
+      <c r="B9" s="79" t="inlineStr">
         <is>
           <t>PS5-03-10 - FZ-10 - Power Generation Building - Engine Bay 2</t>
         </is>
@@ -1413,13 +1395,13 @@
         </is>
       </c>
       <c r="F9" s="23" t="inlineStr"/>
-      <c r="G9" s="67" t="inlineStr"/>
+      <c r="G9" s="66" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="81" t="n">
+      <c r="A10" s="77" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="83" t="inlineStr">
+      <c r="B10" s="79" t="inlineStr">
         <is>
           <t>PS5-03-13 - FZ-13 - Power Generation Building - Instrument Air Room</t>
         </is>
@@ -1444,13 +1426,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G10" s="67" t="inlineStr"/>
+      <c r="G10" s="66" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="81" t="n">
+      <c r="A11" s="77" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="83" t="inlineStr">
+      <c r="B11" s="79" t="inlineStr">
         <is>
           <t>PS5-03-20 - FZ-20 - Emergency Diesel Generator Enclosure</t>
         </is>
@@ -1467,7 +1449,7 @@
       </c>
       <c r="E11" s="27" t="inlineStr">
         <is>
-          <t>07-Aug-26</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F11" s="23" t="inlineStr">
@@ -1475,13 +1457,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G11" s="67" t="inlineStr"/>
+      <c r="G11" s="66" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="81" t="n">
+      <c r="A12" s="77" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="83" t="inlineStr">
+      <c r="B12" s="79" t="inlineStr">
         <is>
           <t>PS5-05-01 - Emergency Diesel Generator Package</t>
         </is>
@@ -1498,7 +1480,7 @@
       </c>
       <c r="E12" s="27" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F12" s="23" t="inlineStr">
@@ -1506,13 +1488,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G12" s="67" t="inlineStr"/>
+      <c r="G12" s="66" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="81" t="n">
+      <c r="A13" s="77" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="83" t="inlineStr">
+      <c r="B13" s="79" t="inlineStr">
         <is>
           <t>PS5-05-02 - Emergency Diesel Generator Package (UCP)</t>
         </is>
@@ -1529,7 +1511,7 @@
       </c>
       <c r="E13" s="27" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F13" s="23" t="inlineStr">
@@ -1537,13 +1519,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G13" s="67" t="inlineStr"/>
+      <c r="G13" s="66" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="81" t="n">
+      <c r="A14" s="77" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="83" t="inlineStr">
+      <c r="B14" s="79" t="inlineStr">
         <is>
           <t>PS5-06-02 - AC UPS - Power Generator Building</t>
         </is>
@@ -1568,13 +1550,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G14" s="67" t="inlineStr"/>
+      <c r="G14" s="66" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="81" t="n">
+      <c r="A15" s="77" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="83" t="inlineStr">
+      <c r="B15" s="79" t="inlineStr">
         <is>
           <t>PS5-09-05 - HVAC for EITS Building</t>
         </is>
@@ -1591,13 +1573,13 @@
         </is>
       </c>
       <c r="F15" s="23" t="inlineStr"/>
-      <c r="G15" s="67" t="inlineStr"/>
+      <c r="G15" s="66" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="81" t="n">
+      <c r="A16" s="77" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="83" t="inlineStr">
+      <c r="B16" s="79" t="inlineStr">
         <is>
           <t>PS5-28-02 - Closed Drain Header 2</t>
         </is>
@@ -1618,13 +1600,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G16" s="67" t="inlineStr"/>
+      <c r="G16" s="66" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="81" t="n">
+      <c r="A17" s="77" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="83" t="inlineStr">
+      <c r="B17" s="79" t="inlineStr">
         <is>
           <t>PS5-28-05 - HP Relief Header</t>
         </is>
@@ -1649,13 +1631,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G17" s="67" t="inlineStr"/>
+      <c r="G17" s="66" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="85" t="n">
+      <c r="A18" s="81" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="83" t="inlineStr">
+      <c r="B18" s="79" t="inlineStr">
         <is>
           <t>PS5-53-01 - Utility Water / Storage Tank</t>
         </is>
@@ -1670,7 +1652,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="E18" s="69" t="inlineStr">
+      <c r="E18" s="68" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -1680,13 +1662,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G18" s="67" t="inlineStr"/>
+      <c r="G18" s="66" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="81" t="n">
+      <c r="A19" s="77" t="n">
         <v>17</v>
       </c>
-      <c r="B19" s="83" t="inlineStr">
+      <c r="B19" s="79" t="inlineStr">
         <is>
           <t>PS5-60-01 - Power Generation Package A</t>
         </is>
@@ -1711,13 +1693,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G19" s="67" t="inlineStr"/>
+      <c r="G19" s="66" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="81" t="n">
+      <c r="A20" s="77" t="n">
         <v>18</v>
       </c>
-      <c r="B20" s="83" t="inlineStr">
+      <c r="B20" s="79" t="inlineStr">
         <is>
           <t>PS5-60-02 - Power Gen Package A (UCP)</t>
         </is>
@@ -1729,7 +1711,7 @@
       </c>
       <c r="D20" s="24" t="inlineStr">
         <is>
-          <t>PS5 - Milestone B</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="E20" s="27" t="inlineStr">
@@ -1739,16 +1721,16 @@
       </c>
       <c r="F20" s="23" t="inlineStr">
         <is>
-          <t>WALKDOWN COMPLETE-20-08-26--ATTENDENCE SHEET TO BE SUBMITTED</t>
-        </is>
-      </c>
-      <c r="G20" s="67" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="66" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="81" t="n">
+      <c r="A21" s="77" t="n">
         <v>19</v>
       </c>
-      <c r="B21" s="83" t="inlineStr">
+      <c r="B21" s="79" t="inlineStr">
         <is>
           <t>PS5-60-04 - Power Generation Package B</t>
         </is>
@@ -1773,13 +1755,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G21" s="67" t="inlineStr"/>
+      <c r="G21" s="66" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="81" t="n">
+      <c r="A22" s="77" t="n">
         <v>20</v>
       </c>
-      <c r="B22" s="83" t="inlineStr">
+      <c r="B22" s="79" t="inlineStr">
         <is>
           <t>PS5-60-23 - Instrument Air Distribution lines</t>
         </is>
@@ -1800,13 +1782,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G22" s="67" t="inlineStr"/>
+      <c r="G22" s="66" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="81" t="n">
+      <c r="A23" s="77" t="n">
         <v>21</v>
       </c>
-      <c r="B23" s="83" t="inlineStr">
+      <c r="B23" s="79" t="inlineStr">
         <is>
           <t>PS5-60-26 - Instrument Air Compressor Skid</t>
         </is>
@@ -1831,13 +1813,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G23" s="67" t="inlineStr"/>
+      <c r="G23" s="66" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="81" t="n">
+      <c r="A24" s="77" t="n">
         <v>22</v>
       </c>
-      <c r="B24" s="83" t="inlineStr">
+      <c r="B24" s="79" t="inlineStr">
         <is>
           <t>PS5-60-27 - Compressed Air Starting Skid</t>
         </is>
@@ -1862,13 +1844,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G24" s="67" t="inlineStr"/>
+      <c r="G24" s="66" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="81" t="n">
+      <c r="A25" s="77" t="n">
         <v>23</v>
       </c>
-      <c r="B25" s="83" t="inlineStr">
+      <c r="B25" s="79" t="inlineStr">
         <is>
           <t>PS5-60-28 - Air Receiver A &amp; Air Regulator A</t>
         </is>
@@ -1885,7 +1867,7 @@
       </c>
       <c r="E25" s="27" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F25" s="23" t="inlineStr">
@@ -1893,13 +1875,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G25" s="67" t="inlineStr"/>
+      <c r="G25" s="66" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="81" t="n">
+      <c r="A26" s="77" t="n">
         <v>24</v>
       </c>
-      <c r="B26" s="83" t="inlineStr">
+      <c r="B26" s="79" t="inlineStr">
         <is>
           <t>PS5-60-29 - Air Receiver B &amp; Air Regulator B</t>
         </is>
@@ -1924,13 +1906,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G26" s="67" t="inlineStr"/>
+      <c r="G26" s="66" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="81" t="n">
+      <c r="A27" s="77" t="n">
         <v>25</v>
       </c>
-      <c r="B27" s="83" t="inlineStr">
+      <c r="B27" s="79" t="inlineStr">
         <is>
           <t>PS5-60-30 - Air Receiver C &amp; Air Regulator C</t>
         </is>
@@ -1955,13 +1937,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G27" s="67" t="inlineStr"/>
+      <c r="G27" s="66" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="81" t="n">
+      <c r="A28" s="77" t="n">
         <v>26</v>
       </c>
-      <c r="B28" s="83" t="inlineStr">
+      <c r="B28" s="79" t="inlineStr">
         <is>
           <t>PS5-60-31 - Air Receiver D &amp; Air Regulator D</t>
         </is>
@@ -1986,13 +1968,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G28" s="67" t="inlineStr"/>
+      <c r="G28" s="66" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="81" t="n">
+      <c r="A29" s="77" t="n">
         <v>27</v>
       </c>
-      <c r="B29" s="83" t="inlineStr">
+      <c r="B29" s="79" t="inlineStr">
         <is>
           <t>PS5-60-32 - Air Receiver E &amp; Air Regulator E</t>
         </is>
@@ -2017,13 +1999,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G29" s="67" t="inlineStr"/>
+      <c r="G29" s="66" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="81" t="n">
+      <c r="A30" s="77" t="n">
         <v>28</v>
       </c>
-      <c r="B30" s="83" t="inlineStr">
+      <c r="B30" s="79" t="inlineStr">
         <is>
           <t>PS5-60-33 - Air Receiver F &amp; Air Regulator F</t>
         </is>
@@ -2048,13 +2030,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G30" s="67" t="inlineStr"/>
+      <c r="G30" s="66" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="81" t="n">
+      <c r="A31" s="77" t="n">
         <v>29</v>
       </c>
-      <c r="B31" s="83" t="inlineStr">
+      <c r="B31" s="79" t="inlineStr">
         <is>
           <t>PS5-60-34 - Air Receiver G &amp; Air Regulator G</t>
         </is>
@@ -2079,13 +2061,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G31" s="67" t="inlineStr"/>
+      <c r="G31" s="66" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="81" t="n">
+      <c r="A32" s="77" t="n">
         <v>30</v>
       </c>
-      <c r="B32" s="83" t="inlineStr">
+      <c r="B32" s="79" t="inlineStr">
         <is>
           <t>PS5-60-35 - Injector Tip Cooling Module A</t>
         </is>
@@ -2102,7 +2084,7 @@
       </c>
       <c r="E32" s="27" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F32" s="23" t="inlineStr">
@@ -2110,13 +2092,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G32" s="67" t="inlineStr"/>
+      <c r="G32" s="66" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="81" t="n">
+      <c r="A33" s="77" t="n">
         <v>31</v>
       </c>
-      <c r="B33" s="83" t="inlineStr">
+      <c r="B33" s="79" t="inlineStr">
         <is>
           <t>PS5-60-36 - Injector Tip Cooling Module B</t>
         </is>
@@ -2141,13 +2123,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G33" s="67" t="inlineStr"/>
+      <c r="G33" s="66" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="81" t="n">
+      <c r="A34" s="77" t="n">
         <v>32</v>
       </c>
-      <c r="B34" s="83" t="inlineStr">
+      <c r="B34" s="79" t="inlineStr">
         <is>
           <t>PS5-60-37 - Injector Tip Cooling Module C</t>
         </is>
@@ -2172,13 +2154,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G34" s="67" t="inlineStr"/>
+      <c r="G34" s="66" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="81" t="n">
+      <c r="A35" s="77" t="n">
         <v>33</v>
       </c>
-      <c r="B35" s="83" t="inlineStr">
+      <c r="B35" s="79" t="inlineStr">
         <is>
           <t>PS5-60-38 - Injector Tip Cooling Module D</t>
         </is>
@@ -2203,13 +2185,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G35" s="67" t="inlineStr"/>
+      <c r="G35" s="66" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="81" t="n">
+      <c r="A36" s="77" t="n">
         <v>34</v>
       </c>
-      <c r="B36" s="83" t="inlineStr">
+      <c r="B36" s="79" t="inlineStr">
         <is>
           <t>PS5-60-39 - Injector Tip Cooling Module E</t>
         </is>
@@ -2234,13 +2216,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G36" s="67" t="inlineStr"/>
+      <c r="G36" s="66" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="81" t="n">
+      <c r="A37" s="77" t="n">
         <v>35</v>
       </c>
-      <c r="B37" s="83" t="inlineStr">
+      <c r="B37" s="79" t="inlineStr">
         <is>
           <t>PS5-60-40 - Injector Tip Cooling Module F</t>
         </is>
@@ -2265,13 +2247,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G37" s="67" t="inlineStr"/>
+      <c r="G37" s="66" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="81" t="n">
+      <c r="A38" s="77" t="n">
         <v>36</v>
       </c>
-      <c r="B38" s="83" t="inlineStr">
+      <c r="B38" s="79" t="inlineStr">
         <is>
           <t>PS5-60-42 - Oil Mist Separator Skid PS5-60-VS-9100A</t>
         </is>
@@ -2288,7 +2270,7 @@
       </c>
       <c r="E38" s="27" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F38" s="23" t="inlineStr">
@@ -2296,13 +2278,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G38" s="67" t="inlineStr"/>
+      <c r="G38" s="66" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="81" t="n">
+      <c r="A39" s="77" t="n">
         <v>37</v>
       </c>
-      <c r="B39" s="83" t="inlineStr">
+      <c r="B39" s="79" t="inlineStr">
         <is>
           <t>PS5-60-43 - Oil Mist Separator Skid PS5-60-VS-9100B</t>
         </is>
@@ -2327,13 +2309,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G39" s="67" t="inlineStr"/>
+      <c r="G39" s="66" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="81" t="n">
+      <c r="A40" s="77" t="n">
         <v>38</v>
       </c>
-      <c r="B40" s="83" t="inlineStr">
+      <c r="B40" s="79" t="inlineStr">
         <is>
           <t>PS5-60-44 - Oil Mist Separator Skid PS5-60-VS-9100C</t>
         </is>
@@ -2358,13 +2340,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G40" s="67" t="inlineStr"/>
+      <c r="G40" s="66" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="81" t="n">
+      <c r="A41" s="77" t="n">
         <v>39</v>
       </c>
-      <c r="B41" s="83" t="inlineStr">
+      <c r="B41" s="79" t="inlineStr">
         <is>
           <t>PS5-60-45 - Oil Mist Separator Skid PS5-60-VS-9100D</t>
         </is>
@@ -2389,13 +2371,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G41" s="67" t="inlineStr"/>
+      <c r="G41" s="66" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="81" t="n">
+      <c r="A42" s="77" t="n">
         <v>40</v>
       </c>
-      <c r="B42" s="83" t="inlineStr">
+      <c r="B42" s="79" t="inlineStr">
         <is>
           <t>PS5-60-46 - Oil Mist Separator Skid PS5-60-VS-9100E</t>
         </is>
@@ -2416,13 +2398,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G42" s="67" t="inlineStr"/>
+      <c r="G42" s="66" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="81" t="n">
+      <c r="A43" s="77" t="n">
         <v>41</v>
       </c>
-      <c r="B43" s="83" t="inlineStr">
+      <c r="B43" s="79" t="inlineStr">
         <is>
           <t>PS5-60-47 - Oil Mist Separator Skid PS5-60-VS-9100F</t>
         </is>
@@ -2447,13 +2429,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G43" s="67" t="inlineStr"/>
+      <c r="G43" s="66" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="81" t="n">
+      <c r="A44" s="77" t="n">
         <v>42</v>
       </c>
-      <c r="B44" s="83" t="inlineStr">
+      <c r="B44" s="79" t="inlineStr">
         <is>
           <t>PS5-60-56 - Fuel Conditioning Module PS5-60-UZ-8900A</t>
         </is>
@@ -2474,13 +2456,13 @@
         </is>
       </c>
       <c r="F44" s="23" t="inlineStr"/>
-      <c r="G44" s="67" t="inlineStr"/>
+      <c r="G44" s="66" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="81" t="n">
+      <c r="A45" s="77" t="n">
         <v>43</v>
       </c>
-      <c r="B45" s="83" t="inlineStr">
+      <c r="B45" s="79" t="inlineStr">
         <is>
           <t>PS5-60-58 - Fuel Conditioning Module PS5-60-UZ-8900B</t>
         </is>
@@ -2501,13 +2483,13 @@
         </is>
       </c>
       <c r="F45" s="23" t="inlineStr"/>
-      <c r="G45" s="67" t="inlineStr"/>
+      <c r="G45" s="66" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="81" t="n">
+      <c r="A46" s="77" t="n">
         <v>44</v>
       </c>
-      <c r="B46" s="83" t="inlineStr">
+      <c r="B46" s="79" t="inlineStr">
         <is>
           <t>PS5-60-60 - Fuel Conditioning Module PS5-60-UZ-8900C</t>
         </is>
@@ -2528,13 +2510,13 @@
         </is>
       </c>
       <c r="F46" s="23" t="inlineStr"/>
-      <c r="G46" s="67" t="inlineStr"/>
+      <c r="G46" s="66" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="81" t="n">
+      <c r="A47" s="77" t="n">
         <v>45</v>
       </c>
-      <c r="B47" s="83" t="inlineStr">
+      <c r="B47" s="79" t="inlineStr">
         <is>
           <t>PS5-60-62 - Fuel Conditioning Module PS5-60-UZ-8900D</t>
         </is>
@@ -2555,13 +2537,13 @@
         </is>
       </c>
       <c r="F47" s="23" t="inlineStr"/>
-      <c r="G47" s="67" t="inlineStr"/>
+      <c r="G47" s="66" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="81" t="n">
+      <c r="A48" s="77" t="n">
         <v>46</v>
       </c>
-      <c r="B48" s="83" t="inlineStr">
+      <c r="B48" s="79" t="inlineStr">
         <is>
           <t>PS5-60-70 - Engine A Cooling system</t>
         </is>
@@ -2586,13 +2568,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G48" s="67" t="inlineStr"/>
+      <c r="G48" s="66" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="81" t="n">
+      <c r="A49" s="77" t="n">
         <v>47</v>
       </c>
-      <c r="B49" s="83" t="inlineStr">
+      <c r="B49" s="79" t="inlineStr">
         <is>
           <t>PS5-60-71 - Engine B Cooling system</t>
         </is>
@@ -2617,13 +2599,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G49" s="67" t="inlineStr"/>
+      <c r="G49" s="66" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="81" t="n">
+      <c r="A50" s="77" t="n">
         <v>48</v>
       </c>
-      <c r="B50" s="83" t="inlineStr">
+      <c r="B50" s="79" t="inlineStr">
         <is>
           <t>PS5-60-72 - Engine C Cooling system</t>
         </is>
@@ -2648,13 +2630,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G50" s="67" t="inlineStr"/>
+      <c r="G50" s="66" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="81" t="n">
+      <c r="A51" s="77" t="n">
         <v>49</v>
       </c>
-      <c r="B51" s="83" t="inlineStr">
+      <c r="B51" s="79" t="inlineStr">
         <is>
           <t>PS5-60-73 - Engine D Cooling system</t>
         </is>
@@ -2679,13 +2661,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G51" s="67" t="inlineStr"/>
+      <c r="G51" s="66" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="81" t="n">
+      <c r="A52" s="77" t="n">
         <v>50</v>
       </c>
-      <c r="B52" s="83" t="inlineStr">
+      <c r="B52" s="79" t="inlineStr">
         <is>
           <t>PS5-60-74 - Engine E Cooling system</t>
         </is>
@@ -2710,13 +2692,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G52" s="67" t="inlineStr"/>
+      <c r="G52" s="66" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="81" t="n">
+      <c r="A53" s="77" t="n">
         <v>51</v>
       </c>
-      <c r="B53" s="83" t="inlineStr">
+      <c r="B53" s="79" t="inlineStr">
         <is>
           <t>PS5-60-75 - Engine F Cooling system</t>
         </is>
@@ -2741,13 +2723,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G53" s="67" t="inlineStr"/>
+      <c r="G53" s="66" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="81" t="n">
+      <c r="A54" s="77" t="n">
         <v>52</v>
       </c>
-      <c r="B54" s="83" t="inlineStr">
+      <c r="B54" s="79" t="inlineStr">
         <is>
           <t>PS5-61-05 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0003)</t>
         </is>
@@ -2772,13 +2754,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G54" s="67" t="inlineStr"/>
+      <c r="G54" s="66" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="81" t="n">
+      <c r="A55" s="77" t="n">
         <v>53</v>
       </c>
-      <c r="B55" s="83" t="inlineStr">
+      <c r="B55" s="79" t="inlineStr">
         <is>
           <t>PS5-61-07 - 0.4kV Switchboard EITS Building (PS5-61-IK-0001)</t>
         </is>
@@ -2803,13 +2785,13 @@
           <t>PS5-61-IV-0001B cannot close ITR due to transformer leakage issue.</t>
         </is>
       </c>
-      <c r="G55" s="67" t="inlineStr"/>
+      <c r="G55" s="66" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="81" t="n">
+      <c r="A56" s="77" t="n">
         <v>54</v>
       </c>
-      <c r="B56" s="83" t="inlineStr">
+      <c r="B56" s="79" t="inlineStr">
         <is>
           <t>PS5-61-10 - Outdoor Valves Distribution Board - PS5-61-IG-0042</t>
         </is>
@@ -2834,13 +2816,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G56" s="67" t="inlineStr"/>
+      <c r="G56" s="66" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="81" t="n">
+      <c r="A57" s="77" t="n">
         <v>55</v>
       </c>
-      <c r="B57" s="83" t="inlineStr">
+      <c r="B57" s="79" t="inlineStr">
         <is>
           <t>PS5-61-11 - Outdoor Valves Distribution Board - PS5-61-IG-0043</t>
         </is>
@@ -2865,13 +2847,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G57" s="67" t="inlineStr"/>
+      <c r="G57" s="66" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="81" t="n">
+      <c r="A58" s="77" t="n">
         <v>56</v>
       </c>
-      <c r="B58" s="83" t="inlineStr">
+      <c r="B58" s="79" t="inlineStr">
         <is>
           <t>PS5-62-04 - Outdoor Emergency Lighting DB  - PS5-05-IG-0006</t>
         </is>
@@ -2896,13 +2878,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G58" s="67" t="inlineStr"/>
+      <c r="G58" s="66" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="81" t="n">
+      <c r="A59" s="77" t="n">
         <v>57</v>
       </c>
-      <c r="B59" s="83" t="inlineStr">
+      <c r="B59" s="79" t="inlineStr">
         <is>
           <t>PS5-63-04 - Electrical Earthing - EITS Building</t>
         </is>
@@ -2919,13 +2901,13 @@
         </is>
       </c>
       <c r="F59" s="23" t="inlineStr"/>
-      <c r="G59" s="67" t="inlineStr"/>
+      <c r="G59" s="66" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="81" t="n">
+      <c r="A60" s="77" t="n">
         <v>58</v>
       </c>
-      <c r="B60" s="83" t="inlineStr">
+      <c r="B60" s="79" t="inlineStr">
         <is>
           <t>PS5-71-22 - Diesel Fuel Pre Pressure Module</t>
         </is>
@@ -2942,7 +2924,7 @@
       </c>
       <c r="E60" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F60" s="23" t="inlineStr">
@@ -2950,13 +2932,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G60" s="67" t="inlineStr"/>
+      <c r="G60" s="66" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="81" t="n">
+      <c r="A61" s="77" t="n">
         <v>59</v>
       </c>
-      <c r="B61" s="83" t="inlineStr">
+      <c r="B61" s="79" t="inlineStr">
         <is>
           <t>PS5-74-03 - Nitrogen Receiver</t>
         </is>
@@ -2981,13 +2963,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G61" s="67" t="inlineStr"/>
+      <c r="G61" s="66" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="85" t="n">
+      <c r="A62" s="81" t="n">
         <v>60</v>
       </c>
-      <c r="B62" s="83" t="inlineStr">
+      <c r="B62" s="79" t="inlineStr">
         <is>
           <t>PS5-78-01 - Lifting and handling equipment</t>
         </is>
@@ -3002,7 +2984,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="E62" s="69" t="inlineStr">
+      <c r="E62" s="68" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -3012,13 +2994,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G62" s="67" t="inlineStr"/>
+      <c r="G62" s="66" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="81" t="n">
+      <c r="A63" s="77" t="n">
         <v>61</v>
       </c>
-      <c r="B63" s="83" t="inlineStr">
+      <c r="B63" s="79" t="inlineStr">
         <is>
           <t>PS5-83-01 - EITS Building</t>
         </is>
@@ -3043,13 +3025,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G63" s="67" t="inlineStr"/>
+      <c r="G63" s="66" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="81" t="n">
+      <c r="A64" s="77" t="n">
         <v>62</v>
       </c>
-      <c r="B64" s="83" t="inlineStr">
+      <c r="B64" s="79" t="inlineStr">
         <is>
           <t>PS5-84-03 - Shelters</t>
         </is>
@@ -3070,13 +3052,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G64" s="67" t="inlineStr"/>
+      <c r="G64" s="66" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="81" t="n">
+      <c r="A65" s="77" t="n">
         <v>63</v>
       </c>
-      <c r="B65" s="83" t="inlineStr">
+      <c r="B65" s="79" t="inlineStr">
         <is>
           <t>PS5-86-01 - Shelters</t>
         </is>
@@ -3097,13 +3079,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G65" s="67" t="inlineStr"/>
+      <c r="G65" s="66" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="81" t="n">
+      <c r="A66" s="77" t="n">
         <v>64</v>
       </c>
-      <c r="B66" s="83" t="inlineStr">
+      <c r="B66" s="79" t="inlineStr">
         <is>
           <t>PS5-91-01 - Multicore cables &amp; JB</t>
         </is>
@@ -3128,7 +3110,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G66" s="67" t="inlineStr"/>
+      <c r="G66" s="66" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G66"/>

--- a/EXCEL/7 - COMPLETE.xlsx
+++ b/EXCEL/7 - COMPLETE.xlsx
@@ -172,7 +172,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="38">
     <fill>
       <patternFill/>
     </fill>
@@ -303,6 +303,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFfff8e1"/>
         <bgColor rgb="FFfff8e1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD7EE"/>
+        <bgColor rgb="FFBDD7EE"/>
       </patternFill>
     </fill>
     <fill>
@@ -498,7 +504,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -512,9 +518,6 @@
     <xf numFmtId="0" fontId="19" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -524,12 +527,12 @@
     <xf numFmtId="0" fontId="19" fillId="32" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -539,16 +542,19 @@
     <xf numFmtId="0" fontId="2" fillId="32" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -558,12 +564,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -573,21 +579,21 @@
     <xf numFmtId="0" fontId="10" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="36" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="36" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="37" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -677,40 +683,52 @@
     <xf numFmtId="0" fontId="11" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -719,37 +737,37 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1152,12 +1170,12 @@
           <t>PS5 COMPLETION PLATFORM  |  DONE - subsystems at 100%</t>
         </is>
       </c>
-      <c r="B1" s="96" t="n"/>
-      <c r="C1" s="96" t="n"/>
-      <c r="D1" s="96" t="n"/>
-      <c r="E1" s="96" t="n"/>
-      <c r="F1" s="96" t="n"/>
-      <c r="G1" s="97" t="n"/>
+      <c r="B1" s="100" t="n"/>
+      <c r="C1" s="100" t="n"/>
+      <c r="D1" s="100" t="n"/>
+      <c r="E1" s="100" t="n"/>
+      <c r="F1" s="100" t="n"/>
+      <c r="G1" s="101" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="22" t="inlineStr">
@@ -1197,10 +1215,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="77" t="n">
+      <c r="A3" s="81" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="79" t="inlineStr">
+      <c r="B3" s="83" t="inlineStr">
         <is>
           <t>PS5-01-04 - Fire Water Pump Mini Flow Recycle</t>
         </is>
@@ -1221,13 +1239,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G3" s="66" t="inlineStr"/>
+      <c r="G3" s="67" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="77" t="n">
+      <c r="A4" s="81" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="79" t="inlineStr">
+      <c r="B4" s="83" t="inlineStr">
         <is>
           <t>PS5-01-06 - Foam Concentrate Distribution</t>
         </is>
@@ -1248,13 +1266,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G4" s="66" t="inlineStr"/>
+      <c r="G4" s="67" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="77" t="n">
+      <c r="A5" s="81" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="79" t="inlineStr">
+      <c r="B5" s="83" t="inlineStr">
         <is>
           <t>PS5-01-09 - Inergen for EITS Building</t>
         </is>
@@ -1267,7 +1285,7 @@
       <c r="D5" s="24" t="inlineStr"/>
       <c r="E5" s="27" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="F5" s="23" t="inlineStr">
@@ -1275,13 +1293,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G5" s="66" t="inlineStr"/>
+      <c r="G5" s="67" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="77" t="n">
+      <c r="A6" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="79" t="inlineStr">
+      <c r="B6" s="83" t="inlineStr">
         <is>
           <t>PS5-01-10 - Water Mist Package</t>
         </is>
@@ -1306,13 +1324,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G6" s="66" t="inlineStr"/>
+      <c r="G6" s="67" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="77" t="n">
+      <c r="A7" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="79" t="inlineStr">
+      <c r="B7" s="83" t="inlineStr">
         <is>
           <t>PS5-03-07 - FZ-07 - Pretreatment Area</t>
         </is>
@@ -1337,13 +1355,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G7" s="66" t="inlineStr"/>
+      <c r="G7" s="67" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="77" t="n">
+      <c r="A8" s="81" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="79" t="inlineStr">
+      <c r="B8" s="83" t="inlineStr">
         <is>
           <t>PS5-03-09 - FZ-09 - Power Generation Building - Engine Bay 1</t>
         </is>
@@ -1368,13 +1386,13 @@
           <t>Due to gland plate issue of SEA-0001 we cannot terminate the cablesof F&amp;G Instruments.</t>
         </is>
       </c>
-      <c r="G8" s="66" t="inlineStr"/>
+      <c r="G8" s="67" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="77" t="n">
+      <c r="A9" s="81" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="79" t="inlineStr">
+      <c r="B9" s="83" t="inlineStr">
         <is>
           <t>PS5-03-10 - FZ-10 - Power Generation Building - Engine Bay 2</t>
         </is>
@@ -1395,13 +1413,13 @@
         </is>
       </c>
       <c r="F9" s="23" t="inlineStr"/>
-      <c r="G9" s="66" t="inlineStr"/>
+      <c r="G9" s="67" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="77" t="n">
+      <c r="A10" s="81" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="79" t="inlineStr">
+      <c r="B10" s="83" t="inlineStr">
         <is>
           <t>PS5-03-13 - FZ-13 - Power Generation Building - Instrument Air Room</t>
         </is>
@@ -1426,13 +1444,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G10" s="66" t="inlineStr"/>
+      <c r="G10" s="67" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="77" t="n">
+      <c r="A11" s="81" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="79" t="inlineStr">
+      <c r="B11" s="83" t="inlineStr">
         <is>
           <t>PS5-03-20 - FZ-20 - Emergency Diesel Generator Enclosure</t>
         </is>
@@ -1449,114 +1467,114 @@
       </c>
       <c r="E11" s="27" t="inlineStr">
         <is>
+          <t>07-Aug-26</t>
+        </is>
+      </c>
+      <c r="F11" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="67" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="81" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="83" t="inlineStr">
+        <is>
+          <t>PS5-05-01 - Emergency Diesel Generator Package</t>
+        </is>
+      </c>
+      <c r="C12" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D12" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E12" s="27" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="F12" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G12" s="67" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="81" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="83" t="inlineStr">
+        <is>
+          <t>PS5-05-02 - Emergency Diesel Generator Package (UCP)</t>
+        </is>
+      </c>
+      <c r="C13" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D13" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E13" s="27" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+      <c r="F13" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="67" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="81" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="83" t="inlineStr">
+        <is>
+          <t>PS5-06-02 - AC UPS - Power Generator Building</t>
+        </is>
+      </c>
+      <c r="C14" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E14" s="27" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F11" s="23" t="inlineStr">
+      <c r="F14" s="23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G11" s="66" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="77" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" s="79" t="inlineStr">
-        <is>
-          <t>PS5-05-01 - Emergency Diesel Generator Package</t>
-        </is>
-      </c>
-      <c r="C12" s="27" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D12" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E12" s="27" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F12" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G12" s="66" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="77" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" s="79" t="inlineStr">
-        <is>
-          <t>PS5-05-02 - Emergency Diesel Generator Package (UCP)</t>
-        </is>
-      </c>
-      <c r="C13" s="27" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D13" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E13" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F13" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" s="66" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="77" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" s="79" t="inlineStr">
-        <is>
-          <t>PS5-06-02 - AC UPS - Power Generator Building</t>
-        </is>
-      </c>
-      <c r="C14" s="27" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D14" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E14" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F14" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G14" s="66" t="inlineStr"/>
+      <c r="G14" s="67" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="77" t="n">
+      <c r="A15" s="81" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="79" t="inlineStr">
+      <c r="B15" s="83" t="inlineStr">
         <is>
           <t>PS5-09-05 - HVAC for EITS Building</t>
         </is>
@@ -1573,13 +1591,13 @@
         </is>
       </c>
       <c r="F15" s="23" t="inlineStr"/>
-      <c r="G15" s="66" t="inlineStr"/>
+      <c r="G15" s="67" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="77" t="n">
+      <c r="A16" s="81" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="79" t="inlineStr">
+      <c r="B16" s="83" t="inlineStr">
         <is>
           <t>PS5-28-02 - Closed Drain Header 2</t>
         </is>
@@ -1600,13 +1618,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G16" s="66" t="inlineStr"/>
+      <c r="G16" s="67" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="77" t="n">
+      <c r="A17" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="79" t="inlineStr">
+      <c r="B17" s="83" t="inlineStr">
         <is>
           <t>PS5-28-05 - HP Relief Header</t>
         </is>
@@ -1631,13 +1649,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G17" s="66" t="inlineStr"/>
+      <c r="G17" s="67" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="81" t="n">
+      <c r="A18" s="85" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="79" t="inlineStr">
+      <c r="B18" s="83" t="inlineStr">
         <is>
           <t>PS5-53-01 - Utility Water / Storage Tank</t>
         </is>
@@ -1652,7 +1670,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="E18" s="68" t="inlineStr">
+      <c r="E18" s="69" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -1662,13 +1680,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G18" s="66" t="inlineStr"/>
+      <c r="G18" s="67" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="77" t="n">
+      <c r="A19" s="81" t="n">
         <v>17</v>
       </c>
-      <c r="B19" s="79" t="inlineStr">
+      <c r="B19" s="83" t="inlineStr">
         <is>
           <t>PS5-60-01 - Power Generation Package A</t>
         </is>
@@ -1693,13 +1711,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G19" s="66" t="inlineStr"/>
+      <c r="G19" s="67" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="77" t="n">
+      <c r="A20" s="81" t="n">
         <v>18</v>
       </c>
-      <c r="B20" s="79" t="inlineStr">
+      <c r="B20" s="83" t="inlineStr">
         <is>
           <t>PS5-60-02 - Power Gen Package A (UCP)</t>
         </is>
@@ -1711,7 +1729,7 @@
       </c>
       <c r="D20" s="24" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>PS5 - Milestone B</t>
         </is>
       </c>
       <c r="E20" s="27" t="inlineStr">
@@ -1721,47 +1739,47 @@
       </c>
       <c r="F20" s="23" t="inlineStr">
         <is>
+          <t>WALKDOWN COMPLETE-20-08-26--ATTENDENCE SHEET TO BE SUBMITTED</t>
+        </is>
+      </c>
+      <c r="G20" s="67" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="81" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-04 - Power Generation Package B</t>
+        </is>
+      </c>
+      <c r="C21" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D21" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E21" s="27" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F21" s="23" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G20" s="66" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="77" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" s="79" t="inlineStr">
-        <is>
-          <t>PS5-60-04 - Power Generation Package B</t>
-        </is>
-      </c>
-      <c r="C21" s="27" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D21" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E21" s="27" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F21" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G21" s="66" t="inlineStr"/>
+      <c r="G21" s="67" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="77" t="n">
+      <c r="A22" s="81" t="n">
         <v>20</v>
       </c>
-      <c r="B22" s="79" t="inlineStr">
+      <c r="B22" s="83" t="inlineStr">
         <is>
           <t>PS5-60-23 - Instrument Air Distribution lines</t>
         </is>
@@ -1782,13 +1800,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G22" s="66" t="inlineStr"/>
+      <c r="G22" s="67" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="77" t="n">
+      <c r="A23" s="81" t="n">
         <v>21</v>
       </c>
-      <c r="B23" s="79" t="inlineStr">
+      <c r="B23" s="83" t="inlineStr">
         <is>
           <t>PS5-60-26 - Instrument Air Compressor Skid</t>
         </is>
@@ -1813,13 +1831,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G23" s="66" t="inlineStr"/>
+      <c r="G23" s="67" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="77" t="n">
+      <c r="A24" s="81" t="n">
         <v>22</v>
       </c>
-      <c r="B24" s="79" t="inlineStr">
+      <c r="B24" s="83" t="inlineStr">
         <is>
           <t>PS5-60-27 - Compressed Air Starting Skid</t>
         </is>
@@ -1844,13 +1862,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G24" s="66" t="inlineStr"/>
+      <c r="G24" s="67" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="77" t="n">
+      <c r="A25" s="81" t="n">
         <v>23</v>
       </c>
-      <c r="B25" s="79" t="inlineStr">
+      <c r="B25" s="83" t="inlineStr">
         <is>
           <t>PS5-60-28 - Air Receiver A &amp; Air Regulator A</t>
         </is>
@@ -1867,7 +1885,7 @@
       </c>
       <c r="E25" s="27" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="F25" s="23" t="inlineStr">
@@ -1875,13 +1893,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G25" s="66" t="inlineStr"/>
+      <c r="G25" s="67" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="77" t="n">
+      <c r="A26" s="81" t="n">
         <v>24</v>
       </c>
-      <c r="B26" s="79" t="inlineStr">
+      <c r="B26" s="83" t="inlineStr">
         <is>
           <t>PS5-60-29 - Air Receiver B &amp; Air Regulator B</t>
         </is>
@@ -1906,13 +1924,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G26" s="66" t="inlineStr"/>
+      <c r="G26" s="67" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="77" t="n">
+      <c r="A27" s="81" t="n">
         <v>25</v>
       </c>
-      <c r="B27" s="79" t="inlineStr">
+      <c r="B27" s="83" t="inlineStr">
         <is>
           <t>PS5-60-30 - Air Receiver C &amp; Air Regulator C</t>
         </is>
@@ -1937,13 +1955,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G27" s="66" t="inlineStr"/>
+      <c r="G27" s="67" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="77" t="n">
+      <c r="A28" s="81" t="n">
         <v>26</v>
       </c>
-      <c r="B28" s="79" t="inlineStr">
+      <c r="B28" s="83" t="inlineStr">
         <is>
           <t>PS5-60-31 - Air Receiver D &amp; Air Regulator D</t>
         </is>
@@ -1968,13 +1986,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G28" s="66" t="inlineStr"/>
+      <c r="G28" s="67" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="77" t="n">
+      <c r="A29" s="81" t="n">
         <v>27</v>
       </c>
-      <c r="B29" s="79" t="inlineStr">
+      <c r="B29" s="83" t="inlineStr">
         <is>
           <t>PS5-60-32 - Air Receiver E &amp; Air Regulator E</t>
         </is>
@@ -1999,13 +2017,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G29" s="66" t="inlineStr"/>
+      <c r="G29" s="67" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="77" t="n">
+      <c r="A30" s="81" t="n">
         <v>28</v>
       </c>
-      <c r="B30" s="79" t="inlineStr">
+      <c r="B30" s="83" t="inlineStr">
         <is>
           <t>PS5-60-33 - Air Receiver F &amp; Air Regulator F</t>
         </is>
@@ -2030,13 +2048,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G30" s="66" t="inlineStr"/>
+      <c r="G30" s="67" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="77" t="n">
+      <c r="A31" s="81" t="n">
         <v>29</v>
       </c>
-      <c r="B31" s="79" t="inlineStr">
+      <c r="B31" s="83" t="inlineStr">
         <is>
           <t>PS5-60-34 - Air Receiver G &amp; Air Regulator G</t>
         </is>
@@ -2061,13 +2079,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G31" s="66" t="inlineStr"/>
+      <c r="G31" s="67" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="77" t="n">
+      <c r="A32" s="81" t="n">
         <v>30</v>
       </c>
-      <c r="B32" s="79" t="inlineStr">
+      <c r="B32" s="83" t="inlineStr">
         <is>
           <t>PS5-60-35 - Injector Tip Cooling Module A</t>
         </is>
@@ -2084,7 +2102,7 @@
       </c>
       <c r="E32" s="27" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="F32" s="23" t="inlineStr">
@@ -2092,13 +2110,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G32" s="66" t="inlineStr"/>
+      <c r="G32" s="67" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="77" t="n">
+      <c r="A33" s="81" t="n">
         <v>31</v>
       </c>
-      <c r="B33" s="79" t="inlineStr">
+      <c r="B33" s="83" t="inlineStr">
         <is>
           <t>PS5-60-36 - Injector Tip Cooling Module B</t>
         </is>
@@ -2123,13 +2141,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G33" s="66" t="inlineStr"/>
+      <c r="G33" s="67" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="77" t="n">
+      <c r="A34" s="81" t="n">
         <v>32</v>
       </c>
-      <c r="B34" s="79" t="inlineStr">
+      <c r="B34" s="83" t="inlineStr">
         <is>
           <t>PS5-60-37 - Injector Tip Cooling Module C</t>
         </is>
@@ -2154,13 +2172,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G34" s="66" t="inlineStr"/>
+      <c r="G34" s="67" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="77" t="n">
+      <c r="A35" s="81" t="n">
         <v>33</v>
       </c>
-      <c r="B35" s="79" t="inlineStr">
+      <c r="B35" s="83" t="inlineStr">
         <is>
           <t>PS5-60-38 - Injector Tip Cooling Module D</t>
         </is>
@@ -2185,13 +2203,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G35" s="66" t="inlineStr"/>
+      <c r="G35" s="67" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="77" t="n">
+      <c r="A36" s="81" t="n">
         <v>34</v>
       </c>
-      <c r="B36" s="79" t="inlineStr">
+      <c r="B36" s="83" t="inlineStr">
         <is>
           <t>PS5-60-39 - Injector Tip Cooling Module E</t>
         </is>
@@ -2216,13 +2234,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G36" s="66" t="inlineStr"/>
+      <c r="G36" s="67" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="77" t="n">
+      <c r="A37" s="81" t="n">
         <v>35</v>
       </c>
-      <c r="B37" s="79" t="inlineStr">
+      <c r="B37" s="83" t="inlineStr">
         <is>
           <t>PS5-60-40 - Injector Tip Cooling Module F</t>
         </is>
@@ -2247,13 +2265,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G37" s="66" t="inlineStr"/>
+      <c r="G37" s="67" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="77" t="n">
+      <c r="A38" s="81" t="n">
         <v>36</v>
       </c>
-      <c r="B38" s="79" t="inlineStr">
+      <c r="B38" s="83" t="inlineStr">
         <is>
           <t>PS5-60-42 - Oil Mist Separator Skid PS5-60-VS-9100A</t>
         </is>
@@ -2270,7 +2288,7 @@
       </c>
       <c r="E38" s="27" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="F38" s="23" t="inlineStr">
@@ -2278,13 +2296,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G38" s="66" t="inlineStr"/>
+      <c r="G38" s="67" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="77" t="n">
+      <c r="A39" s="81" t="n">
         <v>37</v>
       </c>
-      <c r="B39" s="79" t="inlineStr">
+      <c r="B39" s="83" t="inlineStr">
         <is>
           <t>PS5-60-43 - Oil Mist Separator Skid PS5-60-VS-9100B</t>
         </is>
@@ -2309,13 +2327,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G39" s="66" t="inlineStr"/>
+      <c r="G39" s="67" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="77" t="n">
+      <c r="A40" s="81" t="n">
         <v>38</v>
       </c>
-      <c r="B40" s="79" t="inlineStr">
+      <c r="B40" s="83" t="inlineStr">
         <is>
           <t>PS5-60-44 - Oil Mist Separator Skid PS5-60-VS-9100C</t>
         </is>
@@ -2340,13 +2358,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G40" s="66" t="inlineStr"/>
+      <c r="G40" s="67" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="77" t="n">
+      <c r="A41" s="81" t="n">
         <v>39</v>
       </c>
-      <c r="B41" s="79" t="inlineStr">
+      <c r="B41" s="83" t="inlineStr">
         <is>
           <t>PS5-60-45 - Oil Mist Separator Skid PS5-60-VS-9100D</t>
         </is>
@@ -2371,13 +2389,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G41" s="66" t="inlineStr"/>
+      <c r="G41" s="67" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="77" t="n">
+      <c r="A42" s="81" t="n">
         <v>40</v>
       </c>
-      <c r="B42" s="79" t="inlineStr">
+      <c r="B42" s="83" t="inlineStr">
         <is>
           <t>PS5-60-46 - Oil Mist Separator Skid PS5-60-VS-9100E</t>
         </is>
@@ -2398,13 +2416,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G42" s="66" t="inlineStr"/>
+      <c r="G42" s="67" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="77" t="n">
+      <c r="A43" s="81" t="n">
         <v>41</v>
       </c>
-      <c r="B43" s="79" t="inlineStr">
+      <c r="B43" s="83" t="inlineStr">
         <is>
           <t>PS5-60-47 - Oil Mist Separator Skid PS5-60-VS-9100F</t>
         </is>
@@ -2429,13 +2447,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G43" s="66" t="inlineStr"/>
+      <c r="G43" s="67" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="77" t="n">
+      <c r="A44" s="81" t="n">
         <v>42</v>
       </c>
-      <c r="B44" s="79" t="inlineStr">
+      <c r="B44" s="83" t="inlineStr">
         <is>
           <t>PS5-60-56 - Fuel Conditioning Module PS5-60-UZ-8900A</t>
         </is>
@@ -2456,13 +2474,13 @@
         </is>
       </c>
       <c r="F44" s="23" t="inlineStr"/>
-      <c r="G44" s="66" t="inlineStr"/>
+      <c r="G44" s="67" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="77" t="n">
+      <c r="A45" s="81" t="n">
         <v>43</v>
       </c>
-      <c r="B45" s="79" t="inlineStr">
+      <c r="B45" s="83" t="inlineStr">
         <is>
           <t>PS5-60-58 - Fuel Conditioning Module PS5-60-UZ-8900B</t>
         </is>
@@ -2483,13 +2501,13 @@
         </is>
       </c>
       <c r="F45" s="23" t="inlineStr"/>
-      <c r="G45" s="66" t="inlineStr"/>
+      <c r="G45" s="67" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="77" t="n">
+      <c r="A46" s="81" t="n">
         <v>44</v>
       </c>
-      <c r="B46" s="79" t="inlineStr">
+      <c r="B46" s="83" t="inlineStr">
         <is>
           <t>PS5-60-60 - Fuel Conditioning Module PS5-60-UZ-8900C</t>
         </is>
@@ -2510,13 +2528,13 @@
         </is>
       </c>
       <c r="F46" s="23" t="inlineStr"/>
-      <c r="G46" s="66" t="inlineStr"/>
+      <c r="G46" s="67" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="77" t="n">
+      <c r="A47" s="81" t="n">
         <v>45</v>
       </c>
-      <c r="B47" s="79" t="inlineStr">
+      <c r="B47" s="83" t="inlineStr">
         <is>
           <t>PS5-60-62 - Fuel Conditioning Module PS5-60-UZ-8900D</t>
         </is>
@@ -2537,13 +2555,13 @@
         </is>
       </c>
       <c r="F47" s="23" t="inlineStr"/>
-      <c r="G47" s="66" t="inlineStr"/>
+      <c r="G47" s="67" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="77" t="n">
+      <c r="A48" s="81" t="n">
         <v>46</v>
       </c>
-      <c r="B48" s="79" t="inlineStr">
+      <c r="B48" s="83" t="inlineStr">
         <is>
           <t>PS5-60-70 - Engine A Cooling system</t>
         </is>
@@ -2568,13 +2586,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G48" s="66" t="inlineStr"/>
+      <c r="G48" s="67" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="77" t="n">
+      <c r="A49" s="81" t="n">
         <v>47</v>
       </c>
-      <c r="B49" s="79" t="inlineStr">
+      <c r="B49" s="83" t="inlineStr">
         <is>
           <t>PS5-60-71 - Engine B Cooling system</t>
         </is>
@@ -2599,13 +2617,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G49" s="66" t="inlineStr"/>
+      <c r="G49" s="67" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="77" t="n">
+      <c r="A50" s="81" t="n">
         <v>48</v>
       </c>
-      <c r="B50" s="79" t="inlineStr">
+      <c r="B50" s="83" t="inlineStr">
         <is>
           <t>PS5-60-72 - Engine C Cooling system</t>
         </is>
@@ -2630,13 +2648,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G50" s="66" t="inlineStr"/>
+      <c r="G50" s="67" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="77" t="n">
+      <c r="A51" s="81" t="n">
         <v>49</v>
       </c>
-      <c r="B51" s="79" t="inlineStr">
+      <c r="B51" s="83" t="inlineStr">
         <is>
           <t>PS5-60-73 - Engine D Cooling system</t>
         </is>
@@ -2661,13 +2679,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G51" s="66" t="inlineStr"/>
+      <c r="G51" s="67" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="77" t="n">
+      <c r="A52" s="81" t="n">
         <v>50</v>
       </c>
-      <c r="B52" s="79" t="inlineStr">
+      <c r="B52" s="83" t="inlineStr">
         <is>
           <t>PS5-60-74 - Engine E Cooling system</t>
         </is>
@@ -2692,13 +2710,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G52" s="66" t="inlineStr"/>
+      <c r="G52" s="67" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="77" t="n">
+      <c r="A53" s="81" t="n">
         <v>51</v>
       </c>
-      <c r="B53" s="79" t="inlineStr">
+      <c r="B53" s="83" t="inlineStr">
         <is>
           <t>PS5-60-75 - Engine F Cooling system</t>
         </is>
@@ -2723,13 +2741,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G53" s="66" t="inlineStr"/>
+      <c r="G53" s="67" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="77" t="n">
+      <c r="A54" s="81" t="n">
         <v>52</v>
       </c>
-      <c r="B54" s="79" t="inlineStr">
+      <c r="B54" s="83" t="inlineStr">
         <is>
           <t>PS5-61-05 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0003)</t>
         </is>
@@ -2754,13 +2772,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G54" s="66" t="inlineStr"/>
+      <c r="G54" s="67" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="77" t="n">
+      <c r="A55" s="81" t="n">
         <v>53</v>
       </c>
-      <c r="B55" s="79" t="inlineStr">
+      <c r="B55" s="83" t="inlineStr">
         <is>
           <t>PS5-61-07 - 0.4kV Switchboard EITS Building (PS5-61-IK-0001)</t>
         </is>
@@ -2785,13 +2803,13 @@
           <t>PS5-61-IV-0001B cannot close ITR due to transformer leakage issue.</t>
         </is>
       </c>
-      <c r="G55" s="66" t="inlineStr"/>
+      <c r="G55" s="67" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="77" t="n">
+      <c r="A56" s="81" t="n">
         <v>54</v>
       </c>
-      <c r="B56" s="79" t="inlineStr">
+      <c r="B56" s="83" t="inlineStr">
         <is>
           <t>PS5-61-10 - Outdoor Valves Distribution Board - PS5-61-IG-0042</t>
         </is>
@@ -2816,13 +2834,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G56" s="66" t="inlineStr"/>
+      <c r="G56" s="67" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="77" t="n">
+      <c r="A57" s="81" t="n">
         <v>55</v>
       </c>
-      <c r="B57" s="79" t="inlineStr">
+      <c r="B57" s="83" t="inlineStr">
         <is>
           <t>PS5-61-11 - Outdoor Valves Distribution Board - PS5-61-IG-0043</t>
         </is>
@@ -2847,13 +2865,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G57" s="66" t="inlineStr"/>
+      <c r="G57" s="67" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="77" t="n">
+      <c r="A58" s="81" t="n">
         <v>56</v>
       </c>
-      <c r="B58" s="79" t="inlineStr">
+      <c r="B58" s="83" t="inlineStr">
         <is>
           <t>PS5-62-04 - Outdoor Emergency Lighting DB  - PS5-05-IG-0006</t>
         </is>
@@ -2878,13 +2896,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G58" s="66" t="inlineStr"/>
+      <c r="G58" s="67" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="77" t="n">
+      <c r="A59" s="81" t="n">
         <v>57</v>
       </c>
-      <c r="B59" s="79" t="inlineStr">
+      <c r="B59" s="83" t="inlineStr">
         <is>
           <t>PS5-63-04 - Electrical Earthing - EITS Building</t>
         </is>
@@ -2901,13 +2919,13 @@
         </is>
       </c>
       <c r="F59" s="23" t="inlineStr"/>
-      <c r="G59" s="66" t="inlineStr"/>
+      <c r="G59" s="67" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="77" t="n">
+      <c r="A60" s="81" t="n">
         <v>58</v>
       </c>
-      <c r="B60" s="79" t="inlineStr">
+      <c r="B60" s="83" t="inlineStr">
         <is>
           <t>PS5-71-22 - Diesel Fuel Pre Pressure Module</t>
         </is>
@@ -2924,7 +2942,7 @@
       </c>
       <c r="E60" s="27" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>DONE(full)</t>
         </is>
       </c>
       <c r="F60" s="23" t="inlineStr">
@@ -2932,13 +2950,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G60" s="66" t="inlineStr"/>
+      <c r="G60" s="67" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="77" t="n">
+      <c r="A61" s="81" t="n">
         <v>59</v>
       </c>
-      <c r="B61" s="79" t="inlineStr">
+      <c r="B61" s="83" t="inlineStr">
         <is>
           <t>PS5-74-03 - Nitrogen Receiver</t>
         </is>
@@ -2963,13 +2981,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G61" s="66" t="inlineStr"/>
+      <c r="G61" s="67" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="81" t="n">
+      <c r="A62" s="85" t="n">
         <v>60</v>
       </c>
-      <c r="B62" s="79" t="inlineStr">
+      <c r="B62" s="83" t="inlineStr">
         <is>
           <t>PS5-78-01 - Lifting and handling equipment</t>
         </is>
@@ -2984,7 +3002,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="E62" s="68" t="inlineStr">
+      <c r="E62" s="69" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -2994,13 +3012,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G62" s="66" t="inlineStr"/>
+      <c r="G62" s="67" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="77" t="n">
+      <c r="A63" s="81" t="n">
         <v>61</v>
       </c>
-      <c r="B63" s="79" t="inlineStr">
+      <c r="B63" s="83" t="inlineStr">
         <is>
           <t>PS5-83-01 - EITS Building</t>
         </is>
@@ -3025,13 +3043,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G63" s="66" t="inlineStr"/>
+      <c r="G63" s="67" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="77" t="n">
+      <c r="A64" s="81" t="n">
         <v>62</v>
       </c>
-      <c r="B64" s="79" t="inlineStr">
+      <c r="B64" s="83" t="inlineStr">
         <is>
           <t>PS5-84-03 - Shelters</t>
         </is>
@@ -3052,13 +3070,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G64" s="66" t="inlineStr"/>
+      <c r="G64" s="67" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="77" t="n">
+      <c r="A65" s="81" t="n">
         <v>63</v>
       </c>
-      <c r="B65" s="79" t="inlineStr">
+      <c r="B65" s="83" t="inlineStr">
         <is>
           <t>PS5-86-01 - Shelters</t>
         </is>
@@ -3079,13 +3097,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G65" s="66" t="inlineStr"/>
+      <c r="G65" s="67" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="77" t="n">
+      <c r="A66" s="81" t="n">
         <v>64</v>
       </c>
-      <c r="B66" s="79" t="inlineStr">
+      <c r="B66" s="83" t="inlineStr">
         <is>
           <t>PS5-91-01 - Multicore cables &amp; JB</t>
         </is>
@@ -3110,7 +3128,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G66" s="66" t="inlineStr"/>
+      <c r="G66" s="67" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G66"/>

--- a/EXCEL/7 - COMPLETE.xlsx
+++ b/EXCEL/7 - COMPLETE.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SIDMAP" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'7 · COMPLETE'!$A$2:$G$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'7 · COMPLETE'!$A$2:$G$67</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -241,6 +241,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFffeb9c"/>
+        <bgColor rgb="FFffeb9c"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFe8d5c4"/>
         <bgColor rgb="FFe8d5c4"/>
       </patternFill>
@@ -309,12 +315,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFBDD7EE"/>
         <bgColor rgb="FFBDD7EE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFffeb9c"/>
-        <bgColor rgb="FFffeb9c"/>
       </patternFill>
     </fill>
     <fill>
@@ -576,7 +576,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -644,88 +644,88 @@
     <xf numFmtId="0" fontId="2" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -740,7 +740,7 @@
     <xf numFmtId="0" fontId="4" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -773,16 +773,16 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1152,7 +1152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="B3" s="83" t="inlineStr">
         <is>
-          <t>PS5-01-04 - Fire Water Pump Mini Flow Recycle</t>
+          <t>PS5-01-01 - Fire Water Jockey Pump A/B</t>
         </is>
       </c>
       <c r="C3" s="27" t="inlineStr">
@@ -1228,7 +1228,11 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="D3" s="24" t="inlineStr"/>
+      <c r="D3" s="24" t="inlineStr">
+        <is>
+          <t>DONE(partial)</t>
+        </is>
+      </c>
       <c r="E3" s="27" t="inlineStr">
         <is>
           <t>Full</t>
@@ -1236,7 +1240,7 @@
       </c>
       <c r="F3" s="23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Hydraulic tubing could not be connected in HPU due to Fittings/socket issues</t>
         </is>
       </c>
       <c r="G3" s="67" t="inlineStr"/>
@@ -1247,7 +1251,7 @@
       </c>
       <c r="B4" s="83" t="inlineStr">
         <is>
-          <t>PS5-01-06 - Foam Concentrate Distribution</t>
+          <t>PS5-01-04 - Fire Water Pump Mini Flow Recycle</t>
         </is>
       </c>
       <c r="C4" s="27" t="inlineStr">
@@ -1274,7 +1278,7 @@
       </c>
       <c r="B5" s="83" t="inlineStr">
         <is>
-          <t>PS5-01-09 - Inergen for EITS Building</t>
+          <t>PS5-01-06 - Foam Concentrate Distribution</t>
         </is>
       </c>
       <c r="C5" s="27" t="inlineStr">
@@ -1285,7 +1289,7 @@
       <c r="D5" s="24" t="inlineStr"/>
       <c r="E5" s="27" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F5" s="23" t="inlineStr">
@@ -1301,7 +1305,7 @@
       </c>
       <c r="B6" s="83" t="inlineStr">
         <is>
-          <t>PS5-01-10 - Water Mist Package</t>
+          <t>PS5-01-09 - Inergen for EITS Building</t>
         </is>
       </c>
       <c r="C6" s="27" t="inlineStr">
@@ -1309,14 +1313,10 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="D6" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
+      <c r="D6" s="24" t="inlineStr"/>
       <c r="E6" s="27" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="F6" s="23" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="B7" s="83" t="inlineStr">
         <is>
-          <t>PS5-03-07 - FZ-07 - Pretreatment Area</t>
+          <t>PS5-01-10 - Water Mist Package</t>
         </is>
       </c>
       <c r="C7" s="27" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="E7" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F7" s="23" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="B8" s="83" t="inlineStr">
         <is>
-          <t>PS5-03-09 - FZ-09 - Power Generation Building - Engine Bay 1</t>
+          <t>PS5-03-07 - FZ-07 - Pretreatment Area</t>
         </is>
       </c>
       <c r="C8" s="27" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="F8" s="23" t="inlineStr">
         <is>
-          <t>Due to gland plate issue of SEA-0001 we cannot terminate the cablesof F&amp;G Instruments.</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G8" s="67" t="inlineStr"/>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="B9" s="83" t="inlineStr">
         <is>
-          <t>PS5-03-10 - FZ-10 - Power Generation Building - Engine Bay 2</t>
+          <t>PS5-03-09 - FZ-09 - Power Generation Building - Engine Bay 1</t>
         </is>
       </c>
       <c r="C9" s="27" t="inlineStr">
@@ -1412,7 +1412,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F9" s="23" t="inlineStr"/>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>Due to gland plate issue of SEA-0001 we cannot terminate the cablesof F&amp;G Instruments.</t>
+        </is>
+      </c>
       <c r="G9" s="67" t="inlineStr"/>
     </row>
     <row r="10">
@@ -1421,7 +1425,7 @@
       </c>
       <c r="B10" s="83" t="inlineStr">
         <is>
-          <t>PS5-03-13 - FZ-13 - Power Generation Building - Instrument Air Room</t>
+          <t>PS5-03-10 - FZ-10 - Power Generation Building - Engine Bay 2</t>
         </is>
       </c>
       <c r="C10" s="27" t="inlineStr">
@@ -1439,11 +1443,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F10" s="23" t="inlineStr"/>
       <c r="G10" s="67" t="inlineStr"/>
     </row>
     <row r="11">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="B11" s="83" t="inlineStr">
         <is>
-          <t>PS5-03-20 - FZ-20 - Emergency Diesel Generator Enclosure</t>
+          <t>PS5-03-13 - FZ-13 - Power Generation Building - Instrument Air Room</t>
         </is>
       </c>
       <c r="C11" s="27" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="E11" s="27" t="inlineStr">
         <is>
-          <t>07-Aug-26</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F11" s="23" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="B12" s="83" t="inlineStr">
         <is>
-          <t>PS5-05-01 - Emergency Diesel Generator Package</t>
+          <t>PS5-03-20 - FZ-20 - Emergency Diesel Generator Enclosure</t>
         </is>
       </c>
       <c r="C12" s="27" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E12" s="27" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>07-Aug-26</t>
         </is>
       </c>
       <c r="F12" s="23" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="B13" s="83" t="inlineStr">
         <is>
-          <t>PS5-05-02 - Emergency Diesel Generator Package (UCP)</t>
+          <t>PS5-05-01 - Emergency Diesel Generator Package</t>
         </is>
       </c>
       <c r="C13" s="27" t="inlineStr">
@@ -1527,9 +1527,9 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E13" s="27" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
+      <c r="E13" s="69" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="F13" s="23" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="B14" s="83" t="inlineStr">
         <is>
-          <t>PS5-06-02 - AC UPS - Power Generator Building</t>
+          <t>PS5-05-02 - Emergency Diesel Generator Package (UCP)</t>
         </is>
       </c>
       <c r="C14" s="27" t="inlineStr">
@@ -1558,9 +1558,9 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E14" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="E14" s="54" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="F14" s="23" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="B15" s="83" t="inlineStr">
         <is>
-          <t>PS5-09-05 - HVAC for EITS Building</t>
+          <t>PS5-06-02 - AC UPS - Power Generator Building</t>
         </is>
       </c>
       <c r="C15" s="27" t="inlineStr">
@@ -1584,13 +1584,21 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="D15" s="24" t="inlineStr"/>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
       <c r="E15" s="27" t="inlineStr">
         <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F15" s="23" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F15" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="G15" s="67" t="inlineStr"/>
     </row>
     <row r="16">
@@ -1599,7 +1607,7 @@
       </c>
       <c r="B16" s="83" t="inlineStr">
         <is>
-          <t>PS5-28-02 - Closed Drain Header 2</t>
+          <t>PS5-09-05 - HVAC for EITS Building</t>
         </is>
       </c>
       <c r="C16" s="27" t="inlineStr">
@@ -1613,11 +1621,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F16" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F16" s="23" t="inlineStr"/>
       <c r="G16" s="67" t="inlineStr"/>
     </row>
     <row r="17">
@@ -1626,84 +1630,80 @@
       </c>
       <c r="B17" s="83" t="inlineStr">
         <is>
+          <t>PS5-28-02 - Closed Drain Header 2</t>
+        </is>
+      </c>
+      <c r="C17" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D17" s="24" t="inlineStr"/>
+      <c r="E17" s="27" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F17" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="67" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="81" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="83" t="inlineStr">
+        <is>
           <t>PS5-28-05 - HP Relief Header</t>
         </is>
       </c>
-      <c r="C17" s="27" t="inlineStr">
+      <c r="C18" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="D17" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E17" s="27" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F17" s="23" t="inlineStr">
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E18" s="27" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F18" s="23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G17" s="67" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="85" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" s="83" t="inlineStr">
+      <c r="G18" s="67" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="85" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="83" t="inlineStr">
         <is>
           <t>PS5-53-01 - Utility Water / Storage Tank</t>
         </is>
       </c>
-      <c r="C18" s="27" t="inlineStr">
+      <c r="C19" s="27" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
       </c>
-      <c r="D18" s="24" t="inlineStr">
+      <c r="D19" s="24" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="E18" s="69" t="inlineStr">
+      <c r="E19" s="69" t="inlineStr">
         <is>
           <t>Partial</t>
-        </is>
-      </c>
-      <c r="F18" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G18" s="67" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="81" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-01 - Power Generation Package A</t>
-        </is>
-      </c>
-      <c r="C19" s="27" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D19" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E19" s="27" t="inlineStr">
-        <is>
-          <t>Full</t>
         </is>
       </c>
       <c r="F19" s="23" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="B20" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-02 - Power Gen Package A (UCP)</t>
+          <t>PS5-60-01 - Power Generation Package A</t>
         </is>
       </c>
       <c r="C20" s="27" t="inlineStr">
@@ -1729,17 +1729,17 @@
       </c>
       <c r="D20" s="24" t="inlineStr">
         <is>
-          <t>PS5 - Milestone B</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="E20" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F20" s="23" t="inlineStr">
         <is>
-          <t>WALKDOWN COMPLETE-20-08-26--ATTENDENCE SHEET TO BE SUBMITTED</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G20" s="67" t="inlineStr"/>
@@ -1750,7 +1750,7 @@
       </c>
       <c r="B21" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-04 - Power Generation Package B</t>
+          <t>PS5-60-02 - Power Gen Package A (UCP)</t>
         </is>
       </c>
       <c r="C21" s="27" t="inlineStr">
@@ -1760,17 +1760,17 @@
       </c>
       <c r="D21" s="24" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>PS5 - Milestone B</t>
         </is>
       </c>
       <c r="E21" s="27" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F21" s="23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>WALKDOWN COMPLETE-20-08-26--ATTENDENCE SHEET TO BE SUBMITTED</t>
         </is>
       </c>
       <c r="G21" s="67" t="inlineStr"/>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="B22" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-23 - Instrument Air Distribution lines</t>
+          <t>PS5-60-04 - Power Generation Package B</t>
         </is>
       </c>
       <c r="C22" s="27" t="inlineStr">
@@ -1789,7 +1789,11 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="D22" s="24" t="inlineStr"/>
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
       <c r="E22" s="27" t="inlineStr">
         <is>
           <t>Full</t>
@@ -1808,7 +1812,7 @@
       </c>
       <c r="B23" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-26 - Instrument Air Compressor Skid</t>
+          <t>PS5-60-23 - Instrument Air Distribution lines</t>
         </is>
       </c>
       <c r="C23" s="27" t="inlineStr">
@@ -1816,11 +1820,7 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="D23" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
+      <c r="D23" s="24" t="inlineStr"/>
       <c r="E23" s="27" t="inlineStr">
         <is>
           <t>Full</t>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="B24" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-27 - Compressed Air Starting Skid</t>
+          <t>PS5-60-26 - Instrument Air Compressor Skid</t>
         </is>
       </c>
       <c r="C24" s="27" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="B25" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-28 - Air Receiver A &amp; Air Regulator A</t>
+          <t>PS5-60-27 - Compressed Air Starting Skid</t>
         </is>
       </c>
       <c r="C25" s="27" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="E25" s="27" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F25" s="23" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="B26" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-29 - Air Receiver B &amp; Air Regulator B</t>
+          <t>PS5-60-28 - Air Receiver A &amp; Air Regulator A</t>
         </is>
       </c>
       <c r="C26" s="27" t="inlineStr">
@@ -1914,9 +1914,9 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E26" s="27" t="inlineStr">
-        <is>
-          <t>Full</t>
+      <c r="E26" s="69" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="F26" s="23" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="B27" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-30 - Air Receiver C &amp; Air Regulator C</t>
+          <t>PS5-60-29 - Air Receiver B &amp; Air Regulator B</t>
         </is>
       </c>
       <c r="C27" s="27" t="inlineStr">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="B28" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-31 - Air Receiver D &amp; Air Regulator D</t>
+          <t>PS5-60-30 - Air Receiver C &amp; Air Regulator C</t>
         </is>
       </c>
       <c r="C28" s="27" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="B29" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-32 - Air Receiver E &amp; Air Regulator E</t>
+          <t>PS5-60-31 - Air Receiver D &amp; Air Regulator D</t>
         </is>
       </c>
       <c r="C29" s="27" t="inlineStr">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="B30" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-33 - Air Receiver F &amp; Air Regulator F</t>
+          <t>PS5-60-32 - Air Receiver E &amp; Air Regulator E</t>
         </is>
       </c>
       <c r="C30" s="27" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="B31" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-34 - Air Receiver G &amp; Air Regulator G</t>
+          <t>PS5-60-33 - Air Receiver F &amp; Air Regulator F</t>
         </is>
       </c>
       <c r="C31" s="27" t="inlineStr">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="B32" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-35 - Injector Tip Cooling Module A</t>
+          <t>PS5-60-34 - Air Receiver G &amp; Air Regulator G</t>
         </is>
       </c>
       <c r="C32" s="27" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="E32" s="27" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F32" s="23" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="B33" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-36 - Injector Tip Cooling Module B</t>
+          <t>PS5-60-35 - Injector Tip Cooling Module A</t>
         </is>
       </c>
       <c r="C33" s="27" t="inlineStr">
@@ -2131,9 +2131,9 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E33" s="27" t="inlineStr">
-        <is>
-          <t>Full</t>
+      <c r="E33" s="54" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="F33" s="23" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="B34" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-37 - Injector Tip Cooling Module C</t>
+          <t>PS5-60-36 - Injector Tip Cooling Module B</t>
         </is>
       </c>
       <c r="C34" s="27" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="B35" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-38 - Injector Tip Cooling Module D</t>
+          <t>PS5-60-37 - Injector Tip Cooling Module C</t>
         </is>
       </c>
       <c r="C35" s="27" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="B36" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-39 - Injector Tip Cooling Module E</t>
+          <t>PS5-60-38 - Injector Tip Cooling Module D</t>
         </is>
       </c>
       <c r="C36" s="27" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="B37" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-40 - Injector Tip Cooling Module F</t>
+          <t>PS5-60-39 - Injector Tip Cooling Module E</t>
         </is>
       </c>
       <c r="C37" s="27" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="B38" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-42 - Oil Mist Separator Skid PS5-60-VS-9100A</t>
+          <t>PS5-60-40 - Injector Tip Cooling Module F</t>
         </is>
       </c>
       <c r="C38" s="27" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="E38" s="27" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F38" s="23" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="B39" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-43 - Oil Mist Separator Skid PS5-60-VS-9100B</t>
+          <t>PS5-60-42 - Oil Mist Separator Skid PS5-60-VS-9100A</t>
         </is>
       </c>
       <c r="C39" s="27" t="inlineStr">
@@ -2317,9 +2317,9 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E39" s="27" t="inlineStr">
-        <is>
-          <t>Full</t>
+      <c r="E39" s="54" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="F39" s="23" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="B40" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-44 - Oil Mist Separator Skid PS5-60-VS-9100C</t>
+          <t>PS5-60-43 - Oil Mist Separator Skid PS5-60-VS-9100B</t>
         </is>
       </c>
       <c r="C40" s="27" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="B41" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-45 - Oil Mist Separator Skid PS5-60-VS-9100D</t>
+          <t>PS5-60-44 - Oil Mist Separator Skid PS5-60-VS-9100C</t>
         </is>
       </c>
       <c r="C41" s="27" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="B42" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-46 - Oil Mist Separator Skid PS5-60-VS-9100E</t>
+          <t>PS5-60-45 - Oil Mist Separator Skid PS5-60-VS-9100D</t>
         </is>
       </c>
       <c r="C42" s="27" t="inlineStr">
@@ -2405,10 +2405,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="D42" s="24" t="inlineStr"/>
+      <c r="D42" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
       <c r="E42" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F42" s="23" t="inlineStr">
@@ -2424,7 +2428,7 @@
       </c>
       <c r="B43" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-47 - Oil Mist Separator Skid PS5-60-VS-9100F</t>
+          <t>PS5-60-46 - Oil Mist Separator Skid PS5-60-VS-9100E</t>
         </is>
       </c>
       <c r="C43" s="27" t="inlineStr">
@@ -2432,14 +2436,10 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="D43" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
+      <c r="D43" s="24" t="inlineStr"/>
       <c r="E43" s="27" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F43" s="23" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="B44" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-56 - Fuel Conditioning Module PS5-60-UZ-8900A</t>
+          <t>PS5-60-47 - Oil Mist Separator Skid PS5-60-VS-9100F</t>
         </is>
       </c>
       <c r="C44" s="27" t="inlineStr">
@@ -2473,7 +2473,11 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F44" s="23" t="inlineStr"/>
+      <c r="F44" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="G44" s="67" t="inlineStr"/>
     </row>
     <row r="45">
@@ -2482,7 +2486,7 @@
       </c>
       <c r="B45" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-58 - Fuel Conditioning Module PS5-60-UZ-8900B</t>
+          <t>PS5-60-56 - Fuel Conditioning Module PS5-60-UZ-8900A</t>
         </is>
       </c>
       <c r="C45" s="27" t="inlineStr">
@@ -2509,7 +2513,7 @@
       </c>
       <c r="B46" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-60 - Fuel Conditioning Module PS5-60-UZ-8900C</t>
+          <t>PS5-60-58 - Fuel Conditioning Module PS5-60-UZ-8900B</t>
         </is>
       </c>
       <c r="C46" s="27" t="inlineStr">
@@ -2536,7 +2540,7 @@
       </c>
       <c r="B47" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-62 - Fuel Conditioning Module PS5-60-UZ-8900D</t>
+          <t>PS5-60-60 - Fuel Conditioning Module PS5-60-UZ-8900C</t>
         </is>
       </c>
       <c r="C47" s="27" t="inlineStr">
@@ -2563,7 +2567,7 @@
       </c>
       <c r="B48" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-70 - Engine A Cooling system</t>
+          <t>PS5-60-62 - Fuel Conditioning Module PS5-60-UZ-8900D</t>
         </is>
       </c>
       <c r="C48" s="27" t="inlineStr">
@@ -2581,11 +2585,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F48" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F48" s="23" t="inlineStr"/>
       <c r="G48" s="67" t="inlineStr"/>
     </row>
     <row r="49">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="B49" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-71 - Engine B Cooling system</t>
+          <t>PS5-60-70 - Engine A Cooling system</t>
         </is>
       </c>
       <c r="C49" s="27" t="inlineStr">
@@ -2625,7 +2625,7 @@
       </c>
       <c r="B50" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-72 - Engine C Cooling system</t>
+          <t>PS5-60-71 - Engine B Cooling system</t>
         </is>
       </c>
       <c r="C50" s="27" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B51" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-73 - Engine D Cooling system</t>
+          <t>PS5-60-72 - Engine C Cooling system</t>
         </is>
       </c>
       <c r="C51" s="27" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B52" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-74 - Engine E Cooling system</t>
+          <t>PS5-60-73 - Engine D Cooling system</t>
         </is>
       </c>
       <c r="C52" s="27" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="E52" s="27" t="inlineStr">
         <is>
-          <t>PLATFORM ISSUE</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F52" s="23" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="B53" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-75 - Engine F Cooling system</t>
+          <t>PS5-60-74 - Engine E Cooling system</t>
         </is>
       </c>
       <c r="C53" s="27" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="E53" s="27" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>PLATFORM ISSUE</t>
         </is>
       </c>
       <c r="F53" s="23" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="B54" s="83" t="inlineStr">
         <is>
-          <t>PS5-61-05 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0003)</t>
+          <t>PS5-60-75 - Engine F Cooling system</t>
         </is>
       </c>
       <c r="C54" s="27" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="E54" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F54" s="23" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="B55" s="83" t="inlineStr">
         <is>
-          <t>PS5-61-07 - 0.4kV Switchboard EITS Building (PS5-61-IK-0001)</t>
+          <t>PS5-61-05 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0003)</t>
         </is>
       </c>
       <c r="C55" s="27" t="inlineStr">
@@ -2790,17 +2790,17 @@
       </c>
       <c r="D55" s="24" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="E55" s="27" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F55" s="23" t="inlineStr">
         <is>
-          <t>PS5-61-IV-0001B cannot close ITR due to transformer leakage issue.</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G55" s="67" t="inlineStr"/>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="B56" s="83" t="inlineStr">
         <is>
-          <t>PS5-61-10 - Outdoor Valves Distribution Board - PS5-61-IG-0042</t>
+          <t>PS5-61-07 - 0.4kV Switchboard EITS Building (PS5-61-IK-0001)</t>
         </is>
       </c>
       <c r="C56" s="27" t="inlineStr">
@@ -2821,17 +2821,17 @@
       </c>
       <c r="D56" s="24" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="E56" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F56" s="23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>PS5-61-IV-0001B cannot close ITR due to transformer leakage issue.</t>
         </is>
       </c>
       <c r="G56" s="67" t="inlineStr"/>
@@ -2842,7 +2842,7 @@
       </c>
       <c r="B57" s="83" t="inlineStr">
         <is>
-          <t>PS5-61-11 - Outdoor Valves Distribution Board - PS5-61-IG-0043</t>
+          <t>PS5-61-10 - Outdoor Valves Distribution Board - PS5-61-IG-0042</t>
         </is>
       </c>
       <c r="C57" s="27" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="B58" s="83" t="inlineStr">
         <is>
-          <t>PS5-62-04 - Outdoor Emergency Lighting DB  - PS5-05-IG-0006</t>
+          <t>PS5-61-11 - Outdoor Valves Distribution Board - PS5-61-IG-0043</t>
         </is>
       </c>
       <c r="C58" s="27" t="inlineStr">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="B59" s="83" t="inlineStr">
         <is>
-          <t>PS5-63-04 - Electrical Earthing - EITS Building</t>
+          <t>PS5-62-04 - Outdoor Emergency Lighting DB  - PS5-05-IG-0006</t>
         </is>
       </c>
       <c r="C59" s="27" t="inlineStr">
@@ -2912,13 +2912,21 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="D59" s="24" t="inlineStr"/>
+      <c r="D59" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
       <c r="E59" s="27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F59" s="23" t="inlineStr"/>
+      <c r="F59" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="G59" s="67" t="inlineStr"/>
     </row>
     <row r="60">
@@ -2927,7 +2935,7 @@
       </c>
       <c r="B60" s="83" t="inlineStr">
         <is>
-          <t>PS5-71-22 - Diesel Fuel Pre Pressure Module</t>
+          <t>PS5-63-04 - Electrical Earthing - EITS Building</t>
         </is>
       </c>
       <c r="C60" s="27" t="inlineStr">
@@ -2935,21 +2943,13 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="D60" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
+      <c r="D60" s="24" t="inlineStr"/>
       <c r="E60" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
-        </is>
-      </c>
-      <c r="F60" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F60" s="23" t="inlineStr"/>
       <c r="G60" s="67" t="inlineStr"/>
     </row>
     <row r="61">
@@ -2958,84 +2958,84 @@
       </c>
       <c r="B61" s="83" t="inlineStr">
         <is>
+          <t>PS5-71-22 - Diesel Fuel Pre Pressure Module</t>
+        </is>
+      </c>
+      <c r="C61" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D61" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E61" s="27" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="F61" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G61" s="67" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="81" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" s="83" t="inlineStr">
+        <is>
           <t>PS5-74-03 - Nitrogen Receiver</t>
         </is>
       </c>
-      <c r="C61" s="27" t="inlineStr">
+      <c r="C62" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="D61" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E61" s="27" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F61" s="23" t="inlineStr">
+      <c r="D62" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E62" s="27" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F62" s="23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G61" s="67" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="85" t="n">
-        <v>60</v>
-      </c>
-      <c r="B62" s="83" t="inlineStr">
+      <c r="G62" s="67" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="85" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" s="83" t="inlineStr">
         <is>
           <t>PS5-78-01 - Lifting and handling equipment</t>
         </is>
       </c>
-      <c r="C62" s="27" t="inlineStr">
+      <c r="C63" s="27" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
       </c>
-      <c r="D62" s="24" t="inlineStr">
+      <c r="D63" s="24" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="E62" s="69" t="inlineStr">
+      <c r="E63" s="69" t="inlineStr">
         <is>
           <t>Partial</t>
-        </is>
-      </c>
-      <c r="F62" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G62" s="67" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="81" t="n">
-        <v>61</v>
-      </c>
-      <c r="B63" s="83" t="inlineStr">
-        <is>
-          <t>PS5-83-01 - EITS Building</t>
-        </is>
-      </c>
-      <c r="C63" s="27" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D63" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E63" s="27" t="inlineStr">
-        <is>
-          <t>Full</t>
         </is>
       </c>
       <c r="F63" s="23" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="B64" s="83" t="inlineStr">
         <is>
-          <t>PS5-84-03 - Shelters</t>
+          <t>PS5-83-01 - EITS Building</t>
         </is>
       </c>
       <c r="C64" s="27" t="inlineStr">
@@ -3059,7 +3059,11 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="D64" s="24" t="inlineStr"/>
+      <c r="D64" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
       <c r="E64" s="27" t="inlineStr">
         <is>
           <t>Full</t>
@@ -3078,7 +3082,7 @@
       </c>
       <c r="B65" s="83" t="inlineStr">
         <is>
-          <t>PS5-86-01 - Shelters</t>
+          <t>PS5-84-03 - Shelters</t>
         </is>
       </c>
       <c r="C65" s="27" t="inlineStr">
@@ -3105,33 +3109,60 @@
       </c>
       <c r="B66" s="83" t="inlineStr">
         <is>
+          <t>PS5-86-01 - Shelters</t>
+        </is>
+      </c>
+      <c r="C66" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D66" s="24" t="inlineStr"/>
+      <c r="E66" s="27" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F66" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G66" s="67" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="81" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" s="83" t="inlineStr">
+        <is>
           <t>PS5-91-01 - Multicore cables &amp; JB</t>
         </is>
       </c>
-      <c r="C66" s="27" t="inlineStr">
+      <c r="C67" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="D66" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E66" s="27" t="inlineStr">
+      <c r="D67" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E67" s="27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F66" s="23" t="inlineStr">
+      <c r="F67" s="23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G66" s="67" t="inlineStr"/>
+      <c r="G67" s="67" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:G66"/>
+  <autoFilter ref="A2:G67"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
@@ -3200,6 +3231,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B64" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B65" r:id="rId63"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B66" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B67" r:id="rId65"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXCEL/7 - COMPLETE.xlsx
+++ b/EXCEL/7 - COMPLETE.xlsx
@@ -172,7 +172,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="37">
     <fill>
       <patternFill/>
     </fill>
@@ -309,12 +309,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFfff8e1"/>
         <bgColor rgb="FFfff8e1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
-        <bgColor rgb="FFBDD7EE"/>
       </patternFill>
     </fill>
     <fill>
@@ -504,7 +498,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -518,6 +512,9 @@
     <xf numFmtId="0" fontId="19" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -527,12 +524,12 @@
     <xf numFmtId="0" fontId="19" fillId="32" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -542,19 +539,16 @@
     <xf numFmtId="0" fontId="2" fillId="32" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -564,12 +558,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -579,23 +573,23 @@
     <xf numFmtId="0" fontId="10" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="36" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="37" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
@@ -683,9 +677,6 @@
     <xf numFmtId="0" fontId="11" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
@@ -707,12 +698,12 @@
     <xf numFmtId="0" fontId="7" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -722,52 +713,46 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1170,12 +1155,12 @@
           <t>PS5 COMPLETION PLATFORM  |  DONE - subsystems at 100%</t>
         </is>
       </c>
-      <c r="B1" s="100" t="n"/>
-      <c r="C1" s="100" t="n"/>
-      <c r="D1" s="100" t="n"/>
-      <c r="E1" s="100" t="n"/>
-      <c r="F1" s="100" t="n"/>
-      <c r="G1" s="101" t="n"/>
+      <c r="B1" s="97" t="n"/>
+      <c r="C1" s="97" t="n"/>
+      <c r="D1" s="97" t="n"/>
+      <c r="E1" s="97" t="n"/>
+      <c r="F1" s="97" t="n"/>
+      <c r="G1" s="98" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="22" t="inlineStr">
@@ -1215,10 +1200,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="81" t="n">
+      <c r="A3" s="78" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="83" t="inlineStr">
+      <c r="B3" s="80" t="inlineStr">
         <is>
           <t>PS5-01-01 - Fire Water Jockey Pump A/B</t>
         </is>
@@ -1243,13 +1228,13 @@
           <t>Hydraulic tubing could not be connected in HPU due to Fittings/socket issues</t>
         </is>
       </c>
-      <c r="G3" s="67" t="inlineStr"/>
+      <c r="G3" s="66" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="81" t="n">
+      <c r="A4" s="78" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="83" t="inlineStr">
+      <c r="B4" s="80" t="inlineStr">
         <is>
           <t>PS5-01-04 - Fire Water Pump Mini Flow Recycle</t>
         </is>
@@ -1270,13 +1255,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G4" s="67" t="inlineStr"/>
+      <c r="G4" s="66" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="81" t="n">
+      <c r="A5" s="78" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="83" t="inlineStr">
+      <c r="B5" s="80" t="inlineStr">
         <is>
           <t>PS5-01-06 - Foam Concentrate Distribution</t>
         </is>
@@ -1297,13 +1282,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G5" s="67" t="inlineStr"/>
+      <c r="G5" s="66" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="81" t="n">
+      <c r="A6" s="78" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="83" t="inlineStr">
+      <c r="B6" s="80" t="inlineStr">
         <is>
           <t>PS5-01-09 - Inergen for EITS Building</t>
         </is>
@@ -1324,13 +1309,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G6" s="67" t="inlineStr"/>
+      <c r="G6" s="66" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="81" t="n">
+      <c r="A7" s="78" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="83" t="inlineStr">
+      <c r="B7" s="80" t="inlineStr">
         <is>
           <t>PS5-01-10 - Water Mist Package</t>
         </is>
@@ -1355,13 +1340,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G7" s="67" t="inlineStr"/>
+      <c r="G7" s="66" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="81" t="n">
+      <c r="A8" s="78" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="83" t="inlineStr">
+      <c r="B8" s="80" t="inlineStr">
         <is>
           <t>PS5-03-07 - FZ-07 - Pretreatment Area</t>
         </is>
@@ -1386,13 +1371,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G8" s="67" t="inlineStr"/>
+      <c r="G8" s="66" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="81" t="n">
+      <c r="A9" s="78" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="83" t="inlineStr">
+      <c r="B9" s="80" t="inlineStr">
         <is>
           <t>PS5-03-09 - FZ-09 - Power Generation Building - Engine Bay 1</t>
         </is>
@@ -1417,13 +1402,13 @@
           <t>Due to gland plate issue of SEA-0001 we cannot terminate the cablesof F&amp;G Instruments.</t>
         </is>
       </c>
-      <c r="G9" s="67" t="inlineStr"/>
+      <c r="G9" s="66" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="81" t="n">
+      <c r="A10" s="78" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="83" t="inlineStr">
+      <c r="B10" s="80" t="inlineStr">
         <is>
           <t>PS5-03-10 - FZ-10 - Power Generation Building - Engine Bay 2</t>
         </is>
@@ -1444,13 +1429,13 @@
         </is>
       </c>
       <c r="F10" s="23" t="inlineStr"/>
-      <c r="G10" s="67" t="inlineStr"/>
+      <c r="G10" s="66" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="81" t="n">
+      <c r="A11" s="78" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="83" t="inlineStr">
+      <c r="B11" s="80" t="inlineStr">
         <is>
           <t>PS5-03-13 - FZ-13 - Power Generation Building - Instrument Air Room</t>
         </is>
@@ -1475,13 +1460,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G11" s="67" t="inlineStr"/>
+      <c r="G11" s="66" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="81" t="n">
+      <c r="A12" s="78" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="83" t="inlineStr">
+      <c r="B12" s="80" t="inlineStr">
         <is>
           <t>PS5-03-20 - FZ-20 - Emergency Diesel Generator Enclosure</t>
         </is>
@@ -1506,13 +1491,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G12" s="67" t="inlineStr"/>
+      <c r="G12" s="66" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="81" t="n">
+      <c r="A13" s="78" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="83" t="inlineStr">
+      <c r="B13" s="80" t="inlineStr">
         <is>
           <t>PS5-05-01 - Emergency Diesel Generator Package</t>
         </is>
@@ -1527,7 +1512,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E13" s="69" t="inlineStr">
+      <c r="E13" s="68" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -1537,13 +1522,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G13" s="67" t="inlineStr"/>
+      <c r="G13" s="66" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="81" t="n">
+      <c r="A14" s="78" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="83" t="inlineStr">
+      <c r="B14" s="80" t="inlineStr">
         <is>
           <t>PS5-05-02 - Emergency Diesel Generator Package (UCP)</t>
         </is>
@@ -1568,13 +1553,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G14" s="67" t="inlineStr"/>
+      <c r="G14" s="66" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="81" t="n">
+      <c r="A15" s="78" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="83" t="inlineStr">
+      <c r="B15" s="80" t="inlineStr">
         <is>
           <t>PS5-06-02 - AC UPS - Power Generator Building</t>
         </is>
@@ -1599,13 +1584,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G15" s="67" t="inlineStr"/>
+      <c r="G15" s="66" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="81" t="n">
+      <c r="A16" s="78" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="83" t="inlineStr">
+      <c r="B16" s="80" t="inlineStr">
         <is>
           <t>PS5-09-05 - HVAC for EITS Building</t>
         </is>
@@ -1622,13 +1607,13 @@
         </is>
       </c>
       <c r="F16" s="23" t="inlineStr"/>
-      <c r="G16" s="67" t="inlineStr"/>
+      <c r="G16" s="66" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="81" t="n">
+      <c r="A17" s="78" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="83" t="inlineStr">
+      <c r="B17" s="80" t="inlineStr">
         <is>
           <t>PS5-28-02 - Closed Drain Header 2</t>
         </is>
@@ -1649,13 +1634,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G17" s="67" t="inlineStr"/>
+      <c r="G17" s="66" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="81" t="n">
+      <c r="A18" s="78" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="83" t="inlineStr">
+      <c r="B18" s="80" t="inlineStr">
         <is>
           <t>PS5-28-05 - HP Relief Header</t>
         </is>
@@ -1680,13 +1665,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G18" s="67" t="inlineStr"/>
+      <c r="G18" s="66" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="85" t="n">
+      <c r="A19" s="82" t="n">
         <v>17</v>
       </c>
-      <c r="B19" s="83" t="inlineStr">
+      <c r="B19" s="80" t="inlineStr">
         <is>
           <t>PS5-53-01 - Utility Water / Storage Tank</t>
         </is>
@@ -1701,7 +1686,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="E19" s="69" t="inlineStr">
+      <c r="E19" s="68" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -1711,13 +1696,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G19" s="67" t="inlineStr"/>
+      <c r="G19" s="66" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="81" t="n">
+      <c r="A20" s="78" t="n">
         <v>18</v>
       </c>
-      <c r="B20" s="83" t="inlineStr">
+      <c r="B20" s="80" t="inlineStr">
         <is>
           <t>PS5-60-01 - Power Generation Package A</t>
         </is>
@@ -1742,13 +1727,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G20" s="67" t="inlineStr"/>
+      <c r="G20" s="66" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="81" t="n">
+      <c r="A21" s="78" t="n">
         <v>19</v>
       </c>
-      <c r="B21" s="83" t="inlineStr">
+      <c r="B21" s="80" t="inlineStr">
         <is>
           <t>PS5-60-02 - Power Gen Package A (UCP)</t>
         </is>
@@ -1770,16 +1755,16 @@
       </c>
       <c r="F21" s="23" t="inlineStr">
         <is>
-          <t>WALKDOWN COMPLETE-20-08-26--ATTENDENCE SHEET TO BE SUBMITTED</t>
-        </is>
-      </c>
-      <c r="G21" s="67" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G21" s="66" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="81" t="n">
+      <c r="A22" s="78" t="n">
         <v>20</v>
       </c>
-      <c r="B22" s="83" t="inlineStr">
+      <c r="B22" s="80" t="inlineStr">
         <is>
           <t>PS5-60-04 - Power Generation Package B</t>
         </is>
@@ -1804,13 +1789,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G22" s="67" t="inlineStr"/>
+      <c r="G22" s="66" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="81" t="n">
+      <c r="A23" s="78" t="n">
         <v>21</v>
       </c>
-      <c r="B23" s="83" t="inlineStr">
+      <c r="B23" s="80" t="inlineStr">
         <is>
           <t>PS5-60-23 - Instrument Air Distribution lines</t>
         </is>
@@ -1831,13 +1816,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G23" s="67" t="inlineStr"/>
+      <c r="G23" s="66" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="81" t="n">
+      <c r="A24" s="78" t="n">
         <v>22</v>
       </c>
-      <c r="B24" s="83" t="inlineStr">
+      <c r="B24" s="80" t="inlineStr">
         <is>
           <t>PS5-60-26 - Instrument Air Compressor Skid</t>
         </is>
@@ -1862,13 +1847,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G24" s="67" t="inlineStr"/>
+      <c r="G24" s="66" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="81" t="n">
+      <c r="A25" s="78" t="n">
         <v>23</v>
       </c>
-      <c r="B25" s="83" t="inlineStr">
+      <c r="B25" s="80" t="inlineStr">
         <is>
           <t>PS5-60-27 - Compressed Air Starting Skid</t>
         </is>
@@ -1893,13 +1878,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G25" s="67" t="inlineStr"/>
+      <c r="G25" s="66" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="81" t="n">
+      <c r="A26" s="78" t="n">
         <v>24</v>
       </c>
-      <c r="B26" s="83" t="inlineStr">
+      <c r="B26" s="80" t="inlineStr">
         <is>
           <t>PS5-60-28 - Air Receiver A &amp; Air Regulator A</t>
         </is>
@@ -1914,7 +1899,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E26" s="69" t="inlineStr">
+      <c r="E26" s="68" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -1924,13 +1909,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G26" s="67" t="inlineStr"/>
+      <c r="G26" s="66" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="81" t="n">
+      <c r="A27" s="78" t="n">
         <v>25</v>
       </c>
-      <c r="B27" s="83" t="inlineStr">
+      <c r="B27" s="80" t="inlineStr">
         <is>
           <t>PS5-60-29 - Air Receiver B &amp; Air Regulator B</t>
         </is>
@@ -1955,13 +1940,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G27" s="67" t="inlineStr"/>
+      <c r="G27" s="66" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="81" t="n">
+      <c r="A28" s="78" t="n">
         <v>26</v>
       </c>
-      <c r="B28" s="83" t="inlineStr">
+      <c r="B28" s="80" t="inlineStr">
         <is>
           <t>PS5-60-30 - Air Receiver C &amp; Air Regulator C</t>
         </is>
@@ -1986,13 +1971,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G28" s="67" t="inlineStr"/>
+      <c r="G28" s="66" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="81" t="n">
+      <c r="A29" s="78" t="n">
         <v>27</v>
       </c>
-      <c r="B29" s="83" t="inlineStr">
+      <c r="B29" s="80" t="inlineStr">
         <is>
           <t>PS5-60-31 - Air Receiver D &amp; Air Regulator D</t>
         </is>
@@ -2017,13 +2002,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G29" s="67" t="inlineStr"/>
+      <c r="G29" s="66" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="81" t="n">
+      <c r="A30" s="78" t="n">
         <v>28</v>
       </c>
-      <c r="B30" s="83" t="inlineStr">
+      <c r="B30" s="80" t="inlineStr">
         <is>
           <t>PS5-60-32 - Air Receiver E &amp; Air Regulator E</t>
         </is>
@@ -2048,13 +2033,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G30" s="67" t="inlineStr"/>
+      <c r="G30" s="66" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="81" t="n">
+      <c r="A31" s="78" t="n">
         <v>29</v>
       </c>
-      <c r="B31" s="83" t="inlineStr">
+      <c r="B31" s="80" t="inlineStr">
         <is>
           <t>PS5-60-33 - Air Receiver F &amp; Air Regulator F</t>
         </is>
@@ -2079,13 +2064,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G31" s="67" t="inlineStr"/>
+      <c r="G31" s="66" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="81" t="n">
+      <c r="A32" s="78" t="n">
         <v>30</v>
       </c>
-      <c r="B32" s="83" t="inlineStr">
+      <c r="B32" s="80" t="inlineStr">
         <is>
           <t>PS5-60-34 - Air Receiver G &amp; Air Regulator G</t>
         </is>
@@ -2110,13 +2095,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G32" s="67" t="inlineStr"/>
+      <c r="G32" s="66" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="81" t="n">
+      <c r="A33" s="78" t="n">
         <v>31</v>
       </c>
-      <c r="B33" s="83" t="inlineStr">
+      <c r="B33" s="80" t="inlineStr">
         <is>
           <t>PS5-60-35 - Injector Tip Cooling Module A</t>
         </is>
@@ -2141,13 +2126,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G33" s="67" t="inlineStr"/>
+      <c r="G33" s="66" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="81" t="n">
+      <c r="A34" s="78" t="n">
         <v>32</v>
       </c>
-      <c r="B34" s="83" t="inlineStr">
+      <c r="B34" s="80" t="inlineStr">
         <is>
           <t>PS5-60-36 - Injector Tip Cooling Module B</t>
         </is>
@@ -2172,13 +2157,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G34" s="67" t="inlineStr"/>
+      <c r="G34" s="66" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="81" t="n">
+      <c r="A35" s="78" t="n">
         <v>33</v>
       </c>
-      <c r="B35" s="83" t="inlineStr">
+      <c r="B35" s="80" t="inlineStr">
         <is>
           <t>PS5-60-37 - Injector Tip Cooling Module C</t>
         </is>
@@ -2203,13 +2188,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G35" s="67" t="inlineStr"/>
+      <c r="G35" s="66" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="81" t="n">
+      <c r="A36" s="78" t="n">
         <v>34</v>
       </c>
-      <c r="B36" s="83" t="inlineStr">
+      <c r="B36" s="80" t="inlineStr">
         <is>
           <t>PS5-60-38 - Injector Tip Cooling Module D</t>
         </is>
@@ -2234,13 +2219,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G36" s="67" t="inlineStr"/>
+      <c r="G36" s="66" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="81" t="n">
+      <c r="A37" s="78" t="n">
         <v>35</v>
       </c>
-      <c r="B37" s="83" t="inlineStr">
+      <c r="B37" s="80" t="inlineStr">
         <is>
           <t>PS5-60-39 - Injector Tip Cooling Module E</t>
         </is>
@@ -2265,13 +2250,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G37" s="67" t="inlineStr"/>
+      <c r="G37" s="66" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="81" t="n">
+      <c r="A38" s="78" t="n">
         <v>36</v>
       </c>
-      <c r="B38" s="83" t="inlineStr">
+      <c r="B38" s="80" t="inlineStr">
         <is>
           <t>PS5-60-40 - Injector Tip Cooling Module F</t>
         </is>
@@ -2296,13 +2281,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G38" s="67" t="inlineStr"/>
+      <c r="G38" s="66" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="81" t="n">
+      <c r="A39" s="78" t="n">
         <v>37</v>
       </c>
-      <c r="B39" s="83" t="inlineStr">
+      <c r="B39" s="80" t="inlineStr">
         <is>
           <t>PS5-60-42 - Oil Mist Separator Skid PS5-60-VS-9100A</t>
         </is>
@@ -2327,13 +2312,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G39" s="67" t="inlineStr"/>
+      <c r="G39" s="66" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="81" t="n">
+      <c r="A40" s="78" t="n">
         <v>38</v>
       </c>
-      <c r="B40" s="83" t="inlineStr">
+      <c r="B40" s="80" t="inlineStr">
         <is>
           <t>PS5-60-43 - Oil Mist Separator Skid PS5-60-VS-9100B</t>
         </is>
@@ -2358,13 +2343,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G40" s="67" t="inlineStr"/>
+      <c r="G40" s="66" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="81" t="n">
+      <c r="A41" s="78" t="n">
         <v>39</v>
       </c>
-      <c r="B41" s="83" t="inlineStr">
+      <c r="B41" s="80" t="inlineStr">
         <is>
           <t>PS5-60-44 - Oil Mist Separator Skid PS5-60-VS-9100C</t>
         </is>
@@ -2389,13 +2374,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G41" s="67" t="inlineStr"/>
+      <c r="G41" s="66" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="81" t="n">
+      <c r="A42" s="78" t="n">
         <v>40</v>
       </c>
-      <c r="B42" s="83" t="inlineStr">
+      <c r="B42" s="80" t="inlineStr">
         <is>
           <t>PS5-60-45 - Oil Mist Separator Skid PS5-60-VS-9100D</t>
         </is>
@@ -2420,13 +2405,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G42" s="67" t="inlineStr"/>
+      <c r="G42" s="66" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="81" t="n">
+      <c r="A43" s="78" t="n">
         <v>41</v>
       </c>
-      <c r="B43" s="83" t="inlineStr">
+      <c r="B43" s="80" t="inlineStr">
         <is>
           <t>PS5-60-46 - Oil Mist Separator Skid PS5-60-VS-9100E</t>
         </is>
@@ -2447,13 +2432,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G43" s="67" t="inlineStr"/>
+      <c r="G43" s="66" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="81" t="n">
+      <c r="A44" s="78" t="n">
         <v>42</v>
       </c>
-      <c r="B44" s="83" t="inlineStr">
+      <c r="B44" s="80" t="inlineStr">
         <is>
           <t>PS5-60-47 - Oil Mist Separator Skid PS5-60-VS-9100F</t>
         </is>
@@ -2478,13 +2463,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G44" s="67" t="inlineStr"/>
+      <c r="G44" s="66" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="81" t="n">
+      <c r="A45" s="78" t="n">
         <v>43</v>
       </c>
-      <c r="B45" s="83" t="inlineStr">
+      <c r="B45" s="80" t="inlineStr">
         <is>
           <t>PS5-60-56 - Fuel Conditioning Module PS5-60-UZ-8900A</t>
         </is>
@@ -2505,13 +2490,13 @@
         </is>
       </c>
       <c r="F45" s="23" t="inlineStr"/>
-      <c r="G45" s="67" t="inlineStr"/>
+      <c r="G45" s="66" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="81" t="n">
+      <c r="A46" s="78" t="n">
         <v>44</v>
       </c>
-      <c r="B46" s="83" t="inlineStr">
+      <c r="B46" s="80" t="inlineStr">
         <is>
           <t>PS5-60-58 - Fuel Conditioning Module PS5-60-UZ-8900B</t>
         </is>
@@ -2532,13 +2517,13 @@
         </is>
       </c>
       <c r="F46" s="23" t="inlineStr"/>
-      <c r="G46" s="67" t="inlineStr"/>
+      <c r="G46" s="66" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="81" t="n">
+      <c r="A47" s="78" t="n">
         <v>45</v>
       </c>
-      <c r="B47" s="83" t="inlineStr">
+      <c r="B47" s="80" t="inlineStr">
         <is>
           <t>PS5-60-60 - Fuel Conditioning Module PS5-60-UZ-8900C</t>
         </is>
@@ -2559,13 +2544,13 @@
         </is>
       </c>
       <c r="F47" s="23" t="inlineStr"/>
-      <c r="G47" s="67" t="inlineStr"/>
+      <c r="G47" s="66" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="81" t="n">
+      <c r="A48" s="78" t="n">
         <v>46</v>
       </c>
-      <c r="B48" s="83" t="inlineStr">
+      <c r="B48" s="80" t="inlineStr">
         <is>
           <t>PS5-60-62 - Fuel Conditioning Module PS5-60-UZ-8900D</t>
         </is>
@@ -2586,13 +2571,13 @@
         </is>
       </c>
       <c r="F48" s="23" t="inlineStr"/>
-      <c r="G48" s="67" t="inlineStr"/>
+      <c r="G48" s="66" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="81" t="n">
+      <c r="A49" s="78" t="n">
         <v>47</v>
       </c>
-      <c r="B49" s="83" t="inlineStr">
+      <c r="B49" s="80" t="inlineStr">
         <is>
           <t>PS5-60-70 - Engine A Cooling system</t>
         </is>
@@ -2617,13 +2602,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G49" s="67" t="inlineStr"/>
+      <c r="G49" s="66" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="81" t="n">
+      <c r="A50" s="78" t="n">
         <v>48</v>
       </c>
-      <c r="B50" s="83" t="inlineStr">
+      <c r="B50" s="80" t="inlineStr">
         <is>
           <t>PS5-60-71 - Engine B Cooling system</t>
         </is>
@@ -2648,13 +2633,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G50" s="67" t="inlineStr"/>
+      <c r="G50" s="66" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="81" t="n">
+      <c r="A51" s="78" t="n">
         <v>49</v>
       </c>
-      <c r="B51" s="83" t="inlineStr">
+      <c r="B51" s="80" t="inlineStr">
         <is>
           <t>PS5-60-72 - Engine C Cooling system</t>
         </is>
@@ -2679,13 +2664,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G51" s="67" t="inlineStr"/>
+      <c r="G51" s="66" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="81" t="n">
+      <c r="A52" s="78" t="n">
         <v>50</v>
       </c>
-      <c r="B52" s="83" t="inlineStr">
+      <c r="B52" s="80" t="inlineStr">
         <is>
           <t>PS5-60-73 - Engine D Cooling system</t>
         </is>
@@ -2710,13 +2695,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G52" s="67" t="inlineStr"/>
+      <c r="G52" s="66" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="81" t="n">
+      <c r="A53" s="78" t="n">
         <v>51</v>
       </c>
-      <c r="B53" s="83" t="inlineStr">
+      <c r="B53" s="80" t="inlineStr">
         <is>
           <t>PS5-60-74 - Engine E Cooling system</t>
         </is>
@@ -2741,13 +2726,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G53" s="67" t="inlineStr"/>
+      <c r="G53" s="66" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="81" t="n">
+      <c r="A54" s="78" t="n">
         <v>52</v>
       </c>
-      <c r="B54" s="83" t="inlineStr">
+      <c r="B54" s="80" t="inlineStr">
         <is>
           <t>PS5-60-75 - Engine F Cooling system</t>
         </is>
@@ -2772,13 +2757,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G54" s="67" t="inlineStr"/>
+      <c r="G54" s="66" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="81" t="n">
+      <c r="A55" s="78" t="n">
         <v>53</v>
       </c>
-      <c r="B55" s="83" t="inlineStr">
+      <c r="B55" s="80" t="inlineStr">
         <is>
           <t>PS5-61-05 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0003)</t>
         </is>
@@ -2803,13 +2788,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G55" s="67" t="inlineStr"/>
+      <c r="G55" s="66" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="81" t="n">
+      <c r="A56" s="78" t="n">
         <v>54</v>
       </c>
-      <c r="B56" s="83" t="inlineStr">
+      <c r="B56" s="80" t="inlineStr">
         <is>
           <t>PS5-61-07 - 0.4kV Switchboard EITS Building (PS5-61-IK-0001)</t>
         </is>
@@ -2834,13 +2819,13 @@
           <t>PS5-61-IV-0001B cannot close ITR due to transformer leakage issue.</t>
         </is>
       </c>
-      <c r="G56" s="67" t="inlineStr"/>
+      <c r="G56" s="66" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="81" t="n">
+      <c r="A57" s="78" t="n">
         <v>55</v>
       </c>
-      <c r="B57" s="83" t="inlineStr">
+      <c r="B57" s="80" t="inlineStr">
         <is>
           <t>PS5-61-10 - Outdoor Valves Distribution Board - PS5-61-IG-0042</t>
         </is>
@@ -2865,13 +2850,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G57" s="67" t="inlineStr"/>
+      <c r="G57" s="66" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="81" t="n">
+      <c r="A58" s="78" t="n">
         <v>56</v>
       </c>
-      <c r="B58" s="83" t="inlineStr">
+      <c r="B58" s="80" t="inlineStr">
         <is>
           <t>PS5-61-11 - Outdoor Valves Distribution Board - PS5-61-IG-0043</t>
         </is>
@@ -2896,13 +2881,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G58" s="67" t="inlineStr"/>
+      <c r="G58" s="66" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="81" t="n">
+      <c r="A59" s="78" t="n">
         <v>57</v>
       </c>
-      <c r="B59" s="83" t="inlineStr">
+      <c r="B59" s="80" t="inlineStr">
         <is>
           <t>PS5-62-04 - Outdoor Emergency Lighting DB  - PS5-05-IG-0006</t>
         </is>
@@ -2927,13 +2912,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G59" s="67" t="inlineStr"/>
+      <c r="G59" s="66" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="81" t="n">
+      <c r="A60" s="78" t="n">
         <v>58</v>
       </c>
-      <c r="B60" s="83" t="inlineStr">
+      <c r="B60" s="80" t="inlineStr">
         <is>
           <t>PS5-63-04 - Electrical Earthing - EITS Building</t>
         </is>
@@ -2950,13 +2935,13 @@
         </is>
       </c>
       <c r="F60" s="23" t="inlineStr"/>
-      <c r="G60" s="67" t="inlineStr"/>
+      <c r="G60" s="66" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="81" t="n">
+      <c r="A61" s="78" t="n">
         <v>59</v>
       </c>
-      <c r="B61" s="83" t="inlineStr">
+      <c r="B61" s="80" t="inlineStr">
         <is>
           <t>PS5-71-22 - Diesel Fuel Pre Pressure Module</t>
         </is>
@@ -2981,13 +2966,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G61" s="67" t="inlineStr"/>
+      <c r="G61" s="66" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="81" t="n">
+      <c r="A62" s="78" t="n">
         <v>60</v>
       </c>
-      <c r="B62" s="83" t="inlineStr">
+      <c r="B62" s="80" t="inlineStr">
         <is>
           <t>PS5-74-03 - Nitrogen Receiver</t>
         </is>
@@ -3012,13 +2997,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G62" s="67" t="inlineStr"/>
+      <c r="G62" s="66" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="85" t="n">
+      <c r="A63" s="82" t="n">
         <v>61</v>
       </c>
-      <c r="B63" s="83" t="inlineStr">
+      <c r="B63" s="80" t="inlineStr">
         <is>
           <t>PS5-78-01 - Lifting and handling equipment</t>
         </is>
@@ -3033,7 +3018,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="E63" s="69" t="inlineStr">
+      <c r="E63" s="68" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -3043,13 +3028,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G63" s="67" t="inlineStr"/>
+      <c r="G63" s="66" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="81" t="n">
+      <c r="A64" s="78" t="n">
         <v>62</v>
       </c>
-      <c r="B64" s="83" t="inlineStr">
+      <c r="B64" s="80" t="inlineStr">
         <is>
           <t>PS5-83-01 - EITS Building</t>
         </is>
@@ -3074,13 +3059,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G64" s="67" t="inlineStr"/>
+      <c r="G64" s="66" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="81" t="n">
+      <c r="A65" s="78" t="n">
         <v>63</v>
       </c>
-      <c r="B65" s="83" t="inlineStr">
+      <c r="B65" s="80" t="inlineStr">
         <is>
           <t>PS5-84-03 - Shelters</t>
         </is>
@@ -3101,13 +3086,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G65" s="67" t="inlineStr"/>
+      <c r="G65" s="66" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="81" t="n">
+      <c r="A66" s="78" t="n">
         <v>64</v>
       </c>
-      <c r="B66" s="83" t="inlineStr">
+      <c r="B66" s="80" t="inlineStr">
         <is>
           <t>PS5-86-01 - Shelters</t>
         </is>
@@ -3128,13 +3113,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G66" s="67" t="inlineStr"/>
+      <c r="G66" s="66" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="81" t="n">
+      <c r="A67" s="78" t="n">
         <v>65</v>
       </c>
-      <c r="B67" s="83" t="inlineStr">
+      <c r="B67" s="80" t="inlineStr">
         <is>
           <t>PS5-91-01 - Multicore cables &amp; JB</t>
         </is>
@@ -3159,7 +3144,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G67" s="67" t="inlineStr"/>
+      <c r="G67" s="66" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G67"/>

--- a/EXCEL/7 - COMPLETE.xlsx
+++ b/EXCEL/7 - COMPLETE.xlsx
@@ -172,7 +172,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="38">
     <fill>
       <patternFill/>
     </fill>
@@ -309,6 +309,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFfff8e1"/>
         <bgColor rgb="FFfff8e1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD7EE"/>
+        <bgColor rgb="FFBDD7EE"/>
       </patternFill>
     </fill>
     <fill>
@@ -498,7 +504,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -512,9 +518,6 @@
     <xf numFmtId="0" fontId="19" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -524,12 +527,12 @@
     <xf numFmtId="0" fontId="19" fillId="32" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -539,16 +542,19 @@
     <xf numFmtId="0" fontId="2" fillId="32" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -558,12 +564,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -573,21 +579,21 @@
     <xf numFmtId="0" fontId="10" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="36" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="36" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="37" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -677,6 +683,9 @@
     <xf numFmtId="0" fontId="11" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
@@ -698,12 +707,12 @@
     <xf numFmtId="0" fontId="7" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -713,7 +722,13 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -722,7 +737,7 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -731,28 +746,28 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1155,12 +1170,12 @@
           <t>PS5 COMPLETION PLATFORM  |  DONE - subsystems at 100%</t>
         </is>
       </c>
-      <c r="B1" s="97" t="n"/>
-      <c r="C1" s="97" t="n"/>
-      <c r="D1" s="97" t="n"/>
-      <c r="E1" s="97" t="n"/>
-      <c r="F1" s="97" t="n"/>
-      <c r="G1" s="98" t="n"/>
+      <c r="B1" s="100" t="n"/>
+      <c r="C1" s="100" t="n"/>
+      <c r="D1" s="100" t="n"/>
+      <c r="E1" s="100" t="n"/>
+      <c r="F1" s="100" t="n"/>
+      <c r="G1" s="101" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="22" t="inlineStr">
@@ -1200,10 +1215,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="78" t="n">
+      <c r="A3" s="81" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="80" t="inlineStr">
+      <c r="B3" s="83" t="inlineStr">
         <is>
           <t>PS5-01-01 - Fire Water Jockey Pump A/B</t>
         </is>
@@ -1228,13 +1243,13 @@
           <t>Hydraulic tubing could not be connected in HPU due to Fittings/socket issues</t>
         </is>
       </c>
-      <c r="G3" s="66" t="inlineStr"/>
+      <c r="G3" s="67" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="78" t="n">
+      <c r="A4" s="81" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="80" t="inlineStr">
+      <c r="B4" s="83" t="inlineStr">
         <is>
           <t>PS5-01-04 - Fire Water Pump Mini Flow Recycle</t>
         </is>
@@ -1255,13 +1270,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G4" s="66" t="inlineStr"/>
+      <c r="G4" s="67" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="78" t="n">
+      <c r="A5" s="81" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="80" t="inlineStr">
+      <c r="B5" s="83" t="inlineStr">
         <is>
           <t>PS5-01-06 - Foam Concentrate Distribution</t>
         </is>
@@ -1282,13 +1297,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G5" s="66" t="inlineStr"/>
+      <c r="G5" s="67" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="78" t="n">
+      <c r="A6" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="80" t="inlineStr">
+      <c r="B6" s="83" t="inlineStr">
         <is>
           <t>PS5-01-09 - Inergen for EITS Building</t>
         </is>
@@ -1309,13 +1324,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G6" s="66" t="inlineStr"/>
+      <c r="G6" s="67" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="78" t="n">
+      <c r="A7" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="80" t="inlineStr">
+      <c r="B7" s="83" t="inlineStr">
         <is>
           <t>PS5-01-10 - Water Mist Package</t>
         </is>
@@ -1340,13 +1355,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G7" s="66" t="inlineStr"/>
+      <c r="G7" s="67" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="78" t="n">
+      <c r="A8" s="81" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="80" t="inlineStr">
+      <c r="B8" s="83" t="inlineStr">
         <is>
           <t>PS5-03-07 - FZ-07 - Pretreatment Area</t>
         </is>
@@ -1371,13 +1386,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G8" s="66" t="inlineStr"/>
+      <c r="G8" s="67" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="78" t="n">
+      <c r="A9" s="81" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="80" t="inlineStr">
+      <c r="B9" s="83" t="inlineStr">
         <is>
           <t>PS5-03-09 - FZ-09 - Power Generation Building - Engine Bay 1</t>
         </is>
@@ -1402,13 +1417,13 @@
           <t>Due to gland plate issue of SEA-0001 we cannot terminate the cablesof F&amp;G Instruments.</t>
         </is>
       </c>
-      <c r="G9" s="66" t="inlineStr"/>
+      <c r="G9" s="67" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="78" t="n">
+      <c r="A10" s="81" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="80" t="inlineStr">
+      <c r="B10" s="83" t="inlineStr">
         <is>
           <t>PS5-03-10 - FZ-10 - Power Generation Building - Engine Bay 2</t>
         </is>
@@ -1429,13 +1444,13 @@
         </is>
       </c>
       <c r="F10" s="23" t="inlineStr"/>
-      <c r="G10" s="66" t="inlineStr"/>
+      <c r="G10" s="67" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="78" t="n">
+      <c r="A11" s="81" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="80" t="inlineStr">
+      <c r="B11" s="83" t="inlineStr">
         <is>
           <t>PS5-03-13 - FZ-13 - Power Generation Building - Instrument Air Room</t>
         </is>
@@ -1460,13 +1475,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G11" s="66" t="inlineStr"/>
+      <c r="G11" s="67" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="78" t="n">
+      <c r="A12" s="81" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="80" t="inlineStr">
+      <c r="B12" s="83" t="inlineStr">
         <is>
           <t>PS5-03-20 - FZ-20 - Emergency Diesel Generator Enclosure</t>
         </is>
@@ -1491,13 +1506,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G12" s="66" t="inlineStr"/>
+      <c r="G12" s="67" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="78" t="n">
+      <c r="A13" s="81" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="80" t="inlineStr">
+      <c r="B13" s="83" t="inlineStr">
         <is>
           <t>PS5-05-01 - Emergency Diesel Generator Package</t>
         </is>
@@ -1512,7 +1527,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E13" s="68" t="inlineStr">
+      <c r="E13" s="69" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -1522,13 +1537,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G13" s="66" t="inlineStr"/>
+      <c r="G13" s="67" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="78" t="n">
+      <c r="A14" s="81" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="80" t="inlineStr">
+      <c r="B14" s="83" t="inlineStr">
         <is>
           <t>PS5-05-02 - Emergency Diesel Generator Package (UCP)</t>
         </is>
@@ -1553,13 +1568,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G14" s="66" t="inlineStr"/>
+      <c r="G14" s="67" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="78" t="n">
+      <c r="A15" s="81" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="80" t="inlineStr">
+      <c r="B15" s="83" t="inlineStr">
         <is>
           <t>PS5-06-02 - AC UPS - Power Generator Building</t>
         </is>
@@ -1584,13 +1599,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G15" s="66" t="inlineStr"/>
+      <c r="G15" s="67" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="78" t="n">
+      <c r="A16" s="81" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="80" t="inlineStr">
+      <c r="B16" s="83" t="inlineStr">
         <is>
           <t>PS5-09-05 - HVAC for EITS Building</t>
         </is>
@@ -1607,13 +1622,13 @@
         </is>
       </c>
       <c r="F16" s="23" t="inlineStr"/>
-      <c r="G16" s="66" t="inlineStr"/>
+      <c r="G16" s="67" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="78" t="n">
+      <c r="A17" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="80" t="inlineStr">
+      <c r="B17" s="83" t="inlineStr">
         <is>
           <t>PS5-28-02 - Closed Drain Header 2</t>
         </is>
@@ -1634,13 +1649,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G17" s="66" t="inlineStr"/>
+      <c r="G17" s="67" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="78" t="n">
+      <c r="A18" s="81" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="80" t="inlineStr">
+      <c r="B18" s="83" t="inlineStr">
         <is>
           <t>PS5-28-05 - HP Relief Header</t>
         </is>
@@ -1665,13 +1680,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G18" s="66" t="inlineStr"/>
+      <c r="G18" s="67" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="82" t="n">
+      <c r="A19" s="85" t="n">
         <v>17</v>
       </c>
-      <c r="B19" s="80" t="inlineStr">
+      <c r="B19" s="83" t="inlineStr">
         <is>
           <t>PS5-53-01 - Utility Water / Storage Tank</t>
         </is>
@@ -1686,7 +1701,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="E19" s="68" t="inlineStr">
+      <c r="E19" s="69" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -1696,13 +1711,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G19" s="66" t="inlineStr"/>
+      <c r="G19" s="67" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="78" t="n">
+      <c r="A20" s="81" t="n">
         <v>18</v>
       </c>
-      <c r="B20" s="80" t="inlineStr">
+      <c r="B20" s="83" t="inlineStr">
         <is>
           <t>PS5-60-01 - Power Generation Package A</t>
         </is>
@@ -1727,13 +1742,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G20" s="66" t="inlineStr"/>
+      <c r="G20" s="67" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="78" t="n">
+      <c r="A21" s="81" t="n">
         <v>19</v>
       </c>
-      <c r="B21" s="80" t="inlineStr">
+      <c r="B21" s="83" t="inlineStr">
         <is>
           <t>PS5-60-02 - Power Gen Package A (UCP)</t>
         </is>
@@ -1755,47 +1770,47 @@
       </c>
       <c r="F21" s="23" t="inlineStr">
         <is>
+          <t>WALKDOWN COMPLETE-20-08-26--ATTENDENCE SHEET TO BE SUBMITTED</t>
+        </is>
+      </c>
+      <c r="G21" s="67" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="81" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-04 - Power Generation Package B</t>
+        </is>
+      </c>
+      <c r="C22" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E22" s="27" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F22" s="23" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G21" s="66" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="78" t="n">
-        <v>20</v>
-      </c>
-      <c r="B22" s="80" t="inlineStr">
-        <is>
-          <t>PS5-60-04 - Power Generation Package B</t>
-        </is>
-      </c>
-      <c r="C22" s="27" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D22" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E22" s="27" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F22" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G22" s="66" t="inlineStr"/>
+      <c r="G22" s="67" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="78" t="n">
+      <c r="A23" s="81" t="n">
         <v>21</v>
       </c>
-      <c r="B23" s="80" t="inlineStr">
+      <c r="B23" s="83" t="inlineStr">
         <is>
           <t>PS5-60-23 - Instrument Air Distribution lines</t>
         </is>
@@ -1816,13 +1831,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G23" s="66" t="inlineStr"/>
+      <c r="G23" s="67" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="78" t="n">
+      <c r="A24" s="81" t="n">
         <v>22</v>
       </c>
-      <c r="B24" s="80" t="inlineStr">
+      <c r="B24" s="83" t="inlineStr">
         <is>
           <t>PS5-60-26 - Instrument Air Compressor Skid</t>
         </is>
@@ -1847,13 +1862,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G24" s="66" t="inlineStr"/>
+      <c r="G24" s="67" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="78" t="n">
+      <c r="A25" s="81" t="n">
         <v>23</v>
       </c>
-      <c r="B25" s="80" t="inlineStr">
+      <c r="B25" s="83" t="inlineStr">
         <is>
           <t>PS5-60-27 - Compressed Air Starting Skid</t>
         </is>
@@ -1878,13 +1893,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G25" s="66" t="inlineStr"/>
+      <c r="G25" s="67" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="78" t="n">
+      <c r="A26" s="81" t="n">
         <v>24</v>
       </c>
-      <c r="B26" s="80" t="inlineStr">
+      <c r="B26" s="83" t="inlineStr">
         <is>
           <t>PS5-60-28 - Air Receiver A &amp; Air Regulator A</t>
         </is>
@@ -1899,7 +1914,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E26" s="68" t="inlineStr">
+      <c r="E26" s="69" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -1909,13 +1924,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G26" s="66" t="inlineStr"/>
+      <c r="G26" s="67" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="78" t="n">
+      <c r="A27" s="81" t="n">
         <v>25</v>
       </c>
-      <c r="B27" s="80" t="inlineStr">
+      <c r="B27" s="83" t="inlineStr">
         <is>
           <t>PS5-60-29 - Air Receiver B &amp; Air Regulator B</t>
         </is>
@@ -1940,13 +1955,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G27" s="66" t="inlineStr"/>
+      <c r="G27" s="67" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="78" t="n">
+      <c r="A28" s="81" t="n">
         <v>26</v>
       </c>
-      <c r="B28" s="80" t="inlineStr">
+      <c r="B28" s="83" t="inlineStr">
         <is>
           <t>PS5-60-30 - Air Receiver C &amp; Air Regulator C</t>
         </is>
@@ -1971,13 +1986,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G28" s="66" t="inlineStr"/>
+      <c r="G28" s="67" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="78" t="n">
+      <c r="A29" s="81" t="n">
         <v>27</v>
       </c>
-      <c r="B29" s="80" t="inlineStr">
+      <c r="B29" s="83" t="inlineStr">
         <is>
           <t>PS5-60-31 - Air Receiver D &amp; Air Regulator D</t>
         </is>
@@ -2002,13 +2017,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G29" s="66" t="inlineStr"/>
+      <c r="G29" s="67" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="78" t="n">
+      <c r="A30" s="81" t="n">
         <v>28</v>
       </c>
-      <c r="B30" s="80" t="inlineStr">
+      <c r="B30" s="83" t="inlineStr">
         <is>
           <t>PS5-60-32 - Air Receiver E &amp; Air Regulator E</t>
         </is>
@@ -2033,13 +2048,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G30" s="66" t="inlineStr"/>
+      <c r="G30" s="67" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="78" t="n">
+      <c r="A31" s="81" t="n">
         <v>29</v>
       </c>
-      <c r="B31" s="80" t="inlineStr">
+      <c r="B31" s="83" t="inlineStr">
         <is>
           <t>PS5-60-33 - Air Receiver F &amp; Air Regulator F</t>
         </is>
@@ -2064,13 +2079,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G31" s="66" t="inlineStr"/>
+      <c r="G31" s="67" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="78" t="n">
+      <c r="A32" s="81" t="n">
         <v>30</v>
       </c>
-      <c r="B32" s="80" t="inlineStr">
+      <c r="B32" s="83" t="inlineStr">
         <is>
           <t>PS5-60-34 - Air Receiver G &amp; Air Regulator G</t>
         </is>
@@ -2095,13 +2110,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G32" s="66" t="inlineStr"/>
+      <c r="G32" s="67" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="78" t="n">
+      <c r="A33" s="81" t="n">
         <v>31</v>
       </c>
-      <c r="B33" s="80" t="inlineStr">
+      <c r="B33" s="83" t="inlineStr">
         <is>
           <t>PS5-60-35 - Injector Tip Cooling Module A</t>
         </is>
@@ -2126,13 +2141,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G33" s="66" t="inlineStr"/>
+      <c r="G33" s="67" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="78" t="n">
+      <c r="A34" s="81" t="n">
         <v>32</v>
       </c>
-      <c r="B34" s="80" t="inlineStr">
+      <c r="B34" s="83" t="inlineStr">
         <is>
           <t>PS5-60-36 - Injector Tip Cooling Module B</t>
         </is>
@@ -2157,13 +2172,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G34" s="66" t="inlineStr"/>
+      <c r="G34" s="67" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="78" t="n">
+      <c r="A35" s="81" t="n">
         <v>33</v>
       </c>
-      <c r="B35" s="80" t="inlineStr">
+      <c r="B35" s="83" t="inlineStr">
         <is>
           <t>PS5-60-37 - Injector Tip Cooling Module C</t>
         </is>
@@ -2188,13 +2203,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G35" s="66" t="inlineStr"/>
+      <c r="G35" s="67" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="78" t="n">
+      <c r="A36" s="81" t="n">
         <v>34</v>
       </c>
-      <c r="B36" s="80" t="inlineStr">
+      <c r="B36" s="83" t="inlineStr">
         <is>
           <t>PS5-60-38 - Injector Tip Cooling Module D</t>
         </is>
@@ -2219,13 +2234,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G36" s="66" t="inlineStr"/>
+      <c r="G36" s="67" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="78" t="n">
+      <c r="A37" s="81" t="n">
         <v>35</v>
       </c>
-      <c r="B37" s="80" t="inlineStr">
+      <c r="B37" s="83" t="inlineStr">
         <is>
           <t>PS5-60-39 - Injector Tip Cooling Module E</t>
         </is>
@@ -2250,13 +2265,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G37" s="66" t="inlineStr"/>
+      <c r="G37" s="67" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="78" t="n">
+      <c r="A38" s="81" t="n">
         <v>36</v>
       </c>
-      <c r="B38" s="80" t="inlineStr">
+      <c r="B38" s="83" t="inlineStr">
         <is>
           <t>PS5-60-40 - Injector Tip Cooling Module F</t>
         </is>
@@ -2281,13 +2296,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G38" s="66" t="inlineStr"/>
+      <c r="G38" s="67" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="78" t="n">
+      <c r="A39" s="81" t="n">
         <v>37</v>
       </c>
-      <c r="B39" s="80" t="inlineStr">
+      <c r="B39" s="83" t="inlineStr">
         <is>
           <t>PS5-60-42 - Oil Mist Separator Skid PS5-60-VS-9100A</t>
         </is>
@@ -2312,13 +2327,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G39" s="66" t="inlineStr"/>
+      <c r="G39" s="67" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="78" t="n">
+      <c r="A40" s="81" t="n">
         <v>38</v>
       </c>
-      <c r="B40" s="80" t="inlineStr">
+      <c r="B40" s="83" t="inlineStr">
         <is>
           <t>PS5-60-43 - Oil Mist Separator Skid PS5-60-VS-9100B</t>
         </is>
@@ -2343,13 +2358,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G40" s="66" t="inlineStr"/>
+      <c r="G40" s="67" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="78" t="n">
+      <c r="A41" s="81" t="n">
         <v>39</v>
       </c>
-      <c r="B41" s="80" t="inlineStr">
+      <c r="B41" s="83" t="inlineStr">
         <is>
           <t>PS5-60-44 - Oil Mist Separator Skid PS5-60-VS-9100C</t>
         </is>
@@ -2374,13 +2389,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G41" s="66" t="inlineStr"/>
+      <c r="G41" s="67" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="78" t="n">
+      <c r="A42" s="81" t="n">
         <v>40</v>
       </c>
-      <c r="B42" s="80" t="inlineStr">
+      <c r="B42" s="83" t="inlineStr">
         <is>
           <t>PS5-60-45 - Oil Mist Separator Skid PS5-60-VS-9100D</t>
         </is>
@@ -2405,13 +2420,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G42" s="66" t="inlineStr"/>
+      <c r="G42" s="67" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="78" t="n">
+      <c r="A43" s="81" t="n">
         <v>41</v>
       </c>
-      <c r="B43" s="80" t="inlineStr">
+      <c r="B43" s="83" t="inlineStr">
         <is>
           <t>PS5-60-46 - Oil Mist Separator Skid PS5-60-VS-9100E</t>
         </is>
@@ -2432,13 +2447,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G43" s="66" t="inlineStr"/>
+      <c r="G43" s="67" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="78" t="n">
+      <c r="A44" s="81" t="n">
         <v>42</v>
       </c>
-      <c r="B44" s="80" t="inlineStr">
+      <c r="B44" s="83" t="inlineStr">
         <is>
           <t>PS5-60-47 - Oil Mist Separator Skid PS5-60-VS-9100F</t>
         </is>
@@ -2463,13 +2478,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G44" s="66" t="inlineStr"/>
+      <c r="G44" s="67" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="78" t="n">
+      <c r="A45" s="81" t="n">
         <v>43</v>
       </c>
-      <c r="B45" s="80" t="inlineStr">
+      <c r="B45" s="83" t="inlineStr">
         <is>
           <t>PS5-60-56 - Fuel Conditioning Module PS5-60-UZ-8900A</t>
         </is>
@@ -2490,13 +2505,13 @@
         </is>
       </c>
       <c r="F45" s="23" t="inlineStr"/>
-      <c r="G45" s="66" t="inlineStr"/>
+      <c r="G45" s="67" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="78" t="n">
+      <c r="A46" s="81" t="n">
         <v>44</v>
       </c>
-      <c r="B46" s="80" t="inlineStr">
+      <c r="B46" s="83" t="inlineStr">
         <is>
           <t>PS5-60-58 - Fuel Conditioning Module PS5-60-UZ-8900B</t>
         </is>
@@ -2517,13 +2532,13 @@
         </is>
       </c>
       <c r="F46" s="23" t="inlineStr"/>
-      <c r="G46" s="66" t="inlineStr"/>
+      <c r="G46" s="67" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="78" t="n">
+      <c r="A47" s="81" t="n">
         <v>45</v>
       </c>
-      <c r="B47" s="80" t="inlineStr">
+      <c r="B47" s="83" t="inlineStr">
         <is>
           <t>PS5-60-60 - Fuel Conditioning Module PS5-60-UZ-8900C</t>
         </is>
@@ -2544,13 +2559,13 @@
         </is>
       </c>
       <c r="F47" s="23" t="inlineStr"/>
-      <c r="G47" s="66" t="inlineStr"/>
+      <c r="G47" s="67" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="78" t="n">
+      <c r="A48" s="81" t="n">
         <v>46</v>
       </c>
-      <c r="B48" s="80" t="inlineStr">
+      <c r="B48" s="83" t="inlineStr">
         <is>
           <t>PS5-60-62 - Fuel Conditioning Module PS5-60-UZ-8900D</t>
         </is>
@@ -2571,13 +2586,13 @@
         </is>
       </c>
       <c r="F48" s="23" t="inlineStr"/>
-      <c r="G48" s="66" t="inlineStr"/>
+      <c r="G48" s="67" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="78" t="n">
+      <c r="A49" s="81" t="n">
         <v>47</v>
       </c>
-      <c r="B49" s="80" t="inlineStr">
+      <c r="B49" s="83" t="inlineStr">
         <is>
           <t>PS5-60-70 - Engine A Cooling system</t>
         </is>
@@ -2602,13 +2617,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G49" s="66" t="inlineStr"/>
+      <c r="G49" s="67" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="78" t="n">
+      <c r="A50" s="81" t="n">
         <v>48</v>
       </c>
-      <c r="B50" s="80" t="inlineStr">
+      <c r="B50" s="83" t="inlineStr">
         <is>
           <t>PS5-60-71 - Engine B Cooling system</t>
         </is>
@@ -2633,13 +2648,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G50" s="66" t="inlineStr"/>
+      <c r="G50" s="67" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="78" t="n">
+      <c r="A51" s="81" t="n">
         <v>49</v>
       </c>
-      <c r="B51" s="80" t="inlineStr">
+      <c r="B51" s="83" t="inlineStr">
         <is>
           <t>PS5-60-72 - Engine C Cooling system</t>
         </is>
@@ -2664,13 +2679,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G51" s="66" t="inlineStr"/>
+      <c r="G51" s="67" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="78" t="n">
+      <c r="A52" s="81" t="n">
         <v>50</v>
       </c>
-      <c r="B52" s="80" t="inlineStr">
+      <c r="B52" s="83" t="inlineStr">
         <is>
           <t>PS5-60-73 - Engine D Cooling system</t>
         </is>
@@ -2695,13 +2710,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G52" s="66" t="inlineStr"/>
+      <c r="G52" s="67" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="78" t="n">
+      <c r="A53" s="81" t="n">
         <v>51</v>
       </c>
-      <c r="B53" s="80" t="inlineStr">
+      <c r="B53" s="83" t="inlineStr">
         <is>
           <t>PS5-60-74 - Engine E Cooling system</t>
         </is>
@@ -2726,13 +2741,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G53" s="66" t="inlineStr"/>
+      <c r="G53" s="67" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="78" t="n">
+      <c r="A54" s="81" t="n">
         <v>52</v>
       </c>
-      <c r="B54" s="80" t="inlineStr">
+      <c r="B54" s="83" t="inlineStr">
         <is>
           <t>PS5-60-75 - Engine F Cooling system</t>
         </is>
@@ -2757,13 +2772,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G54" s="66" t="inlineStr"/>
+      <c r="G54" s="67" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="78" t="n">
+      <c r="A55" s="81" t="n">
         <v>53</v>
       </c>
-      <c r="B55" s="80" t="inlineStr">
+      <c r="B55" s="83" t="inlineStr">
         <is>
           <t>PS5-61-05 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0003)</t>
         </is>
@@ -2788,13 +2803,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G55" s="66" t="inlineStr"/>
+      <c r="G55" s="67" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="78" t="n">
+      <c r="A56" s="81" t="n">
         <v>54</v>
       </c>
-      <c r="B56" s="80" t="inlineStr">
+      <c r="B56" s="83" t="inlineStr">
         <is>
           <t>PS5-61-07 - 0.4kV Switchboard EITS Building (PS5-61-IK-0001)</t>
         </is>
@@ -2819,13 +2834,13 @@
           <t>PS5-61-IV-0001B cannot close ITR due to transformer leakage issue.</t>
         </is>
       </c>
-      <c r="G56" s="66" t="inlineStr"/>
+      <c r="G56" s="67" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="78" t="n">
+      <c r="A57" s="81" t="n">
         <v>55</v>
       </c>
-      <c r="B57" s="80" t="inlineStr">
+      <c r="B57" s="83" t="inlineStr">
         <is>
           <t>PS5-61-10 - Outdoor Valves Distribution Board - PS5-61-IG-0042</t>
         </is>
@@ -2850,13 +2865,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G57" s="66" t="inlineStr"/>
+      <c r="G57" s="67" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="78" t="n">
+      <c r="A58" s="81" t="n">
         <v>56</v>
       </c>
-      <c r="B58" s="80" t="inlineStr">
+      <c r="B58" s="83" t="inlineStr">
         <is>
           <t>PS5-61-11 - Outdoor Valves Distribution Board - PS5-61-IG-0043</t>
         </is>
@@ -2881,13 +2896,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G58" s="66" t="inlineStr"/>
+      <c r="G58" s="67" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="78" t="n">
+      <c r="A59" s="81" t="n">
         <v>57</v>
       </c>
-      <c r="B59" s="80" t="inlineStr">
+      <c r="B59" s="83" t="inlineStr">
         <is>
           <t>PS5-62-04 - Outdoor Emergency Lighting DB  - PS5-05-IG-0006</t>
         </is>
@@ -2912,13 +2927,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G59" s="66" t="inlineStr"/>
+      <c r="G59" s="67" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="78" t="n">
+      <c r="A60" s="81" t="n">
         <v>58</v>
       </c>
-      <c r="B60" s="80" t="inlineStr">
+      <c r="B60" s="83" t="inlineStr">
         <is>
           <t>PS5-63-04 - Electrical Earthing - EITS Building</t>
         </is>
@@ -2935,13 +2950,13 @@
         </is>
       </c>
       <c r="F60" s="23" t="inlineStr"/>
-      <c r="G60" s="66" t="inlineStr"/>
+      <c r="G60" s="67" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="78" t="n">
+      <c r="A61" s="81" t="n">
         <v>59</v>
       </c>
-      <c r="B61" s="80" t="inlineStr">
+      <c r="B61" s="83" t="inlineStr">
         <is>
           <t>PS5-71-22 - Diesel Fuel Pre Pressure Module</t>
         </is>
@@ -2966,13 +2981,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G61" s="66" t="inlineStr"/>
+      <c r="G61" s="67" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="78" t="n">
+      <c r="A62" s="81" t="n">
         <v>60</v>
       </c>
-      <c r="B62" s="80" t="inlineStr">
+      <c r="B62" s="83" t="inlineStr">
         <is>
           <t>PS5-74-03 - Nitrogen Receiver</t>
         </is>
@@ -2997,13 +3012,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G62" s="66" t="inlineStr"/>
+      <c r="G62" s="67" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="82" t="n">
+      <c r="A63" s="85" t="n">
         <v>61</v>
       </c>
-      <c r="B63" s="80" t="inlineStr">
+      <c r="B63" s="83" t="inlineStr">
         <is>
           <t>PS5-78-01 - Lifting and handling equipment</t>
         </is>
@@ -3018,7 +3033,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="E63" s="68" t="inlineStr">
+      <c r="E63" s="69" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -3028,13 +3043,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G63" s="66" t="inlineStr"/>
+      <c r="G63" s="67" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="78" t="n">
+      <c r="A64" s="81" t="n">
         <v>62</v>
       </c>
-      <c r="B64" s="80" t="inlineStr">
+      <c r="B64" s="83" t="inlineStr">
         <is>
           <t>PS5-83-01 - EITS Building</t>
         </is>
@@ -3059,13 +3074,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G64" s="66" t="inlineStr"/>
+      <c r="G64" s="67" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="78" t="n">
+      <c r="A65" s="81" t="n">
         <v>63</v>
       </c>
-      <c r="B65" s="80" t="inlineStr">
+      <c r="B65" s="83" t="inlineStr">
         <is>
           <t>PS5-84-03 - Shelters</t>
         </is>
@@ -3086,13 +3101,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G65" s="66" t="inlineStr"/>
+      <c r="G65" s="67" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="78" t="n">
+      <c r="A66" s="81" t="n">
         <v>64</v>
       </c>
-      <c r="B66" s="80" t="inlineStr">
+      <c r="B66" s="83" t="inlineStr">
         <is>
           <t>PS5-86-01 - Shelters</t>
         </is>
@@ -3113,13 +3128,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G66" s="66" t="inlineStr"/>
+      <c r="G66" s="67" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="78" t="n">
+      <c r="A67" s="81" t="n">
         <v>65</v>
       </c>
-      <c r="B67" s="80" t="inlineStr">
+      <c r="B67" s="83" t="inlineStr">
         <is>
           <t>PS5-91-01 - Multicore cables &amp; JB</t>
         </is>
@@ -3144,7 +3159,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G67" s="66" t="inlineStr"/>
+      <c r="G67" s="67" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G67"/>

--- a/EXCEL/7 - COMPLETE.xlsx
+++ b/EXCEL/7 - COMPLETE.xlsx
@@ -570,14 +570,14 @@
     <xf numFmtId="0" fontId="10" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1223,7 +1223,7 @@
           <t>PS5-01-01 - Fire Water Jockey Pump A/B</t>
         </is>
       </c>
-      <c r="C3" s="27" t="inlineStr">
+      <c r="C3" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1233,7 +1233,7 @@
           <t>DONE(partial)</t>
         </is>
       </c>
-      <c r="E3" s="27" t="inlineStr">
+      <c r="E3" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -1254,13 +1254,13 @@
           <t>PS5-01-04 - Fire Water Pump Mini Flow Recycle</t>
         </is>
       </c>
-      <c r="C4" s="27" t="inlineStr">
+      <c r="C4" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
       <c r="D4" s="24" t="inlineStr"/>
-      <c r="E4" s="27" t="inlineStr">
+      <c r="E4" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -1281,13 +1281,13 @@
           <t>PS5-01-06 - Foam Concentrate Distribution</t>
         </is>
       </c>
-      <c r="C5" s="27" t="inlineStr">
+      <c r="C5" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
       <c r="D5" s="24" t="inlineStr"/>
-      <c r="E5" s="27" t="inlineStr">
+      <c r="E5" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -1308,13 +1308,13 @@
           <t>PS5-01-09 - Inergen for EITS Building</t>
         </is>
       </c>
-      <c r="C6" s="27" t="inlineStr">
+      <c r="C6" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
       <c r="D6" s="24" t="inlineStr"/>
-      <c r="E6" s="27" t="inlineStr">
+      <c r="E6" s="28" t="inlineStr">
         <is>
           <t>2026-08-08</t>
         </is>
@@ -1335,7 +1335,7 @@
           <t>PS5-01-10 - Water Mist Package</t>
         </is>
       </c>
-      <c r="C7" s="27" t="inlineStr">
+      <c r="C7" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1345,7 +1345,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E7" s="27" t="inlineStr">
+      <c r="E7" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -1366,7 +1366,7 @@
           <t>PS5-03-07 - FZ-07 - Pretreatment Area</t>
         </is>
       </c>
-      <c r="C8" s="27" t="inlineStr">
+      <c r="C8" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1376,7 +1376,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E8" s="27" t="inlineStr">
+      <c r="E8" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1397,7 +1397,7 @@
           <t>PS5-03-09 - FZ-09 - Power Generation Building - Engine Bay 1</t>
         </is>
       </c>
-      <c r="C9" s="27" t="inlineStr">
+      <c r="C9" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1407,7 +1407,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E9" s="27" t="inlineStr">
+      <c r="E9" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1428,7 +1428,7 @@
           <t>PS5-03-10 - FZ-10 - Power Generation Building - Engine Bay 2</t>
         </is>
       </c>
-      <c r="C10" s="27" t="inlineStr">
+      <c r="C10" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1438,7 +1438,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E10" s="27" t="inlineStr">
+      <c r="E10" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1455,7 +1455,7 @@
           <t>PS5-03-13 - FZ-13 - Power Generation Building - Instrument Air Room</t>
         </is>
       </c>
-      <c r="C11" s="27" t="inlineStr">
+      <c r="C11" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1465,7 +1465,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E11" s="27" t="inlineStr">
+      <c r="E11" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1486,7 +1486,7 @@
           <t>PS5-03-20 - FZ-20 - Emergency Diesel Generator Enclosure</t>
         </is>
       </c>
-      <c r="C12" s="27" t="inlineStr">
+      <c r="C12" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1496,7 +1496,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E12" s="27" t="inlineStr">
+      <c r="E12" s="28" t="inlineStr">
         <is>
           <t>07-Aug-26</t>
         </is>
@@ -1517,7 +1517,7 @@
           <t>PS5-05-01 - Emergency Diesel Generator Package</t>
         </is>
       </c>
-      <c r="C13" s="27" t="inlineStr">
+      <c r="C13" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1548,7 +1548,7 @@
           <t>PS5-05-02 - Emergency Diesel Generator Package (UCP)</t>
         </is>
       </c>
-      <c r="C14" s="27" t="inlineStr">
+      <c r="C14" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1579,7 +1579,7 @@
           <t>PS5-06-02 - AC UPS - Power Generator Building</t>
         </is>
       </c>
-      <c r="C15" s="27" t="inlineStr">
+      <c r="C15" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1589,7 +1589,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E15" s="27" t="inlineStr">
+      <c r="E15" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1610,13 +1610,13 @@
           <t>PS5-09-05 - HVAC for EITS Building</t>
         </is>
       </c>
-      <c r="C16" s="27" t="inlineStr">
+      <c r="C16" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
       <c r="D16" s="24" t="inlineStr"/>
-      <c r="E16" s="27" t="inlineStr">
+      <c r="E16" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -1633,13 +1633,13 @@
           <t>PS5-28-02 - Closed Drain Header 2</t>
         </is>
       </c>
-      <c r="C17" s="27" t="inlineStr">
+      <c r="C17" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
       <c r="D17" s="24" t="inlineStr"/>
-      <c r="E17" s="27" t="inlineStr">
+      <c r="E17" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -1660,7 +1660,7 @@
           <t>PS5-28-05 - HP Relief Header</t>
         </is>
       </c>
-      <c r="C18" s="27" t="inlineStr">
+      <c r="C18" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1670,7 +1670,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E18" s="27" t="inlineStr">
+      <c r="E18" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -1691,7 +1691,7 @@
           <t>PS5-53-01 - Utility Water / Storage Tank</t>
         </is>
       </c>
-      <c r="C19" s="27" t="inlineStr">
+      <c r="C19" s="28" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -1722,7 +1722,7 @@
           <t>PS5-60-01 - Power Generation Package A</t>
         </is>
       </c>
-      <c r="C20" s="27" t="inlineStr">
+      <c r="C20" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1732,7 +1732,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E20" s="27" t="inlineStr">
+      <c r="E20" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -1753,7 +1753,7 @@
           <t>PS5-60-02 - Power Gen Package A (UCP)</t>
         </is>
       </c>
-      <c r="C21" s="27" t="inlineStr">
+      <c r="C21" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1763,7 +1763,7 @@
           <t>PS5 - Milestone B</t>
         </is>
       </c>
-      <c r="E21" s="27" t="inlineStr">
+      <c r="E21" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1784,7 +1784,7 @@
           <t>PS5-60-04 - Power Generation Package B</t>
         </is>
       </c>
-      <c r="C22" s="27" t="inlineStr">
+      <c r="C22" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1794,7 +1794,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E22" s="27" t="inlineStr">
+      <c r="E22" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -1815,13 +1815,13 @@
           <t>PS5-60-23 - Instrument Air Distribution lines</t>
         </is>
       </c>
-      <c r="C23" s="27" t="inlineStr">
+      <c r="C23" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
       <c r="D23" s="24" t="inlineStr"/>
-      <c r="E23" s="27" t="inlineStr">
+      <c r="E23" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -1842,7 +1842,7 @@
           <t>PS5-60-26 - Instrument Air Compressor Skid</t>
         </is>
       </c>
-      <c r="C24" s="27" t="inlineStr">
+      <c r="C24" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1852,7 +1852,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E24" s="27" t="inlineStr">
+      <c r="E24" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -1873,7 +1873,7 @@
           <t>PS5-60-27 - Compressed Air Starting Skid</t>
         </is>
       </c>
-      <c r="C25" s="27" t="inlineStr">
+      <c r="C25" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1883,7 +1883,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E25" s="27" t="inlineStr">
+      <c r="E25" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -1904,7 +1904,7 @@
           <t>PS5-60-28 - Air Receiver A &amp; Air Regulator A</t>
         </is>
       </c>
-      <c r="C26" s="27" t="inlineStr">
+      <c r="C26" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1935,7 +1935,7 @@
           <t>PS5-60-29 - Air Receiver B &amp; Air Regulator B</t>
         </is>
       </c>
-      <c r="C27" s="27" t="inlineStr">
+      <c r="C27" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1945,7 +1945,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E27" s="27" t="inlineStr">
+      <c r="E27" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -1966,7 +1966,7 @@
           <t>PS5-60-30 - Air Receiver C &amp; Air Regulator C</t>
         </is>
       </c>
-      <c r="C28" s="27" t="inlineStr">
+      <c r="C28" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1976,7 +1976,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E28" s="27" t="inlineStr">
+      <c r="E28" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -1997,7 +1997,7 @@
           <t>PS5-60-31 - Air Receiver D &amp; Air Regulator D</t>
         </is>
       </c>
-      <c r="C29" s="27" t="inlineStr">
+      <c r="C29" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2007,7 +2007,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E29" s="27" t="inlineStr">
+      <c r="E29" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -2028,7 +2028,7 @@
           <t>PS5-60-32 - Air Receiver E &amp; Air Regulator E</t>
         </is>
       </c>
-      <c r="C30" s="27" t="inlineStr">
+      <c r="C30" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2038,7 +2038,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E30" s="27" t="inlineStr">
+      <c r="E30" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -2059,7 +2059,7 @@
           <t>PS5-60-33 - Air Receiver F &amp; Air Regulator F</t>
         </is>
       </c>
-      <c r="C31" s="27" t="inlineStr">
+      <c r="C31" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2069,7 +2069,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E31" s="27" t="inlineStr">
+      <c r="E31" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -2090,7 +2090,7 @@
           <t>PS5-60-34 - Air Receiver G &amp; Air Regulator G</t>
         </is>
       </c>
-      <c r="C32" s="27" t="inlineStr">
+      <c r="C32" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2100,7 +2100,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E32" s="27" t="inlineStr">
+      <c r="E32" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -2121,7 +2121,7 @@
           <t>PS5-60-35 - Injector Tip Cooling Module A</t>
         </is>
       </c>
-      <c r="C33" s="27" t="inlineStr">
+      <c r="C33" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2152,7 +2152,7 @@
           <t>PS5-60-36 - Injector Tip Cooling Module B</t>
         </is>
       </c>
-      <c r="C34" s="27" t="inlineStr">
+      <c r="C34" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2162,7 +2162,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E34" s="27" t="inlineStr">
+      <c r="E34" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -2183,7 +2183,7 @@
           <t>PS5-60-37 - Injector Tip Cooling Module C</t>
         </is>
       </c>
-      <c r="C35" s="27" t="inlineStr">
+      <c r="C35" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2193,7 +2193,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E35" s="27" t="inlineStr">
+      <c r="E35" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -2214,7 +2214,7 @@
           <t>PS5-60-38 - Injector Tip Cooling Module D</t>
         </is>
       </c>
-      <c r="C36" s="27" t="inlineStr">
+      <c r="C36" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2224,7 +2224,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E36" s="27" t="inlineStr">
+      <c r="E36" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -2245,7 +2245,7 @@
           <t>PS5-60-39 - Injector Tip Cooling Module E</t>
         </is>
       </c>
-      <c r="C37" s="27" t="inlineStr">
+      <c r="C37" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2255,7 +2255,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E37" s="27" t="inlineStr">
+      <c r="E37" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -2276,7 +2276,7 @@
           <t>PS5-60-40 - Injector Tip Cooling Module F</t>
         </is>
       </c>
-      <c r="C38" s="27" t="inlineStr">
+      <c r="C38" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2286,7 +2286,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E38" s="27" t="inlineStr">
+      <c r="E38" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -2307,7 +2307,7 @@
           <t>PS5-60-42 - Oil Mist Separator Skid PS5-60-VS-9100A</t>
         </is>
       </c>
-      <c r="C39" s="27" t="inlineStr">
+      <c r="C39" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2338,7 +2338,7 @@
           <t>PS5-60-43 - Oil Mist Separator Skid PS5-60-VS-9100B</t>
         </is>
       </c>
-      <c r="C40" s="27" t="inlineStr">
+      <c r="C40" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2348,7 +2348,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E40" s="27" t="inlineStr">
+      <c r="E40" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -2369,7 +2369,7 @@
           <t>PS5-60-44 - Oil Mist Separator Skid PS5-60-VS-9100C</t>
         </is>
       </c>
-      <c r="C41" s="27" t="inlineStr">
+      <c r="C41" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2379,7 +2379,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E41" s="27" t="inlineStr">
+      <c r="E41" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -2400,7 +2400,7 @@
           <t>PS5-60-45 - Oil Mist Separator Skid PS5-60-VS-9100D</t>
         </is>
       </c>
-      <c r="C42" s="27" t="inlineStr">
+      <c r="C42" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2410,7 +2410,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E42" s="27" t="inlineStr">
+      <c r="E42" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -2431,13 +2431,13 @@
           <t>PS5-60-46 - Oil Mist Separator Skid PS5-60-VS-9100E</t>
         </is>
       </c>
-      <c r="C43" s="27" t="inlineStr">
+      <c r="C43" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
       <c r="D43" s="24" t="inlineStr"/>
-      <c r="E43" s="27" t="inlineStr">
+      <c r="E43" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2458,7 +2458,7 @@
           <t>PS5-60-47 - Oil Mist Separator Skid PS5-60-VS-9100F</t>
         </is>
       </c>
-      <c r="C44" s="27" t="inlineStr">
+      <c r="C44" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2468,7 +2468,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E44" s="27" t="inlineStr">
+      <c r="E44" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -2489,7 +2489,7 @@
           <t>PS5-60-56 - Fuel Conditioning Module PS5-60-UZ-8900A</t>
         </is>
       </c>
-      <c r="C45" s="27" t="inlineStr">
+      <c r="C45" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2499,7 +2499,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E45" s="27" t="inlineStr">
+      <c r="E45" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -2516,7 +2516,7 @@
           <t>PS5-60-58 - Fuel Conditioning Module PS5-60-UZ-8900B</t>
         </is>
       </c>
-      <c r="C46" s="27" t="inlineStr">
+      <c r="C46" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2526,7 +2526,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E46" s="27" t="inlineStr">
+      <c r="E46" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -2543,7 +2543,7 @@
           <t>PS5-60-60 - Fuel Conditioning Module PS5-60-UZ-8900C</t>
         </is>
       </c>
-      <c r="C47" s="27" t="inlineStr">
+      <c r="C47" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2553,7 +2553,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E47" s="27" t="inlineStr">
+      <c r="E47" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -2570,7 +2570,7 @@
           <t>PS5-60-62 - Fuel Conditioning Module PS5-60-UZ-8900D</t>
         </is>
       </c>
-      <c r="C48" s="27" t="inlineStr">
+      <c r="C48" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2580,7 +2580,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E48" s="27" t="inlineStr">
+      <c r="E48" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -2597,7 +2597,7 @@
           <t>PS5-60-70 - Engine A Cooling system</t>
         </is>
       </c>
-      <c r="C49" s="27" t="inlineStr">
+      <c r="C49" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2607,7 +2607,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E49" s="27" t="inlineStr">
+      <c r="E49" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -2628,7 +2628,7 @@
           <t>PS5-60-71 - Engine B Cooling system</t>
         </is>
       </c>
-      <c r="C50" s="27" t="inlineStr">
+      <c r="C50" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2638,7 +2638,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E50" s="27" t="inlineStr">
+      <c r="E50" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -2659,7 +2659,7 @@
           <t>PS5-60-72 - Engine C Cooling system</t>
         </is>
       </c>
-      <c r="C51" s="27" t="inlineStr">
+      <c r="C51" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2669,7 +2669,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E51" s="27" t="inlineStr">
+      <c r="E51" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -2690,7 +2690,7 @@
           <t>PS5-60-73 - Engine D Cooling system</t>
         </is>
       </c>
-      <c r="C52" s="27" t="inlineStr">
+      <c r="C52" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2700,7 +2700,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E52" s="27" t="inlineStr">
+      <c r="E52" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -2721,7 +2721,7 @@
           <t>PS5-60-74 - Engine E Cooling system</t>
         </is>
       </c>
-      <c r="C53" s="27" t="inlineStr">
+      <c r="C53" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2731,7 +2731,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E53" s="27" t="inlineStr">
+      <c r="E53" s="28" t="inlineStr">
         <is>
           <t>PLATFORM ISSUE</t>
         </is>
@@ -2752,7 +2752,7 @@
           <t>PS5-60-75 - Engine F Cooling system</t>
         </is>
       </c>
-      <c r="C54" s="27" t="inlineStr">
+      <c r="C54" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2762,7 +2762,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E54" s="27" t="inlineStr">
+      <c r="E54" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -2783,7 +2783,7 @@
           <t>PS5-61-05 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0003)</t>
         </is>
       </c>
-      <c r="C55" s="27" t="inlineStr">
+      <c r="C55" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2793,7 +2793,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E55" s="27" t="inlineStr">
+      <c r="E55" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2814,7 +2814,7 @@
           <t>PS5-61-07 - 0.4kV Switchboard EITS Building (PS5-61-IK-0001)</t>
         </is>
       </c>
-      <c r="C56" s="27" t="inlineStr">
+      <c r="C56" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2824,7 +2824,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="E56" s="27" t="inlineStr">
+      <c r="E56" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -2845,7 +2845,7 @@
           <t>PS5-61-10 - Outdoor Valves Distribution Board - PS5-61-IG-0042</t>
         </is>
       </c>
-      <c r="C57" s="27" t="inlineStr">
+      <c r="C57" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2855,7 +2855,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E57" s="27" t="inlineStr">
+      <c r="E57" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2876,7 +2876,7 @@
           <t>PS5-61-11 - Outdoor Valves Distribution Board - PS5-61-IG-0043</t>
         </is>
       </c>
-      <c r="C58" s="27" t="inlineStr">
+      <c r="C58" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2886,7 +2886,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E58" s="27" t="inlineStr">
+      <c r="E58" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2907,7 +2907,7 @@
           <t>PS5-62-04 - Outdoor Emergency Lighting DB  - PS5-05-IG-0006</t>
         </is>
       </c>
-      <c r="C59" s="27" t="inlineStr">
+      <c r="C59" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2917,7 +2917,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E59" s="27" t="inlineStr">
+      <c r="E59" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2938,13 +2938,13 @@
           <t>PS5-63-04 - Electrical Earthing - EITS Building</t>
         </is>
       </c>
-      <c r="C60" s="27" t="inlineStr">
+      <c r="C60" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
       <c r="D60" s="24" t="inlineStr"/>
-      <c r="E60" s="27" t="inlineStr">
+      <c r="E60" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2961,7 +2961,7 @@
           <t>PS5-71-22 - Diesel Fuel Pre Pressure Module</t>
         </is>
       </c>
-      <c r="C61" s="27" t="inlineStr">
+      <c r="C61" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2971,7 +2971,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E61" s="27" t="inlineStr">
+      <c r="E61" s="28" t="inlineStr">
         <is>
           <t>DONE(full)</t>
         </is>
@@ -2992,7 +2992,7 @@
           <t>PS5-74-03 - Nitrogen Receiver</t>
         </is>
       </c>
-      <c r="C62" s="27" t="inlineStr">
+      <c r="C62" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3002,7 +3002,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E62" s="27" t="inlineStr">
+      <c r="E62" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -3023,7 +3023,7 @@
           <t>PS5-78-01 - Lifting and handling equipment</t>
         </is>
       </c>
-      <c r="C63" s="27" t="inlineStr">
+      <c r="C63" s="28" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
@@ -3054,7 +3054,7 @@
           <t>PS5-83-01 - EITS Building</t>
         </is>
       </c>
-      <c r="C64" s="27" t="inlineStr">
+      <c r="C64" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3064,7 +3064,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E64" s="27" t="inlineStr">
+      <c r="E64" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -3085,13 +3085,13 @@
           <t>PS5-84-03 - Shelters</t>
         </is>
       </c>
-      <c r="C65" s="27" t="inlineStr">
+      <c r="C65" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
       <c r="D65" s="24" t="inlineStr"/>
-      <c r="E65" s="27" t="inlineStr">
+      <c r="E65" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -3112,13 +3112,13 @@
           <t>PS5-86-01 - Shelters</t>
         </is>
       </c>
-      <c r="C66" s="27" t="inlineStr">
+      <c r="C66" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
       <c r="D66" s="24" t="inlineStr"/>
-      <c r="E66" s="27" t="inlineStr">
+      <c r="E66" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -3139,7 +3139,7 @@
           <t>PS5-91-01 - Multicore cables &amp; JB</t>
         </is>
       </c>
-      <c r="C67" s="27" t="inlineStr">
+      <c r="C67" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3149,7 +3149,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E67" s="27" t="inlineStr">
+      <c r="E67" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3243,7 +3243,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B290"/>
+  <dimension ref="A1:B295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3825,7 +3825,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PS5-08-01 - PAGA</t>
+          <t>PS5-08-01</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3837,2890 +3837,2950 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PS5-08-03 - Telephone</t>
+          <t>PS5-08-01a - PAGA (Required for SU)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PS5-08-03</t>
+          <t>PS5-08-01a</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PS5-08-04 - Hotline</t>
+          <t>PS5-08-01b - PAGA (Not required for SU)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>PS5-08-04</t>
+          <t>PS5-08-01b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>PS5-08-07 - Multi-Channel Voice Recorder</t>
+          <t>PS5-08-03 - Telephone</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PS5-08-07</t>
+          <t>PS5-08-03</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>PS5-08-11 - Corporate LAN  (SIE)</t>
+          <t>PS5-08-04 - Hotline</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PS5-08-11</t>
+          <t>PS5-08-04</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>PS5-08-12 - Corporate Wireless LAN (SIE)</t>
+          <t>PS5-08-07 - Multi-Channel Voice Recorder</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PS5-08-12</t>
+          <t>PS5-08-07</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>PS5-08-13 - Safety Data Network (SII SP3 SAF)</t>
+          <t>PS5-08-11 - Corporate LAN  (SIE)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PS5-08-13</t>
+          <t>PS5-08-11</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>PS5-08-14 - Industrial Data Network (SII SP1)</t>
+          <t>PS5-08-12 - Corporate Wireless LAN (SIE)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PS5-08-14</t>
+          <t>PS5-08-12</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>PS5-08-15 - Security Data Network (SII SP3 SEC)</t>
+          <t>PS5-08-13 - Safety Data Network (SII SP3 SAF)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PS5-08-15</t>
+          <t>PS5-08-13</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PS5-08-23 - VHF Trunk Radio System</t>
+          <t>PS5-08-14 - Industrial Data Network (SII SP1)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PS5-08-23</t>
+          <t>PS5-08-14</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PS5-08-34 - Satphone</t>
+          <t>PS5-08-15 - Security Data Network (SII SP3 SEC)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PS5-08-34</t>
+          <t>PS5-08-15</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PS5-08-35 - Optical Transport Network</t>
+          <t>PS5-08-23 - VHF Trunk Radio System</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PS5-08-35</t>
+          <t>PS5-08-23</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>PS5-08-36 - Pipeline FO Cable &amp; EPRS</t>
+          <t>PS5-08-34 - Satphone</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PS5-08-36</t>
+          <t>PS5-08-34</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>PS5-08-51 - Entertainment</t>
+          <t>PS5-08-35 - Optical Transport Network</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>PS5-08-51</t>
+          <t>PS5-08-35</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>PS5-08-52 - Process &amp; Security CCTV</t>
+          <t>PS5-08-36 - Pipeline FO Cable &amp; EPRS</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PS5-08-52</t>
+          <t>PS5-08-36</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>PS5-08-55 - Videoconference</t>
+          <t>PS5-08-51 - Entertainment</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PS5-08-55</t>
+          <t>PS5-08-51</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>PS5-08-61 - Meteocean</t>
+          <t>PS5-08-52a - Process &amp; Security CCTV (Required for SU)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PS5-08-61</t>
+          <t>PS5-08-52a</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>PS5-08-71 - Structured Cabling (CAT6)</t>
+          <t>PS5-08-52b - Process &amp; Security CCTV (Not required for SU)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PS5-08-71</t>
+          <t>PS5-08-52b</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PS5-08-72 - Structured Cabling (FO)</t>
+          <t>PS5-08-55 - Videoconference</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PS5-08-72</t>
+          <t>PS5-08-55</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>PS5-08-81 - Guard tour</t>
+          <t>PS5-08-61 - Meteocean</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PS5-08-81</t>
+          <t>PS5-08-61</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>PS5-08-82 - Key Management</t>
+          <t>PS5-08-71 - Structured Cabling (CAT6)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PS5-08-82</t>
+          <t>PS5-08-71</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>PS5-08-83 - Perimeter &amp; Pipeline intrusion detection system</t>
+          <t>PS5-08-72 - Structured Cabling (FO)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PS5-08-83</t>
+          <t>PS5-08-72</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>PS5-08-85 - Access Control, POB &amp; e-Mustering</t>
+          <t>PS5-08-81 - Guard tour</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PS5-08-85</t>
+          <t>PS5-08-81</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>PS5-08-86 - Integrated Security Management System</t>
+          <t>PS5-08-82 - Key Management</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PS5-08-86</t>
+          <t>PS5-08-82</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>PS5-08-92 - Telecom Mast</t>
+          <t>PS5-08-83 - Perimeter &amp; Pipeline intrusion detection system</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>PS5-08-92</t>
+          <t>PS5-08-83</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>PS5-08-93 - Telecom Monitoring System</t>
+          <t>PS5-08-85</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>PS5-08-93</t>
+          <t>PS5-08-85</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>PS5-09-01 - HVAC for Office and Facilities building</t>
+          <t>PS5-08-85a - Access Control, POB &amp; e-Mustering (Required for SU)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PS5-09-01</t>
+          <t>PS5-08-85a</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>PS5-09-02 - HVAC for Guard House</t>
+          <t>PS5-08-85b - Access Control, POB &amp; e-Mustering (Not required for SU)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>PS5-09-02</t>
+          <t>PS5-08-85b</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>PS5-09-03 - HVAC for Generator Building</t>
+          <t>PS5-08-86 - Integrated Security Management System</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>PS5-09-03</t>
+          <t>PS5-08-86</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>PS5-09-04 - HVAC for Workshop &amp; Warehouse</t>
+          <t>PS5-08-92 - Telecom Mast</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>PS5-09-04</t>
+          <t>PS5-08-92</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>PS5-09-05 - HVAC for EITS Building</t>
+          <t>PS5-08-93 - Telecom Monitoring System</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>PS5-09-05</t>
+          <t>PS5-08-93</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>PS5-0H-01 - HIPPS</t>
+          <t>PS5-09-01 - HVAC for Office and Facilities building</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>PS5-0H-01</t>
+          <t>PS5-09-01</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>PS5-25-01 - Export Pipeline Pig Receiver</t>
+          <t>PS5-09-02 - HVAC for Guard House</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>PS5-25-01</t>
+          <t>PS5-09-02</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>PS5-25-02 - Crude Oil Export Pump A</t>
+          <t>PS5-09-03 - HVAC for Generator Building</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>PS5-25-02</t>
+          <t>PS5-09-03</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>PS5-25-03 - Crude Oil Export Pump B</t>
+          <t>PS5-09-04 - HVAC for Workshop &amp; Warehouse</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>PS5-25-03</t>
+          <t>PS5-09-04</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>PS5-25-04 - Crude Oil Export Pump C</t>
+          <t>PS5-09-05 - HVAC for EITS Building</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>PS5-25-04</t>
+          <t>PS5-09-05</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>PS5-25-05 - Crude Oil Export Pumps Bypass</t>
+          <t>PS5-0H-01 - HIPPS</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>PS5-25-05</t>
+          <t>PS5-0H-01</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>PS5-25-06 - Crude Oil Export Pumps Discharge</t>
+          <t>PS5-25-01 - Export Pipeline Pig Receiver</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>PS5-25-06</t>
+          <t>PS5-25-01</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>PS5-25-07 - Export Pipeline Pig Launcher</t>
+          <t>PS5-25-02 - Crude Oil Export Pump A</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>PS5-25-07</t>
+          <t>PS5-25-02</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>PS5-28-01 - Closed Drain Header 1</t>
+          <t>PS5-25-03 - Crude Oil Export Pump B</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>PS5-28-01</t>
+          <t>PS5-25-03</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>PS5-28-02 - Closed Drain Header 2</t>
+          <t>PS5-25-04 - Crude Oil Export Pump C</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>PS5-28-02</t>
+          <t>PS5-25-04</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>PS5-28-03 - Closed Drain Drum and Pump 01</t>
+          <t>PS5-25-05 - Crude Oil Export Pumps Bypass</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>PS5-28-03</t>
+          <t>PS5-25-05</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>PS5-28-04 - Closed Drain Drum and Pump 02</t>
+          <t>PS5-25-06 - Crude Oil Export Pumps Discharge</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>PS5-28-04</t>
+          <t>PS5-25-06</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>PS5-28-05 - HP Relief Header</t>
+          <t>PS5-25-07 - Export Pipeline Pig Launcher</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>PS5-28-05</t>
+          <t>PS5-25-07</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>PS5-28-06 - Relief Drum and Pump</t>
+          <t>PS5-28-01 - Closed Drain Header 1</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>PS5-28-06</t>
+          <t>PS5-28-01</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>PS5-28-07 - Open Drains (OD2)</t>
+          <t>PS5-28-02 - Closed Drain Header 2</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>PS5-28-07</t>
+          <t>PS5-28-02</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>PS5-28-08 - Open Drain Sump and Pumps</t>
+          <t>PS5-28-03 - Closed Drain Drum and Pump 01</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>PS5-28-08</t>
+          <t>PS5-28-03</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>PS5-28-09 - Observation Basin</t>
+          <t>PS5-28-04 - Closed Drain Drum and Pump 02</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>PS5-28-09</t>
+          <t>PS5-28-04</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>PS5-28-10 - Oil Skimmer Package</t>
+          <t>PS5-28-05 - HP Relief Header</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>PS5-28-10</t>
+          <t>PS5-28-05</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>PS5-28-11 - Open Drain Interceptor</t>
+          <t>PS5-28-06 - Relief Drum and Pump</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>PS5-28-11</t>
+          <t>PS5-28-06</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>PS5-28-12 - Open Drains (OD3)</t>
+          <t>PS5-28-07 - Open Drains (OD2)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>PS5-28-12</t>
+          <t>PS5-28-07</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>PS5-28-13 - Seal Oil Drain Drum &amp; Pump A</t>
+          <t>PS5-28-08 - Open Drain Sump and Pumps</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>PS5-28-13</t>
+          <t>PS5-28-08</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>PS5-28-14 - Seal Oil Drain Drum &amp; Pump B</t>
+          <t>PS5-28-09 - Observation Basin</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>PS5-28-14</t>
+          <t>PS5-28-09</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>PS5-28-15 - Seal Oil Drain Drum &amp; Pump C</t>
+          <t>PS5-28-10 - Oil Skimmer Package</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>PS5-28-15</t>
+          <t>PS5-28-10</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>PS5-28-16 - LP Relief Header</t>
+          <t>PS5-28-11 - Open Drain Interceptor</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>PS5-28-16</t>
+          <t>PS5-28-11</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>PS5-28-17 - Reinjection Pump</t>
+          <t>PS5-28-12 - Open Drains (OD3)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>PS5-28-17</t>
+          <t>PS5-28-12</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>PS5-50-01 - Water Well Submersible Pumps (3100)</t>
+          <t>PS5-28-13 - Seal Oil Drain Drum &amp; Pump A</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>PS5-50-01</t>
+          <t>PS5-28-13</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>PS5-50-02 - Water Well Submersible Pumps (3200)</t>
+          <t>PS5-28-14 - Seal Oil Drain Drum &amp; Pump B</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>PS5-50-02</t>
+          <t>PS5-28-14</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>PS5-50-03 - Water Pre-Treatment Package</t>
+          <t>PS5-28-15 - Seal Oil Drain Drum &amp; Pump C</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>PS5-50-03</t>
+          <t>PS5-28-15</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>PS5-53-01 - Utility Water / Storage Tank</t>
+          <t>PS5-28-16 - LP Relief Header</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>PS5-53-01</t>
+          <t>PS5-28-16</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>PS5-53-02 - Water Distribution Pump A/B</t>
+          <t>PS5-28-17 - Reinjection Pump</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>PS5-53-02</t>
+          <t>PS5-28-17</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>PS5-53-03 - Water Softener Package</t>
+          <t>PS5-50-01 - Water Well Submersible Pumps (3100)</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>PS5-53-03</t>
+          <t>PS5-50-01</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>PS5-53-04 - Water Treatment Purification Package</t>
+          <t>PS5-50-02 - Water Well Submersible Pumps (3200)</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>PS5-53-04</t>
+          <t>PS5-50-02</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>PS5-53-05 - Water Distribution Header</t>
+          <t>PS5-50-03 - Water Pre-Treatment Package</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>PS5-53-05</t>
+          <t>PS5-50-03</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>PS5-53-06 - Water Distribution Consumers</t>
+          <t>PS5-53-01 - Utility Water / Storage Tank</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>PS5-53-06</t>
+          <t>PS5-53-01</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>PS5-60-01 - Power Generation Package A</t>
+          <t>PS5-53-02 - Water Distribution Pump A/B</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>PS5-60-01</t>
+          <t>PS5-53-02</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>PS5-60-02 - Power Gen Package A (UCP)</t>
+          <t>PS5-53-03 - Water Softener Package</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>PS5-60-02</t>
+          <t>PS5-53-03</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>PS5-60-03 - Power Gen Package A Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-53-04 - Water Treatment Purification Package</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>PS5-60-03</t>
+          <t>PS5-53-04</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>PS5-60-04 - Power Generation Package B</t>
+          <t>PS5-53-05 - Water Distribution Header</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>PS5-60-04</t>
+          <t>PS5-53-05</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>PS5-60-05 - Power Gen Package B (UCP)</t>
+          <t>PS5-53-06 - Water Distribution Consumers</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>PS5-60-05</t>
+          <t>PS5-53-06</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>PS5-60-06 - Power Gen Package B Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-60-01 - Power Generation Package A</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>PS5-60-06</t>
+          <t>PS5-60-01</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>PS5-60-07 - Power Generation Package C</t>
+          <t>PS5-60-02 - Power Gen Package A (UCP)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>PS5-60-07</t>
+          <t>PS5-60-02</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>PS5-60-08 - Power Gen Package C (UCP)</t>
+          <t>PS5-60-03 - Power Gen Package A Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>PS5-60-08</t>
+          <t>PS5-60-03</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>PS5-60-09 - Power Gen Package C Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-60-04 - Power Generation Package B</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>PS5-60-09</t>
+          <t>PS5-60-04</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>PS5-60-10 - Power Generation Package D</t>
+          <t>PS5-60-05 - Power Gen Package B (UCP)</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>PS5-60-10</t>
+          <t>PS5-60-05</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>PS5-60-11 - Power Gen Package D (UCP)</t>
+          <t>PS5-60-06 - Power Gen Package B Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>PS5-60-11</t>
+          <t>PS5-60-06</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>PS5-60-12 - Power Gen Package D Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-60-07 - Power Generation Package C</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>PS5-60-12</t>
+          <t>PS5-60-07</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>PS5-60-13 - Power Generation Package E</t>
+          <t>PS5-60-08 - Power Gen Package C (UCP)</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>PS5-60-13</t>
+          <t>PS5-60-08</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>PS5-60-14 - Power Gen Package E (UCP)</t>
+          <t>PS5-60-09 - Power Gen Package C Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>PS5-60-14</t>
+          <t>PS5-60-09</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>PS5-60-15 - Power Gen Package E Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-60-10 - Power Generation Package D</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>PS5-60-15</t>
+          <t>PS5-60-10</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>PS5-60-16 - Power Generation Package F</t>
+          <t>PS5-60-11 - Power Gen Package D (UCP)</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PS5-60-16</t>
+          <t>PS5-60-11</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>PS5-60-17 - Power Gen Package F (UCP)</t>
+          <t>PS5-60-12 - Power Gen Package D Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PS5-60-17</t>
+          <t>PS5-60-12</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>PS5-60-18 - Power Gen Package F Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-60-13 - Power Generation Package E</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PS5-60-18</t>
+          <t>PS5-60-13</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>PS5-60-19 - Power Generation Package G</t>
+          <t>PS5-60-14 - Power Gen Package E (UCP)</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PS5-60-19</t>
+          <t>PS5-60-14</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>PS5-60-20 - Power Gen Package G (UCP)</t>
+          <t>PS5-60-15 - Power Gen Package E Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PS5-60-20</t>
+          <t>PS5-60-15</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>PS5-60-21 - Power Gen Package G Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-60-16 - Power Generation Package F</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PS5-60-21</t>
+          <t>PS5-60-16</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>PS5-60-22 - Power Gen Master UCP</t>
+          <t>PS5-60-17 - Power Gen Package F (UCP)</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PS5-60-22</t>
+          <t>PS5-60-17</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>PS5-60-23 - Instrument Air Distribution lines</t>
+          <t>PS5-60-18 - Power Gen Package F Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>PS5-60-23</t>
+          <t>PS5-60-18</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>PS5-60-24 - Cooling Water Tank &amp; Pump</t>
+          <t>PS5-60-19 - Power Generation Package G</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>PS5-60-24</t>
+          <t>PS5-60-19</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>PS5-60-25 - Cooling Water Maintenance Tank &amp; Return Pump</t>
+          <t>PS5-60-20 - Power Gen Package G (UCP)</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>PS5-60-25</t>
+          <t>PS5-60-20</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>PS5-60-26 - Instrument Air Compressor Skid</t>
+          <t>PS5-60-21 - Power Gen Package G Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>PS5-60-26</t>
+          <t>PS5-60-21</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>PS5-60-27 - Compressed Air Starting Skid</t>
+          <t>PS5-60-22 - Power Gen Master UCP</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>PS5-60-27</t>
+          <t>PS5-60-22</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>PS5-60-28 - Air Receiver A &amp; Air Regulator A</t>
+          <t>PS5-60-23 - Instrument Air Distribution lines</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>PS5-60-28</t>
+          <t>PS5-60-23</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>PS5-60-29 - Air Receiver B &amp; Air Regulator B</t>
+          <t>PS5-60-24 - Cooling Water Tank &amp; Pump</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>PS5-60-29</t>
+          <t>PS5-60-24</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>PS5-60-30 - Air Receiver C &amp; Air Regulator C</t>
+          <t>PS5-60-25 - Cooling Water Maintenance Tank &amp; Return Pump</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>PS5-60-30</t>
+          <t>PS5-60-25</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>PS5-60-31 - Air Receiver D &amp; Air Regulator D</t>
+          <t>PS5-60-26 - Instrument Air Compressor Skid</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>PS5-60-31</t>
+          <t>PS5-60-26</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>PS5-60-32 - Air Receiver E &amp; Air Regulator E</t>
+          <t>PS5-60-27 - Compressed Air Starting Skid</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>PS5-60-32</t>
+          <t>PS5-60-27</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>PS5-60-33 - Air Receiver F &amp; Air Regulator F</t>
+          <t>PS5-60-28 - Air Receiver A &amp; Air Regulator A</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>PS5-60-33</t>
+          <t>PS5-60-28</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>PS5-60-34 - Air Receiver G &amp; Air Regulator G</t>
+          <t>PS5-60-29 - Air Receiver B &amp; Air Regulator B</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>PS5-60-34</t>
+          <t>PS5-60-29</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>PS5-60-35 - Injector Tip Cooling Module A</t>
+          <t>PS5-60-30 - Air Receiver C &amp; Air Regulator C</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>PS5-60-35</t>
+          <t>PS5-60-30</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>PS5-60-36 - Injector Tip Cooling Module B</t>
+          <t>PS5-60-31 - Air Receiver D &amp; Air Regulator D</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>PS5-60-36</t>
+          <t>PS5-60-31</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>PS5-60-37 - Injector Tip Cooling Module C</t>
+          <t>PS5-60-32 - Air Receiver E &amp; Air Regulator E</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>PS5-60-37</t>
+          <t>PS5-60-32</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>PS5-60-38 - Injector Tip Cooling Module D</t>
+          <t>PS5-60-33 - Air Receiver F &amp; Air Regulator F</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>PS5-60-38</t>
+          <t>PS5-60-33</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>PS5-60-39 - Injector Tip Cooling Module E</t>
+          <t>PS5-60-34 - Air Receiver G &amp; Air Regulator G</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>PS5-60-39</t>
+          <t>PS5-60-34</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>PS5-60-40 - Injector Tip Cooling Module F</t>
+          <t>PS5-60-35 - Injector Tip Cooling Module A</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>PS5-60-40</t>
+          <t>PS5-60-35</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>PS5-60-41 - Injector Tip Cooling Module G</t>
+          <t>PS5-60-36 - Injector Tip Cooling Module B</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>PS5-60-41</t>
+          <t>PS5-60-36</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>PS5-60-42 - Oil Mist Separator Skid PS5-60-VS-9100A</t>
+          <t>PS5-60-37 - Injector Tip Cooling Module C</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>PS5-60-42</t>
+          <t>PS5-60-37</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>PS5-60-43 - Oil Mist Separator Skid PS5-60-VS-9100B</t>
+          <t>PS5-60-38 - Injector Tip Cooling Module D</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>PS5-60-43</t>
+          <t>PS5-60-38</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>PS5-60-44 - Oil Mist Separator Skid PS5-60-VS-9100C</t>
+          <t>PS5-60-39 - Injector Tip Cooling Module E</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>PS5-60-44</t>
+          <t>PS5-60-39</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>PS5-60-45 - Oil Mist Separator Skid PS5-60-VS-9100D</t>
+          <t>PS5-60-40 - Injector Tip Cooling Module F</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>PS5-60-45</t>
+          <t>PS5-60-40</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>PS5-60-46 - Oil Mist Separator Skid PS5-60-VS-9100E</t>
+          <t>PS5-60-41 - Injector Tip Cooling Module G</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>PS5-60-46</t>
+          <t>PS5-60-41</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>PS5-60-47 - Oil Mist Separator Skid PS5-60-VS-9100F</t>
+          <t>PS5-60-42 - Oil Mist Separator Skid PS5-60-VS-9100A</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>PS5-60-47</t>
+          <t>PS5-60-42</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>PS5-60-48 - Oil Mist Separator Skid PS5-60-VS-9100G</t>
+          <t>PS5-60-43 - Oil Mist Separator Skid PS5-60-VS-9100B</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>PS5-60-48</t>
+          <t>PS5-60-43</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>PS5-60-49 - Lube Oil Separator Module PS5-60-UO-81100A</t>
+          <t>PS5-60-44 - Oil Mist Separator Skid PS5-60-VS-9100C</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>PS5-60-49</t>
+          <t>PS5-60-44</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>PS5-60-50 - Lube Oil Separator Module PS5-60-UO-81100B</t>
+          <t>PS5-60-45 - Oil Mist Separator Skid PS5-60-VS-9100D</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>PS5-60-50</t>
+          <t>PS5-60-45</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>PS5-60-51 - Lube Oil Separator Module PS5-60-UO-81100C</t>
+          <t>PS5-60-46 - Oil Mist Separator Skid PS5-60-VS-9100E</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>PS5-60-51</t>
+          <t>PS5-60-46</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>PS5-60-52 - Lube Oil Separator Module PS5-60-UO-81100D</t>
+          <t>PS5-60-47 - Oil Mist Separator Skid PS5-60-VS-9100F</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>PS5-60-52</t>
+          <t>PS5-60-47</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>PS5-60-53 - Lube Oil Separator Module PS5-60-UO-81100E</t>
+          <t>PS5-60-48 - Oil Mist Separator Skid PS5-60-VS-9100G</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>PS5-60-53</t>
+          <t>PS5-60-48</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>PS5-60-54 - Lube Oil Separator Module PS5-60-UO-81100F</t>
+          <t>PS5-60-49 - Lube Oil Separator Module PS5-60-UO-81100A</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>PS5-60-54</t>
+          <t>PS5-60-49</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>PS5-60-55 - Lube Oil Separator Module PS5-60-UO-81100G</t>
+          <t>PS5-60-50 - Lube Oil Separator Module PS5-60-UO-81100B</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>PS5-60-55</t>
+          <t>PS5-60-50</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>PS5-60-56 - Fuel Conditioning Module PS5-60-UZ-8900A</t>
+          <t>PS5-60-51 - Lube Oil Separator Module PS5-60-UO-81100C</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>PS5-60-56</t>
+          <t>PS5-60-51</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>PS5-60-57 - Fuel Conditioning Module PS5-60-UZ-8900A (UCP)</t>
+          <t>PS5-60-52 - Lube Oil Separator Module PS5-60-UO-81100D</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>PS5-60-57</t>
+          <t>PS5-60-52</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>PS5-60-58 - Fuel Conditioning Module PS5-60-UZ-8900B</t>
+          <t>PS5-60-53 - Lube Oil Separator Module PS5-60-UO-81100E</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>PS5-60-58</t>
+          <t>PS5-60-53</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>PS5-60-59 - Fuel Conditioning Module PS5-60-UZ-8900B (UCP)</t>
+          <t>PS5-60-54 - Lube Oil Separator Module PS5-60-UO-81100F</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>PS5-60-59</t>
+          <t>PS5-60-54</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>PS5-60-60 - Fuel Conditioning Module PS5-60-UZ-8900C</t>
+          <t>PS5-60-55 - Lube Oil Separator Module PS5-60-UO-81100G</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>PS5-60-60</t>
+          <t>PS5-60-55</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>PS5-60-61 - Fuel Conditioning Module PS5-60-UZ-8900C (UCP)</t>
+          <t>PS5-60-56 - Fuel Conditioning Module PS5-60-UZ-8900A</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>PS5-60-61</t>
+          <t>PS5-60-56</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>PS5-60-62 - Fuel Conditioning Module PS5-60-UZ-8900D</t>
+          <t>PS5-60-57 - Fuel Conditioning Module PS5-60-UZ-8900A (UCP)</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>PS5-60-62</t>
+          <t>PS5-60-57</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>PS5-60-63 - Fuel Conditioning Module PS5-60-UZ-8900D (UCP)</t>
+          <t>PS5-60-58 - Fuel Conditioning Module PS5-60-UZ-8900B</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>PS5-60-63</t>
+          <t>PS5-60-58</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>PS5-60-64 - Fuel Conditioning Module PS5-60-UZ-8900E</t>
+          <t>PS5-60-59 - Fuel Conditioning Module PS5-60-UZ-8900B (UCP)</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>PS5-60-64</t>
+          <t>PS5-60-59</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>PS5-60-65 - Fuel Conditioning Module PS5-60-UZ-8900E (UCP)</t>
+          <t>PS5-60-60 - Fuel Conditioning Module PS5-60-UZ-8900C</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>PS5-60-65</t>
+          <t>PS5-60-60</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>PS5-60-66 - Fuel Conditioning Module PS5-60-UZ-8900F</t>
+          <t>PS5-60-61 - Fuel Conditioning Module PS5-60-UZ-8900C (UCP)</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>PS5-60-66</t>
+          <t>PS5-60-61</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>PS5-60-67 - Fuel Conditioning Module PS5-60-UZ-8900F (UCP)</t>
+          <t>PS5-60-62 - Fuel Conditioning Module PS5-60-UZ-8900D</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>PS5-60-67</t>
+          <t>PS5-60-62</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>PS5-60-68 - Fuel Conditioning Module PS5-60-UZ-8900G</t>
+          <t>PS5-60-63 - Fuel Conditioning Module PS5-60-UZ-8900D (UCP)</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>PS5-60-68</t>
+          <t>PS5-60-63</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>PS5-60-69 - Fuel Conditioning Module PS5-60-UZ-8900G (UCP)</t>
+          <t>PS5-60-64 - Fuel Conditioning Module PS5-60-UZ-8900E</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>PS5-60-69</t>
+          <t>PS5-60-64</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>PS5-60-70 - Engine A Cooling system</t>
+          <t>PS5-60-65 - Fuel Conditioning Module PS5-60-UZ-8900E (UCP)</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>PS5-60-70</t>
+          <t>PS5-60-65</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>PS5-60-71 - Engine B Cooling system</t>
+          <t>PS5-60-66 - Fuel Conditioning Module PS5-60-UZ-8900F</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>PS5-60-71</t>
+          <t>PS5-60-66</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>PS5-60-72 - Engine C Cooling system</t>
+          <t>PS5-60-67 - Fuel Conditioning Module PS5-60-UZ-8900F (UCP)</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>PS5-60-72</t>
+          <t>PS5-60-67</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>PS5-60-73 - Engine D Cooling system</t>
+          <t>PS5-60-68 - Fuel Conditioning Module PS5-60-UZ-8900G</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>PS5-60-73</t>
+          <t>PS5-60-68</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>PS5-60-74 - Engine E Cooling system</t>
+          <t>PS5-60-69 - Fuel Conditioning Module PS5-60-UZ-8900G (UCP)</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>PS5-60-74</t>
+          <t>PS5-60-69</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>PS5-60-75 - Engine F Cooling system</t>
+          <t>PS5-60-70 - Engine A Cooling system</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>PS5-60-75</t>
+          <t>PS5-60-70</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>PS5-60-76 - Engine G Cooling system</t>
+          <t>PS5-60-71 - Engine B Cooling system</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>PS5-60-76</t>
+          <t>PS5-60-71</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>PS5-61-01 - 33kV Switchboard EITS Building (PS5-61-IJ-0001)</t>
+          <t>PS5-60-72 - Engine C Cooling system</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>PS5-61-01</t>
+          <t>PS5-60-72</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>PS5-61-02 - 6.6kV Switchboard and Transformer LLHT North - EITS Building (PS5-61-IJ-0010)</t>
+          <t>PS5-60-73 - Engine D Cooling system</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>PS5-61-02</t>
+          <t>PS5-60-73</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>PS5-61-03 - 6.6kV Switchboard and Transformer LLHT South - EITS Building (PS5-61-IJ-0011)</t>
+          <t>PS5-60-74 - Engine E Cooling system</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>PS5-61-03</t>
+          <t>PS5-60-74</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>PS5-61-04 - 0.4kV Switchboard Office &amp; Facilities Building (PS5-61-IK-0005)</t>
+          <t>PS5-60-75 - Engine F Cooling system</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>PS5-61-04</t>
+          <t>PS5-60-75</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>PS5-61-05 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0003)</t>
+          <t>PS5-60-76 - Engine G Cooling system</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>PS5-61-05</t>
+          <t>PS5-60-76</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>PS5-61-06 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0006)</t>
+          <t>PS5-61-01 - 33kV Switchboard EITS Building (PS5-61-IJ-0001)</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>PS5-61-06</t>
+          <t>PS5-61-01</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>PS5-61-07 - 0.4kV Switchboard EITS Building (PS5-61-IK-0001)</t>
+          <t>PS5-61-02 - 6.6kV Switchboard and Transformer LLHT North - EITS Building (PS5-61-IJ-0010)</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>PS5-61-07</t>
+          <t>PS5-61-02</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>PS5-61-08 - Electrical Control System</t>
+          <t>PS5-61-03 - 6.6kV Switchboard and Transformer LLHT South - EITS Building (PS5-61-IJ-0011)</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>PS5-61-08</t>
+          <t>PS5-61-03</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>PS5-61-09 - Outdoor Power Distribution Board - PS5-61-IG-0014</t>
+          <t>PS5-61-04 - 0.4kV Switchboard Office &amp; Facilities Building (PS5-61-IK-0005)</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>PS5-61-09</t>
+          <t>PS5-61-04</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>PS5-61-10 - Outdoor Valves Distribution Board - PS5-61-IG-0042</t>
+          <t>PS5-61-05 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0003)</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>PS5-61-10</t>
+          <t>PS5-61-05</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>PS5-61-11 - Outdoor Valves Distribution Board - PS5-61-IG-0043</t>
+          <t>PS5-61-06 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0006)</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>PS5-61-11</t>
+          <t>PS5-61-06</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>PS5-61-12 - EITS 33kV Bld. Normal Auxiliary DP - PS5-61-IG-0008</t>
+          <t>PS5-61-07 - 0.4kV Switchboard EITS Building (PS5-61-IK-0001)</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>PS5-61-12</t>
+          <t>PS5-61-07</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>PS5-61-13 - Power Distribution Board Office Building - PS5-61-IG-0020</t>
+          <t>PS5-61-08 - Electrical Control System</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>PS5-61-13</t>
+          <t>PS5-61-08</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>PS5-61-14 - Power Distribution Board Workshop &amp; Warehouse - PS5-61-IG-0009</t>
+          <t>PS5-61-09 - Outdoor Power Distribution Board - PS5-61-IG-0014</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>PS5-61-14</t>
+          <t>PS5-61-09</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>PS5-62-01 - Lighting Control Panel - PS5-62-IE-0001</t>
+          <t>PS5-61-10 - Outdoor Valves Distribution Board - PS5-61-IG-0042</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>PS5-62-01</t>
+          <t>PS5-61-10</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>PS5-62-02 - Lighting Control Panel - PS5-62-IE-0002</t>
+          <t>PS5-61-11 - Outdoor Valves Distribution Board - PS5-61-IG-0043</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>PS5-62-02</t>
+          <t>PS5-61-11</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>PS5-62-03 - Outdoor Emergency Lighting DB  - PS5-05-IG-0004</t>
+          <t>PS5-61-12 - EITS 33kV Bld. Normal Auxiliary DP - PS5-61-IG-0008</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>PS5-62-03</t>
+          <t>PS5-61-12</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>PS5-62-04 - Outdoor Emergency Lighting DB  - PS5-05-IG-0006</t>
+          <t>PS5-61-13 - Power Distribution Board Office Building - PS5-61-IG-0020</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>PS5-62-04</t>
+          <t>PS5-61-13</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>PS5-62-05 - Guard House Emergency L&amp;SP DB  - PS5-05-IG-0007</t>
+          <t>PS5-61-14 - Power Distribution Board Workshop &amp; Warehouse - PS5-61-IG-0009</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>PS5-62-05</t>
+          <t>PS5-61-14</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>PS5-62-06 - CRO Generator Building Emergency Lighting DB  - PS5-05-IG-0025</t>
+          <t>PS5-62-01 - Lighting Control Panel - PS5-62-IE-0001</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>PS5-62-06</t>
+          <t>PS5-62-01</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>PS5-62-07 - CRO Generator Electrical Building Emergency Lighting DB  - PS5-05-IG-0026</t>
+          <t>PS5-62-02 - Lighting Control Panel - PS5-62-IE-0002</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>PS5-62-07</t>
+          <t>PS5-62-02</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>PS5-62-08 - Outdoor Normal Lighting  DB  - PS5-61-IG-0006</t>
+          <t>PS5-62-03 - Outdoor Emergency Lighting DB  - PS5-05-IG-0004</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>PS5-62-08</t>
+          <t>PS5-62-03</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>PS5-62-09 - Outdoor Normal Lighting DB  - PS5-61-IG-0007</t>
+          <t>PS5-62-04 - Outdoor Emergency Lighting DB  - PS5-05-IG-0006</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>PS5-62-09</t>
+          <t>PS5-62-04</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>PS5-62-10 - CRO Generator Building Normal L&amp;SP DB  - PS5-61-IG-0015</t>
+          <t>PS5-62-05 - Guard House Emergency L&amp;SP DB  - PS5-05-IG-0007</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>PS5-62-10</t>
+          <t>PS5-62-05</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>PS5-62-11 - CRO Generator Electrical Building Normal L&amp;SP DB  - PS5-61-IG-0016</t>
+          <t>PS5-62-06 - CRO Generator Building Emergency Lighting DB  - PS5-05-IG-0025</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>PS5-62-11</t>
+          <t>PS5-62-06</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>PS5-62-12 - EITS 33kV Bld. Emergency L&amp;SP DP - PS5-05-IG-0003</t>
+          <t>PS5-62-07 - CRO Generator Electrical Building Emergency Lighting DB  - PS5-05-IG-0026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>PS5-62-12</t>
+          <t>PS5-62-07</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>PS5-62-13 - EITS 33kV Bld. Normal L&amp;SP DP - PS5-61-IG-0003</t>
+          <t>PS5-62-08 - Outdoor Normal Lighting  DB  - PS5-61-IG-0006</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>PS5-62-13</t>
+          <t>PS5-62-08</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>PS5-62-14 - Office Building Emergency L&amp;SP DB - PS5-05-IG-0002</t>
+          <t>PS5-62-09 - Outdoor Normal Lighting DB  - PS5-61-IG-0007</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>PS5-62-14</t>
+          <t>PS5-62-09</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>PS5-62-15 - Office Building Normal L&amp;SP DB - PS5-61-IG-0002</t>
+          <t>PS5-62-10 - CRO Generator Building Normal L&amp;SP DB  - PS5-61-IG-0015</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>PS5-62-15</t>
+          <t>PS5-62-10</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>PS5-62-16 - Guard Hut A Normal L&amp;SP DB - PS5-61-IG-0111</t>
+          <t>PS5-62-11 - CRO Generator Electrical Building Normal L&amp;SP DB  - PS5-61-IG-0016</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>PS5-62-16</t>
+          <t>PS5-62-11</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>PS5-62-17 - Guard Hut B Normal L&amp;SP DB - PS5-61-IG-0112</t>
+          <t>PS5-62-12 - EITS 33kV Bld. Emergency L&amp;SP DP - PS5-05-IG-0003</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>PS5-62-17</t>
+          <t>PS5-62-12</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>PS5-62-18 - Workshop &amp; Warehouse Normal L&amp;SP DB - PS5-61-IG-0004</t>
+          <t>PS5-62-13 - EITS 33kV Bld. Normal L&amp;SP DP - PS5-61-IG-0003</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>PS5-62-18</t>
+          <t>PS5-62-13</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>PS5-62-19 - Workshop &amp; Warehouse Emergency L&amp;SP DB - PS5-05-IG-0101</t>
+          <t>PS5-62-14 - Office Building Emergency L&amp;SP DB - PS5-05-IG-0002</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>PS5-62-19</t>
+          <t>PS5-62-14</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>PS5-62-20 - Office Building Normal L&amp;SP DB - PS5-61-IG-0010</t>
+          <t>PS5-62-15 - Office Building Normal L&amp;SP DB - PS5-61-IG-0002</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>PS5-62-20</t>
+          <t>PS5-62-15</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>PS5-63-01 - Electrical Earthing</t>
+          <t>PS5-62-16 - Guard Hut A Normal L&amp;SP DB - PS5-61-IG-0111</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>PS5-63-01</t>
+          <t>PS5-62-16</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>PS5-63-02 - Electrical Earthing - Office and Facilities building</t>
+          <t>PS5-62-17 - Guard Hut B Normal L&amp;SP DB - PS5-61-IG-0112</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>PS5-63-02</t>
+          <t>PS5-62-17</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>PS5-63-03 - Electrical Earthing - Generator Building</t>
+          <t>PS5-62-18 - Workshop &amp; Warehouse Normal L&amp;SP DB - PS5-61-IG-0004</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>PS5-63-03</t>
+          <t>PS5-62-18</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>PS5-63-04 - Electrical Earthing - EITS Building</t>
+          <t>PS5-62-19 - Workshop &amp; Warehouse Emergency L&amp;SP DB - PS5-05-IG-0101</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>PS5-63-04</t>
+          <t>PS5-62-19</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>PS5-63-05 - Electrical Earthing - Guard Hut A &amp; B</t>
+          <t>PS5-62-20 - Office Building Normal L&amp;SP DB - PS5-61-IG-0010</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>PS5-63-05</t>
+          <t>PS5-62-20</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>PS5-63-06 - Electrical Earthing - Guard House</t>
+          <t>PS5-63-01 - Electrical Earthing</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>PS5-63-06</t>
+          <t>PS5-63-01</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>PS5-63-07 - Electrical Earthing - Workshop &amp; Warehouse</t>
+          <t>PS5-63-02 - Electrical Earthing - Office and Facilities building</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>PS5-63-07</t>
+          <t>PS5-63-02</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>PS5-71-01 - CFO Storage Tank Feed Heater</t>
+          <t>PS5-63-03 - Electrical Earthing - Generator Building</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>PS5-71-01</t>
+          <t>PS5-63-03</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>PS5-71-02 - CFO Allocation Metering Package</t>
+          <t>PS5-63-04 - Electrical Earthing - EITS Building</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>PS5-71-02</t>
+          <t>PS5-63-04</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>PS5-71-03 - CFO Allocation Metering Package (UCP)</t>
+          <t>PS5-63-05 - Electrical Earthing - Guard Hut A &amp; B</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>PS5-71-03</t>
+          <t>PS5-63-05</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>PS5-71-04 - CFO Storage Tank</t>
+          <t>PS5-63-06 - Electrical Earthing - Guard House</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>PS5-71-04</t>
+          <t>PS5-63-06</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>PS5-71-05 - CFO Transfer Pump A/B</t>
+          <t>PS5-63-07 - Electrical Earthing - Workshop &amp; Warehouse</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>PS5-71-05</t>
+          <t>PS5-63-07</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>PS5-71-06 - Crude Fuel Separation Module</t>
+          <t>PS5-71-01 - CFO Storage Tank Feed Heater</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>PS5-71-06</t>
+          <t>PS5-71-01</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>PS5-71-07 - Crude Fuel Separation Module (UCP)</t>
+          <t>PS5-71-02 - CFO Allocation Metering Package</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>PS5-71-07</t>
+          <t>PS5-71-02</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>PS5-71-08 - CFO Pre-Pressure Modules</t>
+          <t>PS5-71-03 - CFO Allocation Metering Package (UCP)</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>PS5-71-08</t>
+          <t>PS5-71-03</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>PS5-71-09 - CFO Pre-Pressure Modules (UCP)</t>
+          <t>PS5-71-04 - CFO Storage Tank</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>PS5-71-09</t>
+          <t>PS5-71-04</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>PS5-71-12 - CFO Service Tank</t>
+          <t>PS5-71-05 - CFO Transfer Pump A/B</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>PS5-71-12</t>
+          <t>PS5-71-05</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>PS5-71-13 - CFO Service Pump A/B</t>
+          <t>PS5-71-06 - Crude Fuel Separation Module</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>PS5-71-13</t>
+          <t>PS5-71-06</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>PS5-71-14 - Diesel Fuel Transfer and Dispensing Station</t>
+          <t>PS5-71-07 - Crude Fuel Separation Module (UCP)</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>PS5-71-14</t>
+          <t>PS5-71-07</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>PS5-71-15 - Diesel Fuel Storage Tank</t>
+          <t>PS5-71-08 - CFO Pre-Pressure Modules</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>PS5-71-15</t>
+          <t>PS5-71-08</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>PS5-71-16 - Diesel Fuel Supply Pump A/B</t>
+          <t>PS5-71-09 - CFO Pre-Pressure Modules (UCP)</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>PS5-71-16</t>
+          <t>PS5-71-09</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>PS5-71-17 - Diesel Fuel Distribution Header</t>
+          <t>PS5-71-12 - CFO Service Tank</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>PS5-71-17</t>
+          <t>PS5-71-12</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>PS5-71-18 - Diesel Separator Module</t>
+          <t>PS5-71-13 - CFO Service Pump A/B</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>PS5-71-18</t>
+          <t>PS5-71-13</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>PS5-71-19 - Diesel Separator Module (UCP)</t>
+          <t>PS5-71-14 - Diesel Fuel Transfer and Dispensing Station</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>PS5-71-19</t>
+          <t>PS5-71-14</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>PS5-71-20 - Diesel Fuel Day Tank</t>
+          <t>PS5-71-15 - Diesel Fuel Storage Tank</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>PS5-71-20</t>
+          <t>PS5-71-15</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>PS5-71-21 - Diesel Transfer Pump A/B</t>
+          <t>PS5-71-16 - Diesel Fuel Supply Pump A/B</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>PS5-71-21</t>
+          <t>PS5-71-16</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>PS5-71-22 - Diesel Fuel Pre Pressure Module</t>
+          <t>PS5-71-17 - Diesel Fuel Distribution Header</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>PS5-71-22</t>
+          <t>PS5-71-17</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>PS5-71-23 - Diesel Fuel Pre Pressure Module (UCP)</t>
+          <t>PS5-71-18 - Diesel Separator Module</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>PS5-71-23</t>
+          <t>PS5-71-18</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>PS5-74-01 - N2 Generation Skid</t>
+          <t>PS5-71-19 - Diesel Separator Module (UCP)</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>PS5-74-01</t>
+          <t>PS5-71-19</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>PS5-74-02 - N2 Generation Skid (UCP)</t>
+          <t>PS5-71-20 - Diesel Fuel Day Tank</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>PS5-74-02</t>
+          <t>PS5-71-20</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>PS5-74-03 - Nitrogen Receiver</t>
+          <t>PS5-71-21 - Diesel Transfer Pump A/B</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>PS5-74-03</t>
+          <t>PS5-71-21</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>PS5-74-04 - Nitrogen Distribution Header</t>
+          <t>PS5-71-22 - Diesel Fuel Pre Pressure Module</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>PS5-74-04</t>
+          <t>PS5-71-22</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>PS5-75-01 - DRA Injection Package</t>
+          <t>PS5-71-23 - Diesel Fuel Pre Pressure Module (UCP)</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>PS5-75-01</t>
+          <t>PS5-71-23</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>PS5-75-02 - Biocide Injection Package</t>
+          <t>PS5-74-01 - N2 Generation Skid</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>PS5-75-02</t>
+          <t>PS5-74-01</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>PS5-75-03 - Corrosion Inhibitor Injection Package</t>
+          <t>PS5-74-02 - N2 Generation Skid (UCP)</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>PS5-75-03</t>
+          <t>PS5-74-02</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>PS5-78-01 - Lifting and handling equipment</t>
+          <t>PS5-74-03 - Nitrogen Receiver</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>PS5-78-01</t>
+          <t>PS5-74-03</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>PS5-79-01 - Electrical Heat Tracing Transformer/Distribution Board 1 (PS5-79-IG-0001)</t>
+          <t>PS5-74-04 - Nitrogen Distribution Header</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>PS5-79-01</t>
+          <t>PS5-74-04</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>PS5-79-02 - Electrical Heat Tracing Transformer/Distribution Board 2 (PS5-79-IG-0002)</t>
+          <t>PS5-75-01 - DRA Injection Package</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>PS5-79-02</t>
+          <t>PS5-75-01</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>PS5-79-03 - Electrical Heat Tracing Transformer/Distribution Board 3 (PS5-79-IG-0003)</t>
+          <t>PS5-75-02 - Biocide Injection Package</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>PS5-79-03</t>
+          <t>PS5-75-02</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>PS5-79-04 - Electrical Heat Tracing Transformer/Distribution Board 4 (PS5-79-IG-0004)</t>
+          <t>PS5-75-03 - Corrosion Inhibitor Injection Package</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>PS5-79-04</t>
+          <t>PS5-75-03</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>PS5-79-05 - Electrical Heat Tracing Transformer/Distribution Board 5 (PS5-79-IG-0005)</t>
+          <t>PS5-78-01 - Lifting and handling equipment</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>PS5-79-05</t>
+          <t>PS5-78-01</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>PS5-79-06 - Electrical Heat Tracing Transformer/Distribution Board 6 (PS5-79-IG-0006)</t>
+          <t>PS5-79-01 - Electrical Heat Tracing Transformer/Distribution Board 1 (PS5-79-IG-0001)</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>PS5-79-06</t>
+          <t>PS5-79-01</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>PS5-79-07 - Electrical Heat Tracing Transformer/Distribution Board 7 (PS5-79-IG-0007)</t>
+          <t>PS5-79-02 - Electrical Heat Tracing Transformer/Distribution Board 2 (PS5-79-IG-0002)</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>PS5-79-07</t>
+          <t>PS5-79-02</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>PS5-79-08 - Electrical Heat Tracing Transformer/Distribution Board 8 (PS5-79-IG-0008)</t>
+          <t>PS5-79-03 - Electrical Heat Tracing Transformer/Distribution Board 3 (PS5-79-IG-0003)</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>PS5-79-08</t>
+          <t>PS5-79-03</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>PS5-79-09 - Electrical Heat Tracing Transformer/Distribution Board 9 (PS5-79-IG-0009)</t>
+          <t>PS5-79-04 - Electrical Heat Tracing Transformer/Distribution Board 4 (PS5-79-IG-0004)</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>PS5-79-09</t>
+          <t>PS5-79-04</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>PS5-79-10 - Electrical Heat Tracing Transformer/Distribution Board 10 (PS5-79-IG-0010)</t>
+          <t>PS5-79-05 - Electrical Heat Tracing Transformer/Distribution Board 5 (PS5-79-IG-0005)</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>PS5-79-10</t>
+          <t>PS5-79-05</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>PS5-79-11 - Electrical Heat Tracing Transformer/Distribution Board 11 (PS5-79-IG-0011)</t>
+          <t>PS5-79-06 - Electrical Heat Tracing Transformer/Distribution Board 6 (PS5-79-IG-0006)</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>PS5-79-11</t>
+          <t>PS5-79-06</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>PS5-79-12 - Electrical Heat Tracing Transformer/Distribution Board 12 (PS5-79-IG-0012)</t>
+          <t>PS5-79-07 - Electrical Heat Tracing Transformer/Distribution Board 7 (PS5-79-IG-0007)</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>PS5-79-12</t>
+          <t>PS5-79-07</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>PS5-82-01 - Sanitary Sewage Collection</t>
+          <t>PS5-79-08 - Electrical Heat Tracing Transformer/Distribution Board 8 (PS5-79-IG-0008)</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>PS5-82-01</t>
+          <t>PS5-79-08</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>PS5-82-02 - Sewage Treatment Plant Package</t>
+          <t>PS5-79-09 - Electrical Heat Tracing Transformer/Distribution Board 9 (PS5-79-IG-0009)</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>PS5-82-02</t>
+          <t>PS5-79-09</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>PS5-82-03 - Sewage Treatment Plant Package (UCP)</t>
+          <t>PS5-79-10 - Electrical Heat Tracing Transformer/Distribution Board 10 (PS5-79-IG-0010)</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>PS5-82-03</t>
+          <t>PS5-79-10</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>PS5-82-04 - Sewage Treatment Plant Discharge Piping</t>
+          <t>PS5-79-11 - Electrical Heat Tracing Transformer/Distribution Board 11 (PS5-79-IG-0011)</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>PS5-82-04</t>
+          <t>PS5-79-11</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>PS5-82-05 - Office and Facilities building</t>
+          <t>PS5-79-12 - Electrical Heat Tracing Transformer/Distribution Board 12 (PS5-79-IG-0012)</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>PS5-82-05</t>
+          <t>PS5-79-12</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>PS5-82-06 - Guard House Building</t>
+          <t>PS5-82-01 - Sanitary Sewage Collection</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>PS5-82-06</t>
+          <t>PS5-82-01</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>PS5-82-07 - Guard Huts</t>
+          <t>PS5-82-02 - Sewage Treatment Plant Package</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>PS5-82-07</t>
+          <t>PS5-82-02</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>PS5-83-01 - EITS Building</t>
+          <t>PS5-82-03 - Sewage Treatment Plant Package (UCP)</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>PS5-83-01</t>
+          <t>PS5-82-03</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>PS5-84-01 - Generator Building</t>
+          <t>PS5-82-04 - Sewage Treatment Plant Discharge Piping</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>PS5-84-01</t>
+          <t>PS5-82-04</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>PS5-84-02 - Workshop &amp; Warehouse</t>
+          <t>PS5-82-05 - Office and Facilities building</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>PS5-84-02</t>
+          <t>PS5-82-05</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>PS5-84-03 - Shelters</t>
+          <t>PS5-82-06 - Guard House Building</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>PS5-84-03</t>
+          <t>PS5-82-06</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>PS5-86-01 - Shelters</t>
+          <t>PS5-82-07 - Guard Huts</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>PS5-86-01</t>
+          <t>PS5-82-07</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>PS5-91-01 - Multicore cables &amp; JB</t>
+          <t>PS5-83-01 - EITS Building</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>PS5-91-01</t>
+          <t>PS5-83-01</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>PS5-99-01 - Area Completion for Building area</t>
+          <t>PS5-84-01 - Generator Building</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>PS5-99-01</t>
+          <t>PS5-84-01</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>PS5-99-02 - Area Completion for Utility area</t>
+          <t>PS5-84-02 - Workshop &amp; Warehouse</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>PS5-99-02</t>
+          <t>PS5-84-02</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>PS5-99-03 - Area Completion for Power Distribution area</t>
+          <t>PS5-84-03 - Shelters</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>PS5-99-03</t>
+          <t>PS5-84-03</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>PS5-99-04 - Area Completion for Process area</t>
+          <t>PS5-86-01 - Shelters</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>PS5-99-04</t>
+          <t>PS5-86-01</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>PS5-99-05 - Area Completion for CFO area</t>
+          <t>PS5-91-01 - Multicore cables &amp; JB</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>PS5-99-05</t>
+          <t>PS5-91-01</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
+          <t>PS5-99-01 - Area Completion for Building area</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>PS5-99-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>PS5-99-02 - Area Completion for Utility area</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>PS5-99-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>PS5-99-03 - Area Completion for Power Distribution area</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>PS5-99-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>PS5-99-04 - Area Completion for Process area</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>PS5-99-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>PS5-99-05 - Area Completion for CFO area</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>PS5-99-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
           <t>PS5-99-06 - Area Completion for Power Generation area</t>
         </is>
       </c>
-      <c r="B290" t="inlineStr">
+      <c r="B295" t="inlineStr">
         <is>
           <t>PS5-99-06</t>
         </is>

--- a/EXCEL/7 - COMPLETE.xlsx
+++ b/EXCEL/7 - COMPLETE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7 · COMPLETE" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SIDMAP" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="7 · COMPLETE" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="SIDMAP" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'7 · COMPLETE'!$A$2:$G$67</definedName>

--- a/EXCEL/7 - COMPLETE.xlsx
+++ b/EXCEL/7 - COMPLETE.xlsx
@@ -116,14 +116,14 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="FFb35900"/>
+      <color rgb="FF0a58ca"/>
       <sz val="10"/>
+      <u val="single"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="FF0a58ca"/>
+      <color rgb="FFb35900"/>
       <sz val="10"/>
-      <u val="single"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -728,22 +728,22 @@
     <xf numFmtId="0" fontId="15" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -761,13 +761,13 @@
     <xf numFmtId="0" fontId="7" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1215,7 +1215,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="81" t="n">
+      <c r="A3" s="85" t="n">
         <v>1</v>
       </c>
       <c r="B3" s="83" t="inlineStr">
@@ -1246,7 +1246,7 @@
       <c r="G3" s="67" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="81" t="n">
+      <c r="A4" s="85" t="n">
         <v>2</v>
       </c>
       <c r="B4" s="83" t="inlineStr">
@@ -1273,7 +1273,7 @@
       <c r="G4" s="67" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="81" t="n">
+      <c r="A5" s="85" t="n">
         <v>3</v>
       </c>
       <c r="B5" s="83" t="inlineStr">
@@ -1300,7 +1300,7 @@
       <c r="G5" s="67" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="81" t="n">
+      <c r="A6" s="85" t="n">
         <v>4</v>
       </c>
       <c r="B6" s="83" t="inlineStr">
@@ -1327,7 +1327,7 @@
       <c r="G6" s="67" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="81" t="n">
+      <c r="A7" s="85" t="n">
         <v>5</v>
       </c>
       <c r="B7" s="83" t="inlineStr">
@@ -1358,7 +1358,7 @@
       <c r="G7" s="67" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="81" t="n">
+      <c r="A8" s="85" t="n">
         <v>6</v>
       </c>
       <c r="B8" s="83" t="inlineStr">
@@ -1389,7 +1389,7 @@
       <c r="G8" s="67" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="81" t="n">
+      <c r="A9" s="85" t="n">
         <v>7</v>
       </c>
       <c r="B9" s="83" t="inlineStr">
@@ -1420,7 +1420,7 @@
       <c r="G9" s="67" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="81" t="n">
+      <c r="A10" s="85" t="n">
         <v>8</v>
       </c>
       <c r="B10" s="83" t="inlineStr">
@@ -1447,7 +1447,7 @@
       <c r="G10" s="67" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="81" t="n">
+      <c r="A11" s="85" t="n">
         <v>9</v>
       </c>
       <c r="B11" s="83" t="inlineStr">
@@ -1478,7 +1478,7 @@
       <c r="G11" s="67" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="81" t="n">
+      <c r="A12" s="85" t="n">
         <v>10</v>
       </c>
       <c r="B12" s="83" t="inlineStr">
@@ -1509,7 +1509,7 @@
       <c r="G12" s="67" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="81" t="n">
+      <c r="A13" s="85" t="n">
         <v>11</v>
       </c>
       <c r="B13" s="83" t="inlineStr">
@@ -1540,7 +1540,7 @@
       <c r="G13" s="67" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="81" t="n">
+      <c r="A14" s="85" t="n">
         <v>12</v>
       </c>
       <c r="B14" s="83" t="inlineStr">
@@ -1571,7 +1571,7 @@
       <c r="G14" s="67" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="81" t="n">
+      <c r="A15" s="85" t="n">
         <v>13</v>
       </c>
       <c r="B15" s="83" t="inlineStr">
@@ -1602,7 +1602,7 @@
       <c r="G15" s="67" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="81" t="n">
+      <c r="A16" s="85" t="n">
         <v>14</v>
       </c>
       <c r="B16" s="83" t="inlineStr">
@@ -1625,7 +1625,7 @@
       <c r="G16" s="67" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="81" t="n">
+      <c r="A17" s="85" t="n">
         <v>15</v>
       </c>
       <c r="B17" s="83" t="inlineStr">
@@ -1652,7 +1652,7 @@
       <c r="G17" s="67" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="81" t="n">
+      <c r="A18" s="85" t="n">
         <v>16</v>
       </c>
       <c r="B18" s="83" t="inlineStr">
@@ -1683,7 +1683,7 @@
       <c r="G18" s="67" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="85" t="n">
+      <c r="A19" s="81" t="n">
         <v>17</v>
       </c>
       <c r="B19" s="83" t="inlineStr">
@@ -1714,7 +1714,7 @@
       <c r="G19" s="67" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="81" t="n">
+      <c r="A20" s="85" t="n">
         <v>18</v>
       </c>
       <c r="B20" s="83" t="inlineStr">
@@ -1745,7 +1745,7 @@
       <c r="G20" s="67" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="81" t="n">
+      <c r="A21" s="85" t="n">
         <v>19</v>
       </c>
       <c r="B21" s="83" t="inlineStr">
@@ -1776,7 +1776,7 @@
       <c r="G21" s="67" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="81" t="n">
+      <c r="A22" s="85" t="n">
         <v>20</v>
       </c>
       <c r="B22" s="83" t="inlineStr">
@@ -1807,7 +1807,7 @@
       <c r="G22" s="67" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="81" t="n">
+      <c r="A23" s="85" t="n">
         <v>21</v>
       </c>
       <c r="B23" s="83" t="inlineStr">
@@ -1834,7 +1834,7 @@
       <c r="G23" s="67" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="81" t="n">
+      <c r="A24" s="85" t="n">
         <v>22</v>
       </c>
       <c r="B24" s="83" t="inlineStr">
@@ -1865,7 +1865,7 @@
       <c r="G24" s="67" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="81" t="n">
+      <c r="A25" s="85" t="n">
         <v>23</v>
       </c>
       <c r="B25" s="83" t="inlineStr">
@@ -1896,7 +1896,7 @@
       <c r="G25" s="67" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="81" t="n">
+      <c r="A26" s="85" t="n">
         <v>24</v>
       </c>
       <c r="B26" s="83" t="inlineStr">
@@ -1927,7 +1927,7 @@
       <c r="G26" s="67" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="81" t="n">
+      <c r="A27" s="85" t="n">
         <v>25</v>
       </c>
       <c r="B27" s="83" t="inlineStr">
@@ -1958,7 +1958,7 @@
       <c r="G27" s="67" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="81" t="n">
+      <c r="A28" s="85" t="n">
         <v>26</v>
       </c>
       <c r="B28" s="83" t="inlineStr">
@@ -1989,7 +1989,7 @@
       <c r="G28" s="67" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="81" t="n">
+      <c r="A29" s="85" t="n">
         <v>27</v>
       </c>
       <c r="B29" s="83" t="inlineStr">
@@ -2020,7 +2020,7 @@
       <c r="G29" s="67" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="81" t="n">
+      <c r="A30" s="85" t="n">
         <v>28</v>
       </c>
       <c r="B30" s="83" t="inlineStr">
@@ -2051,7 +2051,7 @@
       <c r="G30" s="67" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="81" t="n">
+      <c r="A31" s="85" t="n">
         <v>29</v>
       </c>
       <c r="B31" s="83" t="inlineStr">
@@ -2082,7 +2082,7 @@
       <c r="G31" s="67" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="81" t="n">
+      <c r="A32" s="85" t="n">
         <v>30</v>
       </c>
       <c r="B32" s="83" t="inlineStr">
@@ -2113,7 +2113,7 @@
       <c r="G32" s="67" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="81" t="n">
+      <c r="A33" s="85" t="n">
         <v>31</v>
       </c>
       <c r="B33" s="83" t="inlineStr">
@@ -2144,7 +2144,7 @@
       <c r="G33" s="67" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="81" t="n">
+      <c r="A34" s="85" t="n">
         <v>32</v>
       </c>
       <c r="B34" s="83" t="inlineStr">
@@ -2175,7 +2175,7 @@
       <c r="G34" s="67" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="81" t="n">
+      <c r="A35" s="85" t="n">
         <v>33</v>
       </c>
       <c r="B35" s="83" t="inlineStr">
@@ -2206,7 +2206,7 @@
       <c r="G35" s="67" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="81" t="n">
+      <c r="A36" s="85" t="n">
         <v>34</v>
       </c>
       <c r="B36" s="83" t="inlineStr">
@@ -2237,7 +2237,7 @@
       <c r="G36" s="67" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="81" t="n">
+      <c r="A37" s="85" t="n">
         <v>35</v>
       </c>
       <c r="B37" s="83" t="inlineStr">
@@ -2268,7 +2268,7 @@
       <c r="G37" s="67" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="81" t="n">
+      <c r="A38" s="85" t="n">
         <v>36</v>
       </c>
       <c r="B38" s="83" t="inlineStr">
@@ -2299,7 +2299,7 @@
       <c r="G38" s="67" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="81" t="n">
+      <c r="A39" s="85" t="n">
         <v>37</v>
       </c>
       <c r="B39" s="83" t="inlineStr">
@@ -2330,7 +2330,7 @@
       <c r="G39" s="67" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="81" t="n">
+      <c r="A40" s="85" t="n">
         <v>38</v>
       </c>
       <c r="B40" s="83" t="inlineStr">
@@ -2361,7 +2361,7 @@
       <c r="G40" s="67" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="81" t="n">
+      <c r="A41" s="85" t="n">
         <v>39</v>
       </c>
       <c r="B41" s="83" t="inlineStr">
@@ -2392,7 +2392,7 @@
       <c r="G41" s="67" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="81" t="n">
+      <c r="A42" s="85" t="n">
         <v>40</v>
       </c>
       <c r="B42" s="83" t="inlineStr">
@@ -2423,7 +2423,7 @@
       <c r="G42" s="67" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="81" t="n">
+      <c r="A43" s="85" t="n">
         <v>41</v>
       </c>
       <c r="B43" s="83" t="inlineStr">
@@ -2450,7 +2450,7 @@
       <c r="G43" s="67" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="81" t="n">
+      <c r="A44" s="85" t="n">
         <v>42</v>
       </c>
       <c r="B44" s="83" t="inlineStr">
@@ -2481,7 +2481,7 @@
       <c r="G44" s="67" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="81" t="n">
+      <c r="A45" s="85" t="n">
         <v>43</v>
       </c>
       <c r="B45" s="83" t="inlineStr">
@@ -2508,7 +2508,7 @@
       <c r="G45" s="67" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="81" t="n">
+      <c r="A46" s="85" t="n">
         <v>44</v>
       </c>
       <c r="B46" s="83" t="inlineStr">
@@ -2535,7 +2535,7 @@
       <c r="G46" s="67" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="81" t="n">
+      <c r="A47" s="85" t="n">
         <v>45</v>
       </c>
       <c r="B47" s="83" t="inlineStr">
@@ -2562,7 +2562,7 @@
       <c r="G47" s="67" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="81" t="n">
+      <c r="A48" s="85" t="n">
         <v>46</v>
       </c>
       <c r="B48" s="83" t="inlineStr">
@@ -2589,7 +2589,7 @@
       <c r="G48" s="67" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="81" t="n">
+      <c r="A49" s="85" t="n">
         <v>47</v>
       </c>
       <c r="B49" s="83" t="inlineStr">
@@ -2620,7 +2620,7 @@
       <c r="G49" s="67" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="81" t="n">
+      <c r="A50" s="85" t="n">
         <v>48</v>
       </c>
       <c r="B50" s="83" t="inlineStr">
@@ -2651,7 +2651,7 @@
       <c r="G50" s="67" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="81" t="n">
+      <c r="A51" s="85" t="n">
         <v>49</v>
       </c>
       <c r="B51" s="83" t="inlineStr">
@@ -2682,7 +2682,7 @@
       <c r="G51" s="67" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="81" t="n">
+      <c r="A52" s="85" t="n">
         <v>50</v>
       </c>
       <c r="B52" s="83" t="inlineStr">
@@ -2713,7 +2713,7 @@
       <c r="G52" s="67" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="81" t="n">
+      <c r="A53" s="85" t="n">
         <v>51</v>
       </c>
       <c r="B53" s="83" t="inlineStr">
@@ -2744,7 +2744,7 @@
       <c r="G53" s="67" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="81" t="n">
+      <c r="A54" s="85" t="n">
         <v>52</v>
       </c>
       <c r="B54" s="83" t="inlineStr">
@@ -2775,7 +2775,7 @@
       <c r="G54" s="67" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="81" t="n">
+      <c r="A55" s="85" t="n">
         <v>53</v>
       </c>
       <c r="B55" s="83" t="inlineStr">
@@ -2806,7 +2806,7 @@
       <c r="G55" s="67" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="81" t="n">
+      <c r="A56" s="85" t="n">
         <v>54</v>
       </c>
       <c r="B56" s="83" t="inlineStr">
@@ -2837,7 +2837,7 @@
       <c r="G56" s="67" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="81" t="n">
+      <c r="A57" s="85" t="n">
         <v>55</v>
       </c>
       <c r="B57" s="83" t="inlineStr">
@@ -2868,7 +2868,7 @@
       <c r="G57" s="67" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="81" t="n">
+      <c r="A58" s="85" t="n">
         <v>56</v>
       </c>
       <c r="B58" s="83" t="inlineStr">
@@ -2899,7 +2899,7 @@
       <c r="G58" s="67" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="81" t="n">
+      <c r="A59" s="85" t="n">
         <v>57</v>
       </c>
       <c r="B59" s="83" t="inlineStr">
@@ -2930,7 +2930,7 @@
       <c r="G59" s="67" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="81" t="n">
+      <c r="A60" s="85" t="n">
         <v>58</v>
       </c>
       <c r="B60" s="83" t="inlineStr">
@@ -2953,7 +2953,7 @@
       <c r="G60" s="67" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="81" t="n">
+      <c r="A61" s="85" t="n">
         <v>59</v>
       </c>
       <c r="B61" s="83" t="inlineStr">
@@ -2984,7 +2984,7 @@
       <c r="G61" s="67" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="81" t="n">
+      <c r="A62" s="85" t="n">
         <v>60</v>
       </c>
       <c r="B62" s="83" t="inlineStr">
@@ -3015,7 +3015,7 @@
       <c r="G62" s="67" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="85" t="n">
+      <c r="A63" s="81" t="n">
         <v>61</v>
       </c>
       <c r="B63" s="83" t="inlineStr">
@@ -3046,7 +3046,7 @@
       <c r="G63" s="67" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="81" t="n">
+      <c r="A64" s="85" t="n">
         <v>62</v>
       </c>
       <c r="B64" s="83" t="inlineStr">
@@ -3077,7 +3077,7 @@
       <c r="G64" s="67" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="81" t="n">
+      <c r="A65" s="85" t="n">
         <v>63</v>
       </c>
       <c r="B65" s="83" t="inlineStr">
@@ -3104,7 +3104,7 @@
       <c r="G65" s="67" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="81" t="n">
+      <c r="A66" s="85" t="n">
         <v>64</v>
       </c>
       <c r="B66" s="83" t="inlineStr">
@@ -3131,7 +3131,7 @@
       <c r="G66" s="67" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="81" t="n">
+      <c r="A67" s="85" t="n">
         <v>65</v>
       </c>
       <c r="B67" s="83" t="inlineStr">
@@ -3243,7 +3243,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B295"/>
+  <dimension ref="A1:B293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3825,2962 +3825,2938 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PS5-08-01</t>
+          <t>PS5-08-01a - PAGA (Required for SU)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>PS5-08-01</t>
+          <t>PS5-08-01a</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PS5-08-01a - PAGA (Required for SU)</t>
+          <t>PS5-08-01b - PAGA (Not required for SU)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PS5-08-01a</t>
+          <t>PS5-08-01b</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PS5-08-01b - PAGA (Not required for SU)</t>
+          <t>PS5-08-03 - Telephone</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>PS5-08-01b</t>
+          <t>PS5-08-03</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>PS5-08-03 - Telephone</t>
+          <t>PS5-08-04 - Hotline</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PS5-08-03</t>
+          <t>PS5-08-04</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>PS5-08-04 - Hotline</t>
+          <t>PS5-08-07 - Multi-Channel Voice Recorder</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PS5-08-04</t>
+          <t>PS5-08-07</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>PS5-08-07 - Multi-Channel Voice Recorder</t>
+          <t>PS5-08-11 - Corporate LAN  (SIE)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PS5-08-07</t>
+          <t>PS5-08-11</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>PS5-08-11 - Corporate LAN  (SIE)</t>
+          <t>PS5-08-12 - Corporate Wireless LAN (SIE)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PS5-08-11</t>
+          <t>PS5-08-12</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>PS5-08-12 - Corporate Wireless LAN (SIE)</t>
+          <t>PS5-08-13 - Safety Data Network (SII SP3 SAF)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PS5-08-12</t>
+          <t>PS5-08-13</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>PS5-08-13 - Safety Data Network (SII SP3 SAF)</t>
+          <t>PS5-08-14 - Industrial Data Network (SII SP1)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PS5-08-13</t>
+          <t>PS5-08-14</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PS5-08-14 - Industrial Data Network (SII SP1)</t>
+          <t>PS5-08-15 - Security Data Network (SII SP3 SEC)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PS5-08-14</t>
+          <t>PS5-08-15</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PS5-08-15 - Security Data Network (SII SP3 SEC)</t>
+          <t>PS5-08-23 - VHF Trunk Radio System</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PS5-08-15</t>
+          <t>PS5-08-23</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PS5-08-23 - VHF Trunk Radio System</t>
+          <t>PS5-08-34 - Satphone</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PS5-08-23</t>
+          <t>PS5-08-34</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>PS5-08-34 - Satphone</t>
+          <t>PS5-08-35 - Optical Transport Network</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PS5-08-34</t>
+          <t>PS5-08-35</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>PS5-08-35 - Optical Transport Network</t>
+          <t>PS5-08-36 - Pipeline FO Cable &amp; EPRS</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>PS5-08-35</t>
+          <t>PS5-08-36</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>PS5-08-36 - Pipeline FO Cable &amp; EPRS</t>
+          <t>PS5-08-51 - Entertainment</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PS5-08-36</t>
+          <t>PS5-08-51</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>PS5-08-51 - Entertainment</t>
+          <t>PS5-08-52a - Process &amp; Security CCTV (Required for SU)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PS5-08-51</t>
+          <t>PS5-08-52a</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>PS5-08-52a - Process &amp; Security CCTV (Required for SU)</t>
+          <t>PS5-08-52b - Process &amp; Security CCTV (Not required for SU)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PS5-08-52a</t>
+          <t>PS5-08-52b</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>PS5-08-52b - Process &amp; Security CCTV (Not required for SU)</t>
+          <t>PS5-08-55 - Videoconference</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PS5-08-52b</t>
+          <t>PS5-08-55</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PS5-08-55 - Videoconference</t>
+          <t>PS5-08-61 - Meteocean</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PS5-08-55</t>
+          <t>PS5-08-61</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>PS5-08-61 - Meteocean</t>
+          <t>PS5-08-71 - Structured Cabling (CAT6)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PS5-08-61</t>
+          <t>PS5-08-71</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>PS5-08-71 - Structured Cabling (CAT6)</t>
+          <t>PS5-08-72 - Structured Cabling (FO)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PS5-08-71</t>
+          <t>PS5-08-72</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>PS5-08-72 - Structured Cabling (FO)</t>
+          <t>PS5-08-81 - Guard tour</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PS5-08-72</t>
+          <t>PS5-08-81</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>PS5-08-81 - Guard tour</t>
+          <t>PS5-08-82 - Key Management</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PS5-08-81</t>
+          <t>PS5-08-82</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>PS5-08-82 - Key Management</t>
+          <t>PS5-08-83 - Perimeter &amp; Pipeline intrusion detection system</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PS5-08-82</t>
+          <t>PS5-08-83</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>PS5-08-83 - Perimeter &amp; Pipeline intrusion detection system</t>
+          <t>PS5-08-85a - Access Control, POB &amp; e-Mustering (Required for SU)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>PS5-08-83</t>
+          <t>PS5-08-85a</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>PS5-08-85</t>
+          <t>PS5-08-85b - Access Control, POB &amp; e-Mustering (Not required for SU)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>PS5-08-85</t>
+          <t>PS5-08-85b</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>PS5-08-85a - Access Control, POB &amp; e-Mustering (Required for SU)</t>
+          <t>PS5-08-86 - Integrated Security Management System</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PS5-08-85a</t>
+          <t>PS5-08-86</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>PS5-08-85b - Access Control, POB &amp; e-Mustering (Not required for SU)</t>
+          <t>PS5-08-92 - Telecom Mast</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>PS5-08-85b</t>
+          <t>PS5-08-92</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>PS5-08-86 - Integrated Security Management System</t>
+          <t>PS5-08-93 - Telecom Monitoring System</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>PS5-08-86</t>
+          <t>PS5-08-93</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>PS5-08-92 - Telecom Mast</t>
+          <t>PS5-09-01 - HVAC for Office and Facilities building</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>PS5-08-92</t>
+          <t>PS5-09-01</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>PS5-08-93 - Telecom Monitoring System</t>
+          <t>PS5-09-02 - HVAC for Guard House</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>PS5-08-93</t>
+          <t>PS5-09-02</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>PS5-09-01 - HVAC for Office and Facilities building</t>
+          <t>PS5-09-03 - HVAC for Generator Building</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>PS5-09-01</t>
+          <t>PS5-09-03</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>PS5-09-02 - HVAC for Guard House</t>
+          <t>PS5-09-04 - HVAC for Workshop &amp; Warehouse</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>PS5-09-02</t>
+          <t>PS5-09-04</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>PS5-09-03 - HVAC for Generator Building</t>
+          <t>PS5-09-05 - HVAC for EITS Building</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>PS5-09-03</t>
+          <t>PS5-09-05</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>PS5-09-04 - HVAC for Workshop &amp; Warehouse</t>
+          <t>PS5-0H-01 - HIPPS</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>PS5-09-04</t>
+          <t>PS5-0H-01</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>PS5-09-05 - HVAC for EITS Building</t>
+          <t>PS5-25-01 - Export Pipeline Pig Receiver</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>PS5-09-05</t>
+          <t>PS5-25-01</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>PS5-0H-01 - HIPPS</t>
+          <t>PS5-25-02 - Crude Oil Export Pump A</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>PS5-0H-01</t>
+          <t>PS5-25-02</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>PS5-25-01 - Export Pipeline Pig Receiver</t>
+          <t>PS5-25-03 - Crude Oil Export Pump B</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>PS5-25-01</t>
+          <t>PS5-25-03</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>PS5-25-02 - Crude Oil Export Pump A</t>
+          <t>PS5-25-04 - Crude Oil Export Pump C</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>PS5-25-02</t>
+          <t>PS5-25-04</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>PS5-25-03 - Crude Oil Export Pump B</t>
+          <t>PS5-25-05 - Crude Oil Export Pumps Bypass</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>PS5-25-03</t>
+          <t>PS5-25-05</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>PS5-25-04 - Crude Oil Export Pump C</t>
+          <t>PS5-25-06 - Crude Oil Export Pumps Discharge</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>PS5-25-04</t>
+          <t>PS5-25-06</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>PS5-25-05 - Crude Oil Export Pumps Bypass</t>
+          <t>PS5-25-07 - Export Pipeline Pig Launcher</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>PS5-25-05</t>
+          <t>PS5-25-07</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>PS5-25-06 - Crude Oil Export Pumps Discharge</t>
+          <t>PS5-28-01 - Closed Drain Header 1</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>PS5-25-06</t>
+          <t>PS5-28-01</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>PS5-25-07 - Export Pipeline Pig Launcher</t>
+          <t>PS5-28-02 - Closed Drain Header 2</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>PS5-25-07</t>
+          <t>PS5-28-02</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>PS5-28-01 - Closed Drain Header 1</t>
+          <t>PS5-28-03 - Closed Drain Drum and Pump 01</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>PS5-28-01</t>
+          <t>PS5-28-03</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>PS5-28-02 - Closed Drain Header 2</t>
+          <t>PS5-28-04 - Closed Drain Drum and Pump 02</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>PS5-28-02</t>
+          <t>PS5-28-04</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>PS5-28-03 - Closed Drain Drum and Pump 01</t>
+          <t>PS5-28-05 - HP Relief Header</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>PS5-28-03</t>
+          <t>PS5-28-05</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>PS5-28-04 - Closed Drain Drum and Pump 02</t>
+          <t>PS5-28-06 - Relief Drum and Pump</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>PS5-28-04</t>
+          <t>PS5-28-06</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>PS5-28-05 - HP Relief Header</t>
+          <t>PS5-28-07 - Open Drains (OD2)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>PS5-28-05</t>
+          <t>PS5-28-07</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>PS5-28-06 - Relief Drum and Pump</t>
+          <t>PS5-28-08 - Open Drain Sump and Pumps</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>PS5-28-06</t>
+          <t>PS5-28-08</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>PS5-28-07 - Open Drains (OD2)</t>
+          <t>PS5-28-09 - Observation Basin</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>PS5-28-07</t>
+          <t>PS5-28-09</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>PS5-28-08 - Open Drain Sump and Pumps</t>
+          <t>PS5-28-10 - Oil Skimmer Package</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>PS5-28-08</t>
+          <t>PS5-28-10</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>PS5-28-09 - Observation Basin</t>
+          <t>PS5-28-11 - Open Drain Interceptor</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>PS5-28-09</t>
+          <t>PS5-28-11</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>PS5-28-10 - Oil Skimmer Package</t>
+          <t>PS5-28-12 - Open Drains (OD3)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>PS5-28-10</t>
+          <t>PS5-28-12</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>PS5-28-11 - Open Drain Interceptor</t>
+          <t>PS5-28-13 - Seal Oil Drain Drum &amp; Pump A</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>PS5-28-11</t>
+          <t>PS5-28-13</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>PS5-28-12 - Open Drains (OD3)</t>
+          <t>PS5-28-14 - Seal Oil Drain Drum &amp; Pump B</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>PS5-28-12</t>
+          <t>PS5-28-14</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>PS5-28-13 - Seal Oil Drain Drum &amp; Pump A</t>
+          <t>PS5-28-15 - Seal Oil Drain Drum &amp; Pump C</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>PS5-28-13</t>
+          <t>PS5-28-15</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>PS5-28-14 - Seal Oil Drain Drum &amp; Pump B</t>
+          <t>PS5-28-16 - LP Relief Header</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>PS5-28-14</t>
+          <t>PS5-28-16</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>PS5-28-15 - Seal Oil Drain Drum &amp; Pump C</t>
+          <t>PS5-28-17 - Reinjection Pump</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>PS5-28-15</t>
+          <t>PS5-28-17</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>PS5-28-16 - LP Relief Header</t>
+          <t>PS5-50-01 - Water Well Submersible Pumps (3100)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>PS5-28-16</t>
+          <t>PS5-50-01</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>PS5-28-17 - Reinjection Pump</t>
+          <t>PS5-50-02 - Water Well Submersible Pumps (3200)</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>PS5-28-17</t>
+          <t>PS5-50-02</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>PS5-50-01 - Water Well Submersible Pumps (3100)</t>
+          <t>PS5-50-03 - Water Pre-Treatment Package</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>PS5-50-01</t>
+          <t>PS5-50-03</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>PS5-50-02 - Water Well Submersible Pumps (3200)</t>
+          <t>PS5-53-01 - Utility Water / Storage Tank</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>PS5-50-02</t>
+          <t>PS5-53-01</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>PS5-50-03 - Water Pre-Treatment Package</t>
+          <t>PS5-53-02 - Water Distribution Pump A/B</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>PS5-50-03</t>
+          <t>PS5-53-02</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>PS5-53-01 - Utility Water / Storage Tank</t>
+          <t>PS5-53-03 - Water Softener Package</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>PS5-53-01</t>
+          <t>PS5-53-03</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>PS5-53-02 - Water Distribution Pump A/B</t>
+          <t>PS5-53-04 - Water Treatment Purification Package</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>PS5-53-02</t>
+          <t>PS5-53-04</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>PS5-53-03 - Water Softener Package</t>
+          <t>PS5-53-05 - Water Distribution Header</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>PS5-53-03</t>
+          <t>PS5-53-05</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>PS5-53-04 - Water Treatment Purification Package</t>
+          <t>PS5-53-06 - Water Distribution Consumers</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>PS5-53-04</t>
+          <t>PS5-53-06</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>PS5-53-05 - Water Distribution Header</t>
+          <t>PS5-60-01 - Power Generation Package A</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>PS5-53-05</t>
+          <t>PS5-60-01</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>PS5-53-06 - Water Distribution Consumers</t>
+          <t>PS5-60-02 - Power Gen Package A (UCP)</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>PS5-53-06</t>
+          <t>PS5-60-02</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>PS5-60-01 - Power Generation Package A</t>
+          <t>PS5-60-03 - Power Gen Package A Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>PS5-60-01</t>
+          <t>PS5-60-03</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>PS5-60-02 - Power Gen Package A (UCP)</t>
+          <t>PS5-60-04 - Power Generation Package B</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>PS5-60-02</t>
+          <t>PS5-60-04</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>PS5-60-03 - Power Gen Package A Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-60-05 - Power Gen Package B (UCP)</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>PS5-60-03</t>
+          <t>PS5-60-05</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>PS5-60-04 - Power Generation Package B</t>
+          <t>PS5-60-06 - Power Gen Package B Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>PS5-60-04</t>
+          <t>PS5-60-06</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>PS5-60-05 - Power Gen Package B (UCP)</t>
+          <t>PS5-60-07 - Power Generation Package C</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>PS5-60-05</t>
+          <t>PS5-60-07</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>PS5-60-06 - Power Gen Package B Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-60-08 - Power Gen Package C (UCP)</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>PS5-60-06</t>
+          <t>PS5-60-08</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>PS5-60-07 - Power Generation Package C</t>
+          <t>PS5-60-09 - Power Gen Package C Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>PS5-60-07</t>
+          <t>PS5-60-09</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>PS5-60-08 - Power Gen Package C (UCP)</t>
+          <t>PS5-60-10 - Power Generation Package D</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>PS5-60-08</t>
+          <t>PS5-60-10</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>PS5-60-09 - Power Gen Package C Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-60-11 - Power Gen Package D (UCP)</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>PS5-60-09</t>
+          <t>PS5-60-11</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>PS5-60-10 - Power Generation Package D</t>
+          <t>PS5-60-12 - Power Gen Package D Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>PS5-60-10</t>
+          <t>PS5-60-12</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>PS5-60-11 - Power Gen Package D (UCP)</t>
+          <t>PS5-60-13 - Power Generation Package E</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PS5-60-11</t>
+          <t>PS5-60-13</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>PS5-60-12 - Power Gen Package D Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-60-14 - Power Gen Package E (UCP)</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PS5-60-12</t>
+          <t>PS5-60-14</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>PS5-60-13 - Power Generation Package E</t>
+          <t>PS5-60-15 - Power Gen Package E Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PS5-60-13</t>
+          <t>PS5-60-15</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>PS5-60-14 - Power Gen Package E (UCP)</t>
+          <t>PS5-60-16 - Power Generation Package F</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PS5-60-14</t>
+          <t>PS5-60-16</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>PS5-60-15 - Power Gen Package E Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-60-17 - Power Gen Package F (UCP)</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PS5-60-15</t>
+          <t>PS5-60-17</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>PS5-60-16 - Power Generation Package F</t>
+          <t>PS5-60-18 - Power Gen Package F Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PS5-60-16</t>
+          <t>PS5-60-18</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>PS5-60-17 - Power Gen Package F (UCP)</t>
+          <t>PS5-60-19 - Power Generation Package G</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PS5-60-17</t>
+          <t>PS5-60-19</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>PS5-60-18 - Power Gen Package F Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-60-20 - Power Gen Package G (UCP)</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>PS5-60-18</t>
+          <t>PS5-60-20</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>PS5-60-19 - Power Generation Package G</t>
+          <t>PS5-60-21 - Power Gen Package G Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>PS5-60-19</t>
+          <t>PS5-60-21</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>PS5-60-20 - Power Gen Package G (UCP)</t>
+          <t>PS5-60-22 - Power Gen Master UCP</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>PS5-60-20</t>
+          <t>PS5-60-22</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>PS5-60-21 - Power Gen Package G Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-60-23 - Instrument Air Distribution lines</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>PS5-60-21</t>
+          <t>PS5-60-23</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>PS5-60-22 - Power Gen Master UCP</t>
+          <t>PS5-60-24 - Cooling Water Tank &amp; Pump</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>PS5-60-22</t>
+          <t>PS5-60-24</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>PS5-60-23 - Instrument Air Distribution lines</t>
+          <t>PS5-60-25 - Cooling Water Maintenance Tank &amp; Return Pump</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>PS5-60-23</t>
+          <t>PS5-60-25</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>PS5-60-24 - Cooling Water Tank &amp; Pump</t>
+          <t>PS5-60-26 - Instrument Air Compressor Skid</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>PS5-60-24</t>
+          <t>PS5-60-26</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>PS5-60-25 - Cooling Water Maintenance Tank &amp; Return Pump</t>
+          <t>PS5-60-27 - Compressed Air Starting Skid</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>PS5-60-25</t>
+          <t>PS5-60-27</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>PS5-60-26 - Instrument Air Compressor Skid</t>
+          <t>PS5-60-28 - Air Receiver A &amp; Air Regulator A</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>PS5-60-26</t>
+          <t>PS5-60-28</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>PS5-60-27 - Compressed Air Starting Skid</t>
+          <t>PS5-60-29 - Air Receiver B &amp; Air Regulator B</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>PS5-60-27</t>
+          <t>PS5-60-29</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>PS5-60-28 - Air Receiver A &amp; Air Regulator A</t>
+          <t>PS5-60-30 - Air Receiver C &amp; Air Regulator C</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>PS5-60-28</t>
+          <t>PS5-60-30</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>PS5-60-29 - Air Receiver B &amp; Air Regulator B</t>
+          <t>PS5-60-31 - Air Receiver D &amp; Air Regulator D</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>PS5-60-29</t>
+          <t>PS5-60-31</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>PS5-60-30 - Air Receiver C &amp; Air Regulator C</t>
+          <t>PS5-60-32 - Air Receiver E &amp; Air Regulator E</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>PS5-60-30</t>
+          <t>PS5-60-32</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>PS5-60-31 - Air Receiver D &amp; Air Regulator D</t>
+          <t>PS5-60-33 - Air Receiver F &amp; Air Regulator F</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>PS5-60-31</t>
+          <t>PS5-60-33</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>PS5-60-32 - Air Receiver E &amp; Air Regulator E</t>
+          <t>PS5-60-34 - Air Receiver G &amp; Air Regulator G</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>PS5-60-32</t>
+          <t>PS5-60-34</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>PS5-60-33 - Air Receiver F &amp; Air Regulator F</t>
+          <t>PS5-60-35 - Injector Tip Cooling Module A</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>PS5-60-33</t>
+          <t>PS5-60-35</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>PS5-60-34 - Air Receiver G &amp; Air Regulator G</t>
+          <t>PS5-60-36 - Injector Tip Cooling Module B</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>PS5-60-34</t>
+          <t>PS5-60-36</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>PS5-60-35 - Injector Tip Cooling Module A</t>
+          <t>PS5-60-37 - Injector Tip Cooling Module C</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>PS5-60-35</t>
+          <t>PS5-60-37</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>PS5-60-36 - Injector Tip Cooling Module B</t>
+          <t>PS5-60-38 - Injector Tip Cooling Module D</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>PS5-60-36</t>
+          <t>PS5-60-38</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>PS5-60-37 - Injector Tip Cooling Module C</t>
+          <t>PS5-60-39 - Injector Tip Cooling Module E</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>PS5-60-37</t>
+          <t>PS5-60-39</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>PS5-60-38 - Injector Tip Cooling Module D</t>
+          <t>PS5-60-40 - Injector Tip Cooling Module F</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>PS5-60-38</t>
+          <t>PS5-60-40</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>PS5-60-39 - Injector Tip Cooling Module E</t>
+          <t>PS5-60-41 - Injector Tip Cooling Module G</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>PS5-60-39</t>
+          <t>PS5-60-41</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>PS5-60-40 - Injector Tip Cooling Module F</t>
+          <t>PS5-60-42 - Oil Mist Separator Skid PS5-60-VS-9100A</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>PS5-60-40</t>
+          <t>PS5-60-42</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>PS5-60-41 - Injector Tip Cooling Module G</t>
+          <t>PS5-60-43 - Oil Mist Separator Skid PS5-60-VS-9100B</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>PS5-60-41</t>
+          <t>PS5-60-43</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>PS5-60-42 - Oil Mist Separator Skid PS5-60-VS-9100A</t>
+          <t>PS5-60-44 - Oil Mist Separator Skid PS5-60-VS-9100C</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>PS5-60-42</t>
+          <t>PS5-60-44</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>PS5-60-43 - Oil Mist Separator Skid PS5-60-VS-9100B</t>
+          <t>PS5-60-45 - Oil Mist Separator Skid PS5-60-VS-9100D</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>PS5-60-43</t>
+          <t>PS5-60-45</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>PS5-60-44 - Oil Mist Separator Skid PS5-60-VS-9100C</t>
+          <t>PS5-60-46 - Oil Mist Separator Skid PS5-60-VS-9100E</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>PS5-60-44</t>
+          <t>PS5-60-46</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>PS5-60-45 - Oil Mist Separator Skid PS5-60-VS-9100D</t>
+          <t>PS5-60-47 - Oil Mist Separator Skid PS5-60-VS-9100F</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>PS5-60-45</t>
+          <t>PS5-60-47</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>PS5-60-46 - Oil Mist Separator Skid PS5-60-VS-9100E</t>
+          <t>PS5-60-48 - Oil Mist Separator Skid PS5-60-VS-9100G</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>PS5-60-46</t>
+          <t>PS5-60-48</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>PS5-60-47 - Oil Mist Separator Skid PS5-60-VS-9100F</t>
+          <t>PS5-60-49 - Lube Oil Separator Module PS5-60-UO-81100A</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>PS5-60-47</t>
+          <t>PS5-60-49</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>PS5-60-48 - Oil Mist Separator Skid PS5-60-VS-9100G</t>
+          <t>PS5-60-50 - Lube Oil Separator Module PS5-60-UO-81100B</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>PS5-60-48</t>
+          <t>PS5-60-50</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>PS5-60-49 - Lube Oil Separator Module PS5-60-UO-81100A</t>
+          <t>PS5-60-51 - Lube Oil Separator Module PS5-60-UO-81100C</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>PS5-60-49</t>
+          <t>PS5-60-51</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>PS5-60-50 - Lube Oil Separator Module PS5-60-UO-81100B</t>
+          <t>PS5-60-52 - Lube Oil Separator Module PS5-60-UO-81100D</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>PS5-60-50</t>
+          <t>PS5-60-52</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>PS5-60-51 - Lube Oil Separator Module PS5-60-UO-81100C</t>
+          <t>PS5-60-53 - Lube Oil Separator Module PS5-60-UO-81100E</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>PS5-60-51</t>
+          <t>PS5-60-53</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>PS5-60-52 - Lube Oil Separator Module PS5-60-UO-81100D</t>
+          <t>PS5-60-54 - Lube Oil Separator Module PS5-60-UO-81100F</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>PS5-60-52</t>
+          <t>PS5-60-54</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>PS5-60-53 - Lube Oil Separator Module PS5-60-UO-81100E</t>
+          <t>PS5-60-55 - Lube Oil Separator Module PS5-60-UO-81100G</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>PS5-60-53</t>
+          <t>PS5-60-55</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>PS5-60-54 - Lube Oil Separator Module PS5-60-UO-81100F</t>
+          <t>PS5-60-56 - Fuel Conditioning Module PS5-60-UZ-8900A</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>PS5-60-54</t>
+          <t>PS5-60-56</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>PS5-60-55 - Lube Oil Separator Module PS5-60-UO-81100G</t>
+          <t>PS5-60-57 - Fuel Conditioning Module PS5-60-UZ-8900A (UCP)</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>PS5-60-55</t>
+          <t>PS5-60-57</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>PS5-60-56 - Fuel Conditioning Module PS5-60-UZ-8900A</t>
+          <t>PS5-60-58 - Fuel Conditioning Module PS5-60-UZ-8900B</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>PS5-60-56</t>
+          <t>PS5-60-58</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>PS5-60-57 - Fuel Conditioning Module PS5-60-UZ-8900A (UCP)</t>
+          <t>PS5-60-59 - Fuel Conditioning Module PS5-60-UZ-8900B (UCP)</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>PS5-60-57</t>
+          <t>PS5-60-59</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>PS5-60-58 - Fuel Conditioning Module PS5-60-UZ-8900B</t>
+          <t>PS5-60-60 - Fuel Conditioning Module PS5-60-UZ-8900C</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>PS5-60-58</t>
+          <t>PS5-60-60</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>PS5-60-59 - Fuel Conditioning Module PS5-60-UZ-8900B (UCP)</t>
+          <t>PS5-60-61 - Fuel Conditioning Module PS5-60-UZ-8900C (UCP)</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>PS5-60-59</t>
+          <t>PS5-60-61</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>PS5-60-60 - Fuel Conditioning Module PS5-60-UZ-8900C</t>
+          <t>PS5-60-62 - Fuel Conditioning Module PS5-60-UZ-8900D</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>PS5-60-60</t>
+          <t>PS5-60-62</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>PS5-60-61 - Fuel Conditioning Module PS5-60-UZ-8900C (UCP)</t>
+          <t>PS5-60-63 - Fuel Conditioning Module PS5-60-UZ-8900D (UCP)</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>PS5-60-61</t>
+          <t>PS5-60-63</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>PS5-60-62 - Fuel Conditioning Module PS5-60-UZ-8900D</t>
+          <t>PS5-60-64 - Fuel Conditioning Module PS5-60-UZ-8900E</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>PS5-60-62</t>
+          <t>PS5-60-64</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>PS5-60-63 - Fuel Conditioning Module PS5-60-UZ-8900D (UCP)</t>
+          <t>PS5-60-65 - Fuel Conditioning Module PS5-60-UZ-8900E (UCP)</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>PS5-60-63</t>
+          <t>PS5-60-65</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>PS5-60-64 - Fuel Conditioning Module PS5-60-UZ-8900E</t>
+          <t>PS5-60-66 - Fuel Conditioning Module PS5-60-UZ-8900F</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>PS5-60-64</t>
+          <t>PS5-60-66</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>PS5-60-65 - Fuel Conditioning Module PS5-60-UZ-8900E (UCP)</t>
+          <t>PS5-60-67 - Fuel Conditioning Module PS5-60-UZ-8900F (UCP)</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>PS5-60-65</t>
+          <t>PS5-60-67</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>PS5-60-66 - Fuel Conditioning Module PS5-60-UZ-8900F</t>
+          <t>PS5-60-68 - Fuel Conditioning Module PS5-60-UZ-8900G</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>PS5-60-66</t>
+          <t>PS5-60-68</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>PS5-60-67 - Fuel Conditioning Module PS5-60-UZ-8900F (UCP)</t>
+          <t>PS5-60-69 - Fuel Conditioning Module PS5-60-UZ-8900G (UCP)</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>PS5-60-67</t>
+          <t>PS5-60-69</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>PS5-60-68 - Fuel Conditioning Module PS5-60-UZ-8900G</t>
+          <t>PS5-60-70 - Engine A Cooling system</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>PS5-60-68</t>
+          <t>PS5-60-70</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>PS5-60-69 - Fuel Conditioning Module PS5-60-UZ-8900G (UCP)</t>
+          <t>PS5-60-71 - Engine B Cooling system</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>PS5-60-69</t>
+          <t>PS5-60-71</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>PS5-60-70 - Engine A Cooling system</t>
+          <t>PS5-60-72 - Engine C Cooling system</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>PS5-60-70</t>
+          <t>PS5-60-72</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>PS5-60-71 - Engine B Cooling system</t>
+          <t>PS5-60-73 - Engine D Cooling system</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>PS5-60-71</t>
+          <t>PS5-60-73</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>PS5-60-72 - Engine C Cooling system</t>
+          <t>PS5-60-74 - Engine E Cooling system</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>PS5-60-72</t>
+          <t>PS5-60-74</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>PS5-60-73 - Engine D Cooling system</t>
+          <t>PS5-60-75 - Engine F Cooling system</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>PS5-60-73</t>
+          <t>PS5-60-75</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>PS5-60-74 - Engine E Cooling system</t>
+          <t>PS5-60-76 - Engine G Cooling system</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>PS5-60-74</t>
+          <t>PS5-60-76</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>PS5-60-75 - Engine F Cooling system</t>
+          <t>PS5-61-01 - 33kV Switchboard EITS Building (PS5-61-IJ-0001)</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>PS5-60-75</t>
+          <t>PS5-61-01</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>PS5-60-76 - Engine G Cooling system</t>
+          <t>PS5-61-02 - 6.6kV Switchboard and Transformer LLHT North - EITS Building (PS5-61-IJ-0010)</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>PS5-60-76</t>
+          <t>PS5-61-02</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>PS5-61-01 - 33kV Switchboard EITS Building (PS5-61-IJ-0001)</t>
+          <t>PS5-61-03 - 6.6kV Switchboard and Transformer LLHT South - EITS Building (PS5-61-IJ-0011)</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>PS5-61-01</t>
+          <t>PS5-61-03</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>PS5-61-02 - 6.6kV Switchboard and Transformer LLHT North - EITS Building (PS5-61-IJ-0010)</t>
+          <t>PS5-61-04 - 0.4kV Switchboard Office &amp; Facilities Building (PS5-61-IK-0005)</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>PS5-61-02</t>
+          <t>PS5-61-04</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>PS5-61-03 - 6.6kV Switchboard and Transformer LLHT South - EITS Building (PS5-61-IJ-0011)</t>
+          <t>PS5-61-05 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0003)</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>PS5-61-03</t>
+          <t>PS5-61-05</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>PS5-61-04 - 0.4kV Switchboard Office &amp; Facilities Building (PS5-61-IK-0005)</t>
+          <t>PS5-61-06 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0006)</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>PS5-61-04</t>
+          <t>PS5-61-06</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>PS5-61-05 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0003)</t>
+          <t>PS5-61-07 - 0.4kV Switchboard EITS Building (PS5-61-IK-0001)</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>PS5-61-05</t>
+          <t>PS5-61-07</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>PS5-61-06 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0006)</t>
+          <t>PS5-61-08 - Electrical Control System</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>PS5-61-06</t>
+          <t>PS5-61-08</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>PS5-61-07 - 0.4kV Switchboard EITS Building (PS5-61-IK-0001)</t>
+          <t>PS5-61-09 - Outdoor Power Distribution Board - PS5-61-IG-0014</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>PS5-61-07</t>
+          <t>PS5-61-09</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>PS5-61-08 - Electrical Control System</t>
+          <t>PS5-61-10 - Outdoor Valves Distribution Board - PS5-61-IG-0042</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>PS5-61-08</t>
+          <t>PS5-61-10</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>PS5-61-09 - Outdoor Power Distribution Board - PS5-61-IG-0014</t>
+          <t>PS5-61-11 - Outdoor Valves Distribution Board - PS5-61-IG-0043</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>PS5-61-09</t>
+          <t>PS5-61-11</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>PS5-61-10 - Outdoor Valves Distribution Board - PS5-61-IG-0042</t>
+          <t>PS5-61-12 - EITS 33kV Bld. Normal Auxiliary DP - PS5-61-IG-0008</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>PS5-61-10</t>
+          <t>PS5-61-12</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>PS5-61-11 - Outdoor Valves Distribution Board - PS5-61-IG-0043</t>
+          <t>PS5-61-13 - Power Distribution Board Office Building - PS5-61-IG-0020</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>PS5-61-11</t>
+          <t>PS5-61-13</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>PS5-61-12 - EITS 33kV Bld. Normal Auxiliary DP - PS5-61-IG-0008</t>
+          <t>PS5-61-14 - Power Distribution Board Workshop &amp; Warehouse - PS5-61-IG-0009</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>PS5-61-12</t>
+          <t>PS5-61-14</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>PS5-61-13 - Power Distribution Board Office Building - PS5-61-IG-0020</t>
+          <t>PS5-62-01 - Lighting Control Panel - PS5-62-IE-0001</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>PS5-61-13</t>
+          <t>PS5-62-01</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>PS5-61-14 - Power Distribution Board Workshop &amp; Warehouse - PS5-61-IG-0009</t>
+          <t>PS5-62-02 - Lighting Control Panel - PS5-62-IE-0002</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>PS5-61-14</t>
+          <t>PS5-62-02</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>PS5-62-01 - Lighting Control Panel - PS5-62-IE-0001</t>
+          <t>PS5-62-03 - Outdoor Emergency Lighting DB  - PS5-05-IG-0004</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>PS5-62-01</t>
+          <t>PS5-62-03</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>PS5-62-02 - Lighting Control Panel - PS5-62-IE-0002</t>
+          <t>PS5-62-04 - Outdoor Emergency Lighting DB  - PS5-05-IG-0006</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>PS5-62-02</t>
+          <t>PS5-62-04</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>PS5-62-03 - Outdoor Emergency Lighting DB  - PS5-05-IG-0004</t>
+          <t>PS5-62-05 - Guard House Emergency L&amp;SP DB  - PS5-05-IG-0007</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>PS5-62-03</t>
+          <t>PS5-62-05</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>PS5-62-04 - Outdoor Emergency Lighting DB  - PS5-05-IG-0006</t>
+          <t>PS5-62-06 - CRO Generator Building Emergency Lighting DB  - PS5-05-IG-0025</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>PS5-62-04</t>
+          <t>PS5-62-06</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>PS5-62-05 - Guard House Emergency L&amp;SP DB  - PS5-05-IG-0007</t>
+          <t>PS5-62-07 - CRO Generator Electrical Building Emergency Lighting DB  - PS5-05-IG-0026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>PS5-62-05</t>
+          <t>PS5-62-07</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>PS5-62-06 - CRO Generator Building Emergency Lighting DB  - PS5-05-IG-0025</t>
+          <t>PS5-62-08 - Outdoor Normal Lighting  DB  - PS5-61-IG-0006</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>PS5-62-06</t>
+          <t>PS5-62-08</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>PS5-62-07 - CRO Generator Electrical Building Emergency Lighting DB  - PS5-05-IG-0026</t>
+          <t>PS5-62-09 - Outdoor Normal Lighting DB  - PS5-61-IG-0007</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>PS5-62-07</t>
+          <t>PS5-62-09</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>PS5-62-08 - Outdoor Normal Lighting  DB  - PS5-61-IG-0006</t>
+          <t>PS5-62-10 - CRO Generator Building Normal L&amp;SP DB  - PS5-61-IG-0015</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>PS5-62-08</t>
+          <t>PS5-62-10</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>PS5-62-09 - Outdoor Normal Lighting DB  - PS5-61-IG-0007</t>
+          <t>PS5-62-11 - CRO Generator Electrical Building Normal L&amp;SP DB  - PS5-61-IG-0016</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>PS5-62-09</t>
+          <t>PS5-62-11</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>PS5-62-10 - CRO Generator Building Normal L&amp;SP DB  - PS5-61-IG-0015</t>
+          <t>PS5-62-12 - EITS 33kV Bld. Emergency L&amp;SP DP - PS5-05-IG-0003</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>PS5-62-10</t>
+          <t>PS5-62-12</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>PS5-62-11 - CRO Generator Electrical Building Normal L&amp;SP DB  - PS5-61-IG-0016</t>
+          <t>PS5-62-13 - EITS 33kV Bld. Normal L&amp;SP DP - PS5-61-IG-0003</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>PS5-62-11</t>
+          <t>PS5-62-13</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>PS5-62-12 - EITS 33kV Bld. Emergency L&amp;SP DP - PS5-05-IG-0003</t>
+          <t>PS5-62-14 - Office Building Emergency L&amp;SP DB - PS5-05-IG-0002</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>PS5-62-12</t>
+          <t>PS5-62-14</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>PS5-62-13 - EITS 33kV Bld. Normal L&amp;SP DP - PS5-61-IG-0003</t>
+          <t>PS5-62-15 - Office Building Normal L&amp;SP DB - PS5-61-IG-0002</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>PS5-62-13</t>
+          <t>PS5-62-15</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>PS5-62-14 - Office Building Emergency L&amp;SP DB - PS5-05-IG-0002</t>
+          <t>PS5-62-16 - Guard Hut A Normal L&amp;SP DB - PS5-61-IG-0111</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>PS5-62-14</t>
+          <t>PS5-62-16</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>PS5-62-15 - Office Building Normal L&amp;SP DB - PS5-61-IG-0002</t>
+          <t>PS5-62-17 - Guard Hut B Normal L&amp;SP DB - PS5-61-IG-0112</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>PS5-62-15</t>
+          <t>PS5-62-17</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>PS5-62-16 - Guard Hut A Normal L&amp;SP DB - PS5-61-IG-0111</t>
+          <t>PS5-62-18 - Workshop &amp; Warehouse Normal L&amp;SP DB - PS5-61-IG-0004</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>PS5-62-16</t>
+          <t>PS5-62-18</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>PS5-62-17 - Guard Hut B Normal L&amp;SP DB - PS5-61-IG-0112</t>
+          <t>PS5-62-19 - Workshop &amp; Warehouse Emergency L&amp;SP DB - PS5-05-IG-0101</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>PS5-62-17</t>
+          <t>PS5-62-19</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>PS5-62-18 - Workshop &amp; Warehouse Normal L&amp;SP DB - PS5-61-IG-0004</t>
+          <t>PS5-62-20 - Office Building Normal L&amp;SP DB - PS5-61-IG-0010</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>PS5-62-18</t>
+          <t>PS5-62-20</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>PS5-62-19 - Workshop &amp; Warehouse Emergency L&amp;SP DB - PS5-05-IG-0101</t>
+          <t>PS5-63-01 - Electrical Earthing</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>PS5-62-19</t>
+          <t>PS5-63-01</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>PS5-62-20 - Office Building Normal L&amp;SP DB - PS5-61-IG-0010</t>
+          <t>PS5-63-02 - Electrical Earthing - Office and Facilities building</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>PS5-62-20</t>
+          <t>PS5-63-02</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>PS5-63-01 - Electrical Earthing</t>
+          <t>PS5-63-03 - Electrical Earthing - Generator Building</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>PS5-63-01</t>
+          <t>PS5-63-03</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>PS5-63-02 - Electrical Earthing - Office and Facilities building</t>
+          <t>PS5-63-04 - Electrical Earthing - EITS Building</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>PS5-63-02</t>
+          <t>PS5-63-04</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>PS5-63-03 - Electrical Earthing - Generator Building</t>
+          <t>PS5-63-05 - Electrical Earthing - Guard Hut A &amp; B</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>PS5-63-03</t>
+          <t>PS5-63-05</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>PS5-63-04 - Electrical Earthing - EITS Building</t>
+          <t>PS5-63-06 - Electrical Earthing - Guard House</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>PS5-63-04</t>
+          <t>PS5-63-06</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>PS5-63-05 - Electrical Earthing - Guard Hut A &amp; B</t>
+          <t>PS5-63-07 - Electrical Earthing - Workshop &amp; Warehouse</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>PS5-63-05</t>
+          <t>PS5-63-07</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>PS5-63-06 - Electrical Earthing - Guard House</t>
+          <t>PS5-71-01 - CFO Storage Tank Feed Heater</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>PS5-63-06</t>
+          <t>PS5-71-01</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>PS5-63-07 - Electrical Earthing - Workshop &amp; Warehouse</t>
+          <t>PS5-71-02 - CFO Allocation Metering Package</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>PS5-63-07</t>
+          <t>PS5-71-02</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>PS5-71-01 - CFO Storage Tank Feed Heater</t>
+          <t>PS5-71-03 - CFO Allocation Metering Package (UCP)</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>PS5-71-01</t>
+          <t>PS5-71-03</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>PS5-71-02 - CFO Allocation Metering Package</t>
+          <t>PS5-71-04 - CFO Storage Tank</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>PS5-71-02</t>
+          <t>PS5-71-04</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>PS5-71-03 - CFO Allocation Metering Package (UCP)</t>
+          <t>PS5-71-05 - CFO Transfer Pump A/B</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>PS5-71-03</t>
+          <t>PS5-71-05</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>PS5-71-04 - CFO Storage Tank</t>
+          <t>PS5-71-06 - Crude Fuel Separation Module</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>PS5-71-04</t>
+          <t>PS5-71-06</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>PS5-71-05 - CFO Transfer Pump A/B</t>
+          <t>PS5-71-07 - Crude Fuel Separation Module (UCP)</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>PS5-71-05</t>
+          <t>PS5-71-07</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>PS5-71-06 - Crude Fuel Separation Module</t>
+          <t>PS5-71-08 - CFO Pre-Pressure Modules</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>PS5-71-06</t>
+          <t>PS5-71-08</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>PS5-71-07 - Crude Fuel Separation Module (UCP)</t>
+          <t>PS5-71-09 - CFO Pre-Pressure Modules (UCP)</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>PS5-71-07</t>
+          <t>PS5-71-09</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>PS5-71-08 - CFO Pre-Pressure Modules</t>
+          <t>PS5-71-12 - CFO Service Tank</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>PS5-71-08</t>
+          <t>PS5-71-12</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>PS5-71-09 - CFO Pre-Pressure Modules (UCP)</t>
+          <t>PS5-71-13 - CFO Service Pump A/B</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>PS5-71-09</t>
+          <t>PS5-71-13</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>PS5-71-12 - CFO Service Tank</t>
+          <t>PS5-71-14 - Diesel Fuel Transfer and Dispensing Station</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>PS5-71-12</t>
+          <t>PS5-71-14</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>PS5-71-13 - CFO Service Pump A/B</t>
+          <t>PS5-71-15 - Diesel Fuel Storage Tank</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>PS5-71-13</t>
+          <t>PS5-71-15</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>PS5-71-14 - Diesel Fuel Transfer and Dispensing Station</t>
+          <t>PS5-71-16 - Diesel Fuel Supply Pump A/B</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>PS5-71-14</t>
+          <t>PS5-71-16</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>PS5-71-15 - Diesel Fuel Storage Tank</t>
+          <t>PS5-71-17 - Diesel Fuel Distribution Header</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>PS5-71-15</t>
+          <t>PS5-71-17</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>PS5-71-16 - Diesel Fuel Supply Pump A/B</t>
+          <t>PS5-71-18 - Diesel Separator Module</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>PS5-71-16</t>
+          <t>PS5-71-18</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>PS5-71-17 - Diesel Fuel Distribution Header</t>
+          <t>PS5-71-19 - Diesel Separator Module (UCP)</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>PS5-71-17</t>
+          <t>PS5-71-19</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>PS5-71-18 - Diesel Separator Module</t>
+          <t>PS5-71-20 - Diesel Fuel Day Tank</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>PS5-71-18</t>
+          <t>PS5-71-20</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>PS5-71-19 - Diesel Separator Module (UCP)</t>
+          <t>PS5-71-21 - Diesel Transfer Pump A/B</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>PS5-71-19</t>
+          <t>PS5-71-21</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>PS5-71-20 - Diesel Fuel Day Tank</t>
+          <t>PS5-71-22 - Diesel Fuel Pre Pressure Module</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>PS5-71-20</t>
+          <t>PS5-71-22</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>PS5-71-21 - Diesel Transfer Pump A/B</t>
+          <t>PS5-71-23 - Diesel Fuel Pre Pressure Module (UCP)</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>PS5-71-21</t>
+          <t>PS5-71-23</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>PS5-71-22 - Diesel Fuel Pre Pressure Module</t>
+          <t>PS5-74-01 - N2 Generation Skid</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>PS5-71-22</t>
+          <t>PS5-74-01</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>PS5-71-23 - Diesel Fuel Pre Pressure Module (UCP)</t>
+          <t>PS5-74-02 - N2 Generation Skid (UCP)</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>PS5-71-23</t>
+          <t>PS5-74-02</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>PS5-74-01 - N2 Generation Skid</t>
+          <t>PS5-74-03 - Nitrogen Receiver</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>PS5-74-01</t>
+          <t>PS5-74-03</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>PS5-74-02 - N2 Generation Skid (UCP)</t>
+          <t>PS5-74-04 - Nitrogen Distribution Header</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>PS5-74-02</t>
+          <t>PS5-74-04</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>PS5-74-03 - Nitrogen Receiver</t>
+          <t>PS5-75-01 - DRA Injection Package</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>PS5-74-03</t>
+          <t>PS5-75-01</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>PS5-74-04 - Nitrogen Distribution Header</t>
+          <t>PS5-75-02 - Biocide Injection Package</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>PS5-74-04</t>
+          <t>PS5-75-02</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>PS5-75-01 - DRA Injection Package</t>
+          <t>PS5-75-03 - Corrosion Inhibitor Injection Package</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>PS5-75-01</t>
+          <t>PS5-75-03</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>PS5-75-02 - Biocide Injection Package</t>
+          <t>PS5-78-01 - Lifting and handling equipment</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>PS5-75-02</t>
+          <t>PS5-78-01</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>PS5-75-03 - Corrosion Inhibitor Injection Package</t>
+          <t>PS5-79-01 - Electrical Heat Tracing Transformer/Distribution Board 1 (PS5-79-IG-0001)</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>PS5-75-03</t>
+          <t>PS5-79-01</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>PS5-78-01 - Lifting and handling equipment</t>
+          <t>PS5-79-02 - Electrical Heat Tracing Transformer/Distribution Board 2 (PS5-79-IG-0002)</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>PS5-78-01</t>
+          <t>PS5-79-02</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>PS5-79-01 - Electrical Heat Tracing Transformer/Distribution Board 1 (PS5-79-IG-0001)</t>
+          <t>PS5-79-03 - Electrical Heat Tracing Transformer/Distribution Board 3 (PS5-79-IG-0003)</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>PS5-79-01</t>
+          <t>PS5-79-03</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>PS5-79-02 - Electrical Heat Tracing Transformer/Distribution Board 2 (PS5-79-IG-0002)</t>
+          <t>PS5-79-04 - Electrical Heat Tracing Transformer/Distribution Board 4 (PS5-79-IG-0004)</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>PS5-79-02</t>
+          <t>PS5-79-04</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>PS5-79-03 - Electrical Heat Tracing Transformer/Distribution Board 3 (PS5-79-IG-0003)</t>
+          <t>PS5-79-05 - Electrical Heat Tracing Transformer/Distribution Board 5 (PS5-79-IG-0005)</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>PS5-79-03</t>
+          <t>PS5-79-05</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>PS5-79-04 - Electrical Heat Tracing Transformer/Distribution Board 4 (PS5-79-IG-0004)</t>
+          <t>PS5-79-06 - Electrical Heat Tracing Transformer/Distribution Board 6 (PS5-79-IG-0006)</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>PS5-79-04</t>
+          <t>PS5-79-06</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>PS5-79-05 - Electrical Heat Tracing Transformer/Distribution Board 5 (PS5-79-IG-0005)</t>
+          <t>PS5-79-07 - Electrical Heat Tracing Transformer/Distribution Board 7 (PS5-79-IG-0007)</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>PS5-79-05</t>
+          <t>PS5-79-07</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>PS5-79-06 - Electrical Heat Tracing Transformer/Distribution Board 6 (PS5-79-IG-0006)</t>
+          <t>PS5-79-08 - Electrical Heat Tracing Transformer/Distribution Board 8 (PS5-79-IG-0008)</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>PS5-79-06</t>
+          <t>PS5-79-08</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>PS5-79-07 - Electrical Heat Tracing Transformer/Distribution Board 7 (PS5-79-IG-0007)</t>
+          <t>PS5-79-09 - Electrical Heat Tracing Transformer/Distribution Board 9 (PS5-79-IG-0009)</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>PS5-79-07</t>
+          <t>PS5-79-09</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>PS5-79-08 - Electrical Heat Tracing Transformer/Distribution Board 8 (PS5-79-IG-0008)</t>
+          <t>PS5-79-10 - Electrical Heat Tracing Transformer/Distribution Board 10 (PS5-79-IG-0010)</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>PS5-79-08</t>
+          <t>PS5-79-10</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>PS5-79-09 - Electrical Heat Tracing Transformer/Distribution Board 9 (PS5-79-IG-0009)</t>
+          <t>PS5-79-11 - Electrical Heat Tracing Transformer/Distribution Board 11 (PS5-79-IG-0011)</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>PS5-79-09</t>
+          <t>PS5-79-11</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>PS5-79-10 - Electrical Heat Tracing Transformer/Distribution Board 10 (PS5-79-IG-0010)</t>
+          <t>PS5-79-12 - Electrical Heat Tracing Transformer/Distribution Board 12 (PS5-79-IG-0012)</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>PS5-79-10</t>
+          <t>PS5-79-12</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>PS5-79-11 - Electrical Heat Tracing Transformer/Distribution Board 11 (PS5-79-IG-0011)</t>
+          <t>PS5-82-01 - Sanitary Sewage Collection</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>PS5-79-11</t>
+          <t>PS5-82-01</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>PS5-79-12 - Electrical Heat Tracing Transformer/Distribution Board 12 (PS5-79-IG-0012)</t>
+          <t>PS5-82-02 - Sewage Treatment Plant Package</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>PS5-79-12</t>
+          <t>PS5-82-02</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>PS5-82-01 - Sanitary Sewage Collection</t>
+          <t>PS5-82-03 - Sewage Treatment Plant Package (UCP)</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>PS5-82-01</t>
+          <t>PS5-82-03</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>PS5-82-02 - Sewage Treatment Plant Package</t>
+          <t>PS5-82-04 - Sewage Treatment Plant Discharge Piping</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>PS5-82-02</t>
+          <t>PS5-82-04</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>PS5-82-03 - Sewage Treatment Plant Package (UCP)</t>
+          <t>PS5-82-05 - Office and Facilities building</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>PS5-82-03</t>
+          <t>PS5-82-05</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>PS5-82-04 - Sewage Treatment Plant Discharge Piping</t>
+          <t>PS5-82-06 - Guard House Building</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>PS5-82-04</t>
+          <t>PS5-82-06</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>PS5-82-05 - Office and Facilities building</t>
+          <t>PS5-82-07 - Guard Huts</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>PS5-82-05</t>
+          <t>PS5-82-07</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>PS5-82-06 - Guard House Building</t>
+          <t>PS5-83-01 - EITS Building</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>PS5-82-06</t>
+          <t>PS5-83-01</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>PS5-82-07 - Guard Huts</t>
+          <t>PS5-84-01 - Generator Building</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>PS5-82-07</t>
+          <t>PS5-84-01</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>PS5-83-01 - EITS Building</t>
+          <t>PS5-84-02 - Workshop &amp; Warehouse</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>PS5-83-01</t>
+          <t>PS5-84-02</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>PS5-84-01 - Generator Building</t>
+          <t>PS5-84-03 - Shelters</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>PS5-84-01</t>
+          <t>PS5-84-03</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>PS5-84-02 - Workshop &amp; Warehouse</t>
+          <t>PS5-86-01 - Shelters</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>PS5-84-02</t>
+          <t>PS5-86-01</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>PS5-84-03 - Shelters</t>
+          <t>PS5-91-01 - Multicore cables &amp; JB</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>PS5-84-03</t>
+          <t>PS5-91-01</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>PS5-86-01 - Shelters</t>
+          <t>PS5-99-01 - Area Completion for Building area</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>PS5-86-01</t>
+          <t>PS5-99-01</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>PS5-91-01 - Multicore cables &amp; JB</t>
+          <t>PS5-99-02 - Area Completion for Utility area</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>PS5-91-01</t>
+          <t>PS5-99-02</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>PS5-99-01 - Area Completion for Building area</t>
+          <t>PS5-99-03 - Area Completion for Power Distribution area</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>PS5-99-01</t>
+          <t>PS5-99-03</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>PS5-99-02 - Area Completion for Utility area</t>
+          <t>PS5-99-04 - Area Completion for Process area</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>PS5-99-02</t>
+          <t>PS5-99-04</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>PS5-99-03 - Area Completion for Power Distribution area</t>
+          <t>PS5-99-05 - Area Completion for CFO area</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>PS5-99-03</t>
+          <t>PS5-99-05</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>PS5-99-04 - Area Completion for Process area</t>
+          <t>PS5-99-06 - Area Completion for Power Generation area</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
-        <is>
-          <t>PS5-99-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" t="inlineStr">
-        <is>
-          <t>PS5-99-05 - Area Completion for CFO area</t>
-        </is>
-      </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>PS5-99-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="inlineStr">
-        <is>
-          <t>PS5-99-06 - Area Completion for Power Generation area</t>
-        </is>
-      </c>
-      <c r="B295" t="inlineStr">
         <is>
           <t>PS5-99-06</t>
         </is>

--- a/EXCEL/7 - COMPLETE.xlsx
+++ b/EXCEL/7 - COMPLETE.xlsx
@@ -116,14 +116,14 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <color rgb="FFb35900"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <color rgb="FF0a58ca"/>
       <sz val="10"/>
       <u val="single"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="FFb35900"/>
-      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -570,14 +570,14 @@
     <xf numFmtId="0" fontId="10" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -728,24 +728,24 @@
     <xf numFmtId="0" fontId="15" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -761,13 +761,13 @@
     <xf numFmtId="0" fontId="7" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1215,7 +1215,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="85" t="n">
+      <c r="A3" s="81" t="n">
         <v>1</v>
       </c>
       <c r="B3" s="83" t="inlineStr">
@@ -1223,7 +1223,7 @@
           <t>PS5-01-01 - Fire Water Jockey Pump A/B</t>
         </is>
       </c>
-      <c r="C3" s="28" t="inlineStr">
+      <c r="C3" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1233,7 +1233,7 @@
           <t>DONE(partial)</t>
         </is>
       </c>
-      <c r="E3" s="28" t="inlineStr">
+      <c r="E3" s="27" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -1246,7 +1246,7 @@
       <c r="G3" s="67" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="85" t="n">
+      <c r="A4" s="81" t="n">
         <v>2</v>
       </c>
       <c r="B4" s="83" t="inlineStr">
@@ -1254,13 +1254,13 @@
           <t>PS5-01-04 - Fire Water Pump Mini Flow Recycle</t>
         </is>
       </c>
-      <c r="C4" s="28" t="inlineStr">
+      <c r="C4" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
       <c r="D4" s="24" t="inlineStr"/>
-      <c r="E4" s="28" t="inlineStr">
+      <c r="E4" s="27" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -1273,7 +1273,7 @@
       <c r="G4" s="67" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="85" t="n">
+      <c r="A5" s="81" t="n">
         <v>3</v>
       </c>
       <c r="B5" s="83" t="inlineStr">
@@ -1281,13 +1281,13 @@
           <t>PS5-01-06 - Foam Concentrate Distribution</t>
         </is>
       </c>
-      <c r="C5" s="28" t="inlineStr">
+      <c r="C5" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
       <c r="D5" s="24" t="inlineStr"/>
-      <c r="E5" s="28" t="inlineStr">
+      <c r="E5" s="27" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -1300,7 +1300,7 @@
       <c r="G5" s="67" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="85" t="n">
+      <c r="A6" s="81" t="n">
         <v>4</v>
       </c>
       <c r="B6" s="83" t="inlineStr">
@@ -1308,13 +1308,13 @@
           <t>PS5-01-09 - Inergen for EITS Building</t>
         </is>
       </c>
-      <c r="C6" s="28" t="inlineStr">
+      <c r="C6" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
       <c r="D6" s="24" t="inlineStr"/>
-      <c r="E6" s="28" t="inlineStr">
+      <c r="E6" s="27" t="inlineStr">
         <is>
           <t>2026-08-08</t>
         </is>
@@ -1327,7 +1327,7 @@
       <c r="G6" s="67" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="85" t="n">
+      <c r="A7" s="81" t="n">
         <v>5</v>
       </c>
       <c r="B7" s="83" t="inlineStr">
@@ -1335,7 +1335,7 @@
           <t>PS5-01-10 - Water Mist Package</t>
         </is>
       </c>
-      <c r="C7" s="28" t="inlineStr">
+      <c r="C7" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1345,7 +1345,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E7" s="28" t="inlineStr">
+      <c r="E7" s="27" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -1358,7 +1358,7 @@
       <c r="G7" s="67" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="85" t="n">
+      <c r="A8" s="81" t="n">
         <v>6</v>
       </c>
       <c r="B8" s="83" t="inlineStr">
@@ -1366,7 +1366,7 @@
           <t>PS5-03-07 - FZ-07 - Pretreatment Area</t>
         </is>
       </c>
-      <c r="C8" s="28" t="inlineStr">
+      <c r="C8" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1376,7 +1376,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E8" s="28" t="inlineStr">
+      <c r="E8" s="27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1389,7 +1389,7 @@
       <c r="G8" s="67" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="85" t="n">
+      <c r="A9" s="81" t="n">
         <v>7</v>
       </c>
       <c r="B9" s="83" t="inlineStr">
@@ -1397,7 +1397,7 @@
           <t>PS5-03-09 - FZ-09 - Power Generation Building - Engine Bay 1</t>
         </is>
       </c>
-      <c r="C9" s="28" t="inlineStr">
+      <c r="C9" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1407,7 +1407,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E9" s="28" t="inlineStr">
+      <c r="E9" s="27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1420,7 +1420,7 @@
       <c r="G9" s="67" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="85" t="n">
+      <c r="A10" s="81" t="n">
         <v>8</v>
       </c>
       <c r="B10" s="83" t="inlineStr">
@@ -1428,7 +1428,7 @@
           <t>PS5-03-10 - FZ-10 - Power Generation Building - Engine Bay 2</t>
         </is>
       </c>
-      <c r="C10" s="28" t="inlineStr">
+      <c r="C10" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1438,7 +1438,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E10" s="28" t="inlineStr">
+      <c r="E10" s="27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1447,7 +1447,7 @@
       <c r="G10" s="67" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="85" t="n">
+      <c r="A11" s="81" t="n">
         <v>9</v>
       </c>
       <c r="B11" s="83" t="inlineStr">
@@ -1455,7 +1455,7 @@
           <t>PS5-03-13 - FZ-13 - Power Generation Building - Instrument Air Room</t>
         </is>
       </c>
-      <c r="C11" s="28" t="inlineStr">
+      <c r="C11" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1465,7 +1465,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E11" s="28" t="inlineStr">
+      <c r="E11" s="27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1478,7 +1478,7 @@
       <c r="G11" s="67" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="85" t="n">
+      <c r="A12" s="81" t="n">
         <v>10</v>
       </c>
       <c r="B12" s="83" t="inlineStr">
@@ -1486,7 +1486,7 @@
           <t>PS5-03-20 - FZ-20 - Emergency Diesel Generator Enclosure</t>
         </is>
       </c>
-      <c r="C12" s="28" t="inlineStr">
+      <c r="C12" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1496,7 +1496,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E12" s="28" t="inlineStr">
+      <c r="E12" s="27" t="inlineStr">
         <is>
           <t>07-Aug-26</t>
         </is>
@@ -1509,7 +1509,7 @@
       <c r="G12" s="67" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="85" t="n">
+      <c r="A13" s="81" t="n">
         <v>11</v>
       </c>
       <c r="B13" s="83" t="inlineStr">
@@ -1517,7 +1517,7 @@
           <t>PS5-05-01 - Emergency Diesel Generator Package</t>
         </is>
       </c>
-      <c r="C13" s="28" t="inlineStr">
+      <c r="C13" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1540,7 +1540,7 @@
       <c r="G13" s="67" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="85" t="n">
+      <c r="A14" s="81" t="n">
         <v>12</v>
       </c>
       <c r="B14" s="83" t="inlineStr">
@@ -1548,7 +1548,7 @@
           <t>PS5-05-02 - Emergency Diesel Generator Package (UCP)</t>
         </is>
       </c>
-      <c r="C14" s="28" t="inlineStr">
+      <c r="C14" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1571,7 +1571,7 @@
       <c r="G14" s="67" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="85" t="n">
+      <c r="A15" s="81" t="n">
         <v>13</v>
       </c>
       <c r="B15" s="83" t="inlineStr">
@@ -1579,7 +1579,7 @@
           <t>PS5-06-02 - AC UPS - Power Generator Building</t>
         </is>
       </c>
-      <c r="C15" s="28" t="inlineStr">
+      <c r="C15" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1589,7 +1589,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E15" s="28" t="inlineStr">
+      <c r="E15" s="27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1602,7 +1602,7 @@
       <c r="G15" s="67" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="85" t="n">
+      <c r="A16" s="81" t="n">
         <v>14</v>
       </c>
       <c r="B16" s="83" t="inlineStr">
@@ -1610,13 +1610,13 @@
           <t>PS5-09-05 - HVAC for EITS Building</t>
         </is>
       </c>
-      <c r="C16" s="28" t="inlineStr">
+      <c r="C16" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
       <c r="D16" s="24" t="inlineStr"/>
-      <c r="E16" s="28" t="inlineStr">
+      <c r="E16" s="27" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -1625,7 +1625,7 @@
       <c r="G16" s="67" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="85" t="n">
+      <c r="A17" s="81" t="n">
         <v>15</v>
       </c>
       <c r="B17" s="83" t="inlineStr">
@@ -1633,13 +1633,13 @@
           <t>PS5-28-02 - Closed Drain Header 2</t>
         </is>
       </c>
-      <c r="C17" s="28" t="inlineStr">
+      <c r="C17" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
       <c r="D17" s="24" t="inlineStr"/>
-      <c r="E17" s="28" t="inlineStr">
+      <c r="E17" s="27" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -1652,7 +1652,7 @@
       <c r="G17" s="67" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="85" t="n">
+      <c r="A18" s="81" t="n">
         <v>16</v>
       </c>
       <c r="B18" s="83" t="inlineStr">
@@ -1660,7 +1660,7 @@
           <t>PS5-28-05 - HP Relief Header</t>
         </is>
       </c>
-      <c r="C18" s="28" t="inlineStr">
+      <c r="C18" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1670,7 +1670,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E18" s="28" t="inlineStr">
+      <c r="E18" s="27" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -1683,7 +1683,7 @@
       <c r="G18" s="67" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="81" t="n">
+      <c r="A19" s="85" t="n">
         <v>17</v>
       </c>
       <c r="B19" s="83" t="inlineStr">
@@ -1691,7 +1691,7 @@
           <t>PS5-53-01 - Utility Water / Storage Tank</t>
         </is>
       </c>
-      <c r="C19" s="28" t="inlineStr">
+      <c r="C19" s="27" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -1714,7 +1714,7 @@
       <c r="G19" s="67" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="85" t="n">
+      <c r="A20" s="81" t="n">
         <v>18</v>
       </c>
       <c r="B20" s="83" t="inlineStr">
@@ -1722,7 +1722,7 @@
           <t>PS5-60-01 - Power Generation Package A</t>
         </is>
       </c>
-      <c r="C20" s="28" t="inlineStr">
+      <c r="C20" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1732,7 +1732,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E20" s="28" t="inlineStr">
+      <c r="E20" s="27" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -1745,7 +1745,7 @@
       <c r="G20" s="67" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="85" t="n">
+      <c r="A21" s="81" t="n">
         <v>19</v>
       </c>
       <c r="B21" s="83" t="inlineStr">
@@ -1753,7 +1753,7 @@
           <t>PS5-60-02 - Power Gen Package A (UCP)</t>
         </is>
       </c>
-      <c r="C21" s="28" t="inlineStr">
+      <c r="C21" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1763,7 +1763,7 @@
           <t>PS5 - Milestone B</t>
         </is>
       </c>
-      <c r="E21" s="28" t="inlineStr">
+      <c r="E21" s="27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1776,7 +1776,7 @@
       <c r="G21" s="67" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="85" t="n">
+      <c r="A22" s="81" t="n">
         <v>20</v>
       </c>
       <c r="B22" s="83" t="inlineStr">
@@ -1784,7 +1784,7 @@
           <t>PS5-60-04 - Power Generation Package B</t>
         </is>
       </c>
-      <c r="C22" s="28" t="inlineStr">
+      <c r="C22" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1794,7 +1794,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E22" s="28" t="inlineStr">
+      <c r="E22" s="27" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -1807,7 +1807,7 @@
       <c r="G22" s="67" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="85" t="n">
+      <c r="A23" s="81" t="n">
         <v>21</v>
       </c>
       <c r="B23" s="83" t="inlineStr">
@@ -1815,13 +1815,13 @@
           <t>PS5-60-23 - Instrument Air Distribution lines</t>
         </is>
       </c>
-      <c r="C23" s="28" t="inlineStr">
+      <c r="C23" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
       <c r="D23" s="24" t="inlineStr"/>
-      <c r="E23" s="28" t="inlineStr">
+      <c r="E23" s="27" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -1834,7 +1834,7 @@
       <c r="G23" s="67" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="85" t="n">
+      <c r="A24" s="81" t="n">
         <v>22</v>
       </c>
       <c r="B24" s="83" t="inlineStr">
@@ -1842,7 +1842,7 @@
           <t>PS5-60-26 - Instrument Air Compressor Skid</t>
         </is>
       </c>
-      <c r="C24" s="28" t="inlineStr">
+      <c r="C24" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1852,7 +1852,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E24" s="28" t="inlineStr">
+      <c r="E24" s="27" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -1865,7 +1865,7 @@
       <c r="G24" s="67" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="85" t="n">
+      <c r="A25" s="81" t="n">
         <v>23</v>
       </c>
       <c r="B25" s="83" t="inlineStr">
@@ -1873,7 +1873,7 @@
           <t>PS5-60-27 - Compressed Air Starting Skid</t>
         </is>
       </c>
-      <c r="C25" s="28" t="inlineStr">
+      <c r="C25" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1883,7 +1883,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E25" s="28" t="inlineStr">
+      <c r="E25" s="27" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -1896,7 +1896,7 @@
       <c r="G25" s="67" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="85" t="n">
+      <c r="A26" s="81" t="n">
         <v>24</v>
       </c>
       <c r="B26" s="83" t="inlineStr">
@@ -1904,7 +1904,7 @@
           <t>PS5-60-28 - Air Receiver A &amp; Air Regulator A</t>
         </is>
       </c>
-      <c r="C26" s="28" t="inlineStr">
+      <c r="C26" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1927,7 +1927,7 @@
       <c r="G26" s="67" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="85" t="n">
+      <c r="A27" s="81" t="n">
         <v>25</v>
       </c>
       <c r="B27" s="83" t="inlineStr">
@@ -1935,7 +1935,7 @@
           <t>PS5-60-29 - Air Receiver B &amp; Air Regulator B</t>
         </is>
       </c>
-      <c r="C27" s="28" t="inlineStr">
+      <c r="C27" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1945,7 +1945,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E27" s="28" t="inlineStr">
+      <c r="E27" s="27" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -1958,7 +1958,7 @@
       <c r="G27" s="67" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="85" t="n">
+      <c r="A28" s="81" t="n">
         <v>26</v>
       </c>
       <c r="B28" s="83" t="inlineStr">
@@ -1966,7 +1966,7 @@
           <t>PS5-60-30 - Air Receiver C &amp; Air Regulator C</t>
         </is>
       </c>
-      <c r="C28" s="28" t="inlineStr">
+      <c r="C28" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1976,7 +1976,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E28" s="28" t="inlineStr">
+      <c r="E28" s="27" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -1989,7 +1989,7 @@
       <c r="G28" s="67" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="85" t="n">
+      <c r="A29" s="81" t="n">
         <v>27</v>
       </c>
       <c r="B29" s="83" t="inlineStr">
@@ -1997,7 +1997,7 @@
           <t>PS5-60-31 - Air Receiver D &amp; Air Regulator D</t>
         </is>
       </c>
-      <c r="C29" s="28" t="inlineStr">
+      <c r="C29" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2007,7 +2007,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E29" s="28" t="inlineStr">
+      <c r="E29" s="27" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -2020,7 +2020,7 @@
       <c r="G29" s="67" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="85" t="n">
+      <c r="A30" s="81" t="n">
         <v>28</v>
       </c>
       <c r="B30" s="83" t="inlineStr">
@@ -2028,7 +2028,7 @@
           <t>PS5-60-32 - Air Receiver E &amp; Air Regulator E</t>
         </is>
       </c>
-      <c r="C30" s="28" t="inlineStr">
+      <c r="C30" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2038,7 +2038,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E30" s="28" t="inlineStr">
+      <c r="E30" s="27" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -2051,7 +2051,7 @@
       <c r="G30" s="67" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="85" t="n">
+      <c r="A31" s="81" t="n">
         <v>29</v>
       </c>
       <c r="B31" s="83" t="inlineStr">
@@ -2059,7 +2059,7 @@
           <t>PS5-60-33 - Air Receiver F &amp; Air Regulator F</t>
         </is>
       </c>
-      <c r="C31" s="28" t="inlineStr">
+      <c r="C31" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2069,7 +2069,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E31" s="28" t="inlineStr">
+      <c r="E31" s="27" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -2082,7 +2082,7 @@
       <c r="G31" s="67" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="85" t="n">
+      <c r="A32" s="81" t="n">
         <v>30</v>
       </c>
       <c r="B32" s="83" t="inlineStr">
@@ -2090,7 +2090,7 @@
           <t>PS5-60-34 - Air Receiver G &amp; Air Regulator G</t>
         </is>
       </c>
-      <c r="C32" s="28" t="inlineStr">
+      <c r="C32" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2100,7 +2100,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E32" s="28" t="inlineStr">
+      <c r="E32" s="27" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -2113,7 +2113,7 @@
       <c r="G32" s="67" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="85" t="n">
+      <c r="A33" s="81" t="n">
         <v>31</v>
       </c>
       <c r="B33" s="83" t="inlineStr">
@@ -2121,7 +2121,7 @@
           <t>PS5-60-35 - Injector Tip Cooling Module A</t>
         </is>
       </c>
-      <c r="C33" s="28" t="inlineStr">
+      <c r="C33" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2144,7 +2144,7 @@
       <c r="G33" s="67" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="85" t="n">
+      <c r="A34" s="81" t="n">
         <v>32</v>
       </c>
       <c r="B34" s="83" t="inlineStr">
@@ -2152,7 +2152,7 @@
           <t>PS5-60-36 - Injector Tip Cooling Module B</t>
         </is>
       </c>
-      <c r="C34" s="28" t="inlineStr">
+      <c r="C34" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2162,7 +2162,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E34" s="28" t="inlineStr">
+      <c r="E34" s="27" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -2175,7 +2175,7 @@
       <c r="G34" s="67" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="85" t="n">
+      <c r="A35" s="81" t="n">
         <v>33</v>
       </c>
       <c r="B35" s="83" t="inlineStr">
@@ -2183,7 +2183,7 @@
           <t>PS5-60-37 - Injector Tip Cooling Module C</t>
         </is>
       </c>
-      <c r="C35" s="28" t="inlineStr">
+      <c r="C35" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2193,7 +2193,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E35" s="28" t="inlineStr">
+      <c r="E35" s="27" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -2206,7 +2206,7 @@
       <c r="G35" s="67" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="85" t="n">
+      <c r="A36" s="81" t="n">
         <v>34</v>
       </c>
       <c r="B36" s="83" t="inlineStr">
@@ -2214,7 +2214,7 @@
           <t>PS5-60-38 - Injector Tip Cooling Module D</t>
         </is>
       </c>
-      <c r="C36" s="28" t="inlineStr">
+      <c r="C36" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2224,7 +2224,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E36" s="28" t="inlineStr">
+      <c r="E36" s="27" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -2237,7 +2237,7 @@
       <c r="G36" s="67" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="85" t="n">
+      <c r="A37" s="81" t="n">
         <v>35</v>
       </c>
       <c r="B37" s="83" t="inlineStr">
@@ -2245,7 +2245,7 @@
           <t>PS5-60-39 - Injector Tip Cooling Module E</t>
         </is>
       </c>
-      <c r="C37" s="28" t="inlineStr">
+      <c r="C37" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2255,7 +2255,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E37" s="28" t="inlineStr">
+      <c r="E37" s="27" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -2268,7 +2268,7 @@
       <c r="G37" s="67" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="85" t="n">
+      <c r="A38" s="81" t="n">
         <v>36</v>
       </c>
       <c r="B38" s="83" t="inlineStr">
@@ -2276,7 +2276,7 @@
           <t>PS5-60-40 - Injector Tip Cooling Module F</t>
         </is>
       </c>
-      <c r="C38" s="28" t="inlineStr">
+      <c r="C38" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2286,7 +2286,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E38" s="28" t="inlineStr">
+      <c r="E38" s="27" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -2299,7 +2299,7 @@
       <c r="G38" s="67" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="85" t="n">
+      <c r="A39" s="81" t="n">
         <v>37</v>
       </c>
       <c r="B39" s="83" t="inlineStr">
@@ -2307,7 +2307,7 @@
           <t>PS5-60-42 - Oil Mist Separator Skid PS5-60-VS-9100A</t>
         </is>
       </c>
-      <c r="C39" s="28" t="inlineStr">
+      <c r="C39" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2330,7 +2330,7 @@
       <c r="G39" s="67" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="85" t="n">
+      <c r="A40" s="81" t="n">
         <v>38</v>
       </c>
       <c r="B40" s="83" t="inlineStr">
@@ -2338,7 +2338,7 @@
           <t>PS5-60-43 - Oil Mist Separator Skid PS5-60-VS-9100B</t>
         </is>
       </c>
-      <c r="C40" s="28" t="inlineStr">
+      <c r="C40" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2348,7 +2348,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E40" s="28" t="inlineStr">
+      <c r="E40" s="27" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -2361,7 +2361,7 @@
       <c r="G40" s="67" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="85" t="n">
+      <c r="A41" s="81" t="n">
         <v>39</v>
       </c>
       <c r="B41" s="83" t="inlineStr">
@@ -2369,7 +2369,7 @@
           <t>PS5-60-44 - Oil Mist Separator Skid PS5-60-VS-9100C</t>
         </is>
       </c>
-      <c r="C41" s="28" t="inlineStr">
+      <c r="C41" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2379,7 +2379,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E41" s="28" t="inlineStr">
+      <c r="E41" s="27" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -2392,7 +2392,7 @@
       <c r="G41" s="67" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="85" t="n">
+      <c r="A42" s="81" t="n">
         <v>40</v>
       </c>
       <c r="B42" s="83" t="inlineStr">
@@ -2400,7 +2400,7 @@
           <t>PS5-60-45 - Oil Mist Separator Skid PS5-60-VS-9100D</t>
         </is>
       </c>
-      <c r="C42" s="28" t="inlineStr">
+      <c r="C42" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2410,7 +2410,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E42" s="28" t="inlineStr">
+      <c r="E42" s="27" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -2423,7 +2423,7 @@
       <c r="G42" s="67" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="85" t="n">
+      <c r="A43" s="81" t="n">
         <v>41</v>
       </c>
       <c r="B43" s="83" t="inlineStr">
@@ -2431,13 +2431,13 @@
           <t>PS5-60-46 - Oil Mist Separator Skid PS5-60-VS-9100E</t>
         </is>
       </c>
-      <c r="C43" s="28" t="inlineStr">
+      <c r="C43" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
       <c r="D43" s="24" t="inlineStr"/>
-      <c r="E43" s="28" t="inlineStr">
+      <c r="E43" s="27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2450,7 +2450,7 @@
       <c r="G43" s="67" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="85" t="n">
+      <c r="A44" s="81" t="n">
         <v>42</v>
       </c>
       <c r="B44" s="83" t="inlineStr">
@@ -2458,7 +2458,7 @@
           <t>PS5-60-47 - Oil Mist Separator Skid PS5-60-VS-9100F</t>
         </is>
       </c>
-      <c r="C44" s="28" t="inlineStr">
+      <c r="C44" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2468,7 +2468,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E44" s="28" t="inlineStr">
+      <c r="E44" s="27" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -2481,7 +2481,7 @@
       <c r="G44" s="67" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="85" t="n">
+      <c r="A45" s="81" t="n">
         <v>43</v>
       </c>
       <c r="B45" s="83" t="inlineStr">
@@ -2489,7 +2489,7 @@
           <t>PS5-60-56 - Fuel Conditioning Module PS5-60-UZ-8900A</t>
         </is>
       </c>
-      <c r="C45" s="28" t="inlineStr">
+      <c r="C45" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2499,7 +2499,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E45" s="28" t="inlineStr">
+      <c r="E45" s="27" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -2508,7 +2508,7 @@
       <c r="G45" s="67" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="85" t="n">
+      <c r="A46" s="81" t="n">
         <v>44</v>
       </c>
       <c r="B46" s="83" t="inlineStr">
@@ -2516,7 +2516,7 @@
           <t>PS5-60-58 - Fuel Conditioning Module PS5-60-UZ-8900B</t>
         </is>
       </c>
-      <c r="C46" s="28" t="inlineStr">
+      <c r="C46" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2526,7 +2526,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E46" s="28" t="inlineStr">
+      <c r="E46" s="27" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -2535,7 +2535,7 @@
       <c r="G46" s="67" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="85" t="n">
+      <c r="A47" s="81" t="n">
         <v>45</v>
       </c>
       <c r="B47" s="83" t="inlineStr">
@@ -2543,7 +2543,7 @@
           <t>PS5-60-60 - Fuel Conditioning Module PS5-60-UZ-8900C</t>
         </is>
       </c>
-      <c r="C47" s="28" t="inlineStr">
+      <c r="C47" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2553,7 +2553,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E47" s="28" t="inlineStr">
+      <c r="E47" s="27" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -2562,7 +2562,7 @@
       <c r="G47" s="67" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="85" t="n">
+      <c r="A48" s="81" t="n">
         <v>46</v>
       </c>
       <c r="B48" s="83" t="inlineStr">
@@ -2570,7 +2570,7 @@
           <t>PS5-60-62 - Fuel Conditioning Module PS5-60-UZ-8900D</t>
         </is>
       </c>
-      <c r="C48" s="28" t="inlineStr">
+      <c r="C48" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2580,7 +2580,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E48" s="28" t="inlineStr">
+      <c r="E48" s="27" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -2589,7 +2589,7 @@
       <c r="G48" s="67" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="85" t="n">
+      <c r="A49" s="81" t="n">
         <v>47</v>
       </c>
       <c r="B49" s="83" t="inlineStr">
@@ -2597,7 +2597,7 @@
           <t>PS5-60-70 - Engine A Cooling system</t>
         </is>
       </c>
-      <c r="C49" s="28" t="inlineStr">
+      <c r="C49" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2607,7 +2607,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E49" s="28" t="inlineStr">
+      <c r="E49" s="27" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -2620,7 +2620,7 @@
       <c r="G49" s="67" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="85" t="n">
+      <c r="A50" s="81" t="n">
         <v>48</v>
       </c>
       <c r="B50" s="83" t="inlineStr">
@@ -2628,7 +2628,7 @@
           <t>PS5-60-71 - Engine B Cooling system</t>
         </is>
       </c>
-      <c r="C50" s="28" t="inlineStr">
+      <c r="C50" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2638,7 +2638,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E50" s="28" t="inlineStr">
+      <c r="E50" s="27" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -2651,7 +2651,7 @@
       <c r="G50" s="67" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="85" t="n">
+      <c r="A51" s="81" t="n">
         <v>49</v>
       </c>
       <c r="B51" s="83" t="inlineStr">
@@ -2659,7 +2659,7 @@
           <t>PS5-60-72 - Engine C Cooling system</t>
         </is>
       </c>
-      <c r="C51" s="28" t="inlineStr">
+      <c r="C51" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2669,7 +2669,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E51" s="28" t="inlineStr">
+      <c r="E51" s="27" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -2682,7 +2682,7 @@
       <c r="G51" s="67" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="85" t="n">
+      <c r="A52" s="81" t="n">
         <v>50</v>
       </c>
       <c r="B52" s="83" t="inlineStr">
@@ -2690,7 +2690,7 @@
           <t>PS5-60-73 - Engine D Cooling system</t>
         </is>
       </c>
-      <c r="C52" s="28" t="inlineStr">
+      <c r="C52" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2700,7 +2700,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E52" s="28" t="inlineStr">
+      <c r="E52" s="27" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -2713,7 +2713,7 @@
       <c r="G52" s="67" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="85" t="n">
+      <c r="A53" s="81" t="n">
         <v>51</v>
       </c>
       <c r="B53" s="83" t="inlineStr">
@@ -2721,7 +2721,7 @@
           <t>PS5-60-74 - Engine E Cooling system</t>
         </is>
       </c>
-      <c r="C53" s="28" t="inlineStr">
+      <c r="C53" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2731,7 +2731,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E53" s="28" t="inlineStr">
+      <c r="E53" s="27" t="inlineStr">
         <is>
           <t>PLATFORM ISSUE</t>
         </is>
@@ -2744,7 +2744,7 @@
       <c r="G53" s="67" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="85" t="n">
+      <c r="A54" s="81" t="n">
         <v>52</v>
       </c>
       <c r="B54" s="83" t="inlineStr">
@@ -2752,7 +2752,7 @@
           <t>PS5-60-75 - Engine F Cooling system</t>
         </is>
       </c>
-      <c r="C54" s="28" t="inlineStr">
+      <c r="C54" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2762,7 +2762,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E54" s="28" t="inlineStr">
+      <c r="E54" s="27" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -2775,7 +2775,7 @@
       <c r="G54" s="67" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="85" t="n">
+      <c r="A55" s="81" t="n">
         <v>53</v>
       </c>
       <c r="B55" s="83" t="inlineStr">
@@ -2783,7 +2783,7 @@
           <t>PS5-61-05 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0003)</t>
         </is>
       </c>
-      <c r="C55" s="28" t="inlineStr">
+      <c r="C55" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2793,7 +2793,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E55" s="28" t="inlineStr">
+      <c r="E55" s="27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2806,7 +2806,7 @@
       <c r="G55" s="67" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="85" t="n">
+      <c r="A56" s="81" t="n">
         <v>54</v>
       </c>
       <c r="B56" s="83" t="inlineStr">
@@ -2814,7 +2814,7 @@
           <t>PS5-61-07 - 0.4kV Switchboard EITS Building (PS5-61-IK-0001)</t>
         </is>
       </c>
-      <c r="C56" s="28" t="inlineStr">
+      <c r="C56" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2824,7 +2824,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="E56" s="28" t="inlineStr">
+      <c r="E56" s="27" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -2837,7 +2837,7 @@
       <c r="G56" s="67" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="85" t="n">
+      <c r="A57" s="81" t="n">
         <v>55</v>
       </c>
       <c r="B57" s="83" t="inlineStr">
@@ -2845,7 +2845,7 @@
           <t>PS5-61-10 - Outdoor Valves Distribution Board - PS5-61-IG-0042</t>
         </is>
       </c>
-      <c r="C57" s="28" t="inlineStr">
+      <c r="C57" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2855,7 +2855,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E57" s="28" t="inlineStr">
+      <c r="E57" s="27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2868,7 +2868,7 @@
       <c r="G57" s="67" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="85" t="n">
+      <c r="A58" s="81" t="n">
         <v>56</v>
       </c>
       <c r="B58" s="83" t="inlineStr">
@@ -2876,7 +2876,7 @@
           <t>PS5-61-11 - Outdoor Valves Distribution Board - PS5-61-IG-0043</t>
         </is>
       </c>
-      <c r="C58" s="28" t="inlineStr">
+      <c r="C58" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2886,7 +2886,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E58" s="28" t="inlineStr">
+      <c r="E58" s="27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2899,7 +2899,7 @@
       <c r="G58" s="67" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="85" t="n">
+      <c r="A59" s="81" t="n">
         <v>57</v>
       </c>
       <c r="B59" s="83" t="inlineStr">
@@ -2907,7 +2907,7 @@
           <t>PS5-62-04 - Outdoor Emergency Lighting DB  - PS5-05-IG-0006</t>
         </is>
       </c>
-      <c r="C59" s="28" t="inlineStr">
+      <c r="C59" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2917,7 +2917,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E59" s="28" t="inlineStr">
+      <c r="E59" s="27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2930,7 +2930,7 @@
       <c r="G59" s="67" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="85" t="n">
+      <c r="A60" s="81" t="n">
         <v>58</v>
       </c>
       <c r="B60" s="83" t="inlineStr">
@@ -2938,13 +2938,13 @@
           <t>PS5-63-04 - Electrical Earthing - EITS Building</t>
         </is>
       </c>
-      <c r="C60" s="28" t="inlineStr">
+      <c r="C60" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
       <c r="D60" s="24" t="inlineStr"/>
-      <c r="E60" s="28" t="inlineStr">
+      <c r="E60" s="27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2953,7 +2953,7 @@
       <c r="G60" s="67" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="85" t="n">
+      <c r="A61" s="81" t="n">
         <v>59</v>
       </c>
       <c r="B61" s="83" t="inlineStr">
@@ -2961,7 +2961,7 @@
           <t>PS5-71-22 - Diesel Fuel Pre Pressure Module</t>
         </is>
       </c>
-      <c r="C61" s="28" t="inlineStr">
+      <c r="C61" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2971,7 +2971,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E61" s="28" t="inlineStr">
+      <c r="E61" s="27" t="inlineStr">
         <is>
           <t>DONE(full)</t>
         </is>
@@ -2984,7 +2984,7 @@
       <c r="G61" s="67" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="85" t="n">
+      <c r="A62" s="81" t="n">
         <v>60</v>
       </c>
       <c r="B62" s="83" t="inlineStr">
@@ -2992,7 +2992,7 @@
           <t>PS5-74-03 - Nitrogen Receiver</t>
         </is>
       </c>
-      <c r="C62" s="28" t="inlineStr">
+      <c r="C62" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3002,7 +3002,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E62" s="28" t="inlineStr">
+      <c r="E62" s="27" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -3015,7 +3015,7 @@
       <c r="G62" s="67" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="81" t="n">
+      <c r="A63" s="85" t="n">
         <v>61</v>
       </c>
       <c r="B63" s="83" t="inlineStr">
@@ -3023,7 +3023,7 @@
           <t>PS5-78-01 - Lifting and handling equipment</t>
         </is>
       </c>
-      <c r="C63" s="28" t="inlineStr">
+      <c r="C63" s="27" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
@@ -3046,7 +3046,7 @@
       <c r="G63" s="67" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="85" t="n">
+      <c r="A64" s="81" t="n">
         <v>62</v>
       </c>
       <c r="B64" s="83" t="inlineStr">
@@ -3054,7 +3054,7 @@
           <t>PS5-83-01 - EITS Building</t>
         </is>
       </c>
-      <c r="C64" s="28" t="inlineStr">
+      <c r="C64" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3064,7 +3064,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E64" s="28" t="inlineStr">
+      <c r="E64" s="27" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -3077,7 +3077,7 @@
       <c r="G64" s="67" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="85" t="n">
+      <c r="A65" s="81" t="n">
         <v>63</v>
       </c>
       <c r="B65" s="83" t="inlineStr">
@@ -3085,13 +3085,13 @@
           <t>PS5-84-03 - Shelters</t>
         </is>
       </c>
-      <c r="C65" s="28" t="inlineStr">
+      <c r="C65" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
       <c r="D65" s="24" t="inlineStr"/>
-      <c r="E65" s="28" t="inlineStr">
+      <c r="E65" s="27" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -3104,7 +3104,7 @@
       <c r="G65" s="67" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="85" t="n">
+      <c r="A66" s="81" t="n">
         <v>64</v>
       </c>
       <c r="B66" s="83" t="inlineStr">
@@ -3112,13 +3112,13 @@
           <t>PS5-86-01 - Shelters</t>
         </is>
       </c>
-      <c r="C66" s="28" t="inlineStr">
+      <c r="C66" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
       <c r="D66" s="24" t="inlineStr"/>
-      <c r="E66" s="28" t="inlineStr">
+      <c r="E66" s="27" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
@@ -3131,7 +3131,7 @@
       <c r="G66" s="67" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="85" t="n">
+      <c r="A67" s="81" t="n">
         <v>65</v>
       </c>
       <c r="B67" s="83" t="inlineStr">
@@ -3139,7 +3139,7 @@
           <t>PS5-91-01 - Multicore cables &amp; JB</t>
         </is>
       </c>
-      <c r="C67" s="28" t="inlineStr">
+      <c r="C67" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3149,7 +3149,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E67" s="28" t="inlineStr">
+      <c r="E67" s="27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3243,7 +3243,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B293"/>
+  <dimension ref="A1:B295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3825,2938 +3825,2962 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PS5-08-01a - PAGA (Required for SU)</t>
+          <t>PS5-08-01</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>PS5-08-01a</t>
+          <t>PS5-08-01</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PS5-08-01b - PAGA (Not required for SU)</t>
+          <t>PS5-08-01a - PAGA (Required for SU)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PS5-08-01b</t>
+          <t>PS5-08-01a</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PS5-08-03 - Telephone</t>
+          <t>PS5-08-01b - PAGA (Not required for SU)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>PS5-08-03</t>
+          <t>PS5-08-01b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>PS5-08-04 - Hotline</t>
+          <t>PS5-08-03 - Telephone</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PS5-08-04</t>
+          <t>PS5-08-03</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>PS5-08-07 - Multi-Channel Voice Recorder</t>
+          <t>PS5-08-04 - Hotline</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PS5-08-07</t>
+          <t>PS5-08-04</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>PS5-08-11 - Corporate LAN  (SIE)</t>
+          <t>PS5-08-07 - Multi-Channel Voice Recorder</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PS5-08-11</t>
+          <t>PS5-08-07</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>PS5-08-12 - Corporate Wireless LAN (SIE)</t>
+          <t>PS5-08-11 - Corporate LAN  (SIE)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PS5-08-12</t>
+          <t>PS5-08-11</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>PS5-08-13 - Safety Data Network (SII SP3 SAF)</t>
+          <t>PS5-08-12 - Corporate Wireless LAN (SIE)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PS5-08-13</t>
+          <t>PS5-08-12</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>PS5-08-14 - Industrial Data Network (SII SP1)</t>
+          <t>PS5-08-13 - Safety Data Network (SII SP3 SAF)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PS5-08-14</t>
+          <t>PS5-08-13</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PS5-08-15 - Security Data Network (SII SP3 SEC)</t>
+          <t>PS5-08-14 - Industrial Data Network (SII SP1)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PS5-08-15</t>
+          <t>PS5-08-14</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PS5-08-23 - VHF Trunk Radio System</t>
+          <t>PS5-08-15 - Security Data Network (SII SP3 SEC)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PS5-08-23</t>
+          <t>PS5-08-15</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PS5-08-34 - Satphone</t>
+          <t>PS5-08-23 - VHF Trunk Radio System</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PS5-08-34</t>
+          <t>PS5-08-23</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>PS5-08-35 - Optical Transport Network</t>
+          <t>PS5-08-34 - Satphone</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PS5-08-35</t>
+          <t>PS5-08-34</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>PS5-08-36 - Pipeline FO Cable &amp; EPRS</t>
+          <t>PS5-08-35 - Optical Transport Network</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>PS5-08-36</t>
+          <t>PS5-08-35</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>PS5-08-51 - Entertainment</t>
+          <t>PS5-08-36 - Pipeline FO Cable &amp; EPRS</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PS5-08-51</t>
+          <t>PS5-08-36</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>PS5-08-52a - Process &amp; Security CCTV (Required for SU)</t>
+          <t>PS5-08-51 - Entertainment</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PS5-08-52a</t>
+          <t>PS5-08-51</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>PS5-08-52b - Process &amp; Security CCTV (Not required for SU)</t>
+          <t>PS5-08-52a - Process &amp; Security CCTV (Required for SU)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PS5-08-52b</t>
+          <t>PS5-08-52a</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>PS5-08-55 - Videoconference</t>
+          <t>PS5-08-52b - Process &amp; Security CCTV (Not required for SU)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PS5-08-55</t>
+          <t>PS5-08-52b</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PS5-08-61 - Meteocean</t>
+          <t>PS5-08-55 - Videoconference</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PS5-08-61</t>
+          <t>PS5-08-55</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>PS5-08-71 - Structured Cabling (CAT6)</t>
+          <t>PS5-08-61 - Meteocean</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PS5-08-71</t>
+          <t>PS5-08-61</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>PS5-08-72 - Structured Cabling (FO)</t>
+          <t>PS5-08-71 - Structured Cabling (CAT6)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PS5-08-72</t>
+          <t>PS5-08-71</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>PS5-08-81 - Guard tour</t>
+          <t>PS5-08-72 - Structured Cabling (FO)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PS5-08-81</t>
+          <t>PS5-08-72</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>PS5-08-82 - Key Management</t>
+          <t>PS5-08-81 - Guard tour</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PS5-08-82</t>
+          <t>PS5-08-81</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>PS5-08-83 - Perimeter &amp; Pipeline intrusion detection system</t>
+          <t>PS5-08-82 - Key Management</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PS5-08-83</t>
+          <t>PS5-08-82</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>PS5-08-85a - Access Control, POB &amp; e-Mustering (Required for SU)</t>
+          <t>PS5-08-83 - Perimeter &amp; Pipeline intrusion detection system</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>PS5-08-85a</t>
+          <t>PS5-08-83</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>PS5-08-85b - Access Control, POB &amp; e-Mustering (Not required for SU)</t>
+          <t>PS5-08-85</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>PS5-08-85b</t>
+          <t>PS5-08-85</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>PS5-08-86 - Integrated Security Management System</t>
+          <t>PS5-08-85a - Access Control, POB &amp; e-Mustering (Required for SU)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PS5-08-86</t>
+          <t>PS5-08-85a</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>PS5-08-92 - Telecom Mast</t>
+          <t>PS5-08-85b - Access Control, POB &amp; e-Mustering (Not required for SU)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>PS5-08-92</t>
+          <t>PS5-08-85b</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>PS5-08-93 - Telecom Monitoring System</t>
+          <t>PS5-08-86 - Integrated Security Management System</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>PS5-08-93</t>
+          <t>PS5-08-86</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>PS5-09-01 - HVAC for Office and Facilities building</t>
+          <t>PS5-08-92 - Telecom Mast</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>PS5-09-01</t>
+          <t>PS5-08-92</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>PS5-09-02 - HVAC for Guard House</t>
+          <t>PS5-08-93 - Telecom Monitoring System</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>PS5-09-02</t>
+          <t>PS5-08-93</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>PS5-09-03 - HVAC for Generator Building</t>
+          <t>PS5-09-01 - HVAC for Office and Facilities building</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>PS5-09-03</t>
+          <t>PS5-09-01</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>PS5-09-04 - HVAC for Workshop &amp; Warehouse</t>
+          <t>PS5-09-02 - HVAC for Guard House</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>PS5-09-04</t>
+          <t>PS5-09-02</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>PS5-09-05 - HVAC for EITS Building</t>
+          <t>PS5-09-03 - HVAC for Generator Building</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>PS5-09-05</t>
+          <t>PS5-09-03</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>PS5-0H-01 - HIPPS</t>
+          <t>PS5-09-04 - HVAC for Workshop &amp; Warehouse</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>PS5-0H-01</t>
+          <t>PS5-09-04</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>PS5-25-01 - Export Pipeline Pig Receiver</t>
+          <t>PS5-09-05 - HVAC for EITS Building</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>PS5-25-01</t>
+          <t>PS5-09-05</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>PS5-25-02 - Crude Oil Export Pump A</t>
+          <t>PS5-0H-01 - HIPPS</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>PS5-25-02</t>
+          <t>PS5-0H-01</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>PS5-25-03 - Crude Oil Export Pump B</t>
+          <t>PS5-25-01 - Export Pipeline Pig Receiver</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>PS5-25-03</t>
+          <t>PS5-25-01</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>PS5-25-04 - Crude Oil Export Pump C</t>
+          <t>PS5-25-02 - Crude Oil Export Pump A</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>PS5-25-04</t>
+          <t>PS5-25-02</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>PS5-25-05 - Crude Oil Export Pumps Bypass</t>
+          <t>PS5-25-03 - Crude Oil Export Pump B</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>PS5-25-05</t>
+          <t>PS5-25-03</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>PS5-25-06 - Crude Oil Export Pumps Discharge</t>
+          <t>PS5-25-04 - Crude Oil Export Pump C</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>PS5-25-06</t>
+          <t>PS5-25-04</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>PS5-25-07 - Export Pipeline Pig Launcher</t>
+          <t>PS5-25-05 - Crude Oil Export Pumps Bypass</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>PS5-25-07</t>
+          <t>PS5-25-05</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>PS5-28-01 - Closed Drain Header 1</t>
+          <t>PS5-25-06 - Crude Oil Export Pumps Discharge</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>PS5-28-01</t>
+          <t>PS5-25-06</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>PS5-28-02 - Closed Drain Header 2</t>
+          <t>PS5-25-07 - Export Pipeline Pig Launcher</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>PS5-28-02</t>
+          <t>PS5-25-07</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>PS5-28-03 - Closed Drain Drum and Pump 01</t>
+          <t>PS5-28-01 - Closed Drain Header 1</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>PS5-28-03</t>
+          <t>PS5-28-01</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>PS5-28-04 - Closed Drain Drum and Pump 02</t>
+          <t>PS5-28-02 - Closed Drain Header 2</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>PS5-28-04</t>
+          <t>PS5-28-02</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>PS5-28-05 - HP Relief Header</t>
+          <t>PS5-28-03 - Closed Drain Drum and Pump 01</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>PS5-28-05</t>
+          <t>PS5-28-03</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>PS5-28-06 - Relief Drum and Pump</t>
+          <t>PS5-28-04 - Closed Drain Drum and Pump 02</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>PS5-28-06</t>
+          <t>PS5-28-04</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>PS5-28-07 - Open Drains (OD2)</t>
+          <t>PS5-28-05 - HP Relief Header</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>PS5-28-07</t>
+          <t>PS5-28-05</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>PS5-28-08 - Open Drain Sump and Pumps</t>
+          <t>PS5-28-06 - Relief Drum and Pump</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>PS5-28-08</t>
+          <t>PS5-28-06</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>PS5-28-09 - Observation Basin</t>
+          <t>PS5-28-07 - Open Drains (OD2)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>PS5-28-09</t>
+          <t>PS5-28-07</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>PS5-28-10 - Oil Skimmer Package</t>
+          <t>PS5-28-08 - Open Drain Sump and Pumps</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>PS5-28-10</t>
+          <t>PS5-28-08</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>PS5-28-11 - Open Drain Interceptor</t>
+          <t>PS5-28-09 - Observation Basin</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>PS5-28-11</t>
+          <t>PS5-28-09</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>PS5-28-12 - Open Drains (OD3)</t>
+          <t>PS5-28-10 - Oil Skimmer Package</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>PS5-28-12</t>
+          <t>PS5-28-10</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>PS5-28-13 - Seal Oil Drain Drum &amp; Pump A</t>
+          <t>PS5-28-11 - Open Drain Interceptor</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>PS5-28-13</t>
+          <t>PS5-28-11</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>PS5-28-14 - Seal Oil Drain Drum &amp; Pump B</t>
+          <t>PS5-28-12 - Open Drains (OD3)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>PS5-28-14</t>
+          <t>PS5-28-12</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>PS5-28-15 - Seal Oil Drain Drum &amp; Pump C</t>
+          <t>PS5-28-13 - Seal Oil Drain Drum &amp; Pump A</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>PS5-28-15</t>
+          <t>PS5-28-13</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>PS5-28-16 - LP Relief Header</t>
+          <t>PS5-28-14 - Seal Oil Drain Drum &amp; Pump B</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>PS5-28-16</t>
+          <t>PS5-28-14</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>PS5-28-17 - Reinjection Pump</t>
+          <t>PS5-28-15 - Seal Oil Drain Drum &amp; Pump C</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>PS5-28-17</t>
+          <t>PS5-28-15</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>PS5-50-01 - Water Well Submersible Pumps (3100)</t>
+          <t>PS5-28-16 - LP Relief Header</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>PS5-50-01</t>
+          <t>PS5-28-16</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>PS5-50-02 - Water Well Submersible Pumps (3200)</t>
+          <t>PS5-28-17 - Reinjection Pump</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>PS5-50-02</t>
+          <t>PS5-28-17</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>PS5-50-03 - Water Pre-Treatment Package</t>
+          <t>PS5-50-01 - Water Well Submersible Pumps (3100)</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>PS5-50-03</t>
+          <t>PS5-50-01</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>PS5-53-01 - Utility Water / Storage Tank</t>
+          <t>PS5-50-02 - Water Well Submersible Pumps (3200)</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>PS5-53-01</t>
+          <t>PS5-50-02</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>PS5-53-02 - Water Distribution Pump A/B</t>
+          <t>PS5-50-03 - Water Pre-Treatment Package</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>PS5-53-02</t>
+          <t>PS5-50-03</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>PS5-53-03 - Water Softener Package</t>
+          <t>PS5-53-01 - Utility Water / Storage Tank</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>PS5-53-03</t>
+          <t>PS5-53-01</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>PS5-53-04 - Water Treatment Purification Package</t>
+          <t>PS5-53-02 - Water Distribution Pump A/B</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>PS5-53-04</t>
+          <t>PS5-53-02</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>PS5-53-05 - Water Distribution Header</t>
+          <t>PS5-53-03 - Water Softener Package</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>PS5-53-05</t>
+          <t>PS5-53-03</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>PS5-53-06 - Water Distribution Consumers</t>
+          <t>PS5-53-04 - Water Treatment Purification Package</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>PS5-53-06</t>
+          <t>PS5-53-04</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>PS5-60-01 - Power Generation Package A</t>
+          <t>PS5-53-05 - Water Distribution Header</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>PS5-60-01</t>
+          <t>PS5-53-05</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>PS5-60-02 - Power Gen Package A (UCP)</t>
+          <t>PS5-53-06 - Water Distribution Consumers</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>PS5-60-02</t>
+          <t>PS5-53-06</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>PS5-60-03 - Power Gen Package A Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-60-01 - Power Generation Package A</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>PS5-60-03</t>
+          <t>PS5-60-01</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>PS5-60-04 - Power Generation Package B</t>
+          <t>PS5-60-02 - Power Gen Package A (UCP)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>PS5-60-04</t>
+          <t>PS5-60-02</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>PS5-60-05 - Power Gen Package B (UCP)</t>
+          <t>PS5-60-03 - Power Gen Package A Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>PS5-60-05</t>
+          <t>PS5-60-03</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>PS5-60-06 - Power Gen Package B Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-60-04 - Power Generation Package B</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>PS5-60-06</t>
+          <t>PS5-60-04</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>PS5-60-07 - Power Generation Package C</t>
+          <t>PS5-60-05 - Power Gen Package B (UCP)</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>PS5-60-07</t>
+          <t>PS5-60-05</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>PS5-60-08 - Power Gen Package C (UCP)</t>
+          <t>PS5-60-06 - Power Gen Package B Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>PS5-60-08</t>
+          <t>PS5-60-06</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>PS5-60-09 - Power Gen Package C Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-60-07 - Power Generation Package C</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>PS5-60-09</t>
+          <t>PS5-60-07</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>PS5-60-10 - Power Generation Package D</t>
+          <t>PS5-60-08 - Power Gen Package C (UCP)</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>PS5-60-10</t>
+          <t>PS5-60-08</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>PS5-60-11 - Power Gen Package D (UCP)</t>
+          <t>PS5-60-09 - Power Gen Package C Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>PS5-60-11</t>
+          <t>PS5-60-09</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>PS5-60-12 - Power Gen Package D Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-60-10 - Power Generation Package D</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>PS5-60-12</t>
+          <t>PS5-60-10</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>PS5-60-13 - Power Generation Package E</t>
+          <t>PS5-60-11 - Power Gen Package D (UCP)</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PS5-60-13</t>
+          <t>PS5-60-11</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>PS5-60-14 - Power Gen Package E (UCP)</t>
+          <t>PS5-60-12 - Power Gen Package D Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PS5-60-14</t>
+          <t>PS5-60-12</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>PS5-60-15 - Power Gen Package E Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-60-13 - Power Generation Package E</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PS5-60-15</t>
+          <t>PS5-60-13</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>PS5-60-16 - Power Generation Package F</t>
+          <t>PS5-60-14 - Power Gen Package E (UCP)</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PS5-60-16</t>
+          <t>PS5-60-14</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>PS5-60-17 - Power Gen Package F (UCP)</t>
+          <t>PS5-60-15 - Power Gen Package E Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PS5-60-17</t>
+          <t>PS5-60-15</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>PS5-60-18 - Power Gen Package F Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-60-16 - Power Generation Package F</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PS5-60-18</t>
+          <t>PS5-60-16</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>PS5-60-19 - Power Generation Package G</t>
+          <t>PS5-60-17 - Power Gen Package F (UCP)</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PS5-60-19</t>
+          <t>PS5-60-17</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>PS5-60-20 - Power Gen Package G (UCP)</t>
+          <t>PS5-60-18 - Power Gen Package F Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>PS5-60-20</t>
+          <t>PS5-60-18</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>PS5-60-21 - Power Gen Package G Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-60-19 - Power Generation Package G</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>PS5-60-21</t>
+          <t>PS5-60-19</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>PS5-60-22 - Power Gen Master UCP</t>
+          <t>PS5-60-20 - Power Gen Package G (UCP)</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>PS5-60-22</t>
+          <t>PS5-60-20</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>PS5-60-23 - Instrument Air Distribution lines</t>
+          <t>PS5-60-21 - Power Gen Package G Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>PS5-60-23</t>
+          <t>PS5-60-21</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>PS5-60-24 - Cooling Water Tank &amp; Pump</t>
+          <t>PS5-60-22 - Power Gen Master UCP</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>PS5-60-24</t>
+          <t>PS5-60-22</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>PS5-60-25 - Cooling Water Maintenance Tank &amp; Return Pump</t>
+          <t>PS5-60-23 - Instrument Air Distribution lines</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>PS5-60-25</t>
+          <t>PS5-60-23</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>PS5-60-26 - Instrument Air Compressor Skid</t>
+          <t>PS5-60-24 - Cooling Water Tank &amp; Pump</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>PS5-60-26</t>
+          <t>PS5-60-24</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>PS5-60-27 - Compressed Air Starting Skid</t>
+          <t>PS5-60-25 - Cooling Water Maintenance Tank &amp; Return Pump</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>PS5-60-27</t>
+          <t>PS5-60-25</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>PS5-60-28 - Air Receiver A &amp; Air Regulator A</t>
+          <t>PS5-60-26 - Instrument Air Compressor Skid</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>PS5-60-28</t>
+          <t>PS5-60-26</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>PS5-60-29 - Air Receiver B &amp; Air Regulator B</t>
+          <t>PS5-60-27 - Compressed Air Starting Skid</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>PS5-60-29</t>
+          <t>PS5-60-27</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>PS5-60-30 - Air Receiver C &amp; Air Regulator C</t>
+          <t>PS5-60-28 - Air Receiver A &amp; Air Regulator A</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>PS5-60-30</t>
+          <t>PS5-60-28</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>PS5-60-31 - Air Receiver D &amp; Air Regulator D</t>
+          <t>PS5-60-29 - Air Receiver B &amp; Air Regulator B</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>PS5-60-31</t>
+          <t>PS5-60-29</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>PS5-60-32 - Air Receiver E &amp; Air Regulator E</t>
+          <t>PS5-60-30 - Air Receiver C &amp; Air Regulator C</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>PS5-60-32</t>
+          <t>PS5-60-30</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>PS5-60-33 - Air Receiver F &amp; Air Regulator F</t>
+          <t>PS5-60-31 - Air Receiver D &amp; Air Regulator D</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>PS5-60-33</t>
+          <t>PS5-60-31</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>PS5-60-34 - Air Receiver G &amp; Air Regulator G</t>
+          <t>PS5-60-32 - Air Receiver E &amp; Air Regulator E</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>PS5-60-34</t>
+          <t>PS5-60-32</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>PS5-60-35 - Injector Tip Cooling Module A</t>
+          <t>PS5-60-33 - Air Receiver F &amp; Air Regulator F</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>PS5-60-35</t>
+          <t>PS5-60-33</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>PS5-60-36 - Injector Tip Cooling Module B</t>
+          <t>PS5-60-34 - Air Receiver G &amp; Air Regulator G</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>PS5-60-36</t>
+          <t>PS5-60-34</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>PS5-60-37 - Injector Tip Cooling Module C</t>
+          <t>PS5-60-35 - Injector Tip Cooling Module A</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>PS5-60-37</t>
+          <t>PS5-60-35</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>PS5-60-38 - Injector Tip Cooling Module D</t>
+          <t>PS5-60-36 - Injector Tip Cooling Module B</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>PS5-60-38</t>
+          <t>PS5-60-36</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>PS5-60-39 - Injector Tip Cooling Module E</t>
+          <t>PS5-60-37 - Injector Tip Cooling Module C</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>PS5-60-39</t>
+          <t>PS5-60-37</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>PS5-60-40 - Injector Tip Cooling Module F</t>
+          <t>PS5-60-38 - Injector Tip Cooling Module D</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>PS5-60-40</t>
+          <t>PS5-60-38</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>PS5-60-41 - Injector Tip Cooling Module G</t>
+          <t>PS5-60-39 - Injector Tip Cooling Module E</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>PS5-60-41</t>
+          <t>PS5-60-39</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>PS5-60-42 - Oil Mist Separator Skid PS5-60-VS-9100A</t>
+          <t>PS5-60-40 - Injector Tip Cooling Module F</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>PS5-60-42</t>
+          <t>PS5-60-40</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>PS5-60-43 - Oil Mist Separator Skid PS5-60-VS-9100B</t>
+          <t>PS5-60-41 - Injector Tip Cooling Module G</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>PS5-60-43</t>
+          <t>PS5-60-41</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>PS5-60-44 - Oil Mist Separator Skid PS5-60-VS-9100C</t>
+          <t>PS5-60-42 - Oil Mist Separator Skid PS5-60-VS-9100A</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>PS5-60-44</t>
+          <t>PS5-60-42</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>PS5-60-45 - Oil Mist Separator Skid PS5-60-VS-9100D</t>
+          <t>PS5-60-43 - Oil Mist Separator Skid PS5-60-VS-9100B</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>PS5-60-45</t>
+          <t>PS5-60-43</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>PS5-60-46 - Oil Mist Separator Skid PS5-60-VS-9100E</t>
+          <t>PS5-60-44 - Oil Mist Separator Skid PS5-60-VS-9100C</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>PS5-60-46</t>
+          <t>PS5-60-44</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>PS5-60-47 - Oil Mist Separator Skid PS5-60-VS-9100F</t>
+          <t>PS5-60-45 - Oil Mist Separator Skid PS5-60-VS-9100D</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>PS5-60-47</t>
+          <t>PS5-60-45</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>PS5-60-48 - Oil Mist Separator Skid PS5-60-VS-9100G</t>
+          <t>PS5-60-46 - Oil Mist Separator Skid PS5-60-VS-9100E</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>PS5-60-48</t>
+          <t>PS5-60-46</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>PS5-60-49 - Lube Oil Separator Module PS5-60-UO-81100A</t>
+          <t>PS5-60-47 - Oil Mist Separator Skid PS5-60-VS-9100F</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>PS5-60-49</t>
+          <t>PS5-60-47</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>PS5-60-50 - Lube Oil Separator Module PS5-60-UO-81100B</t>
+          <t>PS5-60-48 - Oil Mist Separator Skid PS5-60-VS-9100G</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>PS5-60-50</t>
+          <t>PS5-60-48</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>PS5-60-51 - Lube Oil Separator Module PS5-60-UO-81100C</t>
+          <t>PS5-60-49 - Lube Oil Separator Module PS5-60-UO-81100A</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>PS5-60-51</t>
+          <t>PS5-60-49</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>PS5-60-52 - Lube Oil Separator Module PS5-60-UO-81100D</t>
+          <t>PS5-60-50 - Lube Oil Separator Module PS5-60-UO-81100B</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>PS5-60-52</t>
+          <t>PS5-60-50</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>PS5-60-53 - Lube Oil Separator Module PS5-60-UO-81100E</t>
+          <t>PS5-60-51 - Lube Oil Separator Module PS5-60-UO-81100C</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>PS5-60-53</t>
+          <t>PS5-60-51</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>PS5-60-54 - Lube Oil Separator Module PS5-60-UO-81100F</t>
+          <t>PS5-60-52 - Lube Oil Separator Module PS5-60-UO-81100D</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>PS5-60-54</t>
+          <t>PS5-60-52</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>PS5-60-55 - Lube Oil Separator Module PS5-60-UO-81100G</t>
+          <t>PS5-60-53 - Lube Oil Separator Module PS5-60-UO-81100E</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>PS5-60-55</t>
+          <t>PS5-60-53</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>PS5-60-56 - Fuel Conditioning Module PS5-60-UZ-8900A</t>
+          <t>PS5-60-54 - Lube Oil Separator Module PS5-60-UO-81100F</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>PS5-60-56</t>
+          <t>PS5-60-54</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>PS5-60-57 - Fuel Conditioning Module PS5-60-UZ-8900A (UCP)</t>
+          <t>PS5-60-55 - Lube Oil Separator Module PS5-60-UO-81100G</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>PS5-60-57</t>
+          <t>PS5-60-55</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>PS5-60-58 - Fuel Conditioning Module PS5-60-UZ-8900B</t>
+          <t>PS5-60-56 - Fuel Conditioning Module PS5-60-UZ-8900A</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>PS5-60-58</t>
+          <t>PS5-60-56</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>PS5-60-59 - Fuel Conditioning Module PS5-60-UZ-8900B (UCP)</t>
+          <t>PS5-60-57 - Fuel Conditioning Module PS5-60-UZ-8900A (UCP)</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>PS5-60-59</t>
+          <t>PS5-60-57</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>PS5-60-60 - Fuel Conditioning Module PS5-60-UZ-8900C</t>
+          <t>PS5-60-58 - Fuel Conditioning Module PS5-60-UZ-8900B</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>PS5-60-60</t>
+          <t>PS5-60-58</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>PS5-60-61 - Fuel Conditioning Module PS5-60-UZ-8900C (UCP)</t>
+          <t>PS5-60-59 - Fuel Conditioning Module PS5-60-UZ-8900B (UCP)</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>PS5-60-61</t>
+          <t>PS5-60-59</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>PS5-60-62 - Fuel Conditioning Module PS5-60-UZ-8900D</t>
+          <t>PS5-60-60 - Fuel Conditioning Module PS5-60-UZ-8900C</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>PS5-60-62</t>
+          <t>PS5-60-60</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>PS5-60-63 - Fuel Conditioning Module PS5-60-UZ-8900D (UCP)</t>
+          <t>PS5-60-61 - Fuel Conditioning Module PS5-60-UZ-8900C (UCP)</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>PS5-60-63</t>
+          <t>PS5-60-61</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>PS5-60-64 - Fuel Conditioning Module PS5-60-UZ-8900E</t>
+          <t>PS5-60-62 - Fuel Conditioning Module PS5-60-UZ-8900D</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>PS5-60-64</t>
+          <t>PS5-60-62</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>PS5-60-65 - Fuel Conditioning Module PS5-60-UZ-8900E (UCP)</t>
+          <t>PS5-60-63 - Fuel Conditioning Module PS5-60-UZ-8900D (UCP)</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>PS5-60-65</t>
+          <t>PS5-60-63</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>PS5-60-66 - Fuel Conditioning Module PS5-60-UZ-8900F</t>
+          <t>PS5-60-64 - Fuel Conditioning Module PS5-60-UZ-8900E</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>PS5-60-66</t>
+          <t>PS5-60-64</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>PS5-60-67 - Fuel Conditioning Module PS5-60-UZ-8900F (UCP)</t>
+          <t>PS5-60-65 - Fuel Conditioning Module PS5-60-UZ-8900E (UCP)</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>PS5-60-67</t>
+          <t>PS5-60-65</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>PS5-60-68 - Fuel Conditioning Module PS5-60-UZ-8900G</t>
+          <t>PS5-60-66 - Fuel Conditioning Module PS5-60-UZ-8900F</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>PS5-60-68</t>
+          <t>PS5-60-66</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>PS5-60-69 - Fuel Conditioning Module PS5-60-UZ-8900G (UCP)</t>
+          <t>PS5-60-67 - Fuel Conditioning Module PS5-60-UZ-8900F (UCP)</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>PS5-60-69</t>
+          <t>PS5-60-67</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>PS5-60-70 - Engine A Cooling system</t>
+          <t>PS5-60-68 - Fuel Conditioning Module PS5-60-UZ-8900G</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>PS5-60-70</t>
+          <t>PS5-60-68</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>PS5-60-71 - Engine B Cooling system</t>
+          <t>PS5-60-69 - Fuel Conditioning Module PS5-60-UZ-8900G (UCP)</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>PS5-60-71</t>
+          <t>PS5-60-69</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>PS5-60-72 - Engine C Cooling system</t>
+          <t>PS5-60-70 - Engine A Cooling system</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>PS5-60-72</t>
+          <t>PS5-60-70</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>PS5-60-73 - Engine D Cooling system</t>
+          <t>PS5-60-71 - Engine B Cooling system</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>PS5-60-73</t>
+          <t>PS5-60-71</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>PS5-60-74 - Engine E Cooling system</t>
+          <t>PS5-60-72 - Engine C Cooling system</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>PS5-60-74</t>
+          <t>PS5-60-72</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>PS5-60-75 - Engine F Cooling system</t>
+          <t>PS5-60-73 - Engine D Cooling system</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>PS5-60-75</t>
+          <t>PS5-60-73</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>PS5-60-76 - Engine G Cooling system</t>
+          <t>PS5-60-74 - Engine E Cooling system</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>PS5-60-76</t>
+          <t>PS5-60-74</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>PS5-61-01 - 33kV Switchboard EITS Building (PS5-61-IJ-0001)</t>
+          <t>PS5-60-75 - Engine F Cooling system</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>PS5-61-01</t>
+          <t>PS5-60-75</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>PS5-61-02 - 6.6kV Switchboard and Transformer LLHT North - EITS Building (PS5-61-IJ-0010)</t>
+          <t>PS5-60-76 - Engine G Cooling system</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>PS5-61-02</t>
+          <t>PS5-60-76</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>PS5-61-03 - 6.6kV Switchboard and Transformer LLHT South - EITS Building (PS5-61-IJ-0011)</t>
+          <t>PS5-61-01 - 33kV Switchboard EITS Building (PS5-61-IJ-0001)</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>PS5-61-03</t>
+          <t>PS5-61-01</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>PS5-61-04 - 0.4kV Switchboard Office &amp; Facilities Building (PS5-61-IK-0005)</t>
+          <t>PS5-61-02 - 6.6kV Switchboard and Transformer LLHT North - EITS Building (PS5-61-IJ-0010)</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>PS5-61-04</t>
+          <t>PS5-61-02</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>PS5-61-05 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0003)</t>
+          <t>PS5-61-03 - 6.6kV Switchboard and Transformer LLHT South - EITS Building (PS5-61-IJ-0011)</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>PS5-61-05</t>
+          <t>PS5-61-03</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>PS5-61-06 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0006)</t>
+          <t>PS5-61-04 - 0.4kV Switchboard Office &amp; Facilities Building (PS5-61-IK-0005)</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>PS5-61-06</t>
+          <t>PS5-61-04</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>PS5-61-07 - 0.4kV Switchboard EITS Building (PS5-61-IK-0001)</t>
+          <t>PS5-61-05 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0003)</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>PS5-61-07</t>
+          <t>PS5-61-05</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>PS5-61-08 - Electrical Control System</t>
+          <t>PS5-61-06 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0006)</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>PS5-61-08</t>
+          <t>PS5-61-06</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>PS5-61-09 - Outdoor Power Distribution Board - PS5-61-IG-0014</t>
+          <t>PS5-61-07 - 0.4kV Switchboard EITS Building (PS5-61-IK-0001)</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>PS5-61-09</t>
+          <t>PS5-61-07</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>PS5-61-10 - Outdoor Valves Distribution Board - PS5-61-IG-0042</t>
+          <t>PS5-61-08 - Electrical Control System</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>PS5-61-10</t>
+          <t>PS5-61-08</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>PS5-61-11 - Outdoor Valves Distribution Board - PS5-61-IG-0043</t>
+          <t>PS5-61-09 - Outdoor Power Distribution Board - PS5-61-IG-0014</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>PS5-61-11</t>
+          <t>PS5-61-09</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>PS5-61-12 - EITS 33kV Bld. Normal Auxiliary DP - PS5-61-IG-0008</t>
+          <t>PS5-61-10 - Outdoor Valves Distribution Board - PS5-61-IG-0042</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>PS5-61-12</t>
+          <t>PS5-61-10</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>PS5-61-13 - Power Distribution Board Office Building - PS5-61-IG-0020</t>
+          <t>PS5-61-11 - Outdoor Valves Distribution Board - PS5-61-IG-0043</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>PS5-61-13</t>
+          <t>PS5-61-11</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>PS5-61-14 - Power Distribution Board Workshop &amp; Warehouse - PS5-61-IG-0009</t>
+          <t>PS5-61-12 - EITS 33kV Bld. Normal Auxiliary DP - PS5-61-IG-0008</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>PS5-61-14</t>
+          <t>PS5-61-12</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>PS5-62-01 - Lighting Control Panel - PS5-62-IE-0001</t>
+          <t>PS5-61-13 - Power Distribution Board Office Building - PS5-61-IG-0020</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>PS5-62-01</t>
+          <t>PS5-61-13</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>PS5-62-02 - Lighting Control Panel - PS5-62-IE-0002</t>
+          <t>PS5-61-14 - Power Distribution Board Workshop &amp; Warehouse - PS5-61-IG-0009</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>PS5-62-02</t>
+          <t>PS5-61-14</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>PS5-62-03 - Outdoor Emergency Lighting DB  - PS5-05-IG-0004</t>
+          <t>PS5-62-01 - Lighting Control Panel - PS5-62-IE-0001</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>PS5-62-03</t>
+          <t>PS5-62-01</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>PS5-62-04 - Outdoor Emergency Lighting DB  - PS5-05-IG-0006</t>
+          <t>PS5-62-02 - Lighting Control Panel - PS5-62-IE-0002</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>PS5-62-04</t>
+          <t>PS5-62-02</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>PS5-62-05 - Guard House Emergency L&amp;SP DB  - PS5-05-IG-0007</t>
+          <t>PS5-62-03 - Outdoor Emergency Lighting DB  - PS5-05-IG-0004</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>PS5-62-05</t>
+          <t>PS5-62-03</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>PS5-62-06 - CRO Generator Building Emergency Lighting DB  - PS5-05-IG-0025</t>
+          <t>PS5-62-04 - Outdoor Emergency Lighting DB  - PS5-05-IG-0006</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>PS5-62-06</t>
+          <t>PS5-62-04</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>PS5-62-07 - CRO Generator Electrical Building Emergency Lighting DB  - PS5-05-IG-0026</t>
+          <t>PS5-62-05 - Guard House Emergency L&amp;SP DB  - PS5-05-IG-0007</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>PS5-62-07</t>
+          <t>PS5-62-05</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>PS5-62-08 - Outdoor Normal Lighting  DB  - PS5-61-IG-0006</t>
+          <t>PS5-62-06 - CRO Generator Building Emergency Lighting DB  - PS5-05-IG-0025</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>PS5-62-08</t>
+          <t>PS5-62-06</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>PS5-62-09 - Outdoor Normal Lighting DB  - PS5-61-IG-0007</t>
+          <t>PS5-62-07 - CRO Generator Electrical Building Emergency Lighting DB  - PS5-05-IG-0026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>PS5-62-09</t>
+          <t>PS5-62-07</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>PS5-62-10 - CRO Generator Building Normal L&amp;SP DB  - PS5-61-IG-0015</t>
+          <t>PS5-62-08 - Outdoor Normal Lighting  DB  - PS5-61-IG-0006</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>PS5-62-10</t>
+          <t>PS5-62-08</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>PS5-62-11 - CRO Generator Electrical Building Normal L&amp;SP DB  - PS5-61-IG-0016</t>
+          <t>PS5-62-09 - Outdoor Normal Lighting DB  - PS5-61-IG-0007</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>PS5-62-11</t>
+          <t>PS5-62-09</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>PS5-62-12 - EITS 33kV Bld. Emergency L&amp;SP DP - PS5-05-IG-0003</t>
+          <t>PS5-62-10 - CRO Generator Building Normal L&amp;SP DB  - PS5-61-IG-0015</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>PS5-62-12</t>
+          <t>PS5-62-10</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>PS5-62-13 - EITS 33kV Bld. Normal L&amp;SP DP - PS5-61-IG-0003</t>
+          <t>PS5-62-11 - CRO Generator Electrical Building Normal L&amp;SP DB  - PS5-61-IG-0016</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>PS5-62-13</t>
+          <t>PS5-62-11</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>PS5-62-14 - Office Building Emergency L&amp;SP DB - PS5-05-IG-0002</t>
+          <t>PS5-62-12 - EITS 33kV Bld. Emergency L&amp;SP DP - PS5-05-IG-0003</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>PS5-62-14</t>
+          <t>PS5-62-12</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>PS5-62-15 - Office Building Normal L&amp;SP DB - PS5-61-IG-0002</t>
+          <t>PS5-62-13 - EITS 33kV Bld. Normal L&amp;SP DP - PS5-61-IG-0003</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>PS5-62-15</t>
+          <t>PS5-62-13</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>PS5-62-16 - Guard Hut A Normal L&amp;SP DB - PS5-61-IG-0111</t>
+          <t>PS5-62-14 - Office Building Emergency L&amp;SP DB - PS5-05-IG-0002</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>PS5-62-16</t>
+          <t>PS5-62-14</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>PS5-62-17 - Guard Hut B Normal L&amp;SP DB - PS5-61-IG-0112</t>
+          <t>PS5-62-15 - Office Building Normal L&amp;SP DB - PS5-61-IG-0002</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>PS5-62-17</t>
+          <t>PS5-62-15</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>PS5-62-18 - Workshop &amp; Warehouse Normal L&amp;SP DB - PS5-61-IG-0004</t>
+          <t>PS5-62-16 - Guard Hut A Normal L&amp;SP DB - PS5-61-IG-0111</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>PS5-62-18</t>
+          <t>PS5-62-16</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>PS5-62-19 - Workshop &amp; Warehouse Emergency L&amp;SP DB - PS5-05-IG-0101</t>
+          <t>PS5-62-17 - Guard Hut B Normal L&amp;SP DB - PS5-61-IG-0112</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>PS5-62-19</t>
+          <t>PS5-62-17</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>PS5-62-20 - Office Building Normal L&amp;SP DB - PS5-61-IG-0010</t>
+          <t>PS5-62-18 - Workshop &amp; Warehouse Normal L&amp;SP DB - PS5-61-IG-0004</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>PS5-62-20</t>
+          <t>PS5-62-18</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>PS5-63-01 - Electrical Earthing</t>
+          <t>PS5-62-19 - Workshop &amp; Warehouse Emergency L&amp;SP DB - PS5-05-IG-0101</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>PS5-63-01</t>
+          <t>PS5-62-19</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>PS5-63-02 - Electrical Earthing - Office and Facilities building</t>
+          <t>PS5-62-20 - Office Building Normal L&amp;SP DB - PS5-61-IG-0010</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>PS5-63-02</t>
+          <t>PS5-62-20</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>PS5-63-03 - Electrical Earthing - Generator Building</t>
+          <t>PS5-63-01 - Electrical Earthing</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>PS5-63-03</t>
+          <t>PS5-63-01</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>PS5-63-04 - Electrical Earthing - EITS Building</t>
+          <t>PS5-63-02 - Electrical Earthing - Office and Facilities building</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>PS5-63-04</t>
+          <t>PS5-63-02</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>PS5-63-05 - Electrical Earthing - Guard Hut A &amp; B</t>
+          <t>PS5-63-03 - Electrical Earthing - Generator Building</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>PS5-63-05</t>
+          <t>PS5-63-03</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>PS5-63-06 - Electrical Earthing - Guard House</t>
+          <t>PS5-63-04 - Electrical Earthing - EITS Building</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>PS5-63-06</t>
+          <t>PS5-63-04</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>PS5-63-07 - Electrical Earthing - Workshop &amp; Warehouse</t>
+          <t>PS5-63-05 - Electrical Earthing - Guard Hut A &amp; B</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>PS5-63-07</t>
+          <t>PS5-63-05</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>PS5-71-01 - CFO Storage Tank Feed Heater</t>
+          <t>PS5-63-06 - Electrical Earthing - Guard House</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>PS5-71-01</t>
+          <t>PS5-63-06</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>PS5-71-02 - CFO Allocation Metering Package</t>
+          <t>PS5-63-07 - Electrical Earthing - Workshop &amp; Warehouse</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>PS5-71-02</t>
+          <t>PS5-63-07</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>PS5-71-03 - CFO Allocation Metering Package (UCP)</t>
+          <t>PS5-71-01 - CFO Storage Tank Feed Heater</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>PS5-71-03</t>
+          <t>PS5-71-01</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>PS5-71-04 - CFO Storage Tank</t>
+          <t>PS5-71-02 - CFO Allocation Metering Package</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>PS5-71-04</t>
+          <t>PS5-71-02</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>PS5-71-05 - CFO Transfer Pump A/B</t>
+          <t>PS5-71-03 - CFO Allocation Metering Package (UCP)</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>PS5-71-05</t>
+          <t>PS5-71-03</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>PS5-71-06 - Crude Fuel Separation Module</t>
+          <t>PS5-71-04 - CFO Storage Tank</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>PS5-71-06</t>
+          <t>PS5-71-04</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>PS5-71-07 - Crude Fuel Separation Module (UCP)</t>
+          <t>PS5-71-05 - CFO Transfer Pump A/B</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>PS5-71-07</t>
+          <t>PS5-71-05</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>PS5-71-08 - CFO Pre-Pressure Modules</t>
+          <t>PS5-71-06 - Crude Fuel Separation Module</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>PS5-71-08</t>
+          <t>PS5-71-06</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>PS5-71-09 - CFO Pre-Pressure Modules (UCP)</t>
+          <t>PS5-71-07 - Crude Fuel Separation Module (UCP)</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>PS5-71-09</t>
+          <t>PS5-71-07</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>PS5-71-12 - CFO Service Tank</t>
+          <t>PS5-71-08 - CFO Pre-Pressure Modules</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>PS5-71-12</t>
+          <t>PS5-71-08</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>PS5-71-13 - CFO Service Pump A/B</t>
+          <t>PS5-71-09 - CFO Pre-Pressure Modules (UCP)</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>PS5-71-13</t>
+          <t>PS5-71-09</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>PS5-71-14 - Diesel Fuel Transfer and Dispensing Station</t>
+          <t>PS5-71-12 - CFO Service Tank</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>PS5-71-14</t>
+          <t>PS5-71-12</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>PS5-71-15 - Diesel Fuel Storage Tank</t>
+          <t>PS5-71-13 - CFO Service Pump A/B</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>PS5-71-15</t>
+          <t>PS5-71-13</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>PS5-71-16 - Diesel Fuel Supply Pump A/B</t>
+          <t>PS5-71-14 - Diesel Fuel Transfer and Dispensing Station</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>PS5-71-16</t>
+          <t>PS5-71-14</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>PS5-71-17 - Diesel Fuel Distribution Header</t>
+          <t>PS5-71-15 - Diesel Fuel Storage Tank</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>PS5-71-17</t>
+          <t>PS5-71-15</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>PS5-71-18 - Diesel Separator Module</t>
+          <t>PS5-71-16 - Diesel Fuel Supply Pump A/B</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>PS5-71-18</t>
+          <t>PS5-71-16</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>PS5-71-19 - Diesel Separator Module (UCP)</t>
+          <t>PS5-71-17 - Diesel Fuel Distribution Header</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>PS5-71-19</t>
+          <t>PS5-71-17</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>PS5-71-20 - Diesel Fuel Day Tank</t>
+          <t>PS5-71-18 - Diesel Separator Module</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>PS5-71-20</t>
+          <t>PS5-71-18</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>PS5-71-21 - Diesel Transfer Pump A/B</t>
+          <t>PS5-71-19 - Diesel Separator Module (UCP)</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>PS5-71-21</t>
+          <t>PS5-71-19</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>PS5-71-22 - Diesel Fuel Pre Pressure Module</t>
+          <t>PS5-71-20 - Diesel Fuel Day Tank</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>PS5-71-22</t>
+          <t>PS5-71-20</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>PS5-71-23 - Diesel Fuel Pre Pressure Module (UCP)</t>
+          <t>PS5-71-21 - Diesel Transfer Pump A/B</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>PS5-71-23</t>
+          <t>PS5-71-21</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>PS5-74-01 - N2 Generation Skid</t>
+          <t>PS5-71-22 - Diesel Fuel Pre Pressure Module</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>PS5-74-01</t>
+          <t>PS5-71-22</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>PS5-74-02 - N2 Generation Skid (UCP)</t>
+          <t>PS5-71-23 - Diesel Fuel Pre Pressure Module (UCP)</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>PS5-74-02</t>
+          <t>PS5-71-23</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>PS5-74-03 - Nitrogen Receiver</t>
+          <t>PS5-74-01 - N2 Generation Skid</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>PS5-74-03</t>
+          <t>PS5-74-01</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>PS5-74-04 - Nitrogen Distribution Header</t>
+          <t>PS5-74-02 - N2 Generation Skid (UCP)</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>PS5-74-04</t>
+          <t>PS5-74-02</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>PS5-75-01 - DRA Injection Package</t>
+          <t>PS5-74-03 - Nitrogen Receiver</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>PS5-75-01</t>
+          <t>PS5-74-03</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>PS5-75-02 - Biocide Injection Package</t>
+          <t>PS5-74-04 - Nitrogen Distribution Header</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>PS5-75-02</t>
+          <t>PS5-74-04</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>PS5-75-03 - Corrosion Inhibitor Injection Package</t>
+          <t>PS5-75-01 - DRA Injection Package</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>PS5-75-03</t>
+          <t>PS5-75-01</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>PS5-78-01 - Lifting and handling equipment</t>
+          <t>PS5-75-02 - Biocide Injection Package</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>PS5-78-01</t>
+          <t>PS5-75-02</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>PS5-79-01 - Electrical Heat Tracing Transformer/Distribution Board 1 (PS5-79-IG-0001)</t>
+          <t>PS5-75-03 - Corrosion Inhibitor Injection Package</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>PS5-79-01</t>
+          <t>PS5-75-03</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>PS5-79-02 - Electrical Heat Tracing Transformer/Distribution Board 2 (PS5-79-IG-0002)</t>
+          <t>PS5-78-01 - Lifting and handling equipment</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>PS5-79-02</t>
+          <t>PS5-78-01</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>PS5-79-03 - Electrical Heat Tracing Transformer/Distribution Board 3 (PS5-79-IG-0003)</t>
+          <t>PS5-79-01 - Electrical Heat Tracing Transformer/Distribution Board 1 (PS5-79-IG-0001)</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>PS5-79-03</t>
+          <t>PS5-79-01</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>PS5-79-04 - Electrical Heat Tracing Transformer/Distribution Board 4 (PS5-79-IG-0004)</t>
+          <t>PS5-79-02 - Electrical Heat Tracing Transformer/Distribution Board 2 (PS5-79-IG-0002)</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>PS5-79-04</t>
+          <t>PS5-79-02</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>PS5-79-05 - Electrical Heat Tracing Transformer/Distribution Board 5 (PS5-79-IG-0005)</t>
+          <t>PS5-79-03 - Electrical Heat Tracing Transformer/Distribution Board 3 (PS5-79-IG-0003)</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>PS5-79-05</t>
+          <t>PS5-79-03</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>PS5-79-06 - Electrical Heat Tracing Transformer/Distribution Board 6 (PS5-79-IG-0006)</t>
+          <t>PS5-79-04 - Electrical Heat Tracing Transformer/Distribution Board 4 (PS5-79-IG-0004)</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>PS5-79-06</t>
+          <t>PS5-79-04</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>PS5-79-07 - Electrical Heat Tracing Transformer/Distribution Board 7 (PS5-79-IG-0007)</t>
+          <t>PS5-79-05 - Electrical Heat Tracing Transformer/Distribution Board 5 (PS5-79-IG-0005)</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>PS5-79-07</t>
+          <t>PS5-79-05</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>PS5-79-08 - Electrical Heat Tracing Transformer/Distribution Board 8 (PS5-79-IG-0008)</t>
+          <t>PS5-79-06 - Electrical Heat Tracing Transformer/Distribution Board 6 (PS5-79-IG-0006)</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>PS5-79-08</t>
+          <t>PS5-79-06</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>PS5-79-09 - Electrical Heat Tracing Transformer/Distribution Board 9 (PS5-79-IG-0009)</t>
+          <t>PS5-79-07 - Electrical Heat Tracing Transformer/Distribution Board 7 (PS5-79-IG-0007)</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>PS5-79-09</t>
+          <t>PS5-79-07</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>PS5-79-10 - Electrical Heat Tracing Transformer/Distribution Board 10 (PS5-79-IG-0010)</t>
+          <t>PS5-79-08 - Electrical Heat Tracing Transformer/Distribution Board 8 (PS5-79-IG-0008)</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>PS5-79-10</t>
+          <t>PS5-79-08</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>PS5-79-11 - Electrical Heat Tracing Transformer/Distribution Board 11 (PS5-79-IG-0011)</t>
+          <t>PS5-79-09 - Electrical Heat Tracing Transformer/Distribution Board 9 (PS5-79-IG-0009)</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>PS5-79-11</t>
+          <t>PS5-79-09</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>PS5-79-12 - Electrical Heat Tracing Transformer/Distribution Board 12 (PS5-79-IG-0012)</t>
+          <t>PS5-79-10 - Electrical Heat Tracing Transformer/Distribution Board 10 (PS5-79-IG-0010)</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>PS5-79-12</t>
+          <t>PS5-79-10</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>PS5-82-01 - Sanitary Sewage Collection</t>
+          <t>PS5-79-11 - Electrical Heat Tracing Transformer/Distribution Board 11 (PS5-79-IG-0011)</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>PS5-82-01</t>
+          <t>PS5-79-11</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>PS5-82-02 - Sewage Treatment Plant Package</t>
+          <t>PS5-79-12 - Electrical Heat Tracing Transformer/Distribution Board 12 (PS5-79-IG-0012)</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>PS5-82-02</t>
+          <t>PS5-79-12</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>PS5-82-03 - Sewage Treatment Plant Package (UCP)</t>
+          <t>PS5-82-01 - Sanitary Sewage Collection</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>PS5-82-03</t>
+          <t>PS5-82-01</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>PS5-82-04 - Sewage Treatment Plant Discharge Piping</t>
+          <t>PS5-82-02 - Sewage Treatment Plant Package</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>PS5-82-04</t>
+          <t>PS5-82-02</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>PS5-82-05 - Office and Facilities building</t>
+          <t>PS5-82-03 - Sewage Treatment Plant Package (UCP)</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>PS5-82-05</t>
+          <t>PS5-82-03</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>PS5-82-06 - Guard House Building</t>
+          <t>PS5-82-04 - Sewage Treatment Plant Discharge Piping</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>PS5-82-06</t>
+          <t>PS5-82-04</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>PS5-82-07 - Guard Huts</t>
+          <t>PS5-82-05 - Office and Facilities building</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>PS5-82-07</t>
+          <t>PS5-82-05</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>PS5-83-01 - EITS Building</t>
+          <t>PS5-82-06 - Guard House Building</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>PS5-83-01</t>
+          <t>PS5-82-06</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>PS5-84-01 - Generator Building</t>
+          <t>PS5-82-07 - Guard Huts</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>PS5-84-01</t>
+          <t>PS5-82-07</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>PS5-84-02 - Workshop &amp; Warehouse</t>
+          <t>PS5-83-01 - EITS Building</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>PS5-84-02</t>
+          <t>PS5-83-01</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>PS5-84-03 - Shelters</t>
+          <t>PS5-84-01 - Generator Building</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>PS5-84-03</t>
+          <t>PS5-84-01</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>PS5-86-01 - Shelters</t>
+          <t>PS5-84-02 - Workshop &amp; Warehouse</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>PS5-86-01</t>
+          <t>PS5-84-02</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>PS5-91-01 - Multicore cables &amp; JB</t>
+          <t>PS5-84-03 - Shelters</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>PS5-91-01</t>
+          <t>PS5-84-03</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>PS5-99-01 - Area Completion for Building area</t>
+          <t>PS5-86-01 - Shelters</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>PS5-99-01</t>
+          <t>PS5-86-01</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>PS5-99-02 - Area Completion for Utility area</t>
+          <t>PS5-91-01 - Multicore cables &amp; JB</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>PS5-99-02</t>
+          <t>PS5-91-01</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>PS5-99-03 - Area Completion for Power Distribution area</t>
+          <t>PS5-99-01 - Area Completion for Building area</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>PS5-99-03</t>
+          <t>PS5-99-01</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>PS5-99-04 - Area Completion for Process area</t>
+          <t>PS5-99-02 - Area Completion for Utility area</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>PS5-99-04</t>
+          <t>PS5-99-02</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>PS5-99-05 - Area Completion for CFO area</t>
+          <t>PS5-99-03 - Area Completion for Power Distribution area</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>PS5-99-05</t>
+          <t>PS5-99-03</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
+          <t>PS5-99-04 - Area Completion for Process area</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>PS5-99-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>PS5-99-05 - Area Completion for CFO area</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>PS5-99-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
           <t>PS5-99-06 - Area Completion for Power Generation area</t>
         </is>
       </c>
-      <c r="B293" t="inlineStr">
+      <c r="B295" t="inlineStr">
         <is>
           <t>PS5-99-06</t>
         </is>

--- a/EXCEL/7 - COMPLETE.xlsx
+++ b/EXCEL/7 - COMPLETE.xlsx
@@ -11,7 +11,7 @@
     <sheet name="SIDMAP" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'7 · COMPLETE'!$A$2:$G$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'7 · COMPLETE'!$A$2:$G$125</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -79,12 +79,6 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="FFed7d31"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="10"/>
     </font>
@@ -92,6 +86,12 @@
       <name val="Calibri"/>
       <color rgb="FF1A2A3A"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFed7d31"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -241,12 +241,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFffeb9c"/>
-        <bgColor rgb="FFffeb9c"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFe8d5c4"/>
         <bgColor rgb="FFe8d5c4"/>
       </patternFill>
@@ -315,6 +309,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFBDD7EE"/>
         <bgColor rgb="FFBDD7EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFffeb9c"/>
+        <bgColor rgb="FFffeb9c"/>
       </patternFill>
     </fill>
     <fill>
@@ -564,10 +564,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -575,9 +578,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -644,12 +644,15 @@
     <xf numFmtId="0" fontId="2" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -671,40 +674,34 @@
     <xf numFmtId="0" fontId="6" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -713,6 +710,9 @@
     <xf numFmtId="0" fontId="5" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -722,10 +722,10 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -740,13 +740,13 @@
     <xf numFmtId="0" fontId="4" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -773,16 +773,16 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1152,7 +1152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1220,29 +1220,21 @@
       </c>
       <c r="B3" s="83" t="inlineStr">
         <is>
-          <t>PS5-01-01 - Fire Water Jockey Pump A/B</t>
-        </is>
-      </c>
-      <c r="C3" s="27" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D3" s="24" t="inlineStr">
-        <is>
-          <t>DONE(partial)</t>
-        </is>
-      </c>
-      <c r="E3" s="27" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F3" s="23" t="inlineStr">
-        <is>
-          <t>Hydraulic tubing could not be connected in HPU due to Fittings/socket issues</t>
-        </is>
-      </c>
+          <t>PS5-01-04 - Fire Water Pump Mini Flow Recycle</t>
+        </is>
+      </c>
+      <c r="C3" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D3" s="24" t="inlineStr"/>
+      <c r="E3" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F3" s="23" t="inlineStr"/>
       <c r="G3" s="67" t="inlineStr"/>
     </row>
     <row r="4">
@@ -1251,25 +1243,25 @@
       </c>
       <c r="B4" s="83" t="inlineStr">
         <is>
-          <t>PS5-01-04 - Fire Water Pump Mini Flow Recycle</t>
-        </is>
-      </c>
-      <c r="C4" s="27" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D4" s="24" t="inlineStr"/>
-      <c r="E4" s="27" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F4" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>PS5-01-05 - Foam Skid</t>
+        </is>
+      </c>
+      <c r="C4" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D4" s="24" t="inlineStr">
+        <is>
+          <t>PS5 - Milestone F</t>
+        </is>
+      </c>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F4" s="23" t="inlineStr"/>
       <c r="G4" s="67" t="inlineStr"/>
     </row>
     <row r="5">
@@ -1281,22 +1273,18 @@
           <t>PS5-01-06 - Foam Concentrate Distribution</t>
         </is>
       </c>
-      <c r="C5" s="27" t="inlineStr">
+      <c r="C5" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
       <c r="D5" s="24" t="inlineStr"/>
-      <c r="E5" s="27" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F5" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F5" s="23" t="inlineStr"/>
       <c r="G5" s="67" t="inlineStr"/>
     </row>
     <row r="6">
@@ -1308,22 +1296,18 @@
           <t>PS5-01-09 - Inergen for EITS Building</t>
         </is>
       </c>
-      <c r="C6" s="27" t="inlineStr">
+      <c r="C6" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
       <c r="D6" s="24" t="inlineStr"/>
-      <c r="E6" s="27" t="inlineStr">
+      <c r="E6" s="28" t="inlineStr">
         <is>
           <t>2026-08-08</t>
         </is>
       </c>
-      <c r="F6" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F6" s="23" t="inlineStr"/>
       <c r="G6" s="67" t="inlineStr"/>
     </row>
     <row r="7">
@@ -1335,7 +1319,7 @@
           <t>PS5-01-10 - Water Mist Package</t>
         </is>
       </c>
-      <c r="C7" s="27" t="inlineStr">
+      <c r="C7" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1345,16 +1329,12 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E7" s="27" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F7" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="E7" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F7" s="23" t="inlineStr"/>
       <c r="G7" s="67" t="inlineStr"/>
     </row>
     <row r="8">
@@ -1363,29 +1343,25 @@
       </c>
       <c r="B8" s="83" t="inlineStr">
         <is>
-          <t>PS5-03-07 - FZ-07 - Pretreatment Area</t>
-        </is>
-      </c>
-      <c r="C8" s="27" t="inlineStr">
+          <t>PS5-01-11 - Inergen for Power Gen Building</t>
+        </is>
+      </c>
+      <c r="C8" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
       <c r="D8" s="24" t="inlineStr">
         <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E8" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="E8" s="28" t="inlineStr">
+        <is>
+          <t>FULL</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr"/>
       <c r="G8" s="67" t="inlineStr"/>
     </row>
     <row r="9">
@@ -1394,10 +1370,10 @@
       </c>
       <c r="B9" s="83" t="inlineStr">
         <is>
-          <t>PS5-03-09 - FZ-09 - Power Generation Building - Engine Bay 1</t>
-        </is>
-      </c>
-      <c r="C9" s="27" t="inlineStr">
+          <t>PS5-03-01 - FZ-01 - Process Area</t>
+        </is>
+      </c>
+      <c r="C9" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1407,16 +1383,12 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E9" s="27" t="inlineStr">
+      <c r="E9" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F9" s="23" t="inlineStr">
-        <is>
-          <t>Due to gland plate issue of SEA-0001 we cannot terminate the cablesof F&amp;G Instruments.</t>
-        </is>
-      </c>
+      <c r="F9" s="23" t="inlineStr"/>
       <c r="G9" s="67" t="inlineStr"/>
     </row>
     <row r="10">
@@ -1425,10 +1397,10 @@
       </c>
       <c r="B10" s="83" t="inlineStr">
         <is>
-          <t>PS5-03-10 - FZ-10 - Power Generation Building - Engine Bay 2</t>
-        </is>
-      </c>
-      <c r="C10" s="27" t="inlineStr">
+          <t>PS5-03-06 - FZ-06 - Transformer Area</t>
+        </is>
+      </c>
+      <c r="C10" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1438,7 +1410,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E10" s="27" t="inlineStr">
+      <c r="E10" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1452,10 +1424,10 @@
       </c>
       <c r="B11" s="83" t="inlineStr">
         <is>
-          <t>PS5-03-13 - FZ-13 - Power Generation Building - Instrument Air Room</t>
-        </is>
-      </c>
-      <c r="C11" s="27" t="inlineStr">
+          <t>PS5-03-07 - FZ-07 - Pretreatment Area</t>
+        </is>
+      </c>
+      <c r="C11" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1465,16 +1437,12 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E11" s="27" t="inlineStr">
+      <c r="E11" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F11" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F11" s="23" t="inlineStr"/>
       <c r="G11" s="67" t="inlineStr"/>
     </row>
     <row r="12">
@@ -1483,10 +1451,10 @@
       </c>
       <c r="B12" s="83" t="inlineStr">
         <is>
-          <t>PS5-03-20 - FZ-20 - Emergency Diesel Generator Enclosure</t>
-        </is>
-      </c>
-      <c r="C12" s="27" t="inlineStr">
+          <t>PS5-03-09 - FZ-09 - Power Generation Building - Engine Bay 1</t>
+        </is>
+      </c>
+      <c r="C12" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1496,16 +1464,12 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E12" s="27" t="inlineStr">
-        <is>
-          <t>07-Aug-26</t>
-        </is>
-      </c>
-      <c r="F12" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="E12" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="23" t="inlineStr"/>
       <c r="G12" s="67" t="inlineStr"/>
     </row>
     <row r="13">
@@ -1514,10 +1478,10 @@
       </c>
       <c r="B13" s="83" t="inlineStr">
         <is>
-          <t>PS5-05-01 - Emergency Diesel Generator Package</t>
-        </is>
-      </c>
-      <c r="C13" s="27" t="inlineStr">
+          <t>PS5-03-10 - FZ-10 - Power Generation Building - Engine Bay 2</t>
+        </is>
+      </c>
+      <c r="C13" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1527,16 +1491,12 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E13" s="69" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="F13" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="E13" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="23" t="inlineStr"/>
       <c r="G13" s="67" t="inlineStr"/>
     </row>
     <row r="14">
@@ -1545,29 +1505,25 @@
       </c>
       <c r="B14" s="83" t="inlineStr">
         <is>
-          <t>PS5-05-02 - Emergency Diesel Generator Package (UCP)</t>
-        </is>
-      </c>
-      <c r="C14" s="27" t="inlineStr">
+          <t>PS5-03-11 - FZ-11 - Power Generation Building - Engine Bay 3</t>
+        </is>
+      </c>
+      <c r="C14" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E14" s="54" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
-        </is>
-      </c>
-      <c r="F14" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="E14" s="28" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="F14" s="23" t="inlineStr"/>
       <c r="G14" s="67" t="inlineStr"/>
     </row>
     <row r="15">
@@ -1576,10 +1532,10 @@
       </c>
       <c r="B15" s="83" t="inlineStr">
         <is>
-          <t>PS5-06-02 - AC UPS - Power Generator Building</t>
-        </is>
-      </c>
-      <c r="C15" s="27" t="inlineStr">
+          <t>PS5-03-12 - FZ-12 - Power Generation Building - Engine Bay 4</t>
+        </is>
+      </c>
+      <c r="C15" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1589,16 +1545,12 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E15" s="27" t="inlineStr">
+      <c r="E15" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F15" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F15" s="23" t="inlineStr"/>
       <c r="G15" s="67" t="inlineStr"/>
     </row>
     <row r="16">
@@ -1607,18 +1559,22 @@
       </c>
       <c r="B16" s="83" t="inlineStr">
         <is>
-          <t>PS5-09-05 - HVAC for EITS Building</t>
-        </is>
-      </c>
-      <c r="C16" s="27" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D16" s="24" t="inlineStr"/>
-      <c r="E16" s="27" t="inlineStr">
-        <is>
-          <t>Full</t>
+          <t>PS5-03-13 - FZ-13 - Power Generation Building - Instrument Air Room</t>
+        </is>
+      </c>
+      <c r="C16" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E16" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="F16" s="23" t="inlineStr"/>
@@ -1630,25 +1586,25 @@
       </c>
       <c r="B17" s="83" t="inlineStr">
         <is>
-          <t>PS5-28-02 - Closed Drain Header 2</t>
-        </is>
-      </c>
-      <c r="C17" s="27" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D17" s="24" t="inlineStr"/>
-      <c r="E17" s="27" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F17" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>PS5-03-20 - FZ-20 - Emergency Diesel Generator Enclosure</t>
+        </is>
+      </c>
+      <c r="C17" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E17" s="28" t="inlineStr">
+        <is>
+          <t>07-Aug-26</t>
+        </is>
+      </c>
+      <c r="F17" s="23" t="inlineStr"/>
       <c r="G17" s="67" t="inlineStr"/>
     </row>
     <row r="18">
@@ -1657,10 +1613,10 @@
       </c>
       <c r="B18" s="83" t="inlineStr">
         <is>
-          <t>PS5-28-05 - HP Relief Header</t>
-        </is>
-      </c>
-      <c r="C18" s="27" t="inlineStr">
+          <t>PS5-05-01 - Emergency Diesel Generator Package</t>
+        </is>
+      </c>
+      <c r="C18" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1670,47 +1626,39 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E18" s="27" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F18" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="E18" s="28" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="F18" s="23" t="inlineStr"/>
       <c r="G18" s="67" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="85" t="n">
+      <c r="A19" s="81" t="n">
         <v>17</v>
       </c>
       <c r="B19" s="83" t="inlineStr">
         <is>
-          <t>PS5-53-01 - Utility Water / Storage Tank</t>
-        </is>
-      </c>
-      <c r="C19" s="27" t="inlineStr">
-        <is>
-          <t>89%</t>
+          <t>PS5-05-02 - Emergency Diesel Generator Package (UCP)</t>
+        </is>
+      </c>
+      <c r="C19" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="D19" s="24" t="inlineStr">
         <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="E19" s="69" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="F19" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E19" s="28" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+      <c r="F19" s="23" t="inlineStr"/>
       <c r="G19" s="67" t="inlineStr"/>
     </row>
     <row r="20">
@@ -1719,10 +1667,10 @@
       </c>
       <c r="B20" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-01 - Power Generation Package A</t>
-        </is>
-      </c>
-      <c r="C20" s="27" t="inlineStr">
+          <t>PS5-06-02 - AC UPS - Power Generator Building</t>
+        </is>
+      </c>
+      <c r="C20" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1732,16 +1680,12 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E20" s="27" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F20" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="E20" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F20" s="23" t="inlineStr"/>
       <c r="G20" s="67" t="inlineStr"/>
     </row>
     <row r="21">
@@ -1750,29 +1694,21 @@
       </c>
       <c r="B21" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-02 - Power Gen Package A (UCP)</t>
-        </is>
-      </c>
-      <c r="C21" s="27" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D21" s="24" t="inlineStr">
-        <is>
-          <t>PS5 - Milestone B</t>
-        </is>
-      </c>
-      <c r="E21" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F21" s="23" t="inlineStr">
-        <is>
-          <t>WALKDOWN COMPLETE-20-08-26--ATTENDENCE SHEET TO BE SUBMITTED</t>
-        </is>
-      </c>
+          <t>PS5-09-05 - HVAC for EITS Building</t>
+        </is>
+      </c>
+      <c r="C21" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D21" s="24" t="inlineStr"/>
+      <c r="E21" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F21" s="23" t="inlineStr"/>
       <c r="G21" s="67" t="inlineStr"/>
     </row>
     <row r="22">
@@ -1781,29 +1717,25 @@
       </c>
       <c r="B22" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-04 - Power Generation Package B</t>
-        </is>
-      </c>
-      <c r="C22" s="27" t="inlineStr">
+          <t>PS5-25-05 - Crude Oil Export Pumps Bypass</t>
+        </is>
+      </c>
+      <c r="C22" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
       <c r="D22" s="24" t="inlineStr">
         <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E22" s="27" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F22" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="E22" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F22" s="23" t="inlineStr"/>
       <c r="G22" s="67" t="inlineStr"/>
     </row>
     <row r="23">
@@ -1812,25 +1744,21 @@
       </c>
       <c r="B23" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-23 - Instrument Air Distribution lines</t>
-        </is>
-      </c>
-      <c r="C23" s="27" t="inlineStr">
+          <t>PS5-28-02 - Closed Drain Header 2</t>
+        </is>
+      </c>
+      <c r="C23" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
       <c r="D23" s="24" t="inlineStr"/>
-      <c r="E23" s="27" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F23" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="E23" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F23" s="23" t="inlineStr"/>
       <c r="G23" s="67" t="inlineStr"/>
     </row>
     <row r="24">
@@ -1839,10 +1767,10 @@
       </c>
       <c r="B24" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-26 - Instrument Air Compressor Skid</t>
-        </is>
-      </c>
-      <c r="C24" s="27" t="inlineStr">
+          <t>PS5-28-05 - HP Relief Header</t>
+        </is>
+      </c>
+      <c r="C24" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1852,16 +1780,12 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E24" s="27" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F24" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="E24" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F24" s="23" t="inlineStr"/>
       <c r="G24" s="67" t="inlineStr"/>
     </row>
     <row r="25">
@@ -1870,10 +1794,10 @@
       </c>
       <c r="B25" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-27 - Compressed Air Starting Skid</t>
-        </is>
-      </c>
-      <c r="C25" s="27" t="inlineStr">
+          <t>PS5-28-06 - Relief Drum and Pump</t>
+        </is>
+      </c>
+      <c r="C25" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1883,16 +1807,12 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E25" s="27" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F25" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="E25" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F25" s="23" t="inlineStr"/>
       <c r="G25" s="67" t="inlineStr"/>
     </row>
     <row r="26">
@@ -1901,58 +1821,54 @@
       </c>
       <c r="B26" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-28 - Air Receiver A &amp; Air Regulator A</t>
-        </is>
-      </c>
-      <c r="C26" s="27" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D26" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E26" s="69" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+          <t>PS5-28-07 - Open Drains (OD2)</t>
+        </is>
+      </c>
+      <c r="C26" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D26" s="24" t="inlineStr"/>
+      <c r="E26" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="F26" s="23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G26" s="67" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="81" t="n">
+      <c r="A27" s="85" t="n">
         <v>25</v>
       </c>
       <c r="B27" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-29 - Air Receiver B &amp; Air Regulator B</t>
-        </is>
-      </c>
-      <c r="C27" s="27" t="inlineStr">
-        <is>
-          <t>100%</t>
+          <t>PS5-28-08 - Open Drain Sump and Pumps</t>
+        </is>
+      </c>
+      <c r="C27" s="28" t="inlineStr">
+        <is>
+          <t>99%</t>
         </is>
       </c>
       <c r="D27" s="24" t="inlineStr">
         <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E27" s="27" t="inlineStr">
-        <is>
-          <t>Full</t>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="E27" s="69" t="inlineStr">
+        <is>
+          <t>partial</t>
         </is>
       </c>
       <c r="F27" s="23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G27" s="67" t="inlineStr"/>
@@ -1963,29 +1879,25 @@
       </c>
       <c r="B28" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-30 - Air Receiver C &amp; Air Regulator C</t>
-        </is>
-      </c>
-      <c r="C28" s="27" t="inlineStr">
+          <t>PS5-28-11 - Open Drain Interceptor</t>
+        </is>
+      </c>
+      <c r="C28" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
       <c r="D28" s="24" t="inlineStr">
         <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E28" s="27" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F28" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>FULL</t>
+        </is>
+      </c>
+      <c r="E28" s="28" t="inlineStr">
+        <is>
+          <t>FULL</t>
+        </is>
+      </c>
+      <c r="F28" s="23" t="inlineStr"/>
       <c r="G28" s="67" t="inlineStr"/>
     </row>
     <row r="29">
@@ -1994,29 +1906,21 @@
       </c>
       <c r="B29" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-31 - Air Receiver D &amp; Air Regulator D</t>
-        </is>
-      </c>
-      <c r="C29" s="27" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D29" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E29" s="27" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F29" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>PS5-28-12 - Open Drains (OD3)</t>
+        </is>
+      </c>
+      <c r="C29" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D29" s="24" t="inlineStr"/>
+      <c r="E29" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F29" s="23" t="inlineStr"/>
       <c r="G29" s="67" t="inlineStr"/>
     </row>
     <row r="30">
@@ -2025,10 +1929,10 @@
       </c>
       <c r="B30" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-32 - Air Receiver E &amp; Air Regulator E</t>
-        </is>
-      </c>
-      <c r="C30" s="27" t="inlineStr">
+          <t>PS5-28-16 - LP Relief Header</t>
+        </is>
+      </c>
+      <c r="C30" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2038,45 +1942,41 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E30" s="27" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F30" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="E30" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F30" s="23" t="inlineStr"/>
       <c r="G30" s="67" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="81" t="n">
+      <c r="A31" s="85" t="n">
         <v>29</v>
       </c>
       <c r="B31" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-33 - Air Receiver F &amp; Air Regulator F</t>
-        </is>
-      </c>
-      <c r="C31" s="27" t="inlineStr">
-        <is>
-          <t>100%</t>
+          <t>PS5-53-01 - Utility Water / Storage Tank</t>
+        </is>
+      </c>
+      <c r="C31" s="28" t="inlineStr">
+        <is>
+          <t>96%</t>
         </is>
       </c>
       <c r="D31" s="24" t="inlineStr">
         <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E31" s="27" t="inlineStr">
-        <is>
-          <t>Full</t>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E31" s="69" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F31" s="23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G31" s="67" t="inlineStr"/>
@@ -2087,10 +1987,10 @@
       </c>
       <c r="B32" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-34 - Air Receiver G &amp; Air Regulator G</t>
-        </is>
-      </c>
-      <c r="C32" s="27" t="inlineStr">
+          <t>PS5-53-02 - Water Distribution Pump A/B</t>
+        </is>
+      </c>
+      <c r="C32" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2100,16 +2000,12 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E32" s="27" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F32" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="E32" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F32" s="23" t="inlineStr"/>
       <c r="G32" s="67" t="inlineStr"/>
     </row>
     <row r="33">
@@ -2118,10 +2014,10 @@
       </c>
       <c r="B33" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-35 - Injector Tip Cooling Module A</t>
-        </is>
-      </c>
-      <c r="C33" s="27" t="inlineStr">
+          <t>PS5-53-05 - Water Distribution Header</t>
+        </is>
+      </c>
+      <c r="C33" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2131,16 +2027,12 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E33" s="54" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
-        </is>
-      </c>
-      <c r="F33" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="E33" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F33" s="23" t="inlineStr"/>
       <c r="G33" s="67" t="inlineStr"/>
     </row>
     <row r="34">
@@ -2149,10 +2041,10 @@
       </c>
       <c r="B34" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-36 - Injector Tip Cooling Module B</t>
-        </is>
-      </c>
-      <c r="C34" s="27" t="inlineStr">
+          <t>PS5-60-01 - Power Generation Package A</t>
+        </is>
+      </c>
+      <c r="C34" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2162,16 +2054,12 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E34" s="27" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F34" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="E34" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F34" s="23" t="inlineStr"/>
       <c r="G34" s="67" t="inlineStr"/>
     </row>
     <row r="35">
@@ -2180,27 +2068,27 @@
       </c>
       <c r="B35" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-37 - Injector Tip Cooling Module C</t>
-        </is>
-      </c>
-      <c r="C35" s="27" t="inlineStr">
+          <t>PS5-60-02 - Power Gen Package A (UCP)</t>
+        </is>
+      </c>
+      <c r="C35" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
       <c r="D35" s="24" t="inlineStr">
         <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E35" s="27" t="inlineStr">
-        <is>
-          <t>Full</t>
+          <t>PS5 - Milestone B</t>
+        </is>
+      </c>
+      <c r="E35" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="F35" s="23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>WALKDOWN COMPLETE-20-08-26--ATTENDENCE SHEET TO BE SUBMITTED</t>
         </is>
       </c>
       <c r="G35" s="67" t="inlineStr"/>
@@ -2211,10 +2099,10 @@
       </c>
       <c r="B36" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-38 - Injector Tip Cooling Module D</t>
-        </is>
-      </c>
-      <c r="C36" s="27" t="inlineStr">
+          <t>PS5-60-03 - Power Gen Package A Generator Auxiliary MCCs &amp; DBs</t>
+        </is>
+      </c>
+      <c r="C36" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2224,16 +2112,12 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E36" s="27" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F36" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="E36" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F36" s="23" t="inlineStr"/>
       <c r="G36" s="67" t="inlineStr"/>
     </row>
     <row r="37">
@@ -2242,10 +2126,10 @@
       </c>
       <c r="B37" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-39 - Injector Tip Cooling Module E</t>
-        </is>
-      </c>
-      <c r="C37" s="27" t="inlineStr">
+          <t>PS5-60-04 - Power Generation Package B</t>
+        </is>
+      </c>
+      <c r="C37" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2255,16 +2139,12 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E37" s="27" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F37" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="E37" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F37" s="23" t="inlineStr"/>
       <c r="G37" s="67" t="inlineStr"/>
     </row>
     <row r="38">
@@ -2273,10 +2153,10 @@
       </c>
       <c r="B38" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-40 - Injector Tip Cooling Module F</t>
-        </is>
-      </c>
-      <c r="C38" s="27" t="inlineStr">
+          <t>PS5-60-05 - Power Gen Package B (UCP)</t>
+        </is>
+      </c>
+      <c r="C38" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2286,16 +2166,12 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E38" s="27" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F38" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="E38" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F38" s="23" t="inlineStr"/>
       <c r="G38" s="67" t="inlineStr"/>
     </row>
     <row r="39">
@@ -2304,10 +2180,10 @@
       </c>
       <c r="B39" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-42 - Oil Mist Separator Skid PS5-60-VS-9100A</t>
-        </is>
-      </c>
-      <c r="C39" s="27" t="inlineStr">
+          <t>PS5-60-06 - Power Gen Package B Generator Auxiliary MCCs &amp; DBs</t>
+        </is>
+      </c>
+      <c r="C39" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2317,16 +2193,12 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E39" s="54" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
-        </is>
-      </c>
-      <c r="F39" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="E39" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F39" s="23" t="inlineStr"/>
       <c r="G39" s="67" t="inlineStr"/>
     </row>
     <row r="40">
@@ -2335,10 +2207,10 @@
       </c>
       <c r="B40" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-43 - Oil Mist Separator Skid PS5-60-VS-9100B</t>
-        </is>
-      </c>
-      <c r="C40" s="27" t="inlineStr">
+          <t>PS5-60-08 - Power Gen Package C (UCP)</t>
+        </is>
+      </c>
+      <c r="C40" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2348,16 +2220,12 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E40" s="27" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F40" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="E40" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F40" s="23" t="inlineStr"/>
       <c r="G40" s="67" t="inlineStr"/>
     </row>
     <row r="41">
@@ -2366,10 +2234,10 @@
       </c>
       <c r="B41" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-44 - Oil Mist Separator Skid PS5-60-VS-9100C</t>
-        </is>
-      </c>
-      <c r="C41" s="27" t="inlineStr">
+          <t>PS5-60-09 - Power Gen Package C Generator Auxiliary MCCs &amp; DBs</t>
+        </is>
+      </c>
+      <c r="C41" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2379,16 +2247,12 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E41" s="27" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F41" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="E41" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F41" s="23" t="inlineStr"/>
       <c r="G41" s="67" t="inlineStr"/>
     </row>
     <row r="42">
@@ -2397,10 +2261,10 @@
       </c>
       <c r="B42" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-45 - Oil Mist Separator Skid PS5-60-VS-9100D</t>
-        </is>
-      </c>
-      <c r="C42" s="27" t="inlineStr">
+          <t>PS5-60-11 - Power Gen Package D (UCP)</t>
+        </is>
+      </c>
+      <c r="C42" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2410,16 +2274,12 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E42" s="27" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F42" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="E42" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F42" s="23" t="inlineStr"/>
       <c r="G42" s="67" t="inlineStr"/>
     </row>
     <row r="43">
@@ -2428,25 +2288,25 @@
       </c>
       <c r="B43" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-46 - Oil Mist Separator Skid PS5-60-VS-9100E</t>
-        </is>
-      </c>
-      <c r="C43" s="27" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D43" s="24" t="inlineStr"/>
-      <c r="E43" s="27" t="inlineStr">
+          <t>PS5-60-12 - Power Gen Package D Generator Auxiliary MCCs &amp; DBs</t>
+        </is>
+      </c>
+      <c r="C43" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D43" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E43" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F43" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F43" s="23" t="inlineStr"/>
       <c r="G43" s="67" t="inlineStr"/>
     </row>
     <row r="44">
@@ -2455,10 +2315,10 @@
       </c>
       <c r="B44" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-47 - Oil Mist Separator Skid PS5-60-VS-9100F</t>
-        </is>
-      </c>
-      <c r="C44" s="27" t="inlineStr">
+          <t>PS5-60-13 - Power Generation Package E</t>
+        </is>
+      </c>
+      <c r="C44" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2468,16 +2328,12 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E44" s="27" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F44" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="E44" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F44" s="23" t="inlineStr"/>
       <c r="G44" s="67" t="inlineStr"/>
     </row>
     <row r="45">
@@ -2486,22 +2342,22 @@
       </c>
       <c r="B45" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-56 - Fuel Conditioning Module PS5-60-UZ-8900A</t>
-        </is>
-      </c>
-      <c r="C45" s="27" t="inlineStr">
+          <t>PS5-60-14 - Power Gen Package E (UCP)</t>
+        </is>
+      </c>
+      <c r="C45" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
       <c r="D45" s="24" t="inlineStr">
         <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E45" s="27" t="inlineStr">
-        <is>
-          <t>Full</t>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="E45" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="F45" s="23" t="inlineStr"/>
@@ -2513,10 +2369,10 @@
       </c>
       <c r="B46" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-58 - Fuel Conditioning Module PS5-60-UZ-8900B</t>
-        </is>
-      </c>
-      <c r="C46" s="27" t="inlineStr">
+          <t>PS5-60-15 - Power Gen Package E Generator Auxiliary MCCs &amp; DBs</t>
+        </is>
+      </c>
+      <c r="C46" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2526,9 +2382,9 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E46" s="27" t="inlineStr">
-        <is>
-          <t>Full</t>
+      <c r="E46" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="F46" s="23" t="inlineStr"/>
@@ -2540,10 +2396,10 @@
       </c>
       <c r="B47" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-60 - Fuel Conditioning Module PS5-60-UZ-8900C</t>
-        </is>
-      </c>
-      <c r="C47" s="27" t="inlineStr">
+          <t>PS5-60-17 - Power Gen Package F (UCP)</t>
+        </is>
+      </c>
+      <c r="C47" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2553,9 +2409,9 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E47" s="27" t="inlineStr">
-        <is>
-          <t>Full</t>
+      <c r="E47" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="F47" s="23" t="inlineStr"/>
@@ -2567,10 +2423,10 @@
       </c>
       <c r="B48" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-62 - Fuel Conditioning Module PS5-60-UZ-8900D</t>
-        </is>
-      </c>
-      <c r="C48" s="27" t="inlineStr">
+          <t>PS5-60-18 - Power Gen Package F Generator Auxiliary MCCs &amp; DBs</t>
+        </is>
+      </c>
+      <c r="C48" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2580,9 +2436,9 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E48" s="27" t="inlineStr">
-        <is>
-          <t>Full</t>
+      <c r="E48" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="F48" s="23" t="inlineStr"/>
@@ -2594,29 +2450,25 @@
       </c>
       <c r="B49" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-70 - Engine A Cooling system</t>
-        </is>
-      </c>
-      <c r="C49" s="27" t="inlineStr">
+          <t>PS5-60-20 - Power Gen Package G (UCP)</t>
+        </is>
+      </c>
+      <c r="C49" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
       <c r="D49" s="24" t="inlineStr">
         <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E49" s="27" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F49" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="E49" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F49" s="23" t="inlineStr"/>
       <c r="G49" s="67" t="inlineStr"/>
     </row>
     <row r="50">
@@ -2625,10 +2477,10 @@
       </c>
       <c r="B50" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-71 - Engine B Cooling system</t>
-        </is>
-      </c>
-      <c r="C50" s="27" t="inlineStr">
+          <t>PS5-60-21 - Power Gen Package G Generator Auxiliary MCCs &amp; DBs</t>
+        </is>
+      </c>
+      <c r="C50" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2638,16 +2490,12 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E50" s="27" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F50" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="E50" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F50" s="23" t="inlineStr"/>
       <c r="G50" s="67" t="inlineStr"/>
     </row>
     <row r="51">
@@ -2656,29 +2504,21 @@
       </c>
       <c r="B51" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-72 - Engine C Cooling system</t>
-        </is>
-      </c>
-      <c r="C51" s="27" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D51" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E51" s="27" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F51" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>PS5-60-23 - Instrument Air Distribution lines</t>
+        </is>
+      </c>
+      <c r="C51" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D51" s="24" t="inlineStr"/>
+      <c r="E51" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F51" s="23" t="inlineStr"/>
       <c r="G51" s="67" t="inlineStr"/>
     </row>
     <row r="52">
@@ -2687,10 +2527,10 @@
       </c>
       <c r="B52" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-73 - Engine D Cooling system</t>
-        </is>
-      </c>
-      <c r="C52" s="27" t="inlineStr">
+          <t>PS5-60-26 - Instrument Air Compressor Skid</t>
+        </is>
+      </c>
+      <c r="C52" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2700,16 +2540,12 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E52" s="27" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F52" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="E52" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F52" s="23" t="inlineStr"/>
       <c r="G52" s="67" t="inlineStr"/>
     </row>
     <row r="53">
@@ -2718,10 +2554,10 @@
       </c>
       <c r="B53" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-74 - Engine E Cooling system</t>
-        </is>
-      </c>
-      <c r="C53" s="27" t="inlineStr">
+          <t>PS5-60-27 - Compressed Air Starting Skid</t>
+        </is>
+      </c>
+      <c r="C53" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2731,16 +2567,12 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E53" s="27" t="inlineStr">
-        <is>
-          <t>PLATFORM ISSUE</t>
-        </is>
-      </c>
-      <c r="F53" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="E53" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F53" s="23" t="inlineStr"/>
       <c r="G53" s="67" t="inlineStr"/>
     </row>
     <row r="54">
@@ -2749,10 +2581,10 @@
       </c>
       <c r="B54" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-75 - Engine F Cooling system</t>
-        </is>
-      </c>
-      <c r="C54" s="27" t="inlineStr">
+          <t>PS5-60-28 - Air Receiver A &amp; Air Regulator A</t>
+        </is>
+      </c>
+      <c r="C54" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2762,16 +2594,12 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E54" s="27" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F54" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="E54" s="28" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="F54" s="23" t="inlineStr"/>
       <c r="G54" s="67" t="inlineStr"/>
     </row>
     <row r="55">
@@ -2780,10 +2608,10 @@
       </c>
       <c r="B55" s="83" t="inlineStr">
         <is>
-          <t>PS5-61-05 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0003)</t>
-        </is>
-      </c>
-      <c r="C55" s="27" t="inlineStr">
+          <t>PS5-60-29 - Air Receiver B &amp; Air Regulator B</t>
+        </is>
+      </c>
+      <c r="C55" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2793,16 +2621,12 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E55" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F55" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="E55" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F55" s="23" t="inlineStr"/>
       <c r="G55" s="67" t="inlineStr"/>
     </row>
     <row r="56">
@@ -2811,29 +2635,25 @@
       </c>
       <c r="B56" s="83" t="inlineStr">
         <is>
-          <t>PS5-61-07 - 0.4kV Switchboard EITS Building (PS5-61-IK-0001)</t>
-        </is>
-      </c>
-      <c r="C56" s="27" t="inlineStr">
+          <t>PS5-60-30 - Air Receiver C &amp; Air Regulator C</t>
+        </is>
+      </c>
+      <c r="C56" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
       <c r="D56" s="24" t="inlineStr">
         <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="E56" s="27" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F56" s="23" t="inlineStr">
-        <is>
-          <t>PS5-61-IV-0001B cannot close ITR due to transformer leakage issue.</t>
-        </is>
-      </c>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E56" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F56" s="23" t="inlineStr"/>
       <c r="G56" s="67" t="inlineStr"/>
     </row>
     <row r="57">
@@ -2842,10 +2662,10 @@
       </c>
       <c r="B57" s="83" t="inlineStr">
         <is>
-          <t>PS5-61-10 - Outdoor Valves Distribution Board - PS5-61-IG-0042</t>
-        </is>
-      </c>
-      <c r="C57" s="27" t="inlineStr">
+          <t>PS5-60-31 - Air Receiver D &amp; Air Regulator D</t>
+        </is>
+      </c>
+      <c r="C57" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2855,16 +2675,12 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E57" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F57" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="E57" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F57" s="23" t="inlineStr"/>
       <c r="G57" s="67" t="inlineStr"/>
     </row>
     <row r="58">
@@ -2873,10 +2689,10 @@
       </c>
       <c r="B58" s="83" t="inlineStr">
         <is>
-          <t>PS5-61-11 - Outdoor Valves Distribution Board - PS5-61-IG-0043</t>
-        </is>
-      </c>
-      <c r="C58" s="27" t="inlineStr">
+          <t>PS5-60-32 - Air Receiver E &amp; Air Regulator E</t>
+        </is>
+      </c>
+      <c r="C58" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2886,16 +2702,12 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E58" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F58" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="E58" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F58" s="23" t="inlineStr"/>
       <c r="G58" s="67" t="inlineStr"/>
     </row>
     <row r="59">
@@ -2904,10 +2716,10 @@
       </c>
       <c r="B59" s="83" t="inlineStr">
         <is>
-          <t>PS5-62-04 - Outdoor Emergency Lighting DB  - PS5-05-IG-0006</t>
-        </is>
-      </c>
-      <c r="C59" s="27" t="inlineStr">
+          <t>PS5-60-33 - Air Receiver F &amp; Air Regulator F</t>
+        </is>
+      </c>
+      <c r="C59" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2917,16 +2729,12 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E59" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F59" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="E59" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F59" s="23" t="inlineStr"/>
       <c r="G59" s="67" t="inlineStr"/>
     </row>
     <row r="60">
@@ -2935,18 +2743,22 @@
       </c>
       <c r="B60" s="83" t="inlineStr">
         <is>
-          <t>PS5-63-04 - Electrical Earthing - EITS Building</t>
-        </is>
-      </c>
-      <c r="C60" s="27" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D60" s="24" t="inlineStr"/>
-      <c r="E60" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>PS5-60-34 - Air Receiver G &amp; Air Regulator G</t>
+        </is>
+      </c>
+      <c r="C60" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D60" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E60" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
         </is>
       </c>
       <c r="F60" s="23" t="inlineStr"/>
@@ -2958,10 +2770,10 @@
       </c>
       <c r="B61" s="83" t="inlineStr">
         <is>
-          <t>PS5-71-22 - Diesel Fuel Pre Pressure Module</t>
-        </is>
-      </c>
-      <c r="C61" s="27" t="inlineStr">
+          <t>PS5-60-35 - Injector Tip Cooling Module A</t>
+        </is>
+      </c>
+      <c r="C61" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2971,16 +2783,12 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E61" s="27" t="inlineStr">
-        <is>
-          <t>DONE(full)</t>
-        </is>
-      </c>
-      <c r="F61" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="E61" s="28" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+      <c r="F61" s="23" t="inlineStr"/>
       <c r="G61" s="67" t="inlineStr"/>
     </row>
     <row r="62">
@@ -2989,10 +2797,10 @@
       </c>
       <c r="B62" s="83" t="inlineStr">
         <is>
-          <t>PS5-74-03 - Nitrogen Receiver</t>
-        </is>
-      </c>
-      <c r="C62" s="27" t="inlineStr">
+          <t>PS5-60-36 - Injector Tip Cooling Module B</t>
+        </is>
+      </c>
+      <c r="C62" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3002,47 +2810,39 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E62" s="27" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F62" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="E62" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F62" s="23" t="inlineStr"/>
       <c r="G62" s="67" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="85" t="n">
+      <c r="A63" s="81" t="n">
         <v>61</v>
       </c>
       <c r="B63" s="83" t="inlineStr">
         <is>
-          <t>PS5-78-01 - Lifting and handling equipment</t>
-        </is>
-      </c>
-      <c r="C63" s="27" t="inlineStr">
-        <is>
-          <t>73%</t>
+          <t>PS5-60-37 - Injector Tip Cooling Module C</t>
+        </is>
+      </c>
+      <c r="C63" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="D63" s="24" t="inlineStr">
         <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="E63" s="69" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="F63" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E63" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F63" s="23" t="inlineStr"/>
       <c r="G63" s="67" t="inlineStr"/>
     </row>
     <row r="64">
@@ -3051,10 +2851,10 @@
       </c>
       <c r="B64" s="83" t="inlineStr">
         <is>
-          <t>PS5-83-01 - EITS Building</t>
-        </is>
-      </c>
-      <c r="C64" s="27" t="inlineStr">
+          <t>PS5-60-38 - Injector Tip Cooling Module D</t>
+        </is>
+      </c>
+      <c r="C64" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3064,16 +2864,12 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E64" s="27" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F64" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="E64" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F64" s="23" t="inlineStr"/>
       <c r="G64" s="67" t="inlineStr"/>
     </row>
     <row r="65">
@@ -3082,25 +2878,25 @@
       </c>
       <c r="B65" s="83" t="inlineStr">
         <is>
-          <t>PS5-84-03 - Shelters</t>
-        </is>
-      </c>
-      <c r="C65" s="27" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D65" s="24" t="inlineStr"/>
-      <c r="E65" s="27" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F65" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>PS5-60-39 - Injector Tip Cooling Module E</t>
+        </is>
+      </c>
+      <c r="C65" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D65" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E65" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F65" s="23" t="inlineStr"/>
       <c r="G65" s="67" t="inlineStr"/>
     </row>
     <row r="66">
@@ -3109,25 +2905,25 @@
       </c>
       <c r="B66" s="83" t="inlineStr">
         <is>
-          <t>PS5-86-01 - Shelters</t>
-        </is>
-      </c>
-      <c r="C66" s="27" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D66" s="24" t="inlineStr"/>
-      <c r="E66" s="27" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F66" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>PS5-60-40 - Injector Tip Cooling Module F</t>
+        </is>
+      </c>
+      <c r="C66" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D66" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E66" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F66" s="23" t="inlineStr"/>
       <c r="G66" s="67" t="inlineStr"/>
     </row>
     <row r="67">
@@ -3136,33 +2932,1591 @@
       </c>
       <c r="B67" s="83" t="inlineStr">
         <is>
+          <t>PS5-60-41 - Injector Tip Cooling Module G</t>
+        </is>
+      </c>
+      <c r="C67" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D67" s="24" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="E67" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F67" s="23" t="inlineStr"/>
+      <c r="G67" s="67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="81" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-42 - Oil Mist Separator Skid PS5-60-VS-9100A</t>
+        </is>
+      </c>
+      <c r="C68" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D68" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E68" s="28" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+      <c r="F68" s="23" t="inlineStr"/>
+      <c r="G68" s="67" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="81" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-43 - Oil Mist Separator Skid PS5-60-VS-9100B</t>
+        </is>
+      </c>
+      <c r="C69" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D69" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E69" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F69" s="23" t="inlineStr"/>
+      <c r="G69" s="67" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="81" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-44 - Oil Mist Separator Skid PS5-60-VS-9100C</t>
+        </is>
+      </c>
+      <c r="C70" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D70" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E70" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F70" s="23" t="inlineStr"/>
+      <c r="G70" s="67" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="81" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-45 - Oil Mist Separator Skid PS5-60-VS-9100D</t>
+        </is>
+      </c>
+      <c r="C71" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D71" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E71" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F71" s="23" t="inlineStr"/>
+      <c r="G71" s="67" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="81" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-46 - Oil Mist Separator Skid PS5-60-VS-9100E</t>
+        </is>
+      </c>
+      <c r="C72" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D72" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E72" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F72" s="23" t="inlineStr"/>
+      <c r="G72" s="67" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="81" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-47 - Oil Mist Separator Skid PS5-60-VS-9100F</t>
+        </is>
+      </c>
+      <c r="C73" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D73" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E73" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F73" s="23" t="inlineStr"/>
+      <c r="G73" s="67" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="81" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-48 - Oil Mist Separator Skid PS5-60-VS-9100G</t>
+        </is>
+      </c>
+      <c r="C74" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D74" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E74" s="69" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="F74" s="23" t="inlineStr"/>
+      <c r="G74" s="67" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="81" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-49 - Lube Oil Separator Module PS5-60-UO-81100A</t>
+        </is>
+      </c>
+      <c r="C75" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D75" s="24" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="E75" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F75" s="23" t="inlineStr">
+        <is>
+          <t>OBSERVATION -CLEANING ON PROGRESS</t>
+        </is>
+      </c>
+      <c r="G75" s="67" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="81" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-50 - Lube Oil Separator Module PS5-60-UO-81100B</t>
+        </is>
+      </c>
+      <c r="C76" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D76" s="24" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="E76" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F76" s="23" t="inlineStr"/>
+      <c r="G76" s="67" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="81" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-51 - Lube Oil Separator Module PS5-60-UO-81100C</t>
+        </is>
+      </c>
+      <c r="C77" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D77" s="24" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="E77" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F77" s="23" t="inlineStr"/>
+      <c r="G77" s="67" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="81" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-52 - Lube Oil Separator Module PS5-60-UO-81100D</t>
+        </is>
+      </c>
+      <c r="C78" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D78" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E78" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F78" s="23" t="inlineStr"/>
+      <c r="G78" s="67" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="81" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-53 - Lube Oil Separator Module PS5-60-UO-81100E</t>
+        </is>
+      </c>
+      <c r="C79" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D79" s="24" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="E79" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F79" s="23" t="inlineStr"/>
+      <c r="G79" s="67" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="81" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-54 - Lube Oil Separator Module PS5-60-UO-81100F</t>
+        </is>
+      </c>
+      <c r="C80" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D80" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E80" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F80" s="23" t="inlineStr"/>
+      <c r="G80" s="67" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="81" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-55 - Lube Oil Separator Module PS5-60-UO-81100G</t>
+        </is>
+      </c>
+      <c r="C81" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D81" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E81" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F81" s="23" t="inlineStr"/>
+      <c r="G81" s="67" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-56 - Fuel Conditioning Module PS5-60-UZ-8900A</t>
+        </is>
+      </c>
+      <c r="C82" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D82" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E82" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F82" s="23" t="inlineStr"/>
+      <c r="G82" s="67" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="81" t="n">
+        <v>81</v>
+      </c>
+      <c r="B83" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-57 - Fuel Conditioning Module PS5-60-UZ-8900A (UCP)</t>
+        </is>
+      </c>
+      <c r="C83" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D83" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E83" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F83" s="23" t="inlineStr"/>
+      <c r="G83" s="67" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="81" t="n">
+        <v>82</v>
+      </c>
+      <c r="B84" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-58 - Fuel Conditioning Module PS5-60-UZ-8900B</t>
+        </is>
+      </c>
+      <c r="C84" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D84" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E84" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F84" s="23" t="inlineStr"/>
+      <c r="G84" s="67" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="81" t="n">
+        <v>83</v>
+      </c>
+      <c r="B85" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-59 - Fuel Conditioning Module PS5-60-UZ-8900B (UCP)</t>
+        </is>
+      </c>
+      <c r="C85" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D85" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E85" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F85" s="23" t="inlineStr"/>
+      <c r="G85" s="67" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="81" t="n">
+        <v>84</v>
+      </c>
+      <c r="B86" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-60 - Fuel Conditioning Module PS5-60-UZ-8900C</t>
+        </is>
+      </c>
+      <c r="C86" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D86" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E86" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F86" s="23" t="inlineStr"/>
+      <c r="G86" s="67" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="81" t="n">
+        <v>85</v>
+      </c>
+      <c r="B87" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-61 - Fuel Conditioning Module PS5-60-UZ-8900C (UCP)</t>
+        </is>
+      </c>
+      <c r="C87" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D87" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E87" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F87" s="23" t="inlineStr"/>
+      <c r="G87" s="67" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="81" t="n">
+        <v>86</v>
+      </c>
+      <c r="B88" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-62 - Fuel Conditioning Module PS5-60-UZ-8900D</t>
+        </is>
+      </c>
+      <c r="C88" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D88" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E88" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F88" s="23" t="inlineStr"/>
+      <c r="G88" s="67" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="81" t="n">
+        <v>87</v>
+      </c>
+      <c r="B89" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-63 - Fuel Conditioning Module PS5-60-UZ-8900D (UCP)</t>
+        </is>
+      </c>
+      <c r="C89" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D89" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E89" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F89" s="23" t="inlineStr"/>
+      <c r="G89" s="67" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="81" t="n">
+        <v>88</v>
+      </c>
+      <c r="B90" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-65 - Fuel Conditioning Module PS5-60-UZ-8900E (UCP)</t>
+        </is>
+      </c>
+      <c r="C90" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D90" s="24" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="E90" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F90" s="23" t="inlineStr"/>
+      <c r="G90" s="67" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="81" t="n">
+        <v>89</v>
+      </c>
+      <c r="B91" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-67 - Fuel Conditioning Module PS5-60-UZ-8900F (UCP)</t>
+        </is>
+      </c>
+      <c r="C91" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D91" s="24" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="E91" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F91" s="23" t="inlineStr"/>
+      <c r="G91" s="67" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="85" t="n">
+        <v>90</v>
+      </c>
+      <c r="B92" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-68 - Fuel Conditioning Module PS5-60-UZ-8900G</t>
+        </is>
+      </c>
+      <c r="C92" s="28" t="inlineStr">
+        <is>
+          <t>93%</t>
+        </is>
+      </c>
+      <c r="D92" s="24" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E92" s="69" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="F92" s="23" t="inlineStr"/>
+      <c r="G92" s="67" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="81" t="n">
+        <v>91</v>
+      </c>
+      <c r="B93" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-69 - Fuel Conditioning Module PS5-60-UZ-8900G (UCP)</t>
+        </is>
+      </c>
+      <c r="C93" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D93" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E93" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F93" s="23" t="inlineStr"/>
+      <c r="G93" s="67" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="81" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-70 - Engine A Cooling system</t>
+        </is>
+      </c>
+      <c r="C94" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D94" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E94" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F94" s="23" t="inlineStr"/>
+      <c r="G94" s="67" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="81" t="n">
+        <v>93</v>
+      </c>
+      <c r="B95" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-71 - Engine B Cooling system</t>
+        </is>
+      </c>
+      <c r="C95" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D95" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E95" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F95" s="23" t="inlineStr"/>
+      <c r="G95" s="67" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="81" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-72 - Engine C Cooling system</t>
+        </is>
+      </c>
+      <c r="C96" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D96" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E96" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F96" s="23" t="inlineStr"/>
+      <c r="G96" s="67" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="81" t="n">
+        <v>95</v>
+      </c>
+      <c r="B97" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-73 - Engine D Cooling system</t>
+        </is>
+      </c>
+      <c r="C97" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D97" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E97" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F97" s="23" t="inlineStr"/>
+      <c r="G97" s="67" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="81" t="n">
+        <v>96</v>
+      </c>
+      <c r="B98" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-74 - Engine E Cooling system</t>
+        </is>
+      </c>
+      <c r="C98" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D98" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E98" s="28" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="F98" s="23" t="inlineStr"/>
+      <c r="G98" s="67" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="81" t="n">
+        <v>97</v>
+      </c>
+      <c r="B99" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-75 - Engine F Cooling system</t>
+        </is>
+      </c>
+      <c r="C99" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D99" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E99" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F99" s="23" t="inlineStr"/>
+      <c r="G99" s="67" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="81" t="n">
+        <v>98</v>
+      </c>
+      <c r="B100" s="83" t="inlineStr">
+        <is>
+          <t>PS5-60-76 - Engine G Cooling system</t>
+        </is>
+      </c>
+      <c r="C100" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D100" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E100" s="28" t="inlineStr">
+        <is>
+          <t>FULL</t>
+        </is>
+      </c>
+      <c r="F100" s="23" t="inlineStr"/>
+      <c r="G100" s="67" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="81" t="n">
+        <v>99</v>
+      </c>
+      <c r="B101" s="83" t="inlineStr">
+        <is>
+          <t>PS5-61-02 - 6.6kV Switchboard and Transformer LLHT North - EITS Building (PS5-61-IJ-0010)</t>
+        </is>
+      </c>
+      <c r="C101" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D101" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E101" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F101" s="23" t="inlineStr"/>
+      <c r="G101" s="67" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="81" t="n">
+        <v>100</v>
+      </c>
+      <c r="B102" s="83" t="inlineStr">
+        <is>
+          <t>PS5-61-03 - 6.6kV Switchboard and Transformer LLHT South - EITS Building (PS5-61-IJ-0011)</t>
+        </is>
+      </c>
+      <c r="C102" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D102" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E102" s="28" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="F102" s="23" t="inlineStr"/>
+      <c r="G102" s="67" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="81" t="n">
+        <v>101</v>
+      </c>
+      <c r="B103" s="83" t="inlineStr">
+        <is>
+          <t>PS5-61-05 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0003)</t>
+        </is>
+      </c>
+      <c r="C103" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D103" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E103" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F103" s="23" t="inlineStr"/>
+      <c r="G103" s="67" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="81" t="n">
+        <v>102</v>
+      </c>
+      <c r="B104" s="83" t="inlineStr">
+        <is>
+          <t>PS5-61-07 - 0.4kV Switchboard EITS Building (PS5-61-IK-0001)</t>
+        </is>
+      </c>
+      <c r="C104" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D104" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E104" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F104" s="23" t="inlineStr"/>
+      <c r="G104" s="67" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="81" t="n">
+        <v>103</v>
+      </c>
+      <c r="B105" s="83" t="inlineStr">
+        <is>
+          <t>PS5-61-10 - Outdoor Valves Distribution Board - PS5-61-IG-0042</t>
+        </is>
+      </c>
+      <c r="C105" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D105" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E105" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F105" s="23" t="inlineStr"/>
+      <c r="G105" s="67" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="81" t="n">
+        <v>104</v>
+      </c>
+      <c r="B106" s="83" t="inlineStr">
+        <is>
+          <t>PS5-61-11 - Outdoor Valves Distribution Board - PS5-61-IG-0043</t>
+        </is>
+      </c>
+      <c r="C106" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D106" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E106" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F106" s="23" t="inlineStr"/>
+      <c r="G106" s="67" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="81" t="n">
+        <v>105</v>
+      </c>
+      <c r="B107" s="83" t="inlineStr">
+        <is>
+          <t>PS5-62-03 - Outdoor Emergency Lighting DB  - PS5-05-IG-0004</t>
+        </is>
+      </c>
+      <c r="C107" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D107" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E107" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F107" s="23" t="inlineStr"/>
+      <c r="G107" s="67" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="81" t="n">
+        <v>106</v>
+      </c>
+      <c r="B108" s="83" t="inlineStr">
+        <is>
+          <t>PS5-62-04 - Outdoor Emergency Lighting DB  - PS5-05-IG-0006</t>
+        </is>
+      </c>
+      <c r="C108" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D108" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E108" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F108" s="23" t="inlineStr"/>
+      <c r="G108" s="67" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="81" t="n">
+        <v>107</v>
+      </c>
+      <c r="B109" s="83" t="inlineStr">
+        <is>
+          <t>PS5-63-04 - Electrical Earthing - EITS Building</t>
+        </is>
+      </c>
+      <c r="C109" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D109" s="24" t="inlineStr"/>
+      <c r="E109" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F109" s="23" t="inlineStr"/>
+      <c r="G109" s="67" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="81" t="n">
+        <v>108</v>
+      </c>
+      <c r="B110" s="83" t="inlineStr">
+        <is>
+          <t>PS5-71-02 - CFO Allocation Metering Package</t>
+        </is>
+      </c>
+      <c r="C110" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D110" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E110" s="28" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="F110" s="23" t="inlineStr"/>
+      <c r="G110" s="67" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="81" t="n">
+        <v>109</v>
+      </c>
+      <c r="B111" s="83" t="inlineStr">
+        <is>
+          <t>PS5-71-09 - CFO Pre-Pressure Modules (UCP)</t>
+        </is>
+      </c>
+      <c r="C111" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D111" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E111" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F111" s="23" t="inlineStr"/>
+      <c r="G111" s="67" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="81" t="n">
+        <v>110</v>
+      </c>
+      <c r="B112" s="83" t="inlineStr">
+        <is>
+          <t>PS5-71-14 - Diesel Fuel Transfer and Dispensing Station</t>
+        </is>
+      </c>
+      <c r="C112" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D112" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E112" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F112" s="23" t="inlineStr"/>
+      <c r="G112" s="67" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="81" t="n">
+        <v>111</v>
+      </c>
+      <c r="B113" s="83" t="inlineStr">
+        <is>
+          <t>PS5-71-16 - Diesel Fuel Supply Pump A/B</t>
+        </is>
+      </c>
+      <c r="C113" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D113" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E113" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F113" s="23" t="inlineStr"/>
+      <c r="G113" s="67" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="81" t="n">
+        <v>112</v>
+      </c>
+      <c r="B114" s="83" t="inlineStr">
+        <is>
+          <t>PS5-71-22 - Diesel Fuel Pre Pressure Module</t>
+        </is>
+      </c>
+      <c r="C114" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D114" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E114" s="28" t="inlineStr">
+        <is>
+          <t>DONE(full)</t>
+        </is>
+      </c>
+      <c r="F114" s="23" t="inlineStr"/>
+      <c r="G114" s="67" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="81" t="n">
+        <v>113</v>
+      </c>
+      <c r="B115" s="83" t="inlineStr">
+        <is>
+          <t>PS5-74-01 - N2 Generation Skid</t>
+        </is>
+      </c>
+      <c r="C115" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D115" s="24" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E115" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F115" s="23" t="inlineStr"/>
+      <c r="G115" s="67" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="81" t="n">
+        <v>114</v>
+      </c>
+      <c r="B116" s="83" t="inlineStr">
+        <is>
+          <t>PS5-74-03 - Nitrogen Receiver</t>
+        </is>
+      </c>
+      <c r="C116" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D116" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E116" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F116" s="23" t="inlineStr"/>
+      <c r="G116" s="67" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="81" t="n">
+        <v>115</v>
+      </c>
+      <c r="B117" s="83" t="inlineStr">
+        <is>
+          <t>PS5-74-04 - Nitrogen Distribution Header</t>
+        </is>
+      </c>
+      <c r="C117" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D117" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E117" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F117" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G117" s="67" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="81" t="n">
+        <v>116</v>
+      </c>
+      <c r="B118" s="83" t="inlineStr">
+        <is>
+          <t>PS5-75-02 - Biocide Injection Package</t>
+        </is>
+      </c>
+      <c r="C118" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D118" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E118" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F118" s="23" t="inlineStr"/>
+      <c r="G118" s="67" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="81" t="n">
+        <v>117</v>
+      </c>
+      <c r="B119" s="83" t="inlineStr">
+        <is>
+          <t>PS5-75-03 - Corrosion Inhibitor Injection Package</t>
+        </is>
+      </c>
+      <c r="C119" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D119" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E119" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F119" s="23" t="inlineStr"/>
+      <c r="G119" s="67" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="85" t="n">
+        <v>118</v>
+      </c>
+      <c r="B120" s="83" t="inlineStr">
+        <is>
+          <t>PS5-78-01 - Lifting and handling equipment</t>
+        </is>
+      </c>
+      <c r="C120" s="28" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="D120" s="24" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E120" s="69" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="F120" s="23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G120" s="67" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="81" t="n">
+        <v>119</v>
+      </c>
+      <c r="B121" s="83" t="inlineStr">
+        <is>
+          <t>PS5-82-01 - Sanitary Sewage Collection</t>
+        </is>
+      </c>
+      <c r="C121" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D121" s="24" t="inlineStr"/>
+      <c r="E121" s="28" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="F121" s="23" t="inlineStr"/>
+      <c r="G121" s="67" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="81" t="n">
+        <v>120</v>
+      </c>
+      <c r="B122" s="83" t="inlineStr">
+        <is>
+          <t>PS5-83-01 - EITS Building</t>
+        </is>
+      </c>
+      <c r="C122" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D122" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E122" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F122" s="23" t="inlineStr"/>
+      <c r="G122" s="67" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="81" t="n">
+        <v>121</v>
+      </c>
+      <c r="B123" s="83" t="inlineStr">
+        <is>
+          <t>PS5-84-03 - Shelters</t>
+        </is>
+      </c>
+      <c r="C123" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D123" s="24" t="inlineStr"/>
+      <c r="E123" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F123" s="23" t="inlineStr"/>
+      <c r="G123" s="67" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="81" t="n">
+        <v>122</v>
+      </c>
+      <c r="B124" s="83" t="inlineStr">
+        <is>
+          <t>PS5-86-01 - Shelters</t>
+        </is>
+      </c>
+      <c r="C124" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D124" s="24" t="inlineStr"/>
+      <c r="E124" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F124" s="23" t="inlineStr"/>
+      <c r="G124" s="67" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="81" t="n">
+        <v>123</v>
+      </c>
+      <c r="B125" s="83" t="inlineStr">
+        <is>
           <t>PS5-91-01 - Multicore cables &amp; JB</t>
         </is>
       </c>
-      <c r="C67" s="27" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D67" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E67" s="27" t="inlineStr">
+      <c r="C125" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D125" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E125" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F67" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G67" s="67" t="inlineStr"/>
+      <c r="F125" s="23" t="inlineStr"/>
+      <c r="G125" s="67" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:G67"/>
+  <autoFilter ref="A2:G125"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
@@ -3232,6 +4586,64 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B65" r:id="rId63"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B66" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B67" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B68" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B69" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B70" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B71" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B72" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B73" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B74" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B75" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B76" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B77" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B78" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B79" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B80" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B81" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B82" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B83" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B84" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B85" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B86" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B87" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B88" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B89" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B90" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B91" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B92" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B93" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B94" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B95" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B96" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B97" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B98" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B99" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B100" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B101" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B102" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B103" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B104" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B105" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B106" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B107" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B108" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B109" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B110" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B111" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B112" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B113" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B114" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B115" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B116" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B117" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B118" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B119" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B120" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B121" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B122" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B123" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B124" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B125" r:id="rId123"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXCEL/7 - COMPLETE.xlsx
+++ b/EXCEL/7 - COMPLETE.xlsx
@@ -11,7 +11,7 @@
     <sheet name="SIDMAP" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'7 · COMPLETE'!$A$2:$G$125</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'7 · COMPLETE'!$A$2:$G$126</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -241,6 +241,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFffeb9c"/>
+        <bgColor rgb="FFffeb9c"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFe8d5c4"/>
         <bgColor rgb="FFe8d5c4"/>
       </patternFill>
@@ -309,12 +315,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFBDD7EE"/>
         <bgColor rgb="FFBDD7EE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFffeb9c"/>
-        <bgColor rgb="FFffeb9c"/>
       </patternFill>
     </fill>
     <fill>
@@ -570,7 +570,7 @@
     <xf numFmtId="0" fontId="9" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -644,88 +644,88 @@
     <xf numFmtId="0" fontId="2" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -740,7 +740,7 @@
     <xf numFmtId="0" fontId="4" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -773,16 +773,16 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1152,7 +1152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G125"/>
+  <dimension ref="A1:G126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="B3" s="83" t="inlineStr">
         <is>
-          <t>PS5-01-04 - Fire Water Pump Mini Flow Recycle</t>
+          <t>PS5-01-01 - Fire Water Jockey Pump A/B</t>
         </is>
       </c>
       <c r="C3" s="28" t="inlineStr">
@@ -1228,7 +1228,11 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="D3" s="24" t="inlineStr"/>
+      <c r="D3" s="24" t="inlineStr">
+        <is>
+          <t>DONE(partial)</t>
+        </is>
+      </c>
       <c r="E3" s="28" t="inlineStr">
         <is>
           <t>Full</t>
@@ -1243,7 +1247,7 @@
       </c>
       <c r="B4" s="83" t="inlineStr">
         <is>
-          <t>PS5-01-05 - Foam Skid</t>
+          <t>PS5-01-04 - Fire Water Pump Mini Flow Recycle</t>
         </is>
       </c>
       <c r="C4" s="28" t="inlineStr">
@@ -1251,11 +1255,7 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="D4" s="24" t="inlineStr">
-        <is>
-          <t>PS5 - Milestone F</t>
-        </is>
-      </c>
+      <c r="D4" s="24" t="inlineStr"/>
       <c r="E4" s="28" t="inlineStr">
         <is>
           <t>Full</t>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="B5" s="83" t="inlineStr">
         <is>
-          <t>PS5-01-06 - Foam Concentrate Distribution</t>
+          <t>PS5-01-05 - Foam Skid</t>
         </is>
       </c>
       <c r="C5" s="28" t="inlineStr">
@@ -1278,7 +1278,11 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="D5" s="24" t="inlineStr"/>
+      <c r="D5" s="24" t="inlineStr">
+        <is>
+          <t>PS5 - Milestone F</t>
+        </is>
+      </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
           <t>Full</t>
@@ -1293,7 +1297,7 @@
       </c>
       <c r="B6" s="83" t="inlineStr">
         <is>
-          <t>PS5-01-09 - Inergen for EITS Building</t>
+          <t>PS5-01-06 - Foam Concentrate Distribution</t>
         </is>
       </c>
       <c r="C6" s="28" t="inlineStr">
@@ -1304,7 +1308,7 @@
       <c r="D6" s="24" t="inlineStr"/>
       <c r="E6" s="28" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F6" s="23" t="inlineStr"/>
@@ -1316,7 +1320,7 @@
       </c>
       <c r="B7" s="83" t="inlineStr">
         <is>
-          <t>PS5-01-10 - Water Mist Package</t>
+          <t>PS5-01-09 - Inergen for EITS Building</t>
         </is>
       </c>
       <c r="C7" s="28" t="inlineStr">
@@ -1324,14 +1328,10 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="D7" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
+      <c r="D7" s="24" t="inlineStr"/>
       <c r="E7" s="28" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="F7" s="23" t="inlineStr"/>
@@ -1343,7 +1343,7 @@
       </c>
       <c r="B8" s="83" t="inlineStr">
         <is>
-          <t>PS5-01-11 - Inergen for Power Gen Building</t>
+          <t>PS5-01-10 - Water Mist Package</t>
         </is>
       </c>
       <c r="C8" s="28" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="D8" s="24" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="E8" s="28" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F8" s="23" t="inlineStr"/>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="B9" s="83" t="inlineStr">
         <is>
-          <t>PS5-03-01 - FZ-01 - Process Area</t>
+          <t>PS5-01-11 - Inergen for Power Gen Building</t>
         </is>
       </c>
       <c r="C9" s="28" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="D9" s="24" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>full</t>
         </is>
       </c>
       <c r="E9" s="28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>FULL</t>
         </is>
       </c>
       <c r="F9" s="23" t="inlineStr"/>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="B10" s="83" t="inlineStr">
         <is>
-          <t>PS5-03-06 - FZ-06 - Transformer Area</t>
+          <t>PS5-03-01 - FZ-01 - Process Area</t>
         </is>
       </c>
       <c r="C10" s="28" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="B11" s="83" t="inlineStr">
         <is>
-          <t>PS5-03-07 - FZ-07 - Pretreatment Area</t>
+          <t>PS5-03-06 - FZ-06 - Transformer Area</t>
         </is>
       </c>
       <c r="C11" s="28" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="B12" s="83" t="inlineStr">
         <is>
-          <t>PS5-03-09 - FZ-09 - Power Generation Building - Engine Bay 1</t>
+          <t>PS5-03-07 - FZ-07 - Pretreatment Area</t>
         </is>
       </c>
       <c r="C12" s="28" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="B13" s="83" t="inlineStr">
         <is>
-          <t>PS5-03-10 - FZ-10 - Power Generation Building - Engine Bay 2</t>
+          <t>PS5-03-09 - FZ-09 - Power Generation Building - Engine Bay 1</t>
         </is>
       </c>
       <c r="C13" s="28" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="B14" s="83" t="inlineStr">
         <is>
-          <t>PS5-03-11 - FZ-11 - Power Generation Building - Engine Bay 3</t>
+          <t>PS5-03-10 - FZ-10 - Power Generation Building - Engine Bay 2</t>
         </is>
       </c>
       <c r="C14" s="28" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="E14" s="28" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F14" s="23" t="inlineStr"/>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B15" s="83" t="inlineStr">
         <is>
-          <t>PS5-03-12 - FZ-12 - Power Generation Building - Engine Bay 4</t>
+          <t>PS5-03-11 - FZ-11 - Power Generation Building - Engine Bay 3</t>
         </is>
       </c>
       <c r="C15" s="28" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="D15" s="24" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>full</t>
         </is>
       </c>
       <c r="E15" s="28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>full</t>
         </is>
       </c>
       <c r="F15" s="23" t="inlineStr"/>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="B16" s="83" t="inlineStr">
         <is>
-          <t>PS5-03-13 - FZ-13 - Power Generation Building - Instrument Air Room</t>
+          <t>PS5-03-12 - FZ-12 - Power Generation Building - Engine Bay 4</t>
         </is>
       </c>
       <c r="C16" s="28" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="B17" s="83" t="inlineStr">
         <is>
-          <t>PS5-03-20 - FZ-20 - Emergency Diesel Generator Enclosure</t>
+          <t>PS5-03-13 - FZ-13 - Power Generation Building - Instrument Air Room</t>
         </is>
       </c>
       <c r="C17" s="28" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="E17" s="28" t="inlineStr">
         <is>
-          <t>07-Aug-26</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F17" s="23" t="inlineStr"/>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="B18" s="83" t="inlineStr">
         <is>
-          <t>PS5-05-01 - Emergency Diesel Generator Package</t>
+          <t>PS5-03-20 - FZ-20 - Emergency Diesel Generator Enclosure</t>
         </is>
       </c>
       <c r="C18" s="28" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="E18" s="28" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>07-Aug-26</t>
         </is>
       </c>
       <c r="F18" s="23" t="inlineStr"/>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="B19" s="83" t="inlineStr">
         <is>
-          <t>PS5-05-02 - Emergency Diesel Generator Package (UCP)</t>
+          <t>PS5-05-01 - Emergency Diesel Generator Package</t>
         </is>
       </c>
       <c r="C19" s="28" t="inlineStr">
@@ -1653,9 +1653,9 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E19" s="28" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
+      <c r="E19" s="69" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="F19" s="23" t="inlineStr"/>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="B20" s="83" t="inlineStr">
         <is>
-          <t>PS5-06-02 - AC UPS - Power Generator Building</t>
+          <t>PS5-05-02 - Emergency Diesel Generator Package (UCP)</t>
         </is>
       </c>
       <c r="C20" s="28" t="inlineStr">
@@ -1680,9 +1680,9 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E20" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="E20" s="54" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="F20" s="23" t="inlineStr"/>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="B21" s="83" t="inlineStr">
         <is>
-          <t>PS5-09-05 - HVAC for EITS Building</t>
+          <t>PS5-06-02 - AC UPS - Power Generator Building</t>
         </is>
       </c>
       <c r="C21" s="28" t="inlineStr">
@@ -1702,10 +1702,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="D21" s="24" t="inlineStr"/>
+      <c r="D21" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
       <c r="E21" s="28" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F21" s="23" t="inlineStr"/>
@@ -1717,7 +1721,7 @@
       </c>
       <c r="B22" s="83" t="inlineStr">
         <is>
-          <t>PS5-25-05 - Crude Oil Export Pumps Bypass</t>
+          <t>PS5-09-05 - HVAC for EITS Building</t>
         </is>
       </c>
       <c r="C22" s="28" t="inlineStr">
@@ -1725,11 +1729,7 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="D22" s="24" t="inlineStr">
-        <is>
-          <t>full</t>
-        </is>
-      </c>
+      <c r="D22" s="24" t="inlineStr"/>
       <c r="E22" s="28" t="inlineStr">
         <is>
           <t>Full</t>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="B23" s="83" t="inlineStr">
         <is>
-          <t>PS5-28-02 - Closed Drain Header 2</t>
+          <t>PS5-25-05 - Crude Oil Export Pumps Bypass</t>
         </is>
       </c>
       <c r="C23" s="28" t="inlineStr">
@@ -1752,7 +1752,11 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="D23" s="24" t="inlineStr"/>
+      <c r="D23" s="24" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
       <c r="E23" s="28" t="inlineStr">
         <is>
           <t>Full</t>
@@ -1767,7 +1771,7 @@
       </c>
       <c r="B24" s="83" t="inlineStr">
         <is>
-          <t>PS5-28-05 - HP Relief Header</t>
+          <t>PS5-28-02 - Closed Drain Header 2</t>
         </is>
       </c>
       <c r="C24" s="28" t="inlineStr">
@@ -1775,11 +1779,7 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="D24" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
+      <c r="D24" s="24" t="inlineStr"/>
       <c r="E24" s="28" t="inlineStr">
         <is>
           <t>Full</t>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="B25" s="83" t="inlineStr">
         <is>
-          <t>PS5-28-06 - Relief Drum and Pump</t>
+          <t>PS5-28-05 - HP Relief Header</t>
         </is>
       </c>
       <c r="C25" s="28" t="inlineStr">
@@ -1821,83 +1821,83 @@
       </c>
       <c r="B26" s="83" t="inlineStr">
         <is>
+          <t>PS5-28-06 - Relief Drum and Pump</t>
+        </is>
+      </c>
+      <c r="C26" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D26" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E26" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F26" s="23" t="inlineStr"/>
+      <c r="G26" s="67" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="81" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="83" t="inlineStr">
+        <is>
           <t>PS5-28-07 - Open Drains (OD2)</t>
         </is>
       </c>
-      <c r="C26" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D26" s="24" t="inlineStr"/>
-      <c r="E26" s="28" t="inlineStr">
+      <c r="C27" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D27" s="24" t="inlineStr"/>
+      <c r="E27" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F26" s="23" t="inlineStr">
+      <c r="F27" s="23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G26" s="67" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="85" t="n">
-        <v>25</v>
-      </c>
-      <c r="B27" s="83" t="inlineStr">
+      <c r="G27" s="67" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="85" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="83" t="inlineStr">
         <is>
           <t>PS5-28-08 - Open Drain Sump and Pumps</t>
         </is>
       </c>
-      <c r="C27" s="28" t="inlineStr">
+      <c r="C28" s="28" t="inlineStr">
         <is>
           <t>99%</t>
         </is>
       </c>
-      <c r="D27" s="24" t="inlineStr">
+      <c r="D28" s="24" t="inlineStr">
         <is>
           <t>full</t>
         </is>
       </c>
-      <c r="E27" s="69" t="inlineStr">
+      <c r="E28" s="69" t="inlineStr">
         <is>
           <t>partial</t>
         </is>
       </c>
-      <c r="F27" s="23" t="inlineStr">
+      <c r="F28" s="23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G27" s="67" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="81" t="n">
-        <v>26</v>
-      </c>
-      <c r="B28" s="83" t="inlineStr">
-        <is>
-          <t>PS5-28-11 - Open Drain Interceptor</t>
-        </is>
-      </c>
-      <c r="C28" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D28" s="24" t="inlineStr">
-        <is>
-          <t>FULL</t>
-        </is>
-      </c>
-      <c r="E28" s="28" t="inlineStr">
-        <is>
-          <t>FULL</t>
-        </is>
-      </c>
-      <c r="F28" s="23" t="inlineStr"/>
       <c r="G28" s="67" t="inlineStr"/>
     </row>
     <row r="29">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="B29" s="83" t="inlineStr">
         <is>
-          <t>PS5-28-12 - Open Drains (OD3)</t>
+          <t>PS5-28-11 - Open Drain Interceptor</t>
         </is>
       </c>
       <c r="C29" s="28" t="inlineStr">
@@ -1914,10 +1914,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="D29" s="24" t="inlineStr"/>
+      <c r="D29" s="24" t="inlineStr">
+        <is>
+          <t>FULL</t>
+        </is>
+      </c>
       <c r="E29" s="28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>FULL</t>
         </is>
       </c>
       <c r="F29" s="23" t="inlineStr"/>
@@ -1929,7 +1933,7 @@
       </c>
       <c r="B30" s="83" t="inlineStr">
         <is>
-          <t>PS5-28-16 - LP Relief Header</t>
+          <t>PS5-28-12 - Open Drains (OD3)</t>
         </is>
       </c>
       <c r="C30" s="28" t="inlineStr">
@@ -1937,75 +1941,71 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="D30" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
+      <c r="D30" s="24" t="inlineStr"/>
       <c r="E30" s="28" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F30" s="23" t="inlineStr"/>
       <c r="G30" s="67" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="85" t="n">
+      <c r="A31" s="81" t="n">
         <v>29</v>
       </c>
       <c r="B31" s="83" t="inlineStr">
         <is>
+          <t>PS5-28-16 - LP Relief Header</t>
+        </is>
+      </c>
+      <c r="C31" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D31" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E31" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F31" s="23" t="inlineStr"/>
+      <c r="G31" s="67" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="85" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="83" t="inlineStr">
+        <is>
           <t>PS5-53-01 - Utility Water / Storage Tank</t>
         </is>
       </c>
-      <c r="C31" s="28" t="inlineStr">
+      <c r="C32" s="28" t="inlineStr">
         <is>
           <t>96%</t>
         </is>
       </c>
-      <c r="D31" s="24" t="inlineStr">
+      <c r="D32" s="24" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="E31" s="69" t="inlineStr">
+      <c r="E32" s="69" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="F31" s="23" t="inlineStr">
+      <c r="F32" s="23" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G31" s="67" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="81" t="n">
-        <v>30</v>
-      </c>
-      <c r="B32" s="83" t="inlineStr">
-        <is>
-          <t>PS5-53-02 - Water Distribution Pump A/B</t>
-        </is>
-      </c>
-      <c r="C32" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D32" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E32" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F32" s="23" t="inlineStr"/>
       <c r="G32" s="67" t="inlineStr"/>
     </row>
     <row r="33">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="B33" s="83" t="inlineStr">
         <is>
-          <t>PS5-53-05 - Water Distribution Header</t>
+          <t>PS5-53-02 - Water Distribution Pump A/B</t>
         </is>
       </c>
       <c r="C33" s="28" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="E33" s="28" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F33" s="23" t="inlineStr"/>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="B34" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-01 - Power Generation Package A</t>
+          <t>PS5-53-05 - Water Distribution Header</t>
         </is>
       </c>
       <c r="C34" s="28" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="B35" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-02 - Power Gen Package A (UCP)</t>
+          <t>PS5-60-01 - Power Generation Package A</t>
         </is>
       </c>
       <c r="C35" s="28" t="inlineStr">
@@ -2078,19 +2078,15 @@
       </c>
       <c r="D35" s="24" t="inlineStr">
         <is>
-          <t>PS5 - Milestone B</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="E35" s="28" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F35" s="23" t="inlineStr">
-        <is>
-          <t>WALKDOWN COMPLETE-20-08-26--ATTENDENCE SHEET TO BE SUBMITTED</t>
-        </is>
-      </c>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F35" s="23" t="inlineStr"/>
       <c r="G35" s="67" t="inlineStr"/>
     </row>
     <row r="36">
@@ -2099,7 +2095,7 @@
       </c>
       <c r="B36" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-03 - Power Gen Package A Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-60-02 - Power Gen Package A (UCP)</t>
         </is>
       </c>
       <c r="C36" s="28" t="inlineStr">
@@ -2109,7 +2105,7 @@
       </c>
       <c r="D36" s="24" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>PS5 - Milestone B</t>
         </is>
       </c>
       <c r="E36" s="28" t="inlineStr">
@@ -2117,7 +2113,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F36" s="23" t="inlineStr"/>
+      <c r="F36" s="23" t="inlineStr">
+        <is>
+          <t>WALKDOWN COMPLETE-20-08-26--ATTENDENCE SHEET TO BE SUBMITTED</t>
+        </is>
+      </c>
       <c r="G36" s="67" t="inlineStr"/>
     </row>
     <row r="37">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="B37" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-04 - Power Generation Package B</t>
+          <t>PS5-60-03 - Power Gen Package A Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="C37" s="28" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="E37" s="28" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F37" s="23" t="inlineStr"/>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="B38" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-05 - Power Gen Package B (UCP)</t>
+          <t>PS5-60-04 - Power Generation Package B</t>
         </is>
       </c>
       <c r="C38" s="28" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="E38" s="28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F38" s="23" t="inlineStr"/>
@@ -2180,7 +2180,7 @@
       </c>
       <c r="B39" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-06 - Power Gen Package B Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-60-05 - Power Gen Package B (UCP)</t>
         </is>
       </c>
       <c r="C39" s="28" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="B40" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-08 - Power Gen Package C (UCP)</t>
+          <t>PS5-60-06 - Power Gen Package B Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="C40" s="28" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="B41" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-09 - Power Gen Package C Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-60-08 - Power Gen Package C (UCP)</t>
         </is>
       </c>
       <c r="C41" s="28" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="B42" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-11 - Power Gen Package D (UCP)</t>
+          <t>PS5-60-09 - Power Gen Package C Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="C42" s="28" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B43" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-12 - Power Gen Package D Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-60-11 - Power Gen Package D (UCP)</t>
         </is>
       </c>
       <c r="C43" s="28" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="B44" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-13 - Power Generation Package E</t>
+          <t>PS5-60-12 - Power Gen Package D Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="C44" s="28" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="E44" s="28" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F44" s="23" t="inlineStr"/>
@@ -2342,7 +2342,7 @@
       </c>
       <c r="B45" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-14 - Power Gen Package E (UCP)</t>
+          <t>PS5-60-13 - Power Generation Package E</t>
         </is>
       </c>
       <c r="C45" s="28" t="inlineStr">
@@ -2352,12 +2352,12 @@
       </c>
       <c r="D45" s="24" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="E45" s="28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F45" s="23" t="inlineStr"/>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="B46" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-15 - Power Gen Package E Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-60-14 - Power Gen Package E (UCP)</t>
         </is>
       </c>
       <c r="C46" s="28" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="D46" s="24" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>full</t>
         </is>
       </c>
       <c r="E46" s="28" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="B47" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-17 - Power Gen Package F (UCP)</t>
+          <t>PS5-60-15 - Power Gen Package E Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="C47" s="28" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="B48" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-18 - Power Gen Package F Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-60-17 - Power Gen Package F (UCP)</t>
         </is>
       </c>
       <c r="C48" s="28" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="B49" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-20 - Power Gen Package G (UCP)</t>
+          <t>PS5-60-18 - Power Gen Package F Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="C49" s="28" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="D49" s="24" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="E49" s="28" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="B50" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-21 - Power Gen Package G Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-60-20 - Power Gen Package G (UCP)</t>
         </is>
       </c>
       <c r="C50" s="28" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="D50" s="24" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="E50" s="28" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B51" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-23 - Instrument Air Distribution lines</t>
+          <t>PS5-60-21 - Power Gen Package G Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="C51" s="28" t="inlineStr">
@@ -2512,10 +2512,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="D51" s="24" t="inlineStr"/>
+      <c r="D51" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
       <c r="E51" s="28" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F51" s="23" t="inlineStr"/>
@@ -2527,7 +2531,7 @@
       </c>
       <c r="B52" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-26 - Instrument Air Compressor Skid</t>
+          <t>PS5-60-23 - Instrument Air Distribution lines</t>
         </is>
       </c>
       <c r="C52" s="28" t="inlineStr">
@@ -2535,11 +2539,7 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="D52" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
+      <c r="D52" s="24" t="inlineStr"/>
       <c r="E52" s="28" t="inlineStr">
         <is>
           <t>Full</t>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="B53" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-27 - Compressed Air Starting Skid</t>
+          <t>PS5-60-26 - Instrument Air Compressor Skid</t>
         </is>
       </c>
       <c r="C53" s="28" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="B54" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-28 - Air Receiver A &amp; Air Regulator A</t>
+          <t>PS5-60-27 - Compressed Air Starting Skid</t>
         </is>
       </c>
       <c r="C54" s="28" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="E54" s="28" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F54" s="23" t="inlineStr"/>
@@ -2608,7 +2608,7 @@
       </c>
       <c r="B55" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-29 - Air Receiver B &amp; Air Regulator B</t>
+          <t>PS5-60-28 - Air Receiver A &amp; Air Regulator A</t>
         </is>
       </c>
       <c r="C55" s="28" t="inlineStr">
@@ -2621,9 +2621,9 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E55" s="28" t="inlineStr">
-        <is>
-          <t>Full</t>
+      <c r="E55" s="69" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="F55" s="23" t="inlineStr"/>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="B56" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-30 - Air Receiver C &amp; Air Regulator C</t>
+          <t>PS5-60-29 - Air Receiver B &amp; Air Regulator B</t>
         </is>
       </c>
       <c r="C56" s="28" t="inlineStr">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="B57" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-31 - Air Receiver D &amp; Air Regulator D</t>
+          <t>PS5-60-30 - Air Receiver C &amp; Air Regulator C</t>
         </is>
       </c>
       <c r="C57" s="28" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="B58" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-32 - Air Receiver E &amp; Air Regulator E</t>
+          <t>PS5-60-31 - Air Receiver D &amp; Air Regulator D</t>
         </is>
       </c>
       <c r="C58" s="28" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="B59" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-33 - Air Receiver F &amp; Air Regulator F</t>
+          <t>PS5-60-32 - Air Receiver E &amp; Air Regulator E</t>
         </is>
       </c>
       <c r="C59" s="28" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="B60" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-34 - Air Receiver G &amp; Air Regulator G</t>
+          <t>PS5-60-33 - Air Receiver F &amp; Air Regulator F</t>
         </is>
       </c>
       <c r="C60" s="28" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="B61" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-35 - Injector Tip Cooling Module A</t>
+          <t>PS5-60-34 - Air Receiver G &amp; Air Regulator G</t>
         </is>
       </c>
       <c r="C61" s="28" t="inlineStr">
@@ -2785,7 +2785,7 @@
       </c>
       <c r="E61" s="28" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F61" s="23" t="inlineStr"/>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="B62" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-36 - Injector Tip Cooling Module B</t>
+          <t>PS5-60-35 - Injector Tip Cooling Module A</t>
         </is>
       </c>
       <c r="C62" s="28" t="inlineStr">
@@ -2810,9 +2810,9 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E62" s="28" t="inlineStr">
-        <is>
-          <t>Full</t>
+      <c r="E62" s="54" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="F62" s="23" t="inlineStr"/>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="B63" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-37 - Injector Tip Cooling Module C</t>
+          <t>PS5-60-36 - Injector Tip Cooling Module B</t>
         </is>
       </c>
       <c r="C63" s="28" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="B64" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-38 - Injector Tip Cooling Module D</t>
+          <t>PS5-60-37 - Injector Tip Cooling Module C</t>
         </is>
       </c>
       <c r="C64" s="28" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="B65" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-39 - Injector Tip Cooling Module E</t>
+          <t>PS5-60-38 - Injector Tip Cooling Module D</t>
         </is>
       </c>
       <c r="C65" s="28" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="B66" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-40 - Injector Tip Cooling Module F</t>
+          <t>PS5-60-39 - Injector Tip Cooling Module E</t>
         </is>
       </c>
       <c r="C66" s="28" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="B67" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-41 - Injector Tip Cooling Module G</t>
+          <t>PS5-60-40 - Injector Tip Cooling Module F</t>
         </is>
       </c>
       <c r="C67" s="28" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="D67" s="24" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="E67" s="28" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B68" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-42 - Oil Mist Separator Skid PS5-60-VS-9100A</t>
+          <t>PS5-60-41 - Injector Tip Cooling Module G</t>
         </is>
       </c>
       <c r="C68" s="28" t="inlineStr">
@@ -2969,12 +2969,12 @@
       </c>
       <c r="D68" s="24" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>full</t>
         </is>
       </c>
       <c r="E68" s="28" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F68" s="23" t="inlineStr"/>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="B69" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-43 - Oil Mist Separator Skid PS5-60-VS-9100B</t>
+          <t>PS5-60-42 - Oil Mist Separator Skid PS5-60-VS-9100A</t>
         </is>
       </c>
       <c r="C69" s="28" t="inlineStr">
@@ -2999,9 +2999,9 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E69" s="28" t="inlineStr">
-        <is>
-          <t>Full</t>
+      <c r="E69" s="54" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="F69" s="23" t="inlineStr"/>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="B70" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-44 - Oil Mist Separator Skid PS5-60-VS-9100C</t>
+          <t>PS5-60-43 - Oil Mist Separator Skid PS5-60-VS-9100B</t>
         </is>
       </c>
       <c r="C70" s="28" t="inlineStr">
@@ -3040,7 +3040,7 @@
       </c>
       <c r="B71" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-45 - Oil Mist Separator Skid PS5-60-VS-9100D</t>
+          <t>PS5-60-44 - Oil Mist Separator Skid PS5-60-VS-9100C</t>
         </is>
       </c>
       <c r="C71" s="28" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="B72" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-46 - Oil Mist Separator Skid PS5-60-VS-9100E</t>
+          <t>PS5-60-45 - Oil Mist Separator Skid PS5-60-VS-9100D</t>
         </is>
       </c>
       <c r="C72" s="28" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="B73" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-47 - Oil Mist Separator Skid PS5-60-VS-9100F</t>
+          <t>PS5-60-46 - Oil Mist Separator Skid PS5-60-VS-9100E</t>
         </is>
       </c>
       <c r="C73" s="28" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="B74" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-48 - Oil Mist Separator Skid PS5-60-VS-9100G</t>
+          <t>PS5-60-47 - Oil Mist Separator Skid PS5-60-VS-9100F</t>
         </is>
       </c>
       <c r="C74" s="28" t="inlineStr">
@@ -3134,9 +3134,9 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="E74" s="69" t="inlineStr">
-        <is>
-          <t>partial</t>
+      <c r="E74" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
         </is>
       </c>
       <c r="F74" s="23" t="inlineStr"/>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="B75" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-49 - Lube Oil Separator Module PS5-60-UO-81100A</t>
+          <t>PS5-60-48 - Oil Mist Separator Skid PS5-60-VS-9100G</t>
         </is>
       </c>
       <c r="C75" s="28" t="inlineStr">
@@ -3158,19 +3158,15 @@
       </c>
       <c r="D75" s="24" t="inlineStr">
         <is>
-          <t>full</t>
-        </is>
-      </c>
-      <c r="E75" s="28" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F75" s="23" t="inlineStr">
-        <is>
-          <t>OBSERVATION -CLEANING ON PROGRESS</t>
-        </is>
-      </c>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E75" s="69" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="F75" s="23" t="inlineStr"/>
       <c r="G75" s="67" t="inlineStr"/>
     </row>
     <row r="76">
@@ -3179,7 +3175,7 @@
       </c>
       <c r="B76" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-50 - Lube Oil Separator Module PS5-60-UO-81100B</t>
+          <t>PS5-60-49 - Lube Oil Separator Module PS5-60-UO-81100A</t>
         </is>
       </c>
       <c r="C76" s="28" t="inlineStr">
@@ -3197,7 +3193,11 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F76" s="23" t="inlineStr"/>
+      <c r="F76" s="23" t="inlineStr">
+        <is>
+          <t>OBSERVATION -CLEANING ON PROGRESS</t>
+        </is>
+      </c>
       <c r="G76" s="67" t="inlineStr"/>
     </row>
     <row r="77">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="B77" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-51 - Lube Oil Separator Module PS5-60-UO-81100C</t>
+          <t>PS5-60-50 - Lube Oil Separator Module PS5-60-UO-81100B</t>
         </is>
       </c>
       <c r="C77" s="28" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="B78" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-52 - Lube Oil Separator Module PS5-60-UO-81100D</t>
+          <t>PS5-60-51 - Lube Oil Separator Module PS5-60-UO-81100C</t>
         </is>
       </c>
       <c r="C78" s="28" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="D78" s="24" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>full</t>
         </is>
       </c>
       <c r="E78" s="28" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="B79" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-53 - Lube Oil Separator Module PS5-60-UO-81100E</t>
+          <t>PS5-60-52 - Lube Oil Separator Module PS5-60-UO-81100D</t>
         </is>
       </c>
       <c r="C79" s="28" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="D79" s="24" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="E79" s="28" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="B80" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-54 - Lube Oil Separator Module PS5-60-UO-81100F</t>
+          <t>PS5-60-53 - Lube Oil Separator Module PS5-60-UO-81100E</t>
         </is>
       </c>
       <c r="C80" s="28" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="D80" s="24" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>full</t>
         </is>
       </c>
       <c r="E80" s="28" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="B81" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-55 - Lube Oil Separator Module PS5-60-UO-81100G</t>
+          <t>PS5-60-54 - Lube Oil Separator Module PS5-60-UO-81100F</t>
         </is>
       </c>
       <c r="C81" s="28" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="B82" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-56 - Fuel Conditioning Module PS5-60-UZ-8900A</t>
+          <t>PS5-60-55 - Lube Oil Separator Module PS5-60-UO-81100G</t>
         </is>
       </c>
       <c r="C82" s="28" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="B83" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-57 - Fuel Conditioning Module PS5-60-UZ-8900A (UCP)</t>
+          <t>PS5-60-56 - Fuel Conditioning Module PS5-60-UZ-8900A</t>
         </is>
       </c>
       <c r="C83" s="28" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="E83" s="28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F83" s="23" t="inlineStr"/>
@@ -3395,7 +3395,7 @@
       </c>
       <c r="B84" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-58 - Fuel Conditioning Module PS5-60-UZ-8900B</t>
+          <t>PS5-60-57 - Fuel Conditioning Module PS5-60-UZ-8900A (UCP)</t>
         </is>
       </c>
       <c r="C84" s="28" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="E84" s="28" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F84" s="23" t="inlineStr"/>
@@ -3422,7 +3422,7 @@
       </c>
       <c r="B85" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-59 - Fuel Conditioning Module PS5-60-UZ-8900B (UCP)</t>
+          <t>PS5-60-58 - Fuel Conditioning Module PS5-60-UZ-8900B</t>
         </is>
       </c>
       <c r="C85" s="28" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="E85" s="28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F85" s="23" t="inlineStr"/>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="B86" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-60 - Fuel Conditioning Module PS5-60-UZ-8900C</t>
+          <t>PS5-60-59 - Fuel Conditioning Module PS5-60-UZ-8900B (UCP)</t>
         </is>
       </c>
       <c r="C86" s="28" t="inlineStr">
@@ -3464,7 +3464,7 @@
       </c>
       <c r="E86" s="28" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F86" s="23" t="inlineStr"/>
@@ -3476,7 +3476,7 @@
       </c>
       <c r="B87" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-61 - Fuel Conditioning Module PS5-60-UZ-8900C (UCP)</t>
+          <t>PS5-60-60 - Fuel Conditioning Module PS5-60-UZ-8900C</t>
         </is>
       </c>
       <c r="C87" s="28" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="E87" s="28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F87" s="23" t="inlineStr"/>
@@ -3503,7 +3503,7 @@
       </c>
       <c r="B88" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-62 - Fuel Conditioning Module PS5-60-UZ-8900D</t>
+          <t>PS5-60-61 - Fuel Conditioning Module PS5-60-UZ-8900C (UCP)</t>
         </is>
       </c>
       <c r="C88" s="28" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="E88" s="28" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F88" s="23" t="inlineStr"/>
@@ -3530,7 +3530,7 @@
       </c>
       <c r="B89" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-63 - Fuel Conditioning Module PS5-60-UZ-8900D (UCP)</t>
+          <t>PS5-60-62 - Fuel Conditioning Module PS5-60-UZ-8900D</t>
         </is>
       </c>
       <c r="C89" s="28" t="inlineStr">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="E89" s="28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F89" s="23" t="inlineStr"/>
@@ -3557,7 +3557,7 @@
       </c>
       <c r="B90" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-65 - Fuel Conditioning Module PS5-60-UZ-8900E (UCP)</t>
+          <t>PS5-60-63 - Fuel Conditioning Module PS5-60-UZ-8900D (UCP)</t>
         </is>
       </c>
       <c r="C90" s="28" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="D90" s="24" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="E90" s="28" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="B91" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-67 - Fuel Conditioning Module PS5-60-UZ-8900F (UCP)</t>
+          <t>PS5-60-65 - Fuel Conditioning Module PS5-60-UZ-8900E (UCP)</t>
         </is>
       </c>
       <c r="C91" s="28" t="inlineStr">
@@ -3606,54 +3606,54 @@
       <c r="G91" s="67" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="85" t="n">
+      <c r="A92" s="81" t="n">
         <v>90</v>
       </c>
       <c r="B92" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-68 - Fuel Conditioning Module PS5-60-UZ-8900G</t>
+          <t>PS5-60-67 - Fuel Conditioning Module PS5-60-UZ-8900F (UCP)</t>
         </is>
       </c>
       <c r="C92" s="28" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="D92" s="24" t="inlineStr">
         <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="E92" s="69" t="inlineStr">
-        <is>
-          <t>partial</t>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="E92" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="F92" s="23" t="inlineStr"/>
       <c r="G92" s="67" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="81" t="n">
+      <c r="A93" s="85" t="n">
         <v>91</v>
       </c>
       <c r="B93" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-69 - Fuel Conditioning Module PS5-60-UZ-8900G (UCP)</t>
+          <t>PS5-60-68 - Fuel Conditioning Module PS5-60-UZ-8900G</t>
         </is>
       </c>
       <c r="C93" s="28" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="D93" s="24" t="inlineStr">
         <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E93" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E93" s="69" t="inlineStr">
+        <is>
+          <t>partial</t>
         </is>
       </c>
       <c r="F93" s="23" t="inlineStr"/>
@@ -3665,7 +3665,7 @@
       </c>
       <c r="B94" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-70 - Engine A Cooling system</t>
+          <t>PS5-60-69 - Fuel Conditioning Module PS5-60-UZ-8900G (UCP)</t>
         </is>
       </c>
       <c r="C94" s="28" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="E94" s="28" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F94" s="23" t="inlineStr"/>
@@ -3692,7 +3692,7 @@
       </c>
       <c r="B95" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-71 - Engine B Cooling system</t>
+          <t>PS5-60-70 - Engine A Cooling system</t>
         </is>
       </c>
       <c r="C95" s="28" t="inlineStr">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="B96" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-72 - Engine C Cooling system</t>
+          <t>PS5-60-71 - Engine B Cooling system</t>
         </is>
       </c>
       <c r="C96" s="28" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="B97" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-73 - Engine D Cooling system</t>
+          <t>PS5-60-72 - Engine C Cooling system</t>
         </is>
       </c>
       <c r="C97" s="28" t="inlineStr">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="B98" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-74 - Engine E Cooling system</t>
+          <t>PS5-60-73 - Engine D Cooling system</t>
         </is>
       </c>
       <c r="C98" s="28" t="inlineStr">
@@ -3788,7 +3788,7 @@
       </c>
       <c r="E98" s="28" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F98" s="23" t="inlineStr"/>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="B99" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-75 - Engine F Cooling system</t>
+          <t>PS5-60-74 - Engine E Cooling system</t>
         </is>
       </c>
       <c r="C99" s="28" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="E99" s="28" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>full</t>
         </is>
       </c>
       <c r="F99" s="23" t="inlineStr"/>
@@ -3827,7 +3827,7 @@
       </c>
       <c r="B100" s="83" t="inlineStr">
         <is>
-          <t>PS5-60-76 - Engine G Cooling system</t>
+          <t>PS5-60-75 - Engine F Cooling system</t>
         </is>
       </c>
       <c r="C100" s="28" t="inlineStr">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="E100" s="28" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F100" s="23" t="inlineStr"/>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="B101" s="83" t="inlineStr">
         <is>
-          <t>PS5-61-02 - 6.6kV Switchboard and Transformer LLHT North - EITS Building (PS5-61-IJ-0010)</t>
+          <t>PS5-60-76 - Engine G Cooling system</t>
         </is>
       </c>
       <c r="C101" s="28" t="inlineStr">
@@ -3869,7 +3869,7 @@
       </c>
       <c r="E101" s="28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>FULL</t>
         </is>
       </c>
       <c r="F101" s="23" t="inlineStr"/>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="B102" s="83" t="inlineStr">
         <is>
-          <t>PS5-61-03 - 6.6kV Switchboard and Transformer LLHT South - EITS Building (PS5-61-IJ-0011)</t>
+          <t>PS5-61-02 - 6.6kV Switchboard and Transformer LLHT North - EITS Building (PS5-61-IJ-0010)</t>
         </is>
       </c>
       <c r="C102" s="28" t="inlineStr">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="E102" s="28" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F102" s="23" t="inlineStr"/>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="B103" s="83" t="inlineStr">
         <is>
-          <t>PS5-61-05 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0003)</t>
+          <t>PS5-61-03 - 6.6kV Switchboard and Transformer LLHT South - EITS Building (PS5-61-IJ-0011)</t>
         </is>
       </c>
       <c r="C103" s="28" t="inlineStr">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="E103" s="28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>full</t>
         </is>
       </c>
       <c r="F103" s="23" t="inlineStr"/>
@@ -3935,7 +3935,7 @@
       </c>
       <c r="B104" s="83" t="inlineStr">
         <is>
-          <t>PS5-61-07 - 0.4kV Switchboard EITS Building (PS5-61-IK-0001)</t>
+          <t>PS5-61-05 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0003)</t>
         </is>
       </c>
       <c r="C104" s="28" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="E104" s="28" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F104" s="23" t="inlineStr"/>
@@ -3962,7 +3962,7 @@
       </c>
       <c r="B105" s="83" t="inlineStr">
         <is>
-          <t>PS5-61-10 - Outdoor Valves Distribution Board - PS5-61-IG-0042</t>
+          <t>PS5-61-07 - 0.4kV Switchboard EITS Building (PS5-61-IK-0001)</t>
         </is>
       </c>
       <c r="C105" s="28" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="E105" s="28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F105" s="23" t="inlineStr"/>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="B106" s="83" t="inlineStr">
         <is>
-          <t>PS5-61-11 - Outdoor Valves Distribution Board - PS5-61-IG-0043</t>
+          <t>PS5-61-10 - Outdoor Valves Distribution Board - PS5-61-IG-0042</t>
         </is>
       </c>
       <c r="C106" s="28" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="B107" s="83" t="inlineStr">
         <is>
-          <t>PS5-62-03 - Outdoor Emergency Lighting DB  - PS5-05-IG-0004</t>
+          <t>PS5-61-11 - Outdoor Valves Distribution Board - PS5-61-IG-0043</t>
         </is>
       </c>
       <c r="C107" s="28" t="inlineStr">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="B108" s="83" t="inlineStr">
         <is>
-          <t>PS5-62-04 - Outdoor Emergency Lighting DB  - PS5-05-IG-0006</t>
+          <t>PS5-62-03 - Outdoor Emergency Lighting DB  - PS5-05-IG-0004</t>
         </is>
       </c>
       <c r="C108" s="28" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="B109" s="83" t="inlineStr">
         <is>
-          <t>PS5-63-04 - Electrical Earthing - EITS Building</t>
+          <t>PS5-62-04 - Outdoor Emergency Lighting DB  - PS5-05-IG-0006</t>
         </is>
       </c>
       <c r="C109" s="28" t="inlineStr">
@@ -4078,7 +4078,11 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="D109" s="24" t="inlineStr"/>
+      <c r="D109" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
       <c r="E109" s="28" t="inlineStr">
         <is>
           <t>-</t>
@@ -4093,7 +4097,7 @@
       </c>
       <c r="B110" s="83" t="inlineStr">
         <is>
-          <t>PS5-71-02 - CFO Allocation Metering Package</t>
+          <t>PS5-63-04 - Electrical Earthing - EITS Building</t>
         </is>
       </c>
       <c r="C110" s="28" t="inlineStr">
@@ -4101,14 +4105,10 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="D110" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
+      <c r="D110" s="24" t="inlineStr"/>
       <c r="E110" s="28" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F110" s="23" t="inlineStr"/>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="B111" s="83" t="inlineStr">
         <is>
-          <t>PS5-71-09 - CFO Pre-Pressure Modules (UCP)</t>
+          <t>PS5-71-02 - CFO Allocation Metering Package</t>
         </is>
       </c>
       <c r="C111" s="28" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="E111" s="28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>full</t>
         </is>
       </c>
       <c r="F111" s="23" t="inlineStr"/>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="B112" s="83" t="inlineStr">
         <is>
-          <t>PS5-71-14 - Diesel Fuel Transfer and Dispensing Station</t>
+          <t>PS5-71-09 - CFO Pre-Pressure Modules (UCP)</t>
         </is>
       </c>
       <c r="C112" s="28" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="E112" s="28" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F112" s="23" t="inlineStr"/>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="B113" s="83" t="inlineStr">
         <is>
-          <t>PS5-71-16 - Diesel Fuel Supply Pump A/B</t>
+          <t>PS5-71-14 - Diesel Fuel Transfer and Dispensing Station</t>
         </is>
       </c>
       <c r="C113" s="28" t="inlineStr">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="B114" s="83" t="inlineStr">
         <is>
-          <t>PS5-71-22 - Diesel Fuel Pre Pressure Module</t>
+          <t>PS5-71-16 - Diesel Fuel Supply Pump A/B</t>
         </is>
       </c>
       <c r="C114" s="28" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="E114" s="28" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F114" s="23" t="inlineStr"/>
@@ -4228,7 +4228,7 @@
       </c>
       <c r="B115" s="83" t="inlineStr">
         <is>
-          <t>PS5-74-01 - N2 Generation Skid</t>
+          <t>PS5-71-22 - Diesel Fuel Pre Pressure Module</t>
         </is>
       </c>
       <c r="C115" s="28" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="D115" s="24" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="E115" s="28" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>DONE(full)</t>
         </is>
       </c>
       <c r="F115" s="23" t="inlineStr"/>
@@ -4255,7 +4255,7 @@
       </c>
       <c r="B116" s="83" t="inlineStr">
         <is>
-          <t>PS5-74-03 - Nitrogen Receiver</t>
+          <t>PS5-74-01 - N2 Generation Skid</t>
         </is>
       </c>
       <c r="C116" s="28" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="D116" s="24" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="E116" s="28" t="inlineStr">
@@ -4282,7 +4282,7 @@
       </c>
       <c r="B117" s="83" t="inlineStr">
         <is>
-          <t>PS5-74-04 - Nitrogen Distribution Header</t>
+          <t>PS5-74-03 - Nitrogen Receiver</t>
         </is>
       </c>
       <c r="C117" s="28" t="inlineStr">
@@ -4300,11 +4300,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F117" s="23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="F117" s="23" t="inlineStr"/>
       <c r="G117" s="67" t="inlineStr"/>
     </row>
     <row r="118">
@@ -4313,7 +4309,7 @@
       </c>
       <c r="B118" s="83" t="inlineStr">
         <is>
-          <t>PS5-75-02 - Biocide Injection Package</t>
+          <t>PS5-74-04 - Nitrogen Distribution Header</t>
         </is>
       </c>
       <c r="C118" s="28" t="inlineStr">
@@ -4331,7 +4327,11 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F118" s="23" t="inlineStr"/>
+      <c r="F118" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="G118" s="67" t="inlineStr"/>
     </row>
     <row r="119">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="B119" s="83" t="inlineStr">
         <is>
-          <t>PS5-75-03 - Corrosion Inhibitor Injection Package</t>
+          <t>PS5-75-02 - Biocide Injection Package</t>
         </is>
       </c>
       <c r="C119" s="28" t="inlineStr">
@@ -4362,57 +4362,61 @@
       <c r="G119" s="67" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="85" t="n">
+      <c r="A120" s="81" t="n">
         <v>118</v>
       </c>
       <c r="B120" s="83" t="inlineStr">
         <is>
+          <t>PS5-75-03 - Corrosion Inhibitor Injection Package</t>
+        </is>
+      </c>
+      <c r="C120" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D120" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E120" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F120" s="23" t="inlineStr"/>
+      <c r="G120" s="67" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="85" t="n">
+        <v>119</v>
+      </c>
+      <c r="B121" s="83" t="inlineStr">
+        <is>
           <t>PS5-78-01 - Lifting and handling equipment</t>
         </is>
       </c>
-      <c r="C120" s="28" t="inlineStr">
+      <c r="C121" s="28" t="inlineStr">
         <is>
           <t>77%</t>
         </is>
       </c>
-      <c r="D120" s="24" t="inlineStr">
+      <c r="D121" s="24" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="E120" s="69" t="inlineStr">
+      <c r="E121" s="69" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="F120" s="23" t="inlineStr">
+      <c r="F121" s="23" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G120" s="67" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="81" t="n">
-        <v>119</v>
-      </c>
-      <c r="B121" s="83" t="inlineStr">
-        <is>
-          <t>PS5-82-01 - Sanitary Sewage Collection</t>
-        </is>
-      </c>
-      <c r="C121" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D121" s="24" t="inlineStr"/>
-      <c r="E121" s="28" t="inlineStr">
-        <is>
-          <t>full</t>
-        </is>
-      </c>
-      <c r="F121" s="23" t="inlineStr"/>
       <c r="G121" s="67" t="inlineStr"/>
     </row>
     <row r="122">
@@ -4421,7 +4425,7 @@
       </c>
       <c r="B122" s="83" t="inlineStr">
         <is>
-          <t>PS5-83-01 - EITS Building</t>
+          <t>PS5-82-01 - Sanitary Sewage Collection</t>
         </is>
       </c>
       <c r="C122" s="28" t="inlineStr">
@@ -4429,14 +4433,10 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="D122" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
+      <c r="D122" s="24" t="inlineStr"/>
       <c r="E122" s="28" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>full</t>
         </is>
       </c>
       <c r="F122" s="23" t="inlineStr"/>
@@ -4448,7 +4448,7 @@
       </c>
       <c r="B123" s="83" t="inlineStr">
         <is>
-          <t>PS5-84-03 - Shelters</t>
+          <t>PS5-83-01 - EITS Building</t>
         </is>
       </c>
       <c r="C123" s="28" t="inlineStr">
@@ -4456,7 +4456,11 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="D123" s="24" t="inlineStr"/>
+      <c r="D123" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
       <c r="E123" s="28" t="inlineStr">
         <is>
           <t>Full</t>
@@ -4471,7 +4475,7 @@
       </c>
       <c r="B124" s="83" t="inlineStr">
         <is>
-          <t>PS5-86-01 - Shelters</t>
+          <t>PS5-84-03 - Shelters</t>
         </is>
       </c>
       <c r="C124" s="28" t="inlineStr">
@@ -4494,7 +4498,7 @@
       </c>
       <c r="B125" s="83" t="inlineStr">
         <is>
-          <t>PS5-91-01 - Multicore cables &amp; JB</t>
+          <t>PS5-86-01 - Shelters</t>
         </is>
       </c>
       <c r="C125" s="28" t="inlineStr">
@@ -4502,21 +4506,44 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="D125" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
+      <c r="D125" s="24" t="inlineStr"/>
       <c r="E125" s="28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F125" s="23" t="inlineStr"/>
       <c r="G125" s="67" t="inlineStr"/>
     </row>
+    <row r="126">
+      <c r="A126" s="81" t="n">
+        <v>124</v>
+      </c>
+      <c r="B126" s="83" t="inlineStr">
+        <is>
+          <t>PS5-91-01 - Multicore cables &amp; JB</t>
+        </is>
+      </c>
+      <c r="C126" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D126" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E126" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F126" s="23" t="inlineStr"/>
+      <c r="G126" s="67" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:G125"/>
+  <autoFilter ref="A2:G126"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
@@ -4644,6 +4671,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B123" r:id="rId121"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B124" r:id="rId122"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B125" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B126" r:id="rId124"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXCEL/7 - COMPLETE.xlsx
+++ b/EXCEL/7 - COMPLETE.xlsx
@@ -11,7 +11,7 @@
     <sheet name="SIDMAP" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'7 · COMPLETE'!$A$2:$G$126</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'7 · COMPLETE'!$A$2:$G$128</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -101,6 +101,12 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF8a97a5"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <color rgb="FFc00000"/>
       <sz val="10"/>
     </font>
@@ -116,6 +122,11 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <color rgb="FF8a97a5"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <color rgb="FFb35900"/>
       <sz val="10"/>
     </font>
@@ -124,12 +135,6 @@
       <color rgb="FF0a58ca"/>
       <sz val="10"/>
       <u val="single"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="FF8a97a5"/>
-      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -172,7 +177,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="39">
     <fill>
       <patternFill/>
     </fill>
@@ -237,12 +242,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF1b4f72"/>
         <bgColor rgb="FF1b4f72"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFffeb9c"/>
-        <bgColor rgb="FFffeb9c"/>
       </patternFill>
     </fill>
     <fill>
@@ -319,6 +318,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFffeb9c"/>
+        <bgColor rgb="FFffeb9c"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFed7d31"/>
         <bgColor rgb="FFed7d31"/>
       </patternFill>
@@ -339,6 +344,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFc6efce"/>
         <bgColor rgb="FFc6efce"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8a97a5"/>
+        <bgColor rgb="FF8a97a5"/>
       </patternFill>
     </fill>
     <fill>
@@ -504,38 +515,35 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="31" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -545,16 +553,19 @@
     <xf numFmtId="0" fontId="2" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -570,7 +581,7 @@
     <xf numFmtId="0" fontId="9" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -579,13 +590,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="36" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="36" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="36" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="37" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -593,7 +604,7 @@
     <xf numFmtId="0" fontId="3" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="37" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="38" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -644,12 +655,15 @@
     <xf numFmtId="0" fontId="2" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -671,25 +685,22 @@
     <xf numFmtId="0" fontId="6" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -698,10 +709,10 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -710,37 +721,46 @@
     <xf numFmtId="0" fontId="5" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -749,40 +769,37 @@
     <xf numFmtId="0" fontId="9" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1152,7 +1169,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G126"/>
+  <dimension ref="A1:G128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1170,12 +1187,12 @@
           <t>PS5 COMPLETION PLATFORM  |  DONE - subsystems at 100%</t>
         </is>
       </c>
-      <c r="B1" s="100" t="n"/>
-      <c r="C1" s="100" t="n"/>
-      <c r="D1" s="100" t="n"/>
-      <c r="E1" s="100" t="n"/>
-      <c r="F1" s="100" t="n"/>
-      <c r="G1" s="101" t="n"/>
+      <c r="B1" s="102" t="n"/>
+      <c r="C1" s="102" t="n"/>
+      <c r="D1" s="102" t="n"/>
+      <c r="E1" s="102" t="n"/>
+      <c r="F1" s="102" t="n"/>
+      <c r="G1" s="103" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="22" t="inlineStr">
@@ -1215,12 +1232,12 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="81" t="n">
+      <c r="A3" s="84" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="83" t="inlineStr">
-        <is>
-          <t>PS5-01-01 - Fire Water Jockey Pump A/B</t>
+      <c r="B3" s="86" t="inlineStr">
+        <is>
+          <t>PS5-01-04 - Fire Water Pump Mini Flow Recycle</t>
         </is>
       </c>
       <c r="C3" s="28" t="inlineStr">
@@ -1228,26 +1245,26 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="D3" s="24" t="inlineStr">
-        <is>
-          <t>DONE(partial)</t>
-        </is>
-      </c>
+      <c r="D3" s="24" t="inlineStr"/>
       <c r="E3" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="F3" s="23" t="inlineStr"/>
+      <c r="F3" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="G3" s="67" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="81" t="n">
+      <c r="A4" s="84" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="83" t="inlineStr">
-        <is>
-          <t>PS5-01-04 - Fire Water Pump Mini Flow Recycle</t>
+      <c r="B4" s="86" t="inlineStr">
+        <is>
+          <t>PS5-01-05 - Foam Skid</t>
         </is>
       </c>
       <c r="C4" s="28" t="inlineStr">
@@ -1255,22 +1272,30 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="D4" s="24" t="inlineStr"/>
+      <c r="D4" s="24" t="inlineStr">
+        <is>
+          <t>PS5 - Milestone F</t>
+        </is>
+      </c>
       <c r="E4" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="F4" s="23" t="inlineStr"/>
+      <c r="F4" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="G4" s="67" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="81" t="n">
+      <c r="A5" s="84" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="83" t="inlineStr">
-        <is>
-          <t>PS5-01-05 - Foam Skid</t>
+      <c r="B5" s="86" t="inlineStr">
+        <is>
+          <t>PS5-01-06 - Foam Concentrate Distribution</t>
         </is>
       </c>
       <c r="C5" s="28" t="inlineStr">
@@ -1278,26 +1303,26 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="D5" s="24" t="inlineStr">
-        <is>
-          <t>PS5 - Milestone F</t>
-        </is>
-      </c>
+      <c r="D5" s="24" t="inlineStr"/>
       <c r="E5" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="F5" s="23" t="inlineStr"/>
+      <c r="F5" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="G5" s="67" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="81" t="n">
+      <c r="A6" s="84" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="83" t="inlineStr">
-        <is>
-          <t>PS5-01-06 - Foam Concentrate Distribution</t>
+      <c r="B6" s="86" t="inlineStr">
+        <is>
+          <t>PS5-01-09 - Inergen for EITS Building</t>
         </is>
       </c>
       <c r="C6" s="28" t="inlineStr">
@@ -1308,19 +1333,23 @@
       <c r="D6" s="24" t="inlineStr"/>
       <c r="E6" s="28" t="inlineStr">
         <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F6" s="23" t="inlineStr"/>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="G6" s="67" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="81" t="n">
+      <c r="A7" s="84" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="83" t="inlineStr">
-        <is>
-          <t>PS5-01-09 - Inergen for EITS Building</t>
+      <c r="B7" s="86" t="inlineStr">
+        <is>
+          <t>PS5-01-10 - Water Mist Package</t>
         </is>
       </c>
       <c r="C7" s="28" t="inlineStr">
@@ -1328,22 +1357,30 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="D7" s="24" t="inlineStr"/>
+      <c r="D7" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
       <c r="E7" s="28" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="F7" s="23" t="inlineStr"/>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F7" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="G7" s="67" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="81" t="n">
+      <c r="A8" s="84" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="83" t="inlineStr">
-        <is>
-          <t>PS5-01-10 - Water Mist Package</t>
+      <c r="B8" s="86" t="inlineStr">
+        <is>
+          <t>PS5-01-11 - Inergen for Power Gen Building</t>
         </is>
       </c>
       <c r="C8" s="28" t="inlineStr">
@@ -1353,24 +1390,28 @@
       </c>
       <c r="D8" s="24" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>full</t>
         </is>
       </c>
       <c r="E8" s="28" t="inlineStr">
         <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F8" s="23" t="inlineStr"/>
+          <t>FULL</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="G8" s="67" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="81" t="n">
+      <c r="A9" s="84" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="83" t="inlineStr">
-        <is>
-          <t>PS5-01-11 - Inergen for Power Gen Building</t>
+      <c r="B9" s="86" t="inlineStr">
+        <is>
+          <t>PS5-03-01 - FZ-01 - Process Area</t>
         </is>
       </c>
       <c r="C9" s="28" t="inlineStr">
@@ -1380,2786 +1421,3178 @@
       </c>
       <c r="D9" s="24" t="inlineStr">
         <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E9" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" s="67" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="84" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="86" t="inlineStr">
+        <is>
+          <t>PS5-03-06 - FZ-06 - Transformer Area</t>
+        </is>
+      </c>
+      <c r="C10" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D10" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E10" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="67" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="84" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="86" t="inlineStr">
+        <is>
+          <t>PS5-03-07 - FZ-07 - Pretreatment Area</t>
+        </is>
+      </c>
+      <c r="C11" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D11" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E11" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="67" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="84" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="86" t="inlineStr">
+        <is>
+          <t>PS5-03-09 - FZ-09 - Power Generation Building - Engine Bay 1</t>
+        </is>
+      </c>
+      <c r="C12" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D12" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E12" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G12" s="67" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="84" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="86" t="inlineStr">
+        <is>
+          <t>PS5-03-10 - FZ-10 - Power Generation Building - Engine Bay 2</t>
+        </is>
+      </c>
+      <c r="C13" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D13" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E13" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="67" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="84" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="86" t="inlineStr">
+        <is>
+          <t>PS5-03-11 - FZ-11 - Power Generation Building - Engine Bay 3</t>
+        </is>
+      </c>
+      <c r="C14" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
           <t>full</t>
         </is>
       </c>
-      <c r="E9" s="28" t="inlineStr">
+      <c r="E14" s="28" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="F14" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="67" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="84" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="86" t="inlineStr">
+        <is>
+          <t>PS5-03-12 - FZ-12 - Power Generation Building - Engine Bay 4</t>
+        </is>
+      </c>
+      <c r="C15" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E15" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F15" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G15" s="67" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="84" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="86" t="inlineStr">
+        <is>
+          <t>PS5-03-13 - FZ-13 - Power Generation Building - Instrument Air Room</t>
+        </is>
+      </c>
+      <c r="C16" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E16" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="67" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="84" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="86" t="inlineStr">
+        <is>
+          <t>PS5-03-20 - FZ-20 - Emergency Diesel Generator Enclosure</t>
+        </is>
+      </c>
+      <c r="C17" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E17" s="28" t="inlineStr">
+        <is>
+          <t>07-Aug-26</t>
+        </is>
+      </c>
+      <c r="F17" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="67" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="84" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="86" t="inlineStr">
+        <is>
+          <t>PS5-05-01 - Emergency Diesel Generator Package</t>
+        </is>
+      </c>
+      <c r="C18" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E18" s="28" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="F18" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G18" s="67" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="84" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="86" t="inlineStr">
+        <is>
+          <t>PS5-05-02 - Emergency Diesel Generator Package (UCP)</t>
+        </is>
+      </c>
+      <c r="C19" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D19" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E19" s="28" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+      <c r="F19" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="67" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="84" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="86" t="inlineStr">
+        <is>
+          <t>PS5-06-02 - AC UPS - Power Generator Building</t>
+        </is>
+      </c>
+      <c r="C20" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D20" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E20" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F20" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="67" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="84" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="86" t="inlineStr">
+        <is>
+          <t>PS5-09-05 - HVAC for EITS Building</t>
+        </is>
+      </c>
+      <c r="C21" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D21" s="24" t="inlineStr"/>
+      <c r="E21" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F21" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G21" s="67" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="84" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="86" t="inlineStr">
+        <is>
+          <t>PS5-25-05 - Crude Oil Export Pumps Bypass</t>
+        </is>
+      </c>
+      <c r="C22" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="E22" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F22" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G22" s="67" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="84" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="86" t="inlineStr">
+        <is>
+          <t>PS5-28-02 - Closed Drain Header 2</t>
+        </is>
+      </c>
+      <c r="C23" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D23" s="24" t="inlineStr"/>
+      <c r="E23" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F23" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G23" s="67" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="84" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="86" t="inlineStr">
+        <is>
+          <t>PS5-28-05 - HP Relief Header</t>
+        </is>
+      </c>
+      <c r="C24" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D24" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E24" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F24" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G24" s="67" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="84" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="86" t="inlineStr">
+        <is>
+          <t>PS5-28-06 - Relief Drum and Pump</t>
+        </is>
+      </c>
+      <c r="C25" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D25" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E25" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F25" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G25" s="67" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="84" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="86" t="inlineStr">
+        <is>
+          <t>PS5-28-07 - Open Drains (OD2)</t>
+        </is>
+      </c>
+      <c r="C26" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D26" s="24" t="inlineStr"/>
+      <c r="E26" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F26" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G26" s="67" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="88" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="86" t="inlineStr">
+        <is>
+          <t>PS5-28-08 - Open Drain Sump and Pumps</t>
+        </is>
+      </c>
+      <c r="C27" s="28" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="D27" s="24" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="E27" s="69" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="F27" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G27" s="67" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="84" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="86" t="inlineStr">
+        <is>
+          <t>PS5-28-11 - Open Drain Interceptor</t>
+        </is>
+      </c>
+      <c r="C28" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D28" s="24" t="inlineStr">
         <is>
           <t>FULL</t>
         </is>
       </c>
-      <c r="F9" s="23" t="inlineStr"/>
-      <c r="G9" s="67" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="81" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" s="83" t="inlineStr">
-        <is>
-          <t>PS5-03-01 - FZ-01 - Process Area</t>
-        </is>
-      </c>
-      <c r="C10" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D10" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E10" s="28" t="inlineStr">
+      <c r="E28" s="28" t="inlineStr">
+        <is>
+          <t>FULL</t>
+        </is>
+      </c>
+      <c r="F28" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G28" s="67" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="84" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="86" t="inlineStr">
+        <is>
+          <t>PS5-28-12 - Open Drains (OD3)</t>
+        </is>
+      </c>
+      <c r="C29" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D29" s="24" t="inlineStr"/>
+      <c r="E29" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="23" t="inlineStr"/>
-      <c r="G10" s="67" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="81" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" s="83" t="inlineStr">
-        <is>
-          <t>PS5-03-06 - FZ-06 - Transformer Area</t>
-        </is>
-      </c>
-      <c r="C11" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D11" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E11" s="28" t="inlineStr">
+      <c r="F29" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G29" s="67" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="84" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="86" t="inlineStr">
+        <is>
+          <t>PS5-28-13 - Seal Oil Drain Drum &amp; Pump A</t>
+        </is>
+      </c>
+      <c r="C30" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D30" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E30" s="28" t="inlineStr">
+        <is>
+          <t>FULL</t>
+        </is>
+      </c>
+      <c r="F30" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G30" s="67" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="84" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="86" t="inlineStr">
+        <is>
+          <t>PS5-28-14 - Seal Oil Drain Drum &amp; Pump B</t>
+        </is>
+      </c>
+      <c r="C31" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D31" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E31" s="28" t="inlineStr">
+        <is>
+          <t>FULL</t>
+        </is>
+      </c>
+      <c r="F31" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G31" s="67" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="84" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="86" t="inlineStr">
+        <is>
+          <t>PS5-28-15 - Seal Oil Drain Drum &amp; Pump C</t>
+        </is>
+      </c>
+      <c r="C32" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D32" s="24" t="inlineStr">
+        <is>
+          <t>FULL</t>
+        </is>
+      </c>
+      <c r="E32" s="28" t="inlineStr">
+        <is>
+          <t>FULL</t>
+        </is>
+      </c>
+      <c r="F32" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G32" s="67" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="84" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="86" t="inlineStr">
+        <is>
+          <t>PS5-28-16 - LP Relief Header</t>
+        </is>
+      </c>
+      <c r="C33" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D33" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E33" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F33" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G33" s="67" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="88" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" s="86" t="inlineStr">
+        <is>
+          <t>PS5-53-01 - Utility Water / Storage Tank</t>
+        </is>
+      </c>
+      <c r="C34" s="28" t="inlineStr">
+        <is>
+          <t>96%</t>
+        </is>
+      </c>
+      <c r="D34" s="24" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E34" s="69" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="F34" s="23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G34" s="67" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="84" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="86" t="inlineStr">
+        <is>
+          <t>PS5-53-02 - Water Distribution Pump A/B</t>
+        </is>
+      </c>
+      <c r="C35" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D35" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E35" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F35" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G35" s="67" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="84" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" s="86" t="inlineStr">
+        <is>
+          <t>PS5-53-05 - Water Distribution Header</t>
+        </is>
+      </c>
+      <c r="C36" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D36" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E36" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F36" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G36" s="67" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="84" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-01 - Power Generation Package A</t>
+        </is>
+      </c>
+      <c r="C37" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D37" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E37" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F37" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G37" s="67" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="84" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-02 - Power Gen Package A (UCP)</t>
+        </is>
+      </c>
+      <c r="C38" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D38" s="24" t="inlineStr">
+        <is>
+          <t>PS5 - Milestone B</t>
+        </is>
+      </c>
+      <c r="E38" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F11" s="23" t="inlineStr"/>
-      <c r="G11" s="67" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="81" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" s="83" t="inlineStr">
-        <is>
-          <t>PS5-03-07 - FZ-07 - Pretreatment Area</t>
-        </is>
-      </c>
-      <c r="C12" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D12" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E12" s="28" t="inlineStr">
+      <c r="F38" s="23" t="inlineStr">
+        <is>
+          <t>WALKDOWN COMPLETE-20-08-26--ATTENDENCE SHEET TO BE SUBMITTED</t>
+        </is>
+      </c>
+      <c r="G38" s="67" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="84" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-03 - Power Gen Package A Generator Auxiliary MCCs &amp; DBs</t>
+        </is>
+      </c>
+      <c r="C39" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D39" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E39" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F12" s="23" t="inlineStr"/>
-      <c r="G12" s="67" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="81" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" s="83" t="inlineStr">
-        <is>
-          <t>PS5-03-09 - FZ-09 - Power Generation Building - Engine Bay 1</t>
-        </is>
-      </c>
-      <c r="C13" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D13" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E13" s="28" t="inlineStr">
+      <c r="F39" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G39" s="67" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="84" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-04 - Power Generation Package B</t>
+        </is>
+      </c>
+      <c r="C40" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D40" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E40" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F40" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G40" s="67" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="84" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-05 - Power Gen Package B (UCP)</t>
+        </is>
+      </c>
+      <c r="C41" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D41" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E41" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F13" s="23" t="inlineStr"/>
-      <c r="G13" s="67" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="81" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" s="83" t="inlineStr">
-        <is>
-          <t>PS5-03-10 - FZ-10 - Power Generation Building - Engine Bay 2</t>
-        </is>
-      </c>
-      <c r="C14" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D14" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E14" s="28" t="inlineStr">
+      <c r="F41" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G41" s="67" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="84" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-06 - Power Gen Package B Generator Auxiliary MCCs &amp; DBs</t>
+        </is>
+      </c>
+      <c r="C42" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D42" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E42" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F14" s="23" t="inlineStr"/>
-      <c r="G14" s="67" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="81" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" s="83" t="inlineStr">
-        <is>
-          <t>PS5-03-11 - FZ-11 - Power Generation Building - Engine Bay 3</t>
-        </is>
-      </c>
-      <c r="C15" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D15" s="24" t="inlineStr">
+      <c r="F42" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G42" s="67" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="84" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-08 - Power Gen Package C (UCP)</t>
+        </is>
+      </c>
+      <c r="C43" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D43" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E43" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F43" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G43" s="67" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="84" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-09 - Power Gen Package C Generator Auxiliary MCCs &amp; DBs</t>
+        </is>
+      </c>
+      <c r="C44" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D44" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E44" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F44" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G44" s="67" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="84" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-11 - Power Gen Package D (UCP)</t>
+        </is>
+      </c>
+      <c r="C45" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D45" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E45" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F45" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G45" s="67" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="84" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-12 - Power Gen Package D Generator Auxiliary MCCs &amp; DBs</t>
+        </is>
+      </c>
+      <c r="C46" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D46" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E46" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F46" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G46" s="67" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="84" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-13 - Power Generation Package E</t>
+        </is>
+      </c>
+      <c r="C47" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D47" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E47" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F47" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G47" s="67" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="84" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-14 - Power Gen Package E (UCP)</t>
+        </is>
+      </c>
+      <c r="C48" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D48" s="24" t="inlineStr">
         <is>
           <t>full</t>
         </is>
       </c>
-      <c r="E15" s="28" t="inlineStr">
+      <c r="E48" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F48" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G48" s="67" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="84" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-15 - Power Gen Package E Generator Auxiliary MCCs &amp; DBs</t>
+        </is>
+      </c>
+      <c r="C49" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D49" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E49" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F49" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G49" s="67" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="84" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-17 - Power Gen Package F (UCP)</t>
+        </is>
+      </c>
+      <c r="C50" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D50" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E50" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F50" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G50" s="67" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="84" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-18 - Power Gen Package F Generator Auxiliary MCCs &amp; DBs</t>
+        </is>
+      </c>
+      <c r="C51" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D51" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E51" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F51" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G51" s="67" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="84" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-20 - Power Gen Package G (UCP)</t>
+        </is>
+      </c>
+      <c r="C52" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D52" s="24" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="E52" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F52" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G52" s="67" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="84" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-21 - Power Gen Package G Generator Auxiliary MCCs &amp; DBs</t>
+        </is>
+      </c>
+      <c r="C53" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D53" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E53" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F53" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G53" s="67" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="84" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-23 - Instrument Air Distribution lines</t>
+        </is>
+      </c>
+      <c r="C54" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D54" s="24" t="inlineStr"/>
+      <c r="E54" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F54" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G54" s="67" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="84" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-26 - Instrument Air Compressor Skid</t>
+        </is>
+      </c>
+      <c r="C55" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D55" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E55" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F55" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G55" s="67" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="84" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-27 - Compressed Air Starting Skid</t>
+        </is>
+      </c>
+      <c r="C56" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D56" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E56" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F56" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G56" s="67" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="84" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-28 - Air Receiver A &amp; Air Regulator A</t>
+        </is>
+      </c>
+      <c r="C57" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D57" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E57" s="28" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="F57" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G57" s="67" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="84" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-29 - Air Receiver B &amp; Air Regulator B</t>
+        </is>
+      </c>
+      <c r="C58" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D58" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E58" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F58" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G58" s="67" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="84" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-30 - Air Receiver C &amp; Air Regulator C</t>
+        </is>
+      </c>
+      <c r="C59" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D59" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E59" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F59" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G59" s="67" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="84" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-31 - Air Receiver D &amp; Air Regulator D</t>
+        </is>
+      </c>
+      <c r="C60" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D60" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E60" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F60" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G60" s="67" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="84" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-32 - Air Receiver E &amp; Air Regulator E</t>
+        </is>
+      </c>
+      <c r="C61" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D61" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E61" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F61" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G61" s="67" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="84" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-33 - Air Receiver F &amp; Air Regulator F</t>
+        </is>
+      </c>
+      <c r="C62" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D62" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E62" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F62" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G62" s="67" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="84" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-34 - Air Receiver G &amp; Air Regulator G</t>
+        </is>
+      </c>
+      <c r="C63" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D63" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E63" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F63" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G63" s="67" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="84" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-35 - Injector Tip Cooling Module A</t>
+        </is>
+      </c>
+      <c r="C64" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D64" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E64" s="28" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+      <c r="F64" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G64" s="67" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="84" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-36 - Injector Tip Cooling Module B</t>
+        </is>
+      </c>
+      <c r="C65" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D65" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E65" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F65" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G65" s="67" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="84" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-37 - Injector Tip Cooling Module C</t>
+        </is>
+      </c>
+      <c r="C66" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D66" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E66" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F66" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G66" s="67" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="84" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-38 - Injector Tip Cooling Module D</t>
+        </is>
+      </c>
+      <c r="C67" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D67" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E67" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F67" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G67" s="67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="84" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-39 - Injector Tip Cooling Module E</t>
+        </is>
+      </c>
+      <c r="C68" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D68" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E68" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F68" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G68" s="67" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="84" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-40 - Injector Tip Cooling Module F</t>
+        </is>
+      </c>
+      <c r="C69" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D69" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E69" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F69" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G69" s="67" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="84" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-41 - Injector Tip Cooling Module G</t>
+        </is>
+      </c>
+      <c r="C70" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D70" s="24" t="inlineStr">
         <is>
           <t>full</t>
         </is>
       </c>
-      <c r="F15" s="23" t="inlineStr"/>
-      <c r="G15" s="67" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="81" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" s="83" t="inlineStr">
-        <is>
-          <t>PS5-03-12 - FZ-12 - Power Generation Building - Engine Bay 4</t>
-        </is>
-      </c>
-      <c r="C16" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D16" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E16" s="28" t="inlineStr">
+      <c r="E70" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F70" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G70" s="67" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="84" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-42 - Oil Mist Separator Skid PS5-60-VS-9100A</t>
+        </is>
+      </c>
+      <c r="C71" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D71" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E71" s="28" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+      <c r="F71" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G71" s="67" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="84" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-43 - Oil Mist Separator Skid PS5-60-VS-9100B</t>
+        </is>
+      </c>
+      <c r="C72" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D72" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E72" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F72" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G72" s="67" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="84" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-44 - Oil Mist Separator Skid PS5-60-VS-9100C</t>
+        </is>
+      </c>
+      <c r="C73" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D73" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E73" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F73" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G73" s="67" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="84" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-45 - Oil Mist Separator Skid PS5-60-VS-9100D</t>
+        </is>
+      </c>
+      <c r="C74" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D74" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E74" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F74" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G74" s="67" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="84" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-46 - Oil Mist Separator Skid PS5-60-VS-9100E</t>
+        </is>
+      </c>
+      <c r="C75" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D75" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E75" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F75" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G75" s="67" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="84" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-47 - Oil Mist Separator Skid PS5-60-VS-9100F</t>
+        </is>
+      </c>
+      <c r="C76" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D76" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E76" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F76" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G76" s="67" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="84" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-48 - Oil Mist Separator Skid PS5-60-VS-9100G</t>
+        </is>
+      </c>
+      <c r="C77" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D77" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E77" s="28" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="F77" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G77" s="67" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="84" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-49 - Lube Oil Separator Module PS5-60-UO-81100A</t>
+        </is>
+      </c>
+      <c r="C78" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D78" s="24" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="E78" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F78" s="23" t="inlineStr">
+        <is>
+          <t>OBSERVATION -CLEANING ON PROGRESS</t>
+        </is>
+      </c>
+      <c r="G78" s="67" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="84" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-50 - Lube Oil Separator Module PS5-60-UO-81100B</t>
+        </is>
+      </c>
+      <c r="C79" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D79" s="24" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="E79" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F79" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G79" s="67" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="84" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-51 - Lube Oil Separator Module PS5-60-UO-81100C</t>
+        </is>
+      </c>
+      <c r="C80" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D80" s="24" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="E80" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F80" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G80" s="67" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="84" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-52 - Lube Oil Separator Module PS5-60-UO-81100D</t>
+        </is>
+      </c>
+      <c r="C81" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D81" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E81" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F81" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G81" s="67" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="84" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-53 - Lube Oil Separator Module PS5-60-UO-81100E</t>
+        </is>
+      </c>
+      <c r="C82" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D82" s="24" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="E82" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F82" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G82" s="67" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="84" t="n">
+        <v>81</v>
+      </c>
+      <c r="B83" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-54 - Lube Oil Separator Module PS5-60-UO-81100F</t>
+        </is>
+      </c>
+      <c r="C83" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D83" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E83" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F83" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G83" s="67" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="84" t="n">
+        <v>82</v>
+      </c>
+      <c r="B84" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-55 - Lube Oil Separator Module PS5-60-UO-81100G</t>
+        </is>
+      </c>
+      <c r="C84" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D84" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E84" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F84" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G84" s="67" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B85" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-56 - Fuel Conditioning Module PS5-60-UZ-8900A</t>
+        </is>
+      </c>
+      <c r="C85" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D85" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E85" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F85" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G85" s="67" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="84" t="n">
+        <v>84</v>
+      </c>
+      <c r="B86" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-57 - Fuel Conditioning Module PS5-60-UZ-8900A (UCP)</t>
+        </is>
+      </c>
+      <c r="C86" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D86" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E86" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F16" s="23" t="inlineStr"/>
-      <c r="G16" s="67" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="81" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" s="83" t="inlineStr">
-        <is>
-          <t>PS5-03-13 - FZ-13 - Power Generation Building - Instrument Air Room</t>
-        </is>
-      </c>
-      <c r="C17" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D17" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E17" s="28" t="inlineStr">
+      <c r="F86" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G86" s="67" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="84" t="n">
+        <v>85</v>
+      </c>
+      <c r="B87" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-58 - Fuel Conditioning Module PS5-60-UZ-8900B</t>
+        </is>
+      </c>
+      <c r="C87" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D87" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E87" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F87" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G87" s="67" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="84" t="n">
+        <v>86</v>
+      </c>
+      <c r="B88" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-59 - Fuel Conditioning Module PS5-60-UZ-8900B (UCP)</t>
+        </is>
+      </c>
+      <c r="C88" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D88" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E88" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F17" s="23" t="inlineStr"/>
-      <c r="G17" s="67" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="81" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" s="83" t="inlineStr">
-        <is>
-          <t>PS5-03-20 - FZ-20 - Emergency Diesel Generator Enclosure</t>
-        </is>
-      </c>
-      <c r="C18" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D18" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E18" s="28" t="inlineStr">
-        <is>
-          <t>07-Aug-26</t>
-        </is>
-      </c>
-      <c r="F18" s="23" t="inlineStr"/>
-      <c r="G18" s="67" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="81" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" s="83" t="inlineStr">
-        <is>
-          <t>PS5-05-01 - Emergency Diesel Generator Package</t>
-        </is>
-      </c>
-      <c r="C19" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D19" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E19" s="69" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="F19" s="23" t="inlineStr"/>
-      <c r="G19" s="67" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="81" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" s="83" t="inlineStr">
-        <is>
-          <t>PS5-05-02 - Emergency Diesel Generator Package (UCP)</t>
-        </is>
-      </c>
-      <c r="C20" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D20" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E20" s="54" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
-        </is>
-      </c>
-      <c r="F20" s="23" t="inlineStr"/>
-      <c r="G20" s="67" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="81" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" s="83" t="inlineStr">
-        <is>
-          <t>PS5-06-02 - AC UPS - Power Generator Building</t>
-        </is>
-      </c>
-      <c r="C21" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D21" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E21" s="28" t="inlineStr">
+      <c r="F88" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G88" s="67" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="84" t="n">
+        <v>87</v>
+      </c>
+      <c r="B89" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-60 - Fuel Conditioning Module PS5-60-UZ-8900C</t>
+        </is>
+      </c>
+      <c r="C89" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D89" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E89" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F89" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G89" s="67" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="84" t="n">
+        <v>88</v>
+      </c>
+      <c r="B90" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-61 - Fuel Conditioning Module PS5-60-UZ-8900C (UCP)</t>
+        </is>
+      </c>
+      <c r="C90" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D90" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E90" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F21" s="23" t="inlineStr"/>
-      <c r="G21" s="67" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="81" t="n">
-        <v>20</v>
-      </c>
-      <c r="B22" s="83" t="inlineStr">
-        <is>
-          <t>PS5-09-05 - HVAC for EITS Building</t>
-        </is>
-      </c>
-      <c r="C22" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D22" s="24" t="inlineStr"/>
-      <c r="E22" s="28" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F22" s="23" t="inlineStr"/>
-      <c r="G22" s="67" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="81" t="n">
-        <v>21</v>
-      </c>
-      <c r="B23" s="83" t="inlineStr">
-        <is>
-          <t>PS5-25-05 - Crude Oil Export Pumps Bypass</t>
-        </is>
-      </c>
-      <c r="C23" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D23" s="24" t="inlineStr">
+      <c r="F90" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G90" s="67" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="84" t="n">
+        <v>89</v>
+      </c>
+      <c r="B91" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-62 - Fuel Conditioning Module PS5-60-UZ-8900D</t>
+        </is>
+      </c>
+      <c r="C91" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D91" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E91" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F91" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G91" s="67" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="84" t="n">
+        <v>90</v>
+      </c>
+      <c r="B92" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-63 - Fuel Conditioning Module PS5-60-UZ-8900D (UCP)</t>
+        </is>
+      </c>
+      <c r="C92" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D92" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E92" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F92" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G92" s="67" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="84" t="n">
+        <v>91</v>
+      </c>
+      <c r="B93" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-65 - Fuel Conditioning Module PS5-60-UZ-8900E (UCP)</t>
+        </is>
+      </c>
+      <c r="C93" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D93" s="24" t="inlineStr">
         <is>
           <t>full</t>
         </is>
       </c>
-      <c r="E23" s="28" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F23" s="23" t="inlineStr"/>
-      <c r="G23" s="67" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="81" t="n">
-        <v>22</v>
-      </c>
-      <c r="B24" s="83" t="inlineStr">
-        <is>
-          <t>PS5-28-02 - Closed Drain Header 2</t>
-        </is>
-      </c>
-      <c r="C24" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D24" s="24" t="inlineStr"/>
-      <c r="E24" s="28" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F24" s="23" t="inlineStr"/>
-      <c r="G24" s="67" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="81" t="n">
-        <v>23</v>
-      </c>
-      <c r="B25" s="83" t="inlineStr">
-        <is>
-          <t>PS5-28-05 - HP Relief Header</t>
-        </is>
-      </c>
-      <c r="C25" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D25" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E25" s="28" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F25" s="23" t="inlineStr"/>
-      <c r="G25" s="67" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="81" t="n">
-        <v>24</v>
-      </c>
-      <c r="B26" s="83" t="inlineStr">
-        <is>
-          <t>PS5-28-06 - Relief Drum and Pump</t>
-        </is>
-      </c>
-      <c r="C26" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D26" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E26" s="28" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F26" s="23" t="inlineStr"/>
-      <c r="G26" s="67" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="81" t="n">
-        <v>25</v>
-      </c>
-      <c r="B27" s="83" t="inlineStr">
-        <is>
-          <t>PS5-28-07 - Open Drains (OD2)</t>
-        </is>
-      </c>
-      <c r="C27" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D27" s="24" t="inlineStr"/>
-      <c r="E27" s="28" t="inlineStr">
+      <c r="E93" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F27" s="23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G27" s="67" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="85" t="n">
-        <v>26</v>
-      </c>
-      <c r="B28" s="83" t="inlineStr">
-        <is>
-          <t>PS5-28-08 - Open Drain Sump and Pumps</t>
-        </is>
-      </c>
-      <c r="C28" s="28" t="inlineStr">
-        <is>
-          <t>99%</t>
-        </is>
-      </c>
-      <c r="D28" s="24" t="inlineStr">
+      <c r="F93" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G93" s="67" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="84" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-67 - Fuel Conditioning Module PS5-60-UZ-8900F (UCP)</t>
+        </is>
+      </c>
+      <c r="C94" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D94" s="24" t="inlineStr">
         <is>
           <t>full</t>
         </is>
       </c>
-      <c r="E28" s="69" t="inlineStr">
+      <c r="E94" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F94" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G94" s="67" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="88" t="n">
+        <v>93</v>
+      </c>
+      <c r="B95" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-68 - Fuel Conditioning Module PS5-60-UZ-8900G</t>
+        </is>
+      </c>
+      <c r="C95" s="28" t="inlineStr">
+        <is>
+          <t>93%</t>
+        </is>
+      </c>
+      <c r="D95" s="24" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E95" s="69" t="inlineStr">
         <is>
           <t>partial</t>
         </is>
       </c>
-      <c r="F28" s="23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G28" s="67" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="81" t="n">
-        <v>27</v>
-      </c>
-      <c r="B29" s="83" t="inlineStr">
-        <is>
-          <t>PS5-28-11 - Open Drain Interceptor</t>
-        </is>
-      </c>
-      <c r="C29" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D29" s="24" t="inlineStr">
+      <c r="F95" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G95" s="67" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="84" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-69 - Fuel Conditioning Module PS5-60-UZ-8900G (UCP)</t>
+        </is>
+      </c>
+      <c r="C96" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D96" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E96" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F96" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G96" s="67" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="84" t="n">
+        <v>95</v>
+      </c>
+      <c r="B97" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-70 - Engine A Cooling system</t>
+        </is>
+      </c>
+      <c r="C97" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D97" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E97" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F97" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G97" s="67" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="84" t="n">
+        <v>96</v>
+      </c>
+      <c r="B98" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-71 - Engine B Cooling system</t>
+        </is>
+      </c>
+      <c r="C98" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D98" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E98" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F98" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G98" s="67" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="84" t="n">
+        <v>97</v>
+      </c>
+      <c r="B99" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-72 - Engine C Cooling system</t>
+        </is>
+      </c>
+      <c r="C99" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D99" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E99" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F99" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G99" s="67" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="84" t="n">
+        <v>98</v>
+      </c>
+      <c r="B100" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-73 - Engine D Cooling system</t>
+        </is>
+      </c>
+      <c r="C100" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D100" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E100" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F100" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G100" s="67" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="84" t="n">
+        <v>99</v>
+      </c>
+      <c r="B101" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-74 - Engine E Cooling system</t>
+        </is>
+      </c>
+      <c r="C101" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D101" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E101" s="28" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="F101" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G101" s="67" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="84" t="n">
+        <v>100</v>
+      </c>
+      <c r="B102" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-75 - Engine F Cooling system</t>
+        </is>
+      </c>
+      <c r="C102" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D102" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E102" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F102" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G102" s="67" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="84" t="n">
+        <v>101</v>
+      </c>
+      <c r="B103" s="86" t="inlineStr">
+        <is>
+          <t>PS5-60-76 - Engine G Cooling system</t>
+        </is>
+      </c>
+      <c r="C103" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D103" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E103" s="28" t="inlineStr">
         <is>
           <t>FULL</t>
         </is>
       </c>
-      <c r="E29" s="28" t="inlineStr">
-        <is>
-          <t>FULL</t>
-        </is>
-      </c>
-      <c r="F29" s="23" t="inlineStr"/>
-      <c r="G29" s="67" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="81" t="n">
-        <v>28</v>
-      </c>
-      <c r="B30" s="83" t="inlineStr">
-        <is>
-          <t>PS5-28-12 - Open Drains (OD3)</t>
-        </is>
-      </c>
-      <c r="C30" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D30" s="24" t="inlineStr"/>
-      <c r="E30" s="28" t="inlineStr">
+      <c r="F103" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G103" s="67" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="84" t="n">
+        <v>102</v>
+      </c>
+      <c r="B104" s="86" t="inlineStr">
+        <is>
+          <t>PS5-61-02 - 6.6kV Switchboard and Transformer LLHT North - EITS Building (PS5-61-IJ-0010)</t>
+        </is>
+      </c>
+      <c r="C104" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D104" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E104" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F30" s="23" t="inlineStr"/>
-      <c r="G30" s="67" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="81" t="n">
-        <v>29</v>
-      </c>
-      <c r="B31" s="83" t="inlineStr">
-        <is>
-          <t>PS5-28-16 - LP Relief Header</t>
-        </is>
-      </c>
-      <c r="C31" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D31" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E31" s="28" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F31" s="23" t="inlineStr"/>
-      <c r="G31" s="67" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="85" t="n">
-        <v>30</v>
-      </c>
-      <c r="B32" s="83" t="inlineStr">
-        <is>
-          <t>PS5-53-01 - Utility Water / Storage Tank</t>
-        </is>
-      </c>
-      <c r="C32" s="28" t="inlineStr">
-        <is>
-          <t>96%</t>
-        </is>
-      </c>
-      <c r="D32" s="24" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="E32" s="69" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="F32" s="23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G32" s="67" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="81" t="n">
-        <v>31</v>
-      </c>
-      <c r="B33" s="83" t="inlineStr">
-        <is>
-          <t>PS5-53-02 - Water Distribution Pump A/B</t>
-        </is>
-      </c>
-      <c r="C33" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D33" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E33" s="28" t="inlineStr">
+      <c r="F104" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G104" s="67" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="84" t="n">
+        <v>103</v>
+      </c>
+      <c r="B105" s="86" t="inlineStr">
+        <is>
+          <t>PS5-61-03 - 6.6kV Switchboard and Transformer LLHT South - EITS Building (PS5-61-IJ-0011)</t>
+        </is>
+      </c>
+      <c r="C105" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D105" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E105" s="28" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="F105" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G105" s="67" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="84" t="n">
+        <v>104</v>
+      </c>
+      <c r="B106" s="86" t="inlineStr">
+        <is>
+          <t>PS5-61-05 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0003)</t>
+        </is>
+      </c>
+      <c r="C106" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D106" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E106" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F33" s="23" t="inlineStr"/>
-      <c r="G33" s="67" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="81" t="n">
-        <v>32</v>
-      </c>
-      <c r="B34" s="83" t="inlineStr">
-        <is>
-          <t>PS5-53-05 - Water Distribution Header</t>
-        </is>
-      </c>
-      <c r="C34" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D34" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E34" s="28" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F34" s="23" t="inlineStr"/>
-      <c r="G34" s="67" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="81" t="n">
-        <v>33</v>
-      </c>
-      <c r="B35" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-01 - Power Generation Package A</t>
-        </is>
-      </c>
-      <c r="C35" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D35" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E35" s="28" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F35" s="23" t="inlineStr"/>
-      <c r="G35" s="67" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="81" t="n">
-        <v>34</v>
-      </c>
-      <c r="B36" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-02 - Power Gen Package A (UCP)</t>
-        </is>
-      </c>
-      <c r="C36" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D36" s="24" t="inlineStr">
-        <is>
-          <t>PS5 - Milestone B</t>
-        </is>
-      </c>
-      <c r="E36" s="28" t="inlineStr">
+      <c r="F106" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G106" s="67" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="84" t="n">
+        <v>105</v>
+      </c>
+      <c r="B107" s="86" t="inlineStr">
+        <is>
+          <t>PS5-61-07 - 0.4kV Switchboard EITS Building (PS5-61-IK-0001)</t>
+        </is>
+      </c>
+      <c r="C107" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D107" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E107" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F107" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G107" s="67" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="84" t="n">
+        <v>106</v>
+      </c>
+      <c r="B108" s="86" t="inlineStr">
+        <is>
+          <t>PS5-61-10 - Outdoor Valves Distribution Board - PS5-61-IG-0042</t>
+        </is>
+      </c>
+      <c r="C108" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D108" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E108" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F36" s="23" t="inlineStr">
-        <is>
-          <t>WALKDOWN COMPLETE-20-08-26--ATTENDENCE SHEET TO BE SUBMITTED</t>
-        </is>
-      </c>
-      <c r="G36" s="67" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="81" t="n">
-        <v>35</v>
-      </c>
-      <c r="B37" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-03 - Power Gen Package A Generator Auxiliary MCCs &amp; DBs</t>
-        </is>
-      </c>
-      <c r="C37" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D37" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E37" s="28" t="inlineStr">
+      <c r="F108" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G108" s="67" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="84" t="n">
+        <v>107</v>
+      </c>
+      <c r="B109" s="86" t="inlineStr">
+        <is>
+          <t>PS5-61-11 - Outdoor Valves Distribution Board - PS5-61-IG-0043</t>
+        </is>
+      </c>
+      <c r="C109" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D109" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E109" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F37" s="23" t="inlineStr"/>
-      <c r="G37" s="67" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="81" t="n">
-        <v>36</v>
-      </c>
-      <c r="B38" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-04 - Power Generation Package B</t>
-        </is>
-      </c>
-      <c r="C38" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D38" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E38" s="28" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F38" s="23" t="inlineStr"/>
-      <c r="G38" s="67" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="81" t="n">
-        <v>37</v>
-      </c>
-      <c r="B39" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-05 - Power Gen Package B (UCP)</t>
-        </is>
-      </c>
-      <c r="C39" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D39" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E39" s="28" t="inlineStr">
+      <c r="F109" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G109" s="67" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="84" t="n">
+        <v>108</v>
+      </c>
+      <c r="B110" s="86" t="inlineStr">
+        <is>
+          <t>PS5-62-03 - Outdoor Emergency Lighting DB  - PS5-05-IG-0004</t>
+        </is>
+      </c>
+      <c r="C110" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D110" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E110" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F39" s="23" t="inlineStr"/>
-      <c r="G39" s="67" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="81" t="n">
-        <v>38</v>
-      </c>
-      <c r="B40" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-06 - Power Gen Package B Generator Auxiliary MCCs &amp; DBs</t>
-        </is>
-      </c>
-      <c r="C40" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D40" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E40" s="28" t="inlineStr">
+      <c r="F110" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G110" s="67" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="84" t="n">
+        <v>109</v>
+      </c>
+      <c r="B111" s="86" t="inlineStr">
+        <is>
+          <t>PS5-62-04 - Outdoor Emergency Lighting DB  - PS5-05-IG-0006</t>
+        </is>
+      </c>
+      <c r="C111" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D111" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E111" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F40" s="23" t="inlineStr"/>
-      <c r="G40" s="67" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="81" t="n">
-        <v>39</v>
-      </c>
-      <c r="B41" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-08 - Power Gen Package C (UCP)</t>
-        </is>
-      </c>
-      <c r="C41" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D41" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E41" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F41" s="23" t="inlineStr"/>
-      <c r="G41" s="67" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="81" t="n">
-        <v>40</v>
-      </c>
-      <c r="B42" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-09 - Power Gen Package C Generator Auxiliary MCCs &amp; DBs</t>
-        </is>
-      </c>
-      <c r="C42" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D42" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E42" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F42" s="23" t="inlineStr"/>
-      <c r="G42" s="67" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="81" t="n">
-        <v>41</v>
-      </c>
-      <c r="B43" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-11 - Power Gen Package D (UCP)</t>
-        </is>
-      </c>
-      <c r="C43" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D43" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E43" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F43" s="23" t="inlineStr"/>
-      <c r="G43" s="67" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="81" t="n">
-        <v>42</v>
-      </c>
-      <c r="B44" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-12 - Power Gen Package D Generator Auxiliary MCCs &amp; DBs</t>
-        </is>
-      </c>
-      <c r="C44" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D44" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E44" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F44" s="23" t="inlineStr"/>
-      <c r="G44" s="67" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="81" t="n">
-        <v>43</v>
-      </c>
-      <c r="B45" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-13 - Power Generation Package E</t>
-        </is>
-      </c>
-      <c r="C45" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D45" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E45" s="28" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F45" s="23" t="inlineStr"/>
-      <c r="G45" s="67" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="81" t="n">
-        <v>44</v>
-      </c>
-      <c r="B46" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-14 - Power Gen Package E (UCP)</t>
-        </is>
-      </c>
-      <c r="C46" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D46" s="24" t="inlineStr">
-        <is>
-          <t>full</t>
-        </is>
-      </c>
-      <c r="E46" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F46" s="23" t="inlineStr"/>
-      <c r="G46" s="67" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="81" t="n">
-        <v>45</v>
-      </c>
-      <c r="B47" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-15 - Power Gen Package E Generator Auxiliary MCCs &amp; DBs</t>
-        </is>
-      </c>
-      <c r="C47" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D47" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E47" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F47" s="23" t="inlineStr"/>
-      <c r="G47" s="67" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="81" t="n">
-        <v>46</v>
-      </c>
-      <c r="B48" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-17 - Power Gen Package F (UCP)</t>
-        </is>
-      </c>
-      <c r="C48" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D48" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E48" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F48" s="23" t="inlineStr"/>
-      <c r="G48" s="67" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="81" t="n">
-        <v>47</v>
-      </c>
-      <c r="B49" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-18 - Power Gen Package F Generator Auxiliary MCCs &amp; DBs</t>
-        </is>
-      </c>
-      <c r="C49" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D49" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E49" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F49" s="23" t="inlineStr"/>
-      <c r="G49" s="67" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="81" t="n">
-        <v>48</v>
-      </c>
-      <c r="B50" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-20 - Power Gen Package G (UCP)</t>
-        </is>
-      </c>
-      <c r="C50" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D50" s="24" t="inlineStr">
-        <is>
-          <t>partial</t>
-        </is>
-      </c>
-      <c r="E50" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F50" s="23" t="inlineStr"/>
-      <c r="G50" s="67" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="81" t="n">
-        <v>49</v>
-      </c>
-      <c r="B51" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-21 - Power Gen Package G Generator Auxiliary MCCs &amp; DBs</t>
-        </is>
-      </c>
-      <c r="C51" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D51" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E51" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F51" s="23" t="inlineStr"/>
-      <c r="G51" s="67" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="81" t="n">
-        <v>50</v>
-      </c>
-      <c r="B52" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-23 - Instrument Air Distribution lines</t>
-        </is>
-      </c>
-      <c r="C52" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D52" s="24" t="inlineStr"/>
-      <c r="E52" s="28" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F52" s="23" t="inlineStr"/>
-      <c r="G52" s="67" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="81" t="n">
-        <v>51</v>
-      </c>
-      <c r="B53" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-26 - Instrument Air Compressor Skid</t>
-        </is>
-      </c>
-      <c r="C53" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D53" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E53" s="28" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F53" s="23" t="inlineStr"/>
-      <c r="G53" s="67" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="81" t="n">
-        <v>52</v>
-      </c>
-      <c r="B54" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-27 - Compressed Air Starting Skid</t>
-        </is>
-      </c>
-      <c r="C54" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D54" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E54" s="28" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F54" s="23" t="inlineStr"/>
-      <c r="G54" s="67" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="81" t="n">
-        <v>53</v>
-      </c>
-      <c r="B55" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-28 - Air Receiver A &amp; Air Regulator A</t>
-        </is>
-      </c>
-      <c r="C55" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D55" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E55" s="69" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="F55" s="23" t="inlineStr"/>
-      <c r="G55" s="67" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="81" t="n">
-        <v>54</v>
-      </c>
-      <c r="B56" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-29 - Air Receiver B &amp; Air Regulator B</t>
-        </is>
-      </c>
-      <c r="C56" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D56" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E56" s="28" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F56" s="23" t="inlineStr"/>
-      <c r="G56" s="67" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="81" t="n">
-        <v>55</v>
-      </c>
-      <c r="B57" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-30 - Air Receiver C &amp; Air Regulator C</t>
-        </is>
-      </c>
-      <c r="C57" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D57" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E57" s="28" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F57" s="23" t="inlineStr"/>
-      <c r="G57" s="67" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="81" t="n">
-        <v>56</v>
-      </c>
-      <c r="B58" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-31 - Air Receiver D &amp; Air Regulator D</t>
-        </is>
-      </c>
-      <c r="C58" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D58" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E58" s="28" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F58" s="23" t="inlineStr"/>
-      <c r="G58" s="67" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="81" t="n">
-        <v>57</v>
-      </c>
-      <c r="B59" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-32 - Air Receiver E &amp; Air Regulator E</t>
-        </is>
-      </c>
-      <c r="C59" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D59" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E59" s="28" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F59" s="23" t="inlineStr"/>
-      <c r="G59" s="67" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="81" t="n">
-        <v>58</v>
-      </c>
-      <c r="B60" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-33 - Air Receiver F &amp; Air Regulator F</t>
-        </is>
-      </c>
-      <c r="C60" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D60" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E60" s="28" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F60" s="23" t="inlineStr"/>
-      <c r="G60" s="67" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="81" t="n">
-        <v>59</v>
-      </c>
-      <c r="B61" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-34 - Air Receiver G &amp; Air Regulator G</t>
-        </is>
-      </c>
-      <c r="C61" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D61" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E61" s="28" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F61" s="23" t="inlineStr"/>
-      <c r="G61" s="67" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="81" t="n">
-        <v>60</v>
-      </c>
-      <c r="B62" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-35 - Injector Tip Cooling Module A</t>
-        </is>
-      </c>
-      <c r="C62" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D62" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E62" s="54" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
-        </is>
-      </c>
-      <c r="F62" s="23" t="inlineStr"/>
-      <c r="G62" s="67" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="81" t="n">
-        <v>61</v>
-      </c>
-      <c r="B63" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-36 - Injector Tip Cooling Module B</t>
-        </is>
-      </c>
-      <c r="C63" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D63" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E63" s="28" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F63" s="23" t="inlineStr"/>
-      <c r="G63" s="67" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="81" t="n">
-        <v>62</v>
-      </c>
-      <c r="B64" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-37 - Injector Tip Cooling Module C</t>
-        </is>
-      </c>
-      <c r="C64" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D64" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E64" s="28" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F64" s="23" t="inlineStr"/>
-      <c r="G64" s="67" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="81" t="n">
-        <v>63</v>
-      </c>
-      <c r="B65" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-38 - Injector Tip Cooling Module D</t>
-        </is>
-      </c>
-      <c r="C65" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D65" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E65" s="28" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F65" s="23" t="inlineStr"/>
-      <c r="G65" s="67" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="81" t="n">
-        <v>64</v>
-      </c>
-      <c r="B66" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-39 - Injector Tip Cooling Module E</t>
-        </is>
-      </c>
-      <c r="C66" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D66" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E66" s="28" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F66" s="23" t="inlineStr"/>
-      <c r="G66" s="67" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="81" t="n">
-        <v>65</v>
-      </c>
-      <c r="B67" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-40 - Injector Tip Cooling Module F</t>
-        </is>
-      </c>
-      <c r="C67" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D67" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E67" s="28" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F67" s="23" t="inlineStr"/>
-      <c r="G67" s="67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="81" t="n">
-        <v>66</v>
-      </c>
-      <c r="B68" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-41 - Injector Tip Cooling Module G</t>
-        </is>
-      </c>
-      <c r="C68" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D68" s="24" t="inlineStr">
-        <is>
-          <t>full</t>
-        </is>
-      </c>
-      <c r="E68" s="28" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F68" s="23" t="inlineStr"/>
-      <c r="G68" s="67" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="81" t="n">
-        <v>67</v>
-      </c>
-      <c r="B69" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-42 - Oil Mist Separator Skid PS5-60-VS-9100A</t>
-        </is>
-      </c>
-      <c r="C69" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D69" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E69" s="54" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
-        </is>
-      </c>
-      <c r="F69" s="23" t="inlineStr"/>
-      <c r="G69" s="67" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="81" t="n">
-        <v>68</v>
-      </c>
-      <c r="B70" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-43 - Oil Mist Separator Skid PS5-60-VS-9100B</t>
-        </is>
-      </c>
-      <c r="C70" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D70" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E70" s="28" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F70" s="23" t="inlineStr"/>
-      <c r="G70" s="67" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="81" t="n">
-        <v>69</v>
-      </c>
-      <c r="B71" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-44 - Oil Mist Separator Skid PS5-60-VS-9100C</t>
-        </is>
-      </c>
-      <c r="C71" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D71" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E71" s="28" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F71" s="23" t="inlineStr"/>
-      <c r="G71" s="67" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="81" t="n">
-        <v>70</v>
-      </c>
-      <c r="B72" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-45 - Oil Mist Separator Skid PS5-60-VS-9100D</t>
-        </is>
-      </c>
-      <c r="C72" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D72" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E72" s="28" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F72" s="23" t="inlineStr"/>
-      <c r="G72" s="67" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="81" t="n">
-        <v>71</v>
-      </c>
-      <c r="B73" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-46 - Oil Mist Separator Skid PS5-60-VS-9100E</t>
-        </is>
-      </c>
-      <c r="C73" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D73" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E73" s="28" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F73" s="23" t="inlineStr"/>
-      <c r="G73" s="67" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="81" t="n">
-        <v>72</v>
-      </c>
-      <c r="B74" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-47 - Oil Mist Separator Skid PS5-60-VS-9100F</t>
-        </is>
-      </c>
-      <c r="C74" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D74" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E74" s="28" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F74" s="23" t="inlineStr"/>
-      <c r="G74" s="67" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="81" t="n">
-        <v>73</v>
-      </c>
-      <c r="B75" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-48 - Oil Mist Separator Skid PS5-60-VS-9100G</t>
-        </is>
-      </c>
-      <c r="C75" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D75" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E75" s="69" t="inlineStr">
-        <is>
-          <t>partial</t>
-        </is>
-      </c>
-      <c r="F75" s="23" t="inlineStr"/>
-      <c r="G75" s="67" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="81" t="n">
-        <v>74</v>
-      </c>
-      <c r="B76" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-49 - Lube Oil Separator Module PS5-60-UO-81100A</t>
-        </is>
-      </c>
-      <c r="C76" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D76" s="24" t="inlineStr">
-        <is>
-          <t>full</t>
-        </is>
-      </c>
-      <c r="E76" s="28" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F76" s="23" t="inlineStr">
-        <is>
-          <t>OBSERVATION -CLEANING ON PROGRESS</t>
-        </is>
-      </c>
-      <c r="G76" s="67" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="81" t="n">
-        <v>75</v>
-      </c>
-      <c r="B77" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-50 - Lube Oil Separator Module PS5-60-UO-81100B</t>
-        </is>
-      </c>
-      <c r="C77" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D77" s="24" t="inlineStr">
-        <is>
-          <t>full</t>
-        </is>
-      </c>
-      <c r="E77" s="28" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F77" s="23" t="inlineStr"/>
-      <c r="G77" s="67" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="81" t="n">
-        <v>76</v>
-      </c>
-      <c r="B78" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-51 - Lube Oil Separator Module PS5-60-UO-81100C</t>
-        </is>
-      </c>
-      <c r="C78" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D78" s="24" t="inlineStr">
-        <is>
-          <t>full</t>
-        </is>
-      </c>
-      <c r="E78" s="28" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F78" s="23" t="inlineStr"/>
-      <c r="G78" s="67" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="81" t="n">
-        <v>77</v>
-      </c>
-      <c r="B79" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-52 - Lube Oil Separator Module PS5-60-UO-81100D</t>
-        </is>
-      </c>
-      <c r="C79" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D79" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E79" s="28" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F79" s="23" t="inlineStr"/>
-      <c r="G79" s="67" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="81" t="n">
-        <v>78</v>
-      </c>
-      <c r="B80" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-53 - Lube Oil Separator Module PS5-60-UO-81100E</t>
-        </is>
-      </c>
-      <c r="C80" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D80" s="24" t="inlineStr">
-        <is>
-          <t>full</t>
-        </is>
-      </c>
-      <c r="E80" s="28" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F80" s="23" t="inlineStr"/>
-      <c r="G80" s="67" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="81" t="n">
-        <v>79</v>
-      </c>
-      <c r="B81" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-54 - Lube Oil Separator Module PS5-60-UO-81100F</t>
-        </is>
-      </c>
-      <c r="C81" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D81" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E81" s="28" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F81" s="23" t="inlineStr"/>
-      <c r="G81" s="67" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="81" t="n">
-        <v>80</v>
-      </c>
-      <c r="B82" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-55 - Lube Oil Separator Module PS5-60-UO-81100G</t>
-        </is>
-      </c>
-      <c r="C82" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D82" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E82" s="28" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F82" s="23" t="inlineStr"/>
-      <c r="G82" s="67" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="81" t="n">
-        <v>81</v>
-      </c>
-      <c r="B83" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-56 - Fuel Conditioning Module PS5-60-UZ-8900A</t>
-        </is>
-      </c>
-      <c r="C83" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D83" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E83" s="28" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F83" s="23" t="inlineStr"/>
-      <c r="G83" s="67" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="81" t="n">
-        <v>82</v>
-      </c>
-      <c r="B84" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-57 - Fuel Conditioning Module PS5-60-UZ-8900A (UCP)</t>
-        </is>
-      </c>
-      <c r="C84" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D84" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E84" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F84" s="23" t="inlineStr"/>
-      <c r="G84" s="67" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="81" t="n">
-        <v>83</v>
-      </c>
-      <c r="B85" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-58 - Fuel Conditioning Module PS5-60-UZ-8900B</t>
-        </is>
-      </c>
-      <c r="C85" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D85" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E85" s="28" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F85" s="23" t="inlineStr"/>
-      <c r="G85" s="67" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="81" t="n">
-        <v>84</v>
-      </c>
-      <c r="B86" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-59 - Fuel Conditioning Module PS5-60-UZ-8900B (UCP)</t>
-        </is>
-      </c>
-      <c r="C86" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D86" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E86" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F86" s="23" t="inlineStr"/>
-      <c r="G86" s="67" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="81" t="n">
-        <v>85</v>
-      </c>
-      <c r="B87" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-60 - Fuel Conditioning Module PS5-60-UZ-8900C</t>
-        </is>
-      </c>
-      <c r="C87" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D87" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E87" s="28" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F87" s="23" t="inlineStr"/>
-      <c r="G87" s="67" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="81" t="n">
-        <v>86</v>
-      </c>
-      <c r="B88" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-61 - Fuel Conditioning Module PS5-60-UZ-8900C (UCP)</t>
-        </is>
-      </c>
-      <c r="C88" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D88" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E88" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F88" s="23" t="inlineStr"/>
-      <c r="G88" s="67" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="81" t="n">
-        <v>87</v>
-      </c>
-      <c r="B89" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-62 - Fuel Conditioning Module PS5-60-UZ-8900D</t>
-        </is>
-      </c>
-      <c r="C89" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D89" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E89" s="28" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F89" s="23" t="inlineStr"/>
-      <c r="G89" s="67" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="81" t="n">
-        <v>88</v>
-      </c>
-      <c r="B90" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-63 - Fuel Conditioning Module PS5-60-UZ-8900D (UCP)</t>
-        </is>
-      </c>
-      <c r="C90" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D90" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E90" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F90" s="23" t="inlineStr"/>
-      <c r="G90" s="67" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="81" t="n">
-        <v>89</v>
-      </c>
-      <c r="B91" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-65 - Fuel Conditioning Module PS5-60-UZ-8900E (UCP)</t>
-        </is>
-      </c>
-      <c r="C91" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D91" s="24" t="inlineStr">
-        <is>
-          <t>full</t>
-        </is>
-      </c>
-      <c r="E91" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F91" s="23" t="inlineStr"/>
-      <c r="G91" s="67" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="81" t="n">
-        <v>90</v>
-      </c>
-      <c r="B92" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-67 - Fuel Conditioning Module PS5-60-UZ-8900F (UCP)</t>
-        </is>
-      </c>
-      <c r="C92" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D92" s="24" t="inlineStr">
-        <is>
-          <t>full</t>
-        </is>
-      </c>
-      <c r="E92" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F92" s="23" t="inlineStr"/>
-      <c r="G92" s="67" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="85" t="n">
-        <v>91</v>
-      </c>
-      <c r="B93" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-68 - Fuel Conditioning Module PS5-60-UZ-8900G</t>
-        </is>
-      </c>
-      <c r="C93" s="28" t="inlineStr">
-        <is>
-          <t>93%</t>
-        </is>
-      </c>
-      <c r="D93" s="24" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="E93" s="69" t="inlineStr">
-        <is>
-          <t>partial</t>
-        </is>
-      </c>
-      <c r="F93" s="23" t="inlineStr"/>
-      <c r="G93" s="67" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="81" t="n">
-        <v>92</v>
-      </c>
-      <c r="B94" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-69 - Fuel Conditioning Module PS5-60-UZ-8900G (UCP)</t>
-        </is>
-      </c>
-      <c r="C94" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D94" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E94" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F94" s="23" t="inlineStr"/>
-      <c r="G94" s="67" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="81" t="n">
-        <v>93</v>
-      </c>
-      <c r="B95" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-70 - Engine A Cooling system</t>
-        </is>
-      </c>
-      <c r="C95" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D95" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E95" s="28" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F95" s="23" t="inlineStr"/>
-      <c r="G95" s="67" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="81" t="n">
-        <v>94</v>
-      </c>
-      <c r="B96" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-71 - Engine B Cooling system</t>
-        </is>
-      </c>
-      <c r="C96" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D96" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E96" s="28" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F96" s="23" t="inlineStr"/>
-      <c r="G96" s="67" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="81" t="n">
-        <v>95</v>
-      </c>
-      <c r="B97" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-72 - Engine C Cooling system</t>
-        </is>
-      </c>
-      <c r="C97" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D97" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E97" s="28" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F97" s="23" t="inlineStr"/>
-      <c r="G97" s="67" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="81" t="n">
-        <v>96</v>
-      </c>
-      <c r="B98" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-73 - Engine D Cooling system</t>
-        </is>
-      </c>
-      <c r="C98" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D98" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E98" s="28" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F98" s="23" t="inlineStr"/>
-      <c r="G98" s="67" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="81" t="n">
-        <v>97</v>
-      </c>
-      <c r="B99" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-74 - Engine E Cooling system</t>
-        </is>
-      </c>
-      <c r="C99" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D99" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E99" s="28" t="inlineStr">
-        <is>
-          <t>full</t>
-        </is>
-      </c>
-      <c r="F99" s="23" t="inlineStr"/>
-      <c r="G99" s="67" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="81" t="n">
-        <v>98</v>
-      </c>
-      <c r="B100" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-75 - Engine F Cooling system</t>
-        </is>
-      </c>
-      <c r="C100" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D100" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E100" s="28" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F100" s="23" t="inlineStr"/>
-      <c r="G100" s="67" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="81" t="n">
-        <v>99</v>
-      </c>
-      <c r="B101" s="83" t="inlineStr">
-        <is>
-          <t>PS5-60-76 - Engine G Cooling system</t>
-        </is>
-      </c>
-      <c r="C101" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D101" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E101" s="28" t="inlineStr">
-        <is>
-          <t>FULL</t>
-        </is>
-      </c>
-      <c r="F101" s="23" t="inlineStr"/>
-      <c r="G101" s="67" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="81" t="n">
-        <v>100</v>
-      </c>
-      <c r="B102" s="83" t="inlineStr">
-        <is>
-          <t>PS5-61-02 - 6.6kV Switchboard and Transformer LLHT North - EITS Building (PS5-61-IJ-0010)</t>
-        </is>
-      </c>
-      <c r="C102" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D102" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E102" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F102" s="23" t="inlineStr"/>
-      <c r="G102" s="67" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="81" t="n">
-        <v>101</v>
-      </c>
-      <c r="B103" s="83" t="inlineStr">
-        <is>
-          <t>PS5-61-03 - 6.6kV Switchboard and Transformer LLHT South - EITS Building (PS5-61-IJ-0011)</t>
-        </is>
-      </c>
-      <c r="C103" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D103" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E103" s="28" t="inlineStr">
-        <is>
-          <t>full</t>
-        </is>
-      </c>
-      <c r="F103" s="23" t="inlineStr"/>
-      <c r="G103" s="67" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="81" t="n">
-        <v>102</v>
-      </c>
-      <c r="B104" s="83" t="inlineStr">
-        <is>
-          <t>PS5-61-05 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0003)</t>
-        </is>
-      </c>
-      <c r="C104" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D104" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E104" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F104" s="23" t="inlineStr"/>
-      <c r="G104" s="67" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="81" t="n">
-        <v>103</v>
-      </c>
-      <c r="B105" s="83" t="inlineStr">
-        <is>
-          <t>PS5-61-07 - 0.4kV Switchboard EITS Building (PS5-61-IK-0001)</t>
-        </is>
-      </c>
-      <c r="C105" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D105" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E105" s="28" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F105" s="23" t="inlineStr"/>
-      <c r="G105" s="67" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="81" t="n">
-        <v>104</v>
-      </c>
-      <c r="B106" s="83" t="inlineStr">
-        <is>
-          <t>PS5-61-10 - Outdoor Valves Distribution Board - PS5-61-IG-0042</t>
-        </is>
-      </c>
-      <c r="C106" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D106" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E106" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F106" s="23" t="inlineStr"/>
-      <c r="G106" s="67" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="81" t="n">
-        <v>105</v>
-      </c>
-      <c r="B107" s="83" t="inlineStr">
-        <is>
-          <t>PS5-61-11 - Outdoor Valves Distribution Board - PS5-61-IG-0043</t>
-        </is>
-      </c>
-      <c r="C107" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D107" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E107" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F107" s="23" t="inlineStr"/>
-      <c r="G107" s="67" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="81" t="n">
-        <v>106</v>
-      </c>
-      <c r="B108" s="83" t="inlineStr">
-        <is>
-          <t>PS5-62-03 - Outdoor Emergency Lighting DB  - PS5-05-IG-0004</t>
-        </is>
-      </c>
-      <c r="C108" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D108" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E108" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F108" s="23" t="inlineStr"/>
-      <c r="G108" s="67" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="81" t="n">
-        <v>107</v>
-      </c>
-      <c r="B109" s="83" t="inlineStr">
-        <is>
-          <t>PS5-62-04 - Outdoor Emergency Lighting DB  - PS5-05-IG-0006</t>
-        </is>
-      </c>
-      <c r="C109" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D109" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E109" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F109" s="23" t="inlineStr"/>
-      <c r="G109" s="67" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="81" t="n">
-        <v>108</v>
-      </c>
-      <c r="B110" s="83" t="inlineStr">
+      <c r="F111" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G111" s="67" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="84" t="n">
+        <v>110</v>
+      </c>
+      <c r="B112" s="86" t="inlineStr">
         <is>
           <t>PS5-63-04 - Electrical Earthing - EITS Building</t>
         </is>
       </c>
-      <c r="C110" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D110" s="24" t="inlineStr"/>
-      <c r="E110" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F110" s="23" t="inlineStr"/>
-      <c r="G110" s="67" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="81" t="n">
-        <v>109</v>
-      </c>
-      <c r="B111" s="83" t="inlineStr">
-        <is>
-          <t>PS5-71-02 - CFO Allocation Metering Package</t>
-        </is>
-      </c>
-      <c r="C111" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D111" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E111" s="28" t="inlineStr">
-        <is>
-          <t>full</t>
-        </is>
-      </c>
-      <c r="F111" s="23" t="inlineStr"/>
-      <c r="G111" s="67" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="81" t="n">
-        <v>110</v>
-      </c>
-      <c r="B112" s="83" t="inlineStr">
-        <is>
-          <t>PS5-71-09 - CFO Pre-Pressure Modules (UCP)</t>
-        </is>
-      </c>
       <c r="C112" s="28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="D112" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
+      <c r="D112" s="24" t="inlineStr"/>
       <c r="E112" s="28" t="inlineStr">
         <is>
           <t>-</t>
@@ -4169,313 +4602,353 @@
       <c r="G112" s="67" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="81" t="n">
+      <c r="A113" s="84" t="n">
         <v>111</v>
       </c>
-      <c r="B113" s="83" t="inlineStr">
+      <c r="B113" s="86" t="inlineStr">
+        <is>
+          <t>PS5-71-02 - CFO Allocation Metering Package</t>
+        </is>
+      </c>
+      <c r="C113" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D113" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E113" s="28" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="F113" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G113" s="67" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="84" t="n">
+        <v>112</v>
+      </c>
+      <c r="B114" s="86" t="inlineStr">
+        <is>
+          <t>PS5-71-09 - CFO Pre-Pressure Modules (UCP)</t>
+        </is>
+      </c>
+      <c r="C114" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D114" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E114" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F114" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G114" s="67" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="84" t="n">
+        <v>113</v>
+      </c>
+      <c r="B115" s="86" t="inlineStr">
         <is>
           <t>PS5-71-14 - Diesel Fuel Transfer and Dispensing Station</t>
         </is>
       </c>
-      <c r="C113" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D113" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E113" s="28" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F113" s="23" t="inlineStr"/>
-      <c r="G113" s="67" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="81" t="n">
-        <v>112</v>
-      </c>
-      <c r="B114" s="83" t="inlineStr">
+      <c r="C115" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D115" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E115" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F115" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G115" s="67" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="84" t="n">
+        <v>114</v>
+      </c>
+      <c r="B116" s="86" t="inlineStr">
         <is>
           <t>PS5-71-16 - Diesel Fuel Supply Pump A/B</t>
         </is>
       </c>
-      <c r="C114" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D114" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E114" s="28" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F114" s="23" t="inlineStr"/>
-      <c r="G114" s="67" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="81" t="n">
-        <v>113</v>
-      </c>
-      <c r="B115" s="83" t="inlineStr">
+      <c r="C116" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D116" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E116" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F116" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G116" s="67" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="84" t="n">
+        <v>115</v>
+      </c>
+      <c r="B117" s="86" t="inlineStr">
         <is>
           <t>PS5-71-22 - Diesel Fuel Pre Pressure Module</t>
         </is>
       </c>
-      <c r="C115" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D115" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E115" s="28" t="inlineStr">
+      <c r="C117" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D117" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E117" s="28" t="inlineStr">
         <is>
           <t>DONE(full)</t>
         </is>
       </c>
-      <c r="F115" s="23" t="inlineStr"/>
-      <c r="G115" s="67" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="81" t="n">
-        <v>114</v>
-      </c>
-      <c r="B116" s="83" t="inlineStr">
+      <c r="F117" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G117" s="67" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="84" t="n">
+        <v>116</v>
+      </c>
+      <c r="B118" s="86" t="inlineStr">
         <is>
           <t>PS5-74-01 - N2 Generation Skid</t>
         </is>
       </c>
-      <c r="C116" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D116" s="24" t="inlineStr">
+      <c r="C118" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D118" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E118" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F118" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G118" s="67" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="84" t="n">
+        <v>117</v>
+      </c>
+      <c r="B119" s="86" t="inlineStr">
+        <is>
+          <t>PS5-74-03 - Nitrogen Receiver</t>
+        </is>
+      </c>
+      <c r="C119" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D119" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E119" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F119" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G119" s="67" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="84" t="n">
+        <v>118</v>
+      </c>
+      <c r="B120" s="86" t="inlineStr">
+        <is>
+          <t>PS5-74-04 - Nitrogen Distribution Header</t>
+        </is>
+      </c>
+      <c r="C120" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D120" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E120" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F120" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G120" s="67" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="84" t="n">
+        <v>119</v>
+      </c>
+      <c r="B121" s="86" t="inlineStr">
+        <is>
+          <t>PS5-75-02 - Biocide Injection Package</t>
+        </is>
+      </c>
+      <c r="C121" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D121" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E121" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F121" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G121" s="67" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="84" t="n">
+        <v>120</v>
+      </c>
+      <c r="B122" s="86" t="inlineStr">
+        <is>
+          <t>PS5-75-03 - Corrosion Inhibitor Injection Package</t>
+        </is>
+      </c>
+      <c r="C122" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D122" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E122" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F122" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G122" s="67" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="88" t="n">
+        <v>121</v>
+      </c>
+      <c r="B123" s="86" t="inlineStr">
+        <is>
+          <t>PS5-78-01 - Lifting and handling equipment</t>
+        </is>
+      </c>
+      <c r="C123" s="28" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="D123" s="24" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="E116" s="28" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F116" s="23" t="inlineStr"/>
-      <c r="G116" s="67" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="81" t="n">
-        <v>115</v>
-      </c>
-      <c r="B117" s="83" t="inlineStr">
-        <is>
-          <t>PS5-74-03 - Nitrogen Receiver</t>
-        </is>
-      </c>
-      <c r="C117" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D117" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E117" s="28" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F117" s="23" t="inlineStr"/>
-      <c r="G117" s="67" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="81" t="n">
-        <v>116</v>
-      </c>
-      <c r="B118" s="83" t="inlineStr">
-        <is>
-          <t>PS5-74-04 - Nitrogen Distribution Header</t>
-        </is>
-      </c>
-      <c r="C118" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D118" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E118" s="28" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F118" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G118" s="67" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="81" t="n">
-        <v>117</v>
-      </c>
-      <c r="B119" s="83" t="inlineStr">
-        <is>
-          <t>PS5-75-02 - Biocide Injection Package</t>
-        </is>
-      </c>
-      <c r="C119" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D119" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E119" s="28" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F119" s="23" t="inlineStr"/>
-      <c r="G119" s="67" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="81" t="n">
-        <v>118</v>
-      </c>
-      <c r="B120" s="83" t="inlineStr">
-        <is>
-          <t>PS5-75-03 - Corrosion Inhibitor Injection Package</t>
-        </is>
-      </c>
-      <c r="C120" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D120" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E120" s="28" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F120" s="23" t="inlineStr"/>
-      <c r="G120" s="67" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="85" t="n">
-        <v>119</v>
-      </c>
-      <c r="B121" s="83" t="inlineStr">
-        <is>
-          <t>PS5-78-01 - Lifting and handling equipment</t>
-        </is>
-      </c>
-      <c r="C121" s="28" t="inlineStr">
-        <is>
-          <t>77%</t>
-        </is>
-      </c>
-      <c r="D121" s="24" t="inlineStr">
+      <c r="E123" s="69" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="E121" s="69" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="F121" s="23" t="inlineStr">
+      <c r="F123" s="23" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G121" s="67" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="81" t="n">
-        <v>120</v>
-      </c>
-      <c r="B122" s="83" t="inlineStr">
+      <c r="G123" s="67" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="84" t="n">
+        <v>122</v>
+      </c>
+      <c r="B124" s="86" t="inlineStr">
         <is>
           <t>PS5-82-01 - Sanitary Sewage Collection</t>
-        </is>
-      </c>
-      <c r="C122" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D122" s="24" t="inlineStr"/>
-      <c r="E122" s="28" t="inlineStr">
-        <is>
-          <t>full</t>
-        </is>
-      </c>
-      <c r="F122" s="23" t="inlineStr"/>
-      <c r="G122" s="67" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="81" t="n">
-        <v>121</v>
-      </c>
-      <c r="B123" s="83" t="inlineStr">
-        <is>
-          <t>PS5-83-01 - EITS Building</t>
-        </is>
-      </c>
-      <c r="C123" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D123" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E123" s="28" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F123" s="23" t="inlineStr"/>
-      <c r="G123" s="67" t="inlineStr"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="81" t="n">
-        <v>122</v>
-      </c>
-      <c r="B124" s="83" t="inlineStr">
-        <is>
-          <t>PS5-84-03 - Shelters</t>
         </is>
       </c>
       <c r="C124" s="28" t="inlineStr">
@@ -4486,64 +4959,134 @@
       <c r="D124" s="24" t="inlineStr"/>
       <c r="E124" s="28" t="inlineStr">
         <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F124" s="23" t="inlineStr"/>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="F124" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="G124" s="67" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="81" t="n">
+      <c r="A125" s="84" t="n">
         <v>123</v>
       </c>
-      <c r="B125" s="83" t="inlineStr">
+      <c r="B125" s="86" t="inlineStr">
+        <is>
+          <t>PS5-83-01 - EITS Building</t>
+        </is>
+      </c>
+      <c r="C125" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D125" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E125" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F125" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G125" s="67" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="84" t="n">
+        <v>124</v>
+      </c>
+      <c r="B126" s="86" t="inlineStr">
+        <is>
+          <t>PS5-84-03 - Shelters</t>
+        </is>
+      </c>
+      <c r="C126" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D126" s="24" t="inlineStr"/>
+      <c r="E126" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F126" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G126" s="67" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="84" t="n">
+        <v>125</v>
+      </c>
+      <c r="B127" s="86" t="inlineStr">
         <is>
           <t>PS5-86-01 - Shelters</t>
         </is>
       </c>
-      <c r="C125" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D125" s="24" t="inlineStr"/>
-      <c r="E125" s="28" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="F125" s="23" t="inlineStr"/>
-      <c r="G125" s="67" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="81" t="n">
-        <v>124</v>
-      </c>
-      <c r="B126" s="83" t="inlineStr">
+      <c r="C127" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D127" s="24" t="inlineStr"/>
+      <c r="E127" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F127" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G127" s="67" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="84" t="n">
+        <v>126</v>
+      </c>
+      <c r="B128" s="86" t="inlineStr">
         <is>
           <t>PS5-91-01 - Multicore cables &amp; JB</t>
         </is>
       </c>
-      <c r="C126" s="28" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D126" s="24" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="E126" s="28" t="inlineStr">
+      <c r="C128" s="28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D128" s="24" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="E128" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F126" s="23" t="inlineStr"/>
-      <c r="G126" s="67" t="inlineStr"/>
+      <c r="F128" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G128" s="67" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:G126"/>
+  <autoFilter ref="A2:G128"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
@@ -4672,6 +5215,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B124" r:id="rId122"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B125" r:id="rId123"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B126" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B127" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B128" r:id="rId126"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXCEL/7 - COMPLETE.xlsx
+++ b/EXCEL/7 - COMPLETE.xlsx
@@ -1251,11 +1251,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F3" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F3" s="23" t="inlineStr"/>
       <c r="G3" s="67" t="inlineStr"/>
     </row>
     <row r="4">
@@ -1282,11 +1278,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F4" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F4" s="23" t="inlineStr"/>
       <c r="G4" s="67" t="inlineStr"/>
     </row>
     <row r="5">
@@ -1309,11 +1301,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F5" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F5" s="23" t="inlineStr"/>
       <c r="G5" s="67" t="inlineStr"/>
     </row>
     <row r="6">
@@ -1336,11 +1324,7 @@
           <t>2026-08-08</t>
         </is>
       </c>
-      <c r="F6" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F6" s="23" t="inlineStr"/>
       <c r="G6" s="67" t="inlineStr"/>
     </row>
     <row r="7">
@@ -1367,11 +1351,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F7" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F7" s="23" t="inlineStr"/>
       <c r="G7" s="67" t="inlineStr"/>
     </row>
     <row r="8">
@@ -1398,11 +1378,7 @@
           <t>FULL</t>
         </is>
       </c>
-      <c r="F8" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F8" s="23" t="inlineStr"/>
       <c r="G8" s="67" t="inlineStr"/>
     </row>
     <row r="9">
@@ -1429,11 +1405,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F9" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F9" s="23" t="inlineStr"/>
       <c r="G9" s="67" t="inlineStr"/>
     </row>
     <row r="10">
@@ -1460,11 +1432,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F10" s="23" t="inlineStr"/>
       <c r="G10" s="67" t="inlineStr"/>
     </row>
     <row r="11">
@@ -1491,11 +1459,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F11" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F11" s="23" t="inlineStr"/>
       <c r="G11" s="67" t="inlineStr"/>
     </row>
     <row r="12">
@@ -1522,11 +1486,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F12" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F12" s="23" t="inlineStr"/>
       <c r="G12" s="67" t="inlineStr"/>
     </row>
     <row r="13">
@@ -1553,11 +1513,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F13" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F13" s="23" t="inlineStr"/>
       <c r="G13" s="67" t="inlineStr"/>
     </row>
     <row r="14">
@@ -1584,11 +1540,7 @@
           <t>full</t>
         </is>
       </c>
-      <c r="F14" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F14" s="23" t="inlineStr"/>
       <c r="G14" s="67" t="inlineStr"/>
     </row>
     <row r="15">
@@ -1615,11 +1567,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F15" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F15" s="23" t="inlineStr"/>
       <c r="G15" s="67" t="inlineStr"/>
     </row>
     <row r="16">
@@ -1646,11 +1594,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F16" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F16" s="23" t="inlineStr"/>
       <c r="G16" s="67" t="inlineStr"/>
     </row>
     <row r="17">
@@ -1677,11 +1621,7 @@
           <t>07-Aug-26</t>
         </is>
       </c>
-      <c r="F17" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F17" s="23" t="inlineStr"/>
       <c r="G17" s="67" t="inlineStr"/>
     </row>
     <row r="18">
@@ -1708,11 +1648,7 @@
           <t>PARTIAL</t>
         </is>
       </c>
-      <c r="F18" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F18" s="23" t="inlineStr"/>
       <c r="G18" s="67" t="inlineStr"/>
     </row>
     <row r="19">
@@ -1739,11 +1675,7 @@
           <t>COMPLETE</t>
         </is>
       </c>
-      <c r="F19" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F19" s="23" t="inlineStr"/>
       <c r="G19" s="67" t="inlineStr"/>
     </row>
     <row r="20">
@@ -1770,11 +1702,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F20" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F20" s="23" t="inlineStr"/>
       <c r="G20" s="67" t="inlineStr"/>
     </row>
     <row r="21">
@@ -1797,11 +1725,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F21" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F21" s="23" t="inlineStr"/>
       <c r="G21" s="67" t="inlineStr"/>
     </row>
     <row r="22">
@@ -1828,11 +1752,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F22" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F22" s="23" t="inlineStr"/>
       <c r="G22" s="67" t="inlineStr"/>
     </row>
     <row r="23">
@@ -1855,11 +1775,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F23" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F23" s="23" t="inlineStr"/>
       <c r="G23" s="67" t="inlineStr"/>
     </row>
     <row r="24">
@@ -1886,11 +1802,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F24" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F24" s="23" t="inlineStr"/>
       <c r="G24" s="67" t="inlineStr"/>
     </row>
     <row r="25">
@@ -1917,11 +1829,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F25" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F25" s="23" t="inlineStr"/>
       <c r="G25" s="67" t="inlineStr"/>
     </row>
     <row r="26">
@@ -1944,11 +1852,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F26" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F26" s="23" t="inlineStr"/>
       <c r="G26" s="67" t="inlineStr"/>
     </row>
     <row r="27">
@@ -1975,11 +1879,7 @@
           <t>partial</t>
         </is>
       </c>
-      <c r="F27" s="23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="F27" s="23" t="inlineStr"/>
       <c r="G27" s="67" t="inlineStr"/>
     </row>
     <row r="28">
@@ -2006,11 +1906,7 @@
           <t>FULL</t>
         </is>
       </c>
-      <c r="F28" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F28" s="23" t="inlineStr"/>
       <c r="G28" s="67" t="inlineStr"/>
     </row>
     <row r="29">
@@ -2033,11 +1929,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F29" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F29" s="23" t="inlineStr"/>
       <c r="G29" s="67" t="inlineStr"/>
     </row>
     <row r="30">
@@ -2064,11 +1956,7 @@
           <t>FULL</t>
         </is>
       </c>
-      <c r="F30" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F30" s="23" t="inlineStr"/>
       <c r="G30" s="67" t="inlineStr"/>
     </row>
     <row r="31">
@@ -2095,11 +1983,7 @@
           <t>FULL</t>
         </is>
       </c>
-      <c r="F31" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F31" s="23" t="inlineStr"/>
       <c r="G31" s="67" t="inlineStr"/>
     </row>
     <row r="32">
@@ -2126,11 +2010,7 @@
           <t>FULL</t>
         </is>
       </c>
-      <c r="F32" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F32" s="23" t="inlineStr"/>
       <c r="G32" s="67" t="inlineStr"/>
     </row>
     <row r="33">
@@ -2157,11 +2037,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F33" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F33" s="23" t="inlineStr"/>
       <c r="G33" s="67" t="inlineStr"/>
     </row>
     <row r="34">
@@ -2188,11 +2064,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="F34" s="23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="F34" s="23" t="inlineStr"/>
       <c r="G34" s="67" t="inlineStr"/>
     </row>
     <row r="35">
@@ -2219,11 +2091,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F35" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F35" s="23" t="inlineStr"/>
       <c r="G35" s="67" t="inlineStr"/>
     </row>
     <row r="36">
@@ -2250,11 +2118,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F36" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F36" s="23" t="inlineStr"/>
       <c r="G36" s="67" t="inlineStr"/>
     </row>
     <row r="37">
@@ -2281,11 +2145,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F37" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F37" s="23" t="inlineStr"/>
       <c r="G37" s="67" t="inlineStr"/>
     </row>
     <row r="38">
@@ -2343,11 +2203,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F39" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F39" s="23" t="inlineStr"/>
       <c r="G39" s="67" t="inlineStr"/>
     </row>
     <row r="40">
@@ -2374,11 +2230,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F40" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F40" s="23" t="inlineStr"/>
       <c r="G40" s="67" t="inlineStr"/>
     </row>
     <row r="41">
@@ -2405,11 +2257,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F41" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F41" s="23" t="inlineStr"/>
       <c r="G41" s="67" t="inlineStr"/>
     </row>
     <row r="42">
@@ -2436,11 +2284,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F42" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F42" s="23" t="inlineStr"/>
       <c r="G42" s="67" t="inlineStr"/>
     </row>
     <row r="43">
@@ -2467,11 +2311,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F43" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F43" s="23" t="inlineStr"/>
       <c r="G43" s="67" t="inlineStr"/>
     </row>
     <row r="44">
@@ -2498,11 +2338,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F44" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F44" s="23" t="inlineStr"/>
       <c r="G44" s="67" t="inlineStr"/>
     </row>
     <row r="45">
@@ -2529,11 +2365,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F45" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F45" s="23" t="inlineStr"/>
       <c r="G45" s="67" t="inlineStr"/>
     </row>
     <row r="46">
@@ -2560,11 +2392,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F46" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F46" s="23" t="inlineStr"/>
       <c r="G46" s="67" t="inlineStr"/>
     </row>
     <row r="47">
@@ -2591,11 +2419,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F47" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F47" s="23" t="inlineStr"/>
       <c r="G47" s="67" t="inlineStr"/>
     </row>
     <row r="48">
@@ -2622,11 +2446,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F48" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F48" s="23" t="inlineStr"/>
       <c r="G48" s="67" t="inlineStr"/>
     </row>
     <row r="49">
@@ -2653,11 +2473,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F49" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F49" s="23" t="inlineStr"/>
       <c r="G49" s="67" t="inlineStr"/>
     </row>
     <row r="50">
@@ -2684,11 +2500,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F50" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F50" s="23" t="inlineStr"/>
       <c r="G50" s="67" t="inlineStr"/>
     </row>
     <row r="51">
@@ -2715,11 +2527,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F51" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F51" s="23" t="inlineStr"/>
       <c r="G51" s="67" t="inlineStr"/>
     </row>
     <row r="52">
@@ -2746,11 +2554,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F52" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F52" s="23" t="inlineStr"/>
       <c r="G52" s="67" t="inlineStr"/>
     </row>
     <row r="53">
@@ -2777,11 +2581,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F53" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F53" s="23" t="inlineStr"/>
       <c r="G53" s="67" t="inlineStr"/>
     </row>
     <row r="54">
@@ -2804,11 +2604,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F54" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F54" s="23" t="inlineStr"/>
       <c r="G54" s="67" t="inlineStr"/>
     </row>
     <row r="55">
@@ -2835,11 +2631,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F55" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F55" s="23" t="inlineStr"/>
       <c r="G55" s="67" t="inlineStr"/>
     </row>
     <row r="56">
@@ -2866,11 +2658,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F56" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F56" s="23" t="inlineStr"/>
       <c r="G56" s="67" t="inlineStr"/>
     </row>
     <row r="57">
@@ -2897,11 +2685,7 @@
           <t>PARTIAL</t>
         </is>
       </c>
-      <c r="F57" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F57" s="23" t="inlineStr"/>
       <c r="G57" s="67" t="inlineStr"/>
     </row>
     <row r="58">
@@ -2928,11 +2712,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F58" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F58" s="23" t="inlineStr"/>
       <c r="G58" s="67" t="inlineStr"/>
     </row>
     <row r="59">
@@ -2959,11 +2739,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F59" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F59" s="23" t="inlineStr"/>
       <c r="G59" s="67" t="inlineStr"/>
     </row>
     <row r="60">
@@ -2990,11 +2766,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F60" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F60" s="23" t="inlineStr"/>
       <c r="G60" s="67" t="inlineStr"/>
     </row>
     <row r="61">
@@ -3021,11 +2793,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F61" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F61" s="23" t="inlineStr"/>
       <c r="G61" s="67" t="inlineStr"/>
     </row>
     <row r="62">
@@ -3052,11 +2820,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F62" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F62" s="23" t="inlineStr"/>
       <c r="G62" s="67" t="inlineStr"/>
     </row>
     <row r="63">
@@ -3083,11 +2847,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F63" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F63" s="23" t="inlineStr"/>
       <c r="G63" s="67" t="inlineStr"/>
     </row>
     <row r="64">
@@ -3114,11 +2874,7 @@
           <t>COMPLETE</t>
         </is>
       </c>
-      <c r="F64" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F64" s="23" t="inlineStr"/>
       <c r="G64" s="67" t="inlineStr"/>
     </row>
     <row r="65">
@@ -3145,11 +2901,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F65" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F65" s="23" t="inlineStr"/>
       <c r="G65" s="67" t="inlineStr"/>
     </row>
     <row r="66">
@@ -3176,11 +2928,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F66" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F66" s="23" t="inlineStr"/>
       <c r="G66" s="67" t="inlineStr"/>
     </row>
     <row r="67">
@@ -3207,11 +2955,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F67" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F67" s="23" t="inlineStr"/>
       <c r="G67" s="67" t="inlineStr"/>
     </row>
     <row r="68">
@@ -3238,11 +2982,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F68" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F68" s="23" t="inlineStr"/>
       <c r="G68" s="67" t="inlineStr"/>
     </row>
     <row r="69">
@@ -3269,11 +3009,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F69" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F69" s="23" t="inlineStr"/>
       <c r="G69" s="67" t="inlineStr"/>
     </row>
     <row r="70">
@@ -3300,11 +3036,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F70" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F70" s="23" t="inlineStr"/>
       <c r="G70" s="67" t="inlineStr"/>
     </row>
     <row r="71">
@@ -3331,11 +3063,7 @@
           <t>COMPLETE</t>
         </is>
       </c>
-      <c r="F71" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F71" s="23" t="inlineStr"/>
       <c r="G71" s="67" t="inlineStr"/>
     </row>
     <row r="72">
@@ -3362,11 +3090,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F72" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F72" s="23" t="inlineStr"/>
       <c r="G72" s="67" t="inlineStr"/>
     </row>
     <row r="73">
@@ -3393,11 +3117,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F73" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F73" s="23" t="inlineStr"/>
       <c r="G73" s="67" t="inlineStr"/>
     </row>
     <row r="74">
@@ -3424,11 +3144,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F74" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F74" s="23" t="inlineStr"/>
       <c r="G74" s="67" t="inlineStr"/>
     </row>
     <row r="75">
@@ -3455,11 +3171,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F75" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F75" s="23" t="inlineStr"/>
       <c r="G75" s="67" t="inlineStr"/>
     </row>
     <row r="76">
@@ -3486,11 +3198,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F76" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F76" s="23" t="inlineStr"/>
       <c r="G76" s="67" t="inlineStr"/>
     </row>
     <row r="77">
@@ -3517,11 +3225,7 @@
           <t>full</t>
         </is>
       </c>
-      <c r="F77" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F77" s="23" t="inlineStr"/>
       <c r="G77" s="67" t="inlineStr"/>
     </row>
     <row r="78">
@@ -3579,11 +3283,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F79" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F79" s="23" t="inlineStr"/>
       <c r="G79" s="67" t="inlineStr"/>
     </row>
     <row r="80">
@@ -3610,11 +3310,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F80" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F80" s="23" t="inlineStr"/>
       <c r="G80" s="67" t="inlineStr"/>
     </row>
     <row r="81">
@@ -3641,11 +3337,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F81" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F81" s="23" t="inlineStr"/>
       <c r="G81" s="67" t="inlineStr"/>
     </row>
     <row r="82">
@@ -3672,11 +3364,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F82" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F82" s="23" t="inlineStr"/>
       <c r="G82" s="67" t="inlineStr"/>
     </row>
     <row r="83">
@@ -3703,11 +3391,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F83" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F83" s="23" t="inlineStr"/>
       <c r="G83" s="67" t="inlineStr"/>
     </row>
     <row r="84">
@@ -3734,11 +3418,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F84" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F84" s="23" t="inlineStr"/>
       <c r="G84" s="67" t="inlineStr"/>
     </row>
     <row r="85">
@@ -3765,11 +3445,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F85" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F85" s="23" t="inlineStr"/>
       <c r="G85" s="67" t="inlineStr"/>
     </row>
     <row r="86">
@@ -3796,11 +3472,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F86" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F86" s="23" t="inlineStr"/>
       <c r="G86" s="67" t="inlineStr"/>
     </row>
     <row r="87">
@@ -3827,11 +3499,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F87" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F87" s="23" t="inlineStr"/>
       <c r="G87" s="67" t="inlineStr"/>
     </row>
     <row r="88">
@@ -3858,11 +3526,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F88" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F88" s="23" t="inlineStr"/>
       <c r="G88" s="67" t="inlineStr"/>
     </row>
     <row r="89">
@@ -3889,11 +3553,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F89" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F89" s="23" t="inlineStr"/>
       <c r="G89" s="67" t="inlineStr"/>
     </row>
     <row r="90">
@@ -3920,11 +3580,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F90" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F90" s="23" t="inlineStr"/>
       <c r="G90" s="67" t="inlineStr"/>
     </row>
     <row r="91">
@@ -3951,11 +3607,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F91" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F91" s="23" t="inlineStr"/>
       <c r="G91" s="67" t="inlineStr"/>
     </row>
     <row r="92">
@@ -3982,11 +3634,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F92" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F92" s="23" t="inlineStr"/>
       <c r="G92" s="67" t="inlineStr"/>
     </row>
     <row r="93">
@@ -4013,11 +3661,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F93" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F93" s="23" t="inlineStr"/>
       <c r="G93" s="67" t="inlineStr"/>
     </row>
     <row r="94">
@@ -4044,11 +3688,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F94" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F94" s="23" t="inlineStr"/>
       <c r="G94" s="67" t="inlineStr"/>
     </row>
     <row r="95">
@@ -4075,11 +3715,7 @@
           <t>partial</t>
         </is>
       </c>
-      <c r="F95" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F95" s="23" t="inlineStr"/>
       <c r="G95" s="67" t="inlineStr"/>
     </row>
     <row r="96">
@@ -4106,11 +3742,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F96" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F96" s="23" t="inlineStr"/>
       <c r="G96" s="67" t="inlineStr"/>
     </row>
     <row r="97">
@@ -4137,11 +3769,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F97" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F97" s="23" t="inlineStr"/>
       <c r="G97" s="67" t="inlineStr"/>
     </row>
     <row r="98">
@@ -4168,11 +3796,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F98" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F98" s="23" t="inlineStr"/>
       <c r="G98" s="67" t="inlineStr"/>
     </row>
     <row r="99">
@@ -4199,11 +3823,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F99" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F99" s="23" t="inlineStr"/>
       <c r="G99" s="67" t="inlineStr"/>
     </row>
     <row r="100">
@@ -4230,11 +3850,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F100" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F100" s="23" t="inlineStr"/>
       <c r="G100" s="67" t="inlineStr"/>
     </row>
     <row r="101">
@@ -4261,11 +3877,7 @@
           <t>full</t>
         </is>
       </c>
-      <c r="F101" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F101" s="23" t="inlineStr"/>
       <c r="G101" s="67" t="inlineStr"/>
     </row>
     <row r="102">
@@ -4292,11 +3904,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F102" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F102" s="23" t="inlineStr"/>
       <c r="G102" s="67" t="inlineStr"/>
     </row>
     <row r="103">
@@ -4323,11 +3931,7 @@
           <t>FULL</t>
         </is>
       </c>
-      <c r="F103" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F103" s="23" t="inlineStr"/>
       <c r="G103" s="67" t="inlineStr"/>
     </row>
     <row r="104">
@@ -4354,11 +3958,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F104" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F104" s="23" t="inlineStr"/>
       <c r="G104" s="67" t="inlineStr"/>
     </row>
     <row r="105">
@@ -4385,11 +3985,7 @@
           <t>full</t>
         </is>
       </c>
-      <c r="F105" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F105" s="23" t="inlineStr"/>
       <c r="G105" s="67" t="inlineStr"/>
     </row>
     <row r="106">
@@ -4416,11 +4012,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F106" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F106" s="23" t="inlineStr"/>
       <c r="G106" s="67" t="inlineStr"/>
     </row>
     <row r="107">
@@ -4447,11 +4039,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F107" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F107" s="23" t="inlineStr"/>
       <c r="G107" s="67" t="inlineStr"/>
     </row>
     <row r="108">
@@ -4478,11 +4066,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F108" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F108" s="23" t="inlineStr"/>
       <c r="G108" s="67" t="inlineStr"/>
     </row>
     <row r="109">
@@ -4509,11 +4093,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F109" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F109" s="23" t="inlineStr"/>
       <c r="G109" s="67" t="inlineStr"/>
     </row>
     <row r="110">
@@ -4540,11 +4120,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F110" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F110" s="23" t="inlineStr"/>
       <c r="G110" s="67" t="inlineStr"/>
     </row>
     <row r="111">
@@ -4571,11 +4147,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F111" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F111" s="23" t="inlineStr"/>
       <c r="G111" s="67" t="inlineStr"/>
     </row>
     <row r="112">
@@ -4625,11 +4197,7 @@
           <t>full</t>
         </is>
       </c>
-      <c r="F113" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F113" s="23" t="inlineStr"/>
       <c r="G113" s="67" t="inlineStr"/>
     </row>
     <row r="114">
@@ -4656,11 +4224,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F114" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F114" s="23" t="inlineStr"/>
       <c r="G114" s="67" t="inlineStr"/>
     </row>
     <row r="115">
@@ -4687,11 +4251,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F115" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F115" s="23" t="inlineStr"/>
       <c r="G115" s="67" t="inlineStr"/>
     </row>
     <row r="116">
@@ -4718,11 +4278,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F116" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F116" s="23" t="inlineStr"/>
       <c r="G116" s="67" t="inlineStr"/>
     </row>
     <row r="117">
@@ -4749,11 +4305,7 @@
           <t>DONE(full)</t>
         </is>
       </c>
-      <c r="F117" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F117" s="23" t="inlineStr"/>
       <c r="G117" s="67" t="inlineStr"/>
     </row>
     <row r="118">
@@ -4780,11 +4332,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F118" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F118" s="23" t="inlineStr"/>
       <c r="G118" s="67" t="inlineStr"/>
     </row>
     <row r="119">
@@ -4811,11 +4359,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F119" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F119" s="23" t="inlineStr"/>
       <c r="G119" s="67" t="inlineStr"/>
     </row>
     <row r="120">
@@ -4842,11 +4386,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F120" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F120" s="23" t="inlineStr"/>
       <c r="G120" s="67" t="inlineStr"/>
     </row>
     <row r="121">
@@ -4873,11 +4413,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F121" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F121" s="23" t="inlineStr"/>
       <c r="G121" s="67" t="inlineStr"/>
     </row>
     <row r="122">
@@ -4904,11 +4440,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F122" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F122" s="23" t="inlineStr"/>
       <c r="G122" s="67" t="inlineStr"/>
     </row>
     <row r="123">
@@ -4935,11 +4467,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="F123" s="23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="F123" s="23" t="inlineStr"/>
       <c r="G123" s="67" t="inlineStr"/>
     </row>
     <row r="124">
@@ -4962,11 +4490,7 @@
           <t>full</t>
         </is>
       </c>
-      <c r="F124" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F124" s="23" t="inlineStr"/>
       <c r="G124" s="67" t="inlineStr"/>
     </row>
     <row r="125">
@@ -4993,11 +4517,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F125" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F125" s="23" t="inlineStr"/>
       <c r="G125" s="67" t="inlineStr"/>
     </row>
     <row r="126">
@@ -5020,11 +4540,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F126" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F126" s="23" t="inlineStr"/>
       <c r="G126" s="67" t="inlineStr"/>
     </row>
     <row r="127">
@@ -5047,11 +4563,7 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F127" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F127" s="23" t="inlineStr"/>
       <c r="G127" s="67" t="inlineStr"/>
     </row>
     <row r="128">
@@ -5078,11 +4590,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F128" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F128" s="23" t="inlineStr"/>
       <c r="G128" s="67" t="inlineStr"/>
     </row>
   </sheetData>
